--- a/2026/EL MIRADOR/Febrero/Febrero - EL MIRADOR.xlsx
+++ b/2026/EL MIRADOR/Febrero/Febrero - EL MIRADOR.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\2026\EL MIRADOR\ENERO\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\EL MIRADOR\Febrero\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9559E049-2CBF-4EF7-ACB1-525558FA34DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{679AAA98-AFE3-491A-BBF5-4F51FF505FA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -822,9 +822,6 @@
     <t>ADMINISTRADORA: CAROLINA CANCIANI MP:1148</t>
   </si>
   <si>
-    <t>HORARIOS DE ATENCION: LUNES A VIERNES - 10 A 16HS - EMERGENCIAS 24HS</t>
-  </si>
-  <si>
     <t xml:space="preserve">MAIL: elmiradorconsorcios@gmail.com
 </t>
   </si>
@@ -1237,6 +1234,9 @@
   </si>
   <si>
     <t>A PAGAR CONSTRUCTORA</t>
+  </si>
+  <si>
+    <t>HORARIOS DE ATENCION: LUNES A VIERNES - 10 A 15HS - EMERGENCIAS 24HS</t>
   </si>
 </sst>
 </file>
@@ -1897,7 +1897,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="314">
+  <cellXfs count="312">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2214,6 +2214,8 @@
     <xf numFmtId="14" fontId="0" fillId="2" borderId="28" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="2" fillId="12" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="2" fillId="12" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2268,14 +2270,26 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -2373,22 +2387,19 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="23" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2402,19 +2413,6 @@
     </xf>
     <xf numFmtId="1" fontId="23" fillId="9" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="0" fillId="2" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="2" fillId="12" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="2" fillId="12" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -2783,28 +2781,28 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:R160"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="33.42578125" customWidth="1"/>
-    <col min="2" max="2" width="36.85546875" customWidth="1"/>
-    <col min="3" max="3" width="17.42578125" customWidth="1"/>
-    <col min="4" max="4" width="21.7109375" customWidth="1"/>
+    <col min="1" max="1" width="33.44140625" customWidth="1"/>
+    <col min="2" max="2" width="36.88671875" customWidth="1"/>
+    <col min="3" max="3" width="17.44140625" customWidth="1"/>
+    <col min="4" max="4" width="21.6640625" customWidth="1"/>
     <col min="5" max="5" width="18" customWidth="1"/>
-    <col min="6" max="9" width="15.7109375" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.85546875" customWidth="1"/>
-    <col min="12" max="12" width="16.140625" customWidth="1"/>
+    <col min="6" max="9" width="15.6640625" customWidth="1"/>
+    <col min="10" max="10" width="14.6640625" customWidth="1"/>
+    <col min="11" max="11" width="15.88671875" customWidth="1"/>
+    <col min="12" max="12" width="16.109375" customWidth="1"/>
     <col min="13" max="13" width="13" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5546875" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="18" customWidth="1"/>
-    <col min="17" max="17" width="18.28515625" customWidth="1"/>
+    <col min="17" max="17" width="18.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="112"/>
       <c r="B1" s="121"/>
       <c r="C1" s="129" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D1" s="129"/>
       <c r="E1" s="130"/>
@@ -2814,7 +2812,7 @@
       <c r="I1" s="110"/>
       <c r="J1" s="111"/>
     </row>
-    <row r="2" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" ht="18" x14ac:dyDescent="0.35">
       <c r="A2" s="113"/>
       <c r="B2" s="122"/>
       <c r="C2" s="122" t="s">
@@ -2828,11 +2826,11 @@
       <c r="I2" s="123"/>
       <c r="J2" s="109"/>
     </row>
-    <row r="3" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" ht="18" x14ac:dyDescent="0.35">
       <c r="A3" s="113"/>
       <c r="B3" s="122"/>
       <c r="C3" s="122" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D3" s="122"/>
       <c r="E3" s="122" t="s">
@@ -2844,7 +2842,7 @@
       <c r="I3" s="123"/>
       <c r="J3" s="109"/>
     </row>
-    <row r="4" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="113"/>
       <c r="B4" s="122"/>
       <c r="C4" s="122" t="s">
@@ -2858,15 +2856,15 @@
       <c r="I4" s="123"/>
       <c r="J4" s="109"/>
     </row>
-    <row r="5" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" ht="18" x14ac:dyDescent="0.35">
       <c r="A5" s="117"/>
       <c r="B5" s="122"/>
       <c r="C5" s="122" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D5" s="122"/>
       <c r="E5" s="122" t="s">
-        <v>264</v>
+        <v>399</v>
       </c>
       <c r="F5" s="122"/>
       <c r="G5" s="122"/>
@@ -2874,7 +2872,7 @@
       <c r="I5" s="122"/>
       <c r="J5" s="118"/>
     </row>
-    <row r="6" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" ht="18" x14ac:dyDescent="0.35">
       <c r="A6" s="117"/>
       <c r="B6" s="122"/>
       <c r="C6" s="122" t="s">
@@ -2888,7 +2886,7 @@
       <c r="I6" s="122"/>
       <c r="J6" s="118"/>
     </row>
-    <row r="7" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="119"/>
       <c r="B7" s="120"/>
       <c r="C7" s="120"/>
@@ -2900,118 +2898,118 @@
       <c r="I7" s="120"/>
       <c r="J7" s="124"/>
     </row>
-    <row r="9" spans="1:10" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="10" spans="1:10" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="244" t="s">
+    <row r="9" spans="1:10" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="10" spans="1:10" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="14" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="246" t="s">
         <v>260</v>
       </c>
-      <c r="B14" s="244"/>
-      <c r="C14" s="244"/>
-      <c r="D14" s="244"/>
-      <c r="E14" s="244"/>
-      <c r="F14" s="244"/>
-      <c r="G14" s="244"/>
-      <c r="H14" s="244"/>
-      <c r="I14" s="244"/>
-      <c r="J14" s="244"/>
-    </row>
-    <row r="15" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="244"/>
-      <c r="B15" s="244"/>
-      <c r="C15" s="244"/>
-      <c r="D15" s="244"/>
-      <c r="E15" s="244"/>
-      <c r="F15" s="244"/>
-      <c r="G15" s="244"/>
-      <c r="H15" s="244"/>
-      <c r="I15" s="244"/>
-      <c r="J15" s="244"/>
-    </row>
-    <row r="16" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="244"/>
-      <c r="B16" s="244"/>
-      <c r="C16" s="244"/>
-      <c r="D16" s="244"/>
-      <c r="E16" s="244"/>
-      <c r="F16" s="244"/>
-      <c r="G16" s="244"/>
-      <c r="H16" s="244"/>
-      <c r="I16" s="244"/>
-      <c r="J16" s="244"/>
-    </row>
-    <row r="17" spans="1:10" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="244"/>
-      <c r="B17" s="244"/>
-      <c r="C17" s="244"/>
-      <c r="D17" s="244"/>
-      <c r="E17" s="244"/>
-      <c r="F17" s="244"/>
-      <c r="G17" s="244"/>
-      <c r="H17" s="244"/>
-      <c r="I17" s="244"/>
-      <c r="J17" s="244"/>
-    </row>
-    <row r="18" spans="1:10" ht="47.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="244"/>
-      <c r="B18" s="244"/>
-      <c r="C18" s="244"/>
-      <c r="D18" s="244"/>
-      <c r="E18" s="244"/>
-      <c r="F18" s="244"/>
-      <c r="G18" s="244"/>
-      <c r="H18" s="244"/>
-      <c r="I18" s="244"/>
-      <c r="J18" s="244"/>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B14" s="246"/>
+      <c r="C14" s="246"/>
+      <c r="D14" s="246"/>
+      <c r="E14" s="246"/>
+      <c r="F14" s="246"/>
+      <c r="G14" s="246"/>
+      <c r="H14" s="246"/>
+      <c r="I14" s="246"/>
+      <c r="J14" s="246"/>
+    </row>
+    <row r="15" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="246"/>
+      <c r="B15" s="246"/>
+      <c r="C15" s="246"/>
+      <c r="D15" s="246"/>
+      <c r="E15" s="246"/>
+      <c r="F15" s="246"/>
+      <c r="G15" s="246"/>
+      <c r="H15" s="246"/>
+      <c r="I15" s="246"/>
+      <c r="J15" s="246"/>
+    </row>
+    <row r="16" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="246"/>
+      <c r="B16" s="246"/>
+      <c r="C16" s="246"/>
+      <c r="D16" s="246"/>
+      <c r="E16" s="246"/>
+      <c r="F16" s="246"/>
+      <c r="G16" s="246"/>
+      <c r="H16" s="246"/>
+      <c r="I16" s="246"/>
+      <c r="J16" s="246"/>
+    </row>
+    <row r="17" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="246"/>
+      <c r="B17" s="246"/>
+      <c r="C17" s="246"/>
+      <c r="D17" s="246"/>
+      <c r="E17" s="246"/>
+      <c r="F17" s="246"/>
+      <c r="G17" s="246"/>
+      <c r="H17" s="246"/>
+      <c r="I17" s="246"/>
+      <c r="J17" s="246"/>
+    </row>
+    <row r="18" spans="1:10" ht="47.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="246"/>
+      <c r="B18" s="246"/>
+      <c r="C18" s="246"/>
+      <c r="D18" s="246"/>
+      <c r="E18" s="246"/>
+      <c r="F18" s="246"/>
+      <c r="G18" s="246"/>
+      <c r="H18" s="246"/>
+      <c r="I18" s="246"/>
+      <c r="J18" s="246"/>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" s="2"/>
       <c r="H19" s="94"/>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A20" s="253" t="s">
-        <v>324</v>
-      </c>
-      <c r="B20" s="253"/>
-      <c r="C20" s="253"/>
-      <c r="D20" s="253"/>
-      <c r="E20" s="253"/>
-      <c r="F20" s="253"/>
-      <c r="G20" s="253"/>
-      <c r="H20" s="253"/>
-      <c r="I20" s="253"/>
-      <c r="J20" s="253"/>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21" s="253"/>
-      <c r="B21" s="253"/>
-      <c r="C21" s="253"/>
-      <c r="D21" s="253"/>
-      <c r="E21" s="253"/>
-      <c r="F21" s="253"/>
-      <c r="G21" s="253"/>
-      <c r="H21" s="253"/>
-      <c r="I21" s="253"/>
-      <c r="J21" s="253"/>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A22" s="253"/>
-      <c r="B22" s="253"/>
-      <c r="C22" s="253"/>
-      <c r="D22" s="253"/>
-      <c r="E22" s="253"/>
-      <c r="F22" s="253"/>
-      <c r="G22" s="253"/>
-      <c r="H22" s="253"/>
-      <c r="I22" s="253"/>
-      <c r="J22" s="253"/>
-    </row>
-    <row r="23" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A20" s="255" t="s">
+        <v>323</v>
+      </c>
+      <c r="B20" s="255"/>
+      <c r="C20" s="255"/>
+      <c r="D20" s="255"/>
+      <c r="E20" s="255"/>
+      <c r="F20" s="255"/>
+      <c r="G20" s="255"/>
+      <c r="H20" s="255"/>
+      <c r="I20" s="255"/>
+      <c r="J20" s="255"/>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A21" s="255"/>
+      <c r="B21" s="255"/>
+      <c r="C21" s="255"/>
+      <c r="D21" s="255"/>
+      <c r="E21" s="255"/>
+      <c r="F21" s="255"/>
+      <c r="G21" s="255"/>
+      <c r="H21" s="255"/>
+      <c r="I21" s="255"/>
+      <c r="J21" s="255"/>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A22" s="255"/>
+      <c r="B22" s="255"/>
+      <c r="C22" s="255"/>
+      <c r="D22" s="255"/>
+      <c r="E22" s="255"/>
+      <c r="F22" s="255"/>
+      <c r="G22" s="255"/>
+      <c r="H22" s="255"/>
+      <c r="I22" s="255"/>
+      <c r="J22" s="255"/>
+    </row>
+    <row r="23" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="H23" s="94"/>
     </row>
-    <row r="24" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="12" t="s">
         <v>19</v>
       </c>
@@ -3037,7 +3035,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="50" t="s">
         <v>235</v>
       </c>
@@ -3051,7 +3049,7 @@
       <c r="I25" s="95"/>
       <c r="J25" s="95"/>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" s="6" t="s">
         <v>43</v>
       </c>
@@ -3067,7 +3065,7 @@
       <c r="I26" s="58"/>
       <c r="J26" s="58"/>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" s="6" t="s">
         <v>238</v>
       </c>
@@ -3083,7 +3081,7 @@
       <c r="I27" s="58"/>
       <c r="J27" s="58"/>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" s="6" t="s">
         <v>236</v>
       </c>
@@ -3100,7 +3098,7 @@
       <c r="I28" s="58"/>
       <c r="J28" s="58"/>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" s="6" t="s">
         <v>237</v>
       </c>
@@ -3116,9 +3114,9 @@
       <c r="I29" s="58"/>
       <c r="J29" s="58"/>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" s="6" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B30" s="6"/>
       <c r="C30" s="6"/>
@@ -3132,7 +3130,7 @@
       <c r="I30" s="58"/>
       <c r="J30" s="58"/>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" s="6" t="s">
         <v>239</v>
       </c>
@@ -3148,9 +3146,9 @@
       <c r="I31" s="58"/>
       <c r="J31" s="58"/>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" s="6" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B32" s="6"/>
       <c r="C32" s="6"/>
@@ -3164,7 +3162,7 @@
       <c r="I32" s="58"/>
       <c r="J32" s="58"/>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" s="93" t="s">
         <v>168</v>
       </c>
@@ -3181,7 +3179,7 @@
       <c r="I33" s="92"/>
       <c r="J33" s="92"/>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" s="50" t="s">
         <v>234</v>
       </c>
@@ -3195,7 +3193,7 @@
       <c r="I34" s="6"/>
       <c r="J34" s="6"/>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" s="6" t="s">
         <v>43</v>
       </c>
@@ -3211,7 +3209,7 @@
       <c r="I35" s="58"/>
       <c r="J35" s="58"/>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" s="6" t="s">
         <v>238</v>
       </c>
@@ -3228,7 +3226,7 @@
       <c r="I36" s="58"/>
       <c r="J36" s="58"/>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" s="6" t="s">
         <v>236</v>
       </c>
@@ -3245,7 +3243,7 @@
       <c r="I37" s="58"/>
       <c r="J37" s="58"/>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38" s="6" t="s">
         <v>237</v>
       </c>
@@ -3262,9 +3260,9 @@
       <c r="I38" s="58"/>
       <c r="J38" s="58"/>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" s="6" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B39" s="6"/>
       <c r="C39" s="6"/>
@@ -3279,7 +3277,7 @@
       <c r="I39" s="58"/>
       <c r="J39" s="58"/>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" s="6" t="s">
         <v>239</v>
       </c>
@@ -3295,9 +3293,9 @@
       <c r="I40" s="58"/>
       <c r="J40" s="58"/>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41" s="6" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B41" s="6"/>
       <c r="C41" s="6"/>
@@ -3311,7 +3309,7 @@
       <c r="I41" s="58"/>
       <c r="J41" s="58"/>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A42" s="93" t="s">
         <v>168</v>
       </c>
@@ -3328,7 +3326,7 @@
       <c r="I42" s="92"/>
       <c r="J42" s="92"/>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A43" s="33" t="s">
         <v>1</v>
       </c>
@@ -3371,9 +3369,9 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A44" s="32" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B44" s="6"/>
       <c r="C44" s="6"/>
@@ -3388,7 +3386,7 @@
       <c r="J44" s="58"/>
       <c r="L44" s="69"/>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A45" s="32"/>
       <c r="B45" s="6"/>
       <c r="C45" s="6"/>
@@ -3401,7 +3399,7 @@
       <c r="J45" s="6"/>
       <c r="L45" s="69"/>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A46" s="33" t="s">
         <v>38</v>
       </c>
@@ -3444,7 +3442,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A47" s="32" t="s">
         <v>249</v>
       </c>
@@ -3462,9 +3460,9 @@
       <c r="J47" s="58"/>
       <c r="L47" s="69"/>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A48" s="6" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B48" s="6"/>
       <c r="C48" s="195">
@@ -3484,9 +3482,9 @@
       <c r="J48" s="58"/>
       <c r="L48" s="69"/>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A49" s="6" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B49" s="6"/>
       <c r="C49" s="195">
@@ -3506,9 +3504,9 @@
       <c r="J49" s="58"/>
       <c r="L49" s="69"/>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A50" s="6" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B50" s="6"/>
       <c r="C50" s="195">
@@ -3528,9 +3526,9 @@
       <c r="J50" s="58"/>
       <c r="L50" s="69"/>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A51" s="6" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B51" s="6"/>
       <c r="C51" s="195">
@@ -3550,9 +3548,9 @@
       <c r="J51" s="58"/>
       <c r="L51" s="69"/>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A52" s="6" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B52" s="6"/>
       <c r="C52" s="195">
@@ -3572,7 +3570,7 @@
       <c r="J52" s="58"/>
       <c r="L52" s="69"/>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A53" s="6"/>
       <c r="B53" s="6"/>
       <c r="C53" s="6"/>
@@ -3585,7 +3583,7 @@
       <c r="J53" s="58"/>
       <c r="L53" s="69"/>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A54" s="33" t="s">
         <v>17</v>
       </c>
@@ -3613,7 +3611,7 @@
         <v/>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A55" s="32" t="s">
         <v>244</v>
       </c>
@@ -3628,7 +3626,7 @@
       <c r="J55" s="49"/>
       <c r="L55" s="69"/>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A56" s="35" t="s">
         <v>247</v>
       </c>
@@ -3643,15 +3641,15 @@
       <c r="J56" s="49"/>
       <c r="L56" s="69"/>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A57" s="35" t="s">
         <v>248</v>
       </c>
       <c r="B57" s="35" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C57" s="35" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D57" s="213">
         <v>249469</v>
@@ -3664,15 +3662,15 @@
       <c r="J57" s="49"/>
       <c r="L57" s="69"/>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A58" s="35" t="s">
         <v>248</v>
       </c>
       <c r="B58" s="35" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C58" s="35" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="D58" s="213">
         <v>249469</v>
@@ -3685,7 +3683,7 @@
       <c r="J58" s="49"/>
       <c r="L58" s="69"/>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A59" s="33" t="s">
         <v>246</v>
       </c>
@@ -3728,7 +3726,7 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A60" s="32" t="s">
         <v>2</v>
       </c>
@@ -3743,13 +3741,13 @@
       <c r="J60" s="6"/>
       <c r="L60" s="69"/>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A61" s="6" t="s">
         <v>240</v>
       </c>
       <c r="B61" s="6"/>
       <c r="C61" s="6" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D61" s="208">
         <v>56231.41</v>
@@ -3762,13 +3760,13 @@
       <c r="J61" s="6"/>
       <c r="L61" s="69"/>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A62" s="6" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B62" s="6"/>
       <c r="C62" s="6" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D62" s="208">
         <v>64941</v>
@@ -3781,15 +3779,15 @@
       <c r="J62" s="6"/>
       <c r="L62" s="69"/>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A63" s="6" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C63" s="184" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D63" s="208">
         <v>64941</v>
@@ -3802,7 +3800,7 @@
       <c r="J63" s="6"/>
       <c r="L63" s="69"/>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A64" s="33" t="s">
         <v>245</v>
       </c>
@@ -3845,7 +3843,7 @@
         <v/>
       </c>
     </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A65" s="32" t="s">
         <v>227</v>
       </c>
@@ -3860,13 +3858,13 @@
       <c r="J65" s="36"/>
       <c r="L65" s="69"/>
     </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A66" s="6" t="s">
         <v>231</v>
       </c>
       <c r="B66" s="6"/>
       <c r="C66" s="6" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D66" s="208">
         <v>160913</v>
@@ -3901,13 +3899,13 @@
       </c>
       <c r="L66" s="69"/>
     </row>
-    <row r="67" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="255" t="s">
+    <row r="67" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="257" t="s">
         <v>232</v>
       </c>
-      <c r="B67" s="256"/>
+      <c r="B67" s="258"/>
       <c r="C67" s="35" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D67" s="208">
         <v>7907</v>
@@ -3941,16 +3939,16 @@
         <v>7907</v>
       </c>
       <c r="L67" s="207" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="68" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="255" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="68" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="257" t="s">
         <v>233</v>
       </c>
-      <c r="B68" s="256"/>
+      <c r="B68" s="258"/>
       <c r="C68" s="35" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D68" s="208">
         <v>7907</v>
@@ -3985,7 +3983,7 @@
       </c>
       <c r="L68" s="69"/>
     </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A69" s="33" t="s">
         <v>3</v>
       </c>
@@ -4028,7 +4026,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A70" s="32" t="s">
         <v>4</v>
       </c>
@@ -4043,13 +4041,13 @@
       <c r="J70" s="6"/>
       <c r="L70" s="69"/>
     </row>
-    <row r="71" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="71" t="s">
         <v>241</v>
       </c>
       <c r="B71" s="6"/>
       <c r="C71" s="35" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D71" s="220">
         <v>1469353.32</v>
@@ -4089,13 +4087,13 @@
       <c r="M71" s="84"/>
       <c r="N71" s="84"/>
     </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A72" s="6" t="s">
         <v>242</v>
       </c>
       <c r="B72" s="6"/>
       <c r="C72" s="35" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="D72" s="220">
         <v>2331402.6</v>
@@ -4135,13 +4133,13 @@
       <c r="M72" s="84"/>
       <c r="N72" s="84"/>
     </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A73" s="6" t="s">
         <v>243</v>
       </c>
       <c r="B73" s="6"/>
       <c r="C73" s="6" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D73" s="208">
         <v>124753.28</v>
@@ -4172,13 +4170,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A74" s="6" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B74" s="6"/>
       <c r="C74" s="6" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D74" s="208">
         <v>352314.06</v>
@@ -4203,13 +4201,13 @@
       <c r="M74" s="84"/>
       <c r="N74" s="84"/>
     </row>
-    <row r="75" spans="1:14" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="251" t="s">
-        <v>328</v>
-      </c>
-      <c r="B75" s="257"/>
+    <row r="75" spans="1:14" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="253" t="s">
+        <v>327</v>
+      </c>
+      <c r="B75" s="259"/>
       <c r="C75" s="35" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="D75" s="208">
         <v>40000</v>
@@ -4240,13 +4238,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="251" t="s">
+    <row r="76" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="253" t="s">
+        <v>355</v>
+      </c>
+      <c r="B76" s="259"/>
+      <c r="C76" s="184" t="s">
         <v>356</v>
-      </c>
-      <c r="B76" s="257"/>
-      <c r="C76" s="184" t="s">
-        <v>357</v>
       </c>
       <c r="D76" s="208">
         <v>130000</v>
@@ -4268,13 +4266,13 @@
       <c r="M76" s="84"/>
       <c r="N76" s="84"/>
     </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A77" s="35" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B77" s="35"/>
       <c r="C77" s="184" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D77" s="208">
         <v>993952.65</v>
@@ -4320,13 +4318,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A78" s="35" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B78" s="35"/>
       <c r="C78" s="184" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D78" s="208">
         <v>5460.69</v>
@@ -4372,13 +4370,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A79" s="142" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B79" s="141"/>
       <c r="C79" s="6" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D79" s="208">
         <v>100000</v>
@@ -4424,7 +4422,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="33" t="s">
         <v>5</v>
       </c>
@@ -4471,7 +4469,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" s="6"/>
       <c r="B81" s="6"/>
       <c r="C81" s="6"/>
@@ -4484,7 +4482,7 @@
       <c r="J81" s="6"/>
       <c r="L81" s="69"/>
     </row>
-    <row r="82" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" s="6"/>
       <c r="B82" s="6"/>
       <c r="C82" s="6"/>
@@ -4497,7 +4495,7 @@
       <c r="J82" s="6"/>
       <c r="L82" s="69"/>
     </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A83" s="32" t="s">
         <v>228</v>
       </c>
@@ -4512,13 +4510,13 @@
       <c r="J83" s="6"/>
       <c r="L83" s="69"/>
     </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A84" s="6" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B84" s="35"/>
       <c r="C84" s="35" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="D84" s="208">
         <v>606800</v>
@@ -4549,13 +4547,13 @@
       </c>
       <c r="L84" s="69"/>
     </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A85" s="6" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B85" s="35"/>
       <c r="C85" s="35" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="D85" s="208">
         <v>216800</v>
@@ -4571,13 +4569,13 @@
       <c r="J85" s="58"/>
       <c r="L85" s="69"/>
     </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A86" s="6" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B86" s="35"/>
       <c r="C86" s="35" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D86" s="208">
         <v>1300</v>
@@ -4608,13 +4606,13 @@
       </c>
       <c r="L86" s="69"/>
     </row>
-    <row r="87" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="71" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B87" s="35"/>
       <c r="C87" s="196" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D87" s="208">
         <v>350000</v>
@@ -4630,13 +4628,13 @@
       <c r="J87" s="58"/>
       <c r="L87" s="69"/>
     </row>
-    <row r="88" spans="1:14" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="260" t="s">
-        <v>347</v>
-      </c>
-      <c r="B88" s="261"/>
+    <row r="88" spans="1:14" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A88" s="262" t="s">
+        <v>346</v>
+      </c>
+      <c r="B88" s="263"/>
       <c r="C88" s="35" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="D88" s="208">
         <v>250000</v>
@@ -4652,13 +4650,13 @@
       <c r="J88" s="58"/>
       <c r="L88" s="69"/>
     </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A89" s="6" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B89" s="35"/>
       <c r="C89" s="35" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="D89" s="208">
         <v>32800</v>
@@ -4674,13 +4672,13 @@
       <c r="J89" s="58"/>
       <c r="L89" s="69"/>
     </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A90" s="6" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B90" s="35"/>
       <c r="C90" s="35" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D90" s="208">
         <v>50000</v>
@@ -4696,13 +4694,13 @@
       <c r="J90" s="58"/>
       <c r="L90" s="69"/>
     </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A91" s="45" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B91" s="197"/>
       <c r="C91" s="35" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D91" s="208">
         <v>60000</v>
@@ -4718,13 +4716,13 @@
       <c r="J91" s="58"/>
       <c r="L91" s="69"/>
     </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A92" s="45" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B92" s="197"/>
       <c r="C92" s="35" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D92" s="208">
         <v>50000</v>
@@ -4740,13 +4738,13 @@
       <c r="J92" s="58"/>
       <c r="L92" s="69"/>
     </row>
-    <row r="93" spans="1:14" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="255" t="s">
-        <v>350</v>
-      </c>
-      <c r="B93" s="256"/>
+    <row r="93" spans="1:14" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A93" s="257" t="s">
+        <v>349</v>
+      </c>
+      <c r="B93" s="258"/>
       <c r="C93" s="137" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="D93" s="208">
         <v>307200</v>
@@ -4762,13 +4760,13 @@
       <c r="J93" s="58"/>
       <c r="L93" s="69"/>
     </row>
-    <row r="94" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="255" t="s">
-        <v>331</v>
-      </c>
-      <c r="B94" s="256"/>
+    <row r="94" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A94" s="257" t="s">
+        <v>330</v>
+      </c>
+      <c r="B94" s="258"/>
       <c r="C94" s="137" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="D94" s="208">
         <v>191400</v>
@@ -4784,13 +4782,13 @@
       <c r="J94" s="58"/>
       <c r="L94" s="69"/>
     </row>
-    <row r="95" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="258" t="s">
-        <v>330</v>
-      </c>
-      <c r="B95" s="259"/>
+    <row r="95" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A95" s="260" t="s">
+        <v>329</v>
+      </c>
+      <c r="B95" s="261"/>
       <c r="C95" s="137" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="D95" s="208">
         <v>95700</v>
@@ -4807,7 +4805,7 @@
       <c r="L95" s="69"/>
       <c r="M95" s="43"/>
     </row>
-    <row r="96" spans="1:14" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:14" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="33" t="s">
         <v>229</v>
       </c>
@@ -4851,7 +4849,7 @@
       </c>
       <c r="N96" s="43"/>
     </row>
-    <row r="97" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" s="6"/>
       <c r="B97" s="6"/>
       <c r="C97" s="6"/>
@@ -4864,7 +4862,7 @@
       <c r="J97" s="6"/>
       <c r="L97" s="69"/>
     </row>
-    <row r="98" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" s="6"/>
       <c r="B98" s="6"/>
       <c r="C98" s="6"/>
@@ -4877,7 +4875,7 @@
       <c r="J98" s="6"/>
       <c r="L98" s="69"/>
     </row>
-    <row r="99" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A99" s="32" t="s">
         <v>6</v>
       </c>
@@ -4892,7 +4890,7 @@
       <c r="J99" s="6"/>
       <c r="L99" s="69"/>
     </row>
-    <row r="100" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="6" t="s">
         <v>7</v>
       </c>
@@ -4928,10 +4926,10 @@
         <v>13114.38</v>
       </c>
       <c r="L100" s="69" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="101" spans="1:14" x14ac:dyDescent="0.25">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="101" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A101" s="32"/>
       <c r="B101" s="6"/>
       <c r="C101" s="6"/>
@@ -4945,7 +4943,7 @@
       <c r="L101" s="69"/>
       <c r="N101" s="44"/>
     </row>
-    <row r="102" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A102" s="6"/>
       <c r="B102" s="6"/>
       <c r="C102" s="6"/>
@@ -4959,7 +4957,7 @@
       <c r="L102" s="69"/>
       <c r="N102" s="43"/>
     </row>
-    <row r="103" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A103" s="33" t="s">
         <v>8</v>
       </c>
@@ -5003,7 +5001,7 @@
       </c>
       <c r="N103" s="43"/>
     </row>
-    <row r="104" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A104" s="6" t="s">
         <v>28</v>
       </c>
@@ -5039,7 +5037,7 @@
       </c>
       <c r="L104" s="69"/>
     </row>
-    <row r="105" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A105" s="6" t="s">
         <v>29</v>
       </c>
@@ -5072,7 +5070,7 @@
       </c>
       <c r="L105" s="69"/>
     </row>
-    <row r="106" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A106" s="33" t="s">
         <v>230</v>
       </c>
@@ -5115,7 +5113,7 @@
         <v/>
       </c>
     </row>
-    <row r="107" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A107" s="98"/>
       <c r="B107" s="98"/>
       <c r="C107" s="98"/>
@@ -5128,9 +5126,9 @@
       <c r="J107" s="98"/>
       <c r="L107" s="69"/>
     </row>
-    <row r="108" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A108" s="100" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B108" s="101"/>
       <c r="C108" s="101"/>
@@ -5171,7 +5169,7 @@
         <v/>
       </c>
     </row>
-    <row r="109" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A109" s="103"/>
       <c r="B109" s="104"/>
       <c r="C109" s="104"/>
@@ -5185,7 +5183,7 @@
       <c r="K109" s="43"/>
       <c r="L109" s="69"/>
     </row>
-    <row r="110" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A110" s="3" t="s">
         <v>30</v>
       </c>
@@ -5232,7 +5230,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D111" s="85"/>
       <c r="E111" s="43"/>
       <c r="F111" s="43"/>
@@ -5240,7 +5238,7 @@
       <c r="H111" s="43"/>
       <c r="I111" s="43"/>
     </row>
-    <row r="112" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A112" s="64" t="s">
         <v>39</v>
       </c>
@@ -5252,12 +5250,12 @@
       <c r="H112" s="43"/>
       <c r="I112" s="43"/>
     </row>
-    <row r="113" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A113" s="1" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B113" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C113" s="128">
         <v>25000</v>
@@ -5268,7 +5266,7 @@
       <c r="H113" s="43"/>
       <c r="I113" s="43"/>
     </row>
-    <row r="114" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A114" s="1"/>
       <c r="C114" s="128"/>
       <c r="E114" s="43"/>
@@ -5277,7 +5275,7 @@
       <c r="H114" s="43"/>
       <c r="I114" s="43"/>
     </row>
-    <row r="115" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A115" s="65" t="s">
         <v>17</v>
       </c>
@@ -5292,27 +5290,27 @@
       <c r="H115" s="43"/>
       <c r="I115" s="43"/>
     </row>
-    <row r="116" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:13" x14ac:dyDescent="0.3">
       <c r="E116" s="43"/>
       <c r="F116" s="43"/>
       <c r="G116" s="43"/>
       <c r="H116" s="43"/>
       <c r="I116" s="43"/>
     </row>
-    <row r="117" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:13" x14ac:dyDescent="0.3">
       <c r="E117" s="60"/>
       <c r="F117" s="60"/>
       <c r="G117" s="60"/>
       <c r="H117" s="60"/>
       <c r="I117" s="60"/>
     </row>
-    <row r="118" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A118" s="249" t="s">
+    <row r="118" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A118" s="251" t="s">
         <v>34</v>
       </c>
-      <c r="B118" s="250"/>
-      <c r="C118" s="250"/>
-      <c r="D118" s="250"/>
+      <c r="B118" s="252"/>
+      <c r="C118" s="252"/>
+      <c r="D118" s="252"/>
       <c r="E118" s="80" t="s">
         <v>11</v>
       </c>
@@ -5332,9 +5330,9 @@
         <v>174</v>
       </c>
     </row>
-    <row r="119" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A119" s="251"/>
-      <c r="B119" s="252"/>
+    <row r="119" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A119" s="253"/>
+      <c r="B119" s="254"/>
       <c r="C119" s="82"/>
       <c r="D119" s="44"/>
       <c r="E119" s="68">
@@ -5347,9 +5345,9 @@
       <c r="I119" s="68"/>
       <c r="J119" s="58"/>
     </row>
-    <row r="120" spans="1:13" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A120" s="251"/>
-      <c r="B120" s="252"/>
+    <row r="120" spans="1:13" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A120" s="253"/>
+      <c r="B120" s="254"/>
       <c r="C120" s="82"/>
       <c r="D120" s="44"/>
       <c r="E120" s="68"/>
@@ -5359,12 +5357,12 @@
       <c r="I120" s="68"/>
       <c r="J120" s="58"/>
     </row>
-    <row r="121" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A121" s="246" t="s">
+    <row r="121" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A121" s="248" t="s">
         <v>17</v>
       </c>
-      <c r="B121" s="247"/>
-      <c r="C121" s="248"/>
+      <c r="B121" s="249"/>
+      <c r="C121" s="250"/>
       <c r="D121" s="79">
         <f>SUM(D119:D120)</f>
         <v>0</v>
@@ -5390,14 +5388,14 @@
         <v/>
       </c>
     </row>
-    <row r="123" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E123" s="43"/>
       <c r="F123" s="43"/>
       <c r="G123" s="43"/>
       <c r="H123" s="43"/>
       <c r="I123" s="43"/>
     </row>
-    <row r="124" spans="1:13" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:13" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A124" s="38" t="s">
         <v>31</v>
       </c>
@@ -5406,7 +5404,7 @@
         <v>15667206.089999998</v>
       </c>
     </row>
-    <row r="125" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A125" s="40" t="s">
         <v>33</v>
       </c>
@@ -5414,37 +5412,37 @@
         <f>D110-D108</f>
         <v>12343887.129999999</v>
       </c>
-      <c r="D125" s="254" t="s">
-        <v>305</v>
-      </c>
-      <c r="E125" s="254"/>
-      <c r="F125" s="254"/>
-      <c r="G125" s="254"/>
-      <c r="H125" s="254"/>
-      <c r="I125" s="254"/>
-    </row>
-    <row r="126" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="D126" s="254"/>
-      <c r="E126" s="254"/>
-      <c r="F126" s="254"/>
-      <c r="G126" s="254"/>
-      <c r="H126" s="254"/>
-      <c r="I126" s="254"/>
-    </row>
-    <row r="127" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="D125" s="256" t="s">
+        <v>304</v>
+      </c>
+      <c r="E125" s="256"/>
+      <c r="F125" s="256"/>
+      <c r="G125" s="256"/>
+      <c r="H125" s="256"/>
+      <c r="I125" s="256"/>
+    </row>
+    <row r="126" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="D126" s="256"/>
+      <c r="E126" s="256"/>
+      <c r="F126" s="256"/>
+      <c r="G126" s="256"/>
+      <c r="H126" s="256"/>
+      <c r="I126" s="256"/>
+    </row>
+    <row r="127" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A127" s="16" t="s">
         <v>20</v>
       </c>
       <c r="B127" s="17"/>
       <c r="C127" s="18"/>
-      <c r="D127" s="254"/>
-      <c r="E127" s="254"/>
-      <c r="F127" s="254"/>
-      <c r="G127" s="254"/>
-      <c r="H127" s="254"/>
-      <c r="I127" s="254"/>
-    </row>
-    <row r="128" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="D127" s="256"/>
+      <c r="E127" s="256"/>
+      <c r="F127" s="256"/>
+      <c r="G127" s="256"/>
+      <c r="H127" s="256"/>
+      <c r="I127" s="256"/>
+    </row>
+    <row r="128" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A128" s="19" t="s">
         <v>21</v>
       </c>
@@ -5452,14 +5450,14 @@
         <v>-1002261.6181467418</v>
       </c>
       <c r="C128" s="20"/>
-      <c r="D128" s="254"/>
-      <c r="E128" s="254"/>
-      <c r="F128" s="254"/>
-      <c r="G128" s="254"/>
-      <c r="H128" s="254"/>
-      <c r="I128" s="254"/>
-    </row>
-    <row r="129" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D128" s="256"/>
+      <c r="E128" s="256"/>
+      <c r="F128" s="256"/>
+      <c r="G128" s="256"/>
+      <c r="H128" s="256"/>
+      <c r="I128" s="256"/>
+    </row>
+    <row r="129" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A129" s="21" t="s">
         <v>22</v>
       </c>
@@ -5470,14 +5468,14 @@
       <c r="C129" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="D129" s="254"/>
-      <c r="E129" s="254"/>
-      <c r="F129" s="254"/>
-      <c r="G129" s="254"/>
-      <c r="H129" s="254"/>
-      <c r="I129" s="254"/>
-    </row>
-    <row r="130" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D129" s="256"/>
+      <c r="E129" s="256"/>
+      <c r="F129" s="256"/>
+      <c r="G129" s="256"/>
+      <c r="H129" s="256"/>
+      <c r="I129" s="256"/>
+    </row>
+    <row r="130" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A130" s="21" t="s">
         <v>36</v>
       </c>
@@ -5486,15 +5484,15 @@
         <v>-12343887.129999999</v>
       </c>
       <c r="C130" s="18"/>
-      <c r="D130" s="254"/>
-      <c r="E130" s="254"/>
-      <c r="F130" s="254"/>
-      <c r="G130" s="254"/>
-      <c r="H130" s="254"/>
-      <c r="I130" s="254"/>
+      <c r="D130" s="256"/>
+      <c r="E130" s="256"/>
+      <c r="F130" s="256"/>
+      <c r="G130" s="256"/>
+      <c r="H130" s="256"/>
+      <c r="I130" s="256"/>
       <c r="K130" s="44"/>
     </row>
-    <row r="131" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A131" s="21" t="s">
         <v>35</v>
       </c>
@@ -5503,32 +5501,32 @@
         <v>0</v>
       </c>
       <c r="C131" s="18"/>
-      <c r="D131" s="254"/>
-      <c r="E131" s="254"/>
-      <c r="F131" s="254"/>
-      <c r="G131" s="254"/>
-      <c r="H131" s="254"/>
-      <c r="I131" s="254"/>
+      <c r="D131" s="256"/>
+      <c r="E131" s="256"/>
+      <c r="F131" s="256"/>
+      <c r="G131" s="256"/>
+      <c r="H131" s="256"/>
+      <c r="I131" s="256"/>
       <c r="K131" s="52"/>
     </row>
-    <row r="132" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A132" s="21" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B132" s="30">
         <f>B142</f>
         <v>143267</v>
       </c>
       <c r="C132" s="18"/>
-      <c r="D132" s="254"/>
-      <c r="E132" s="254"/>
-      <c r="F132" s="254"/>
-      <c r="G132" s="254"/>
-      <c r="H132" s="254"/>
-      <c r="I132" s="254"/>
+      <c r="D132" s="256"/>
+      <c r="E132" s="256"/>
+      <c r="F132" s="256"/>
+      <c r="G132" s="256"/>
+      <c r="H132" s="256"/>
+      <c r="I132" s="256"/>
       <c r="K132" s="52"/>
     </row>
-    <row r="133" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A133" s="21" t="s">
         <v>32</v>
       </c>
@@ -5537,45 +5535,45 @@
         <v>-120000</v>
       </c>
       <c r="C133" s="22"/>
-      <c r="D133" s="254"/>
-      <c r="E133" s="254"/>
-      <c r="F133" s="254"/>
-      <c r="G133" s="254"/>
-      <c r="H133" s="254"/>
-      <c r="I133" s="254"/>
-    </row>
-    <row r="134" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D133" s="256"/>
+      <c r="E133" s="256"/>
+      <c r="F133" s="256"/>
+      <c r="G133" s="256"/>
+      <c r="H133" s="256"/>
+      <c r="I133" s="256"/>
+    </row>
+    <row r="134" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="224" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B134" s="30">
         <v>426600</v>
       </c>
       <c r="C134" s="22"/>
-      <c r="D134" s="254"/>
-      <c r="E134" s="254"/>
-      <c r="F134" s="254"/>
-      <c r="G134" s="254"/>
-      <c r="H134" s="254"/>
-      <c r="I134" s="254"/>
-    </row>
-    <row r="135" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D134" s="256"/>
+      <c r="E134" s="256"/>
+      <c r="F134" s="256"/>
+      <c r="G134" s="256"/>
+      <c r="H134" s="256"/>
+      <c r="I134" s="256"/>
+    </row>
+    <row r="135" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A135" s="21" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B135" s="191">
         <f>-87300</f>
         <v>-87300</v>
       </c>
       <c r="C135" s="22"/>
-      <c r="D135" s="254"/>
-      <c r="E135" s="254"/>
-      <c r="F135" s="254"/>
-      <c r="G135" s="254"/>
-      <c r="H135" s="254"/>
-      <c r="I135" s="254"/>
-    </row>
-    <row r="136" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D135" s="256"/>
+      <c r="E135" s="256"/>
+      <c r="F135" s="256"/>
+      <c r="G135" s="256"/>
+      <c r="H135" s="256"/>
+      <c r="I135" s="256"/>
+    </row>
+    <row r="136" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A136" s="21" t="s">
         <v>39</v>
       </c>
@@ -5584,25 +5582,25 @@
         <v>-25000</v>
       </c>
       <c r="C136" s="22"/>
-      <c r="D136" s="254"/>
-      <c r="E136" s="254"/>
-      <c r="F136" s="254"/>
-      <c r="G136" s="254"/>
-      <c r="H136" s="254"/>
-      <c r="I136" s="254"/>
-    </row>
-    <row r="137" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D136" s="256"/>
+      <c r="E136" s="256"/>
+      <c r="F136" s="256"/>
+      <c r="G136" s="256"/>
+      <c r="H136" s="256"/>
+      <c r="I136" s="256"/>
+    </row>
+    <row r="137" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A137" s="21"/>
       <c r="B137" s="169"/>
       <c r="C137" s="22"/>
-      <c r="D137" s="254"/>
-      <c r="E137" s="254"/>
-      <c r="F137" s="254"/>
-      <c r="G137" s="254"/>
-      <c r="H137" s="254"/>
-      <c r="I137" s="254"/>
-    </row>
-    <row r="138" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D137" s="256"/>
+      <c r="E137" s="256"/>
+      <c r="F137" s="256"/>
+      <c r="G137" s="256"/>
+      <c r="H137" s="256"/>
+      <c r="I137" s="256"/>
+    </row>
+    <row r="138" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A138" s="19" t="s">
         <v>24</v>
       </c>
@@ -5611,39 +5609,39 @@
         <v>1767072.6013971008</v>
       </c>
       <c r="C138" s="70"/>
-      <c r="D138" s="254"/>
-      <c r="E138" s="254"/>
-      <c r="F138" s="254"/>
-      <c r="G138" s="254"/>
-      <c r="H138" s="254"/>
-      <c r="I138" s="254"/>
-    </row>
-    <row r="139" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D138" s="256"/>
+      <c r="E138" s="256"/>
+      <c r="F138" s="256"/>
+      <c r="G138" s="256"/>
+      <c r="H138" s="256"/>
+      <c r="I138" s="256"/>
+    </row>
+    <row r="139" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A139" s="22"/>
       <c r="C139" s="18"/>
-      <c r="D139" s="254"/>
-      <c r="E139" s="254"/>
-      <c r="F139" s="254"/>
-      <c r="G139" s="254"/>
-      <c r="H139" s="254"/>
-      <c r="I139" s="254"/>
-    </row>
-    <row r="140" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D139" s="256"/>
+      <c r="E139" s="256"/>
+      <c r="F139" s="256"/>
+      <c r="G139" s="256"/>
+      <c r="H139" s="256"/>
+      <c r="I139" s="256"/>
+    </row>
+    <row r="140" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A140" s="16" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B140" s="8"/>
       <c r="C140" s="18"/>
-      <c r="D140" s="254"/>
-      <c r="E140" s="254"/>
-      <c r="F140" s="254"/>
-      <c r="G140" s="254"/>
-      <c r="H140" s="254"/>
-      <c r="I140" s="254"/>
-    </row>
-    <row r="141" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D140" s="256"/>
+      <c r="E140" s="256"/>
+      <c r="F140" s="256"/>
+      <c r="G140" s="256"/>
+      <c r="H140" s="256"/>
+      <c r="I140" s="256"/>
+    </row>
+    <row r="141" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" s="19" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B141" s="30">
         <v>143267</v>
@@ -5651,7 +5649,7 @@
       <c r="C141" s="18"/>
       <c r="D141" s="25"/>
     </row>
-    <row r="142" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A142" s="36" t="s">
         <v>17</v>
       </c>
@@ -5662,17 +5660,17 @@
       <c r="C142" s="18"/>
       <c r="D142" s="25"/>
     </row>
-    <row r="143" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A143" s="22"/>
       <c r="C143" s="18"/>
       <c r="D143" s="25"/>
     </row>
-    <row r="144" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A144" s="22"/>
       <c r="C144" s="18"/>
       <c r="D144" s="25"/>
     </row>
-    <row r="145" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:18" x14ac:dyDescent="0.3">
       <c r="C145" s="18"/>
       <c r="D145" s="43"/>
       <c r="E145" s="84"/>
@@ -5681,7 +5679,7 @@
       <c r="H145" s="84"/>
       <c r="I145" s="84"/>
     </row>
-    <row r="146" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A146" s="16" t="s">
         <v>25</v>
       </c>
@@ -5697,7 +5695,7 @@
       <c r="I146" s="84"/>
       <c r="J146" s="84"/>
     </row>
-    <row r="147" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147" s="19" t="s">
         <v>255</v>
       </c>
@@ -5712,9 +5710,9 @@
       <c r="H147" s="88"/>
       <c r="I147" s="88"/>
     </row>
-    <row r="148" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A148" s="19" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B148" s="83">
         <v>-20000</v>
@@ -5727,7 +5725,7 @@
       <c r="H148" s="43"/>
       <c r="I148" s="43"/>
     </row>
-    <row r="149" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A149" s="36" t="s">
         <v>17</v>
       </c>
@@ -5737,62 +5735,62 @@
       </c>
       <c r="C149" s="24"/>
     </row>
-    <row r="150" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:18" x14ac:dyDescent="0.3">
       <c r="C150" s="25"/>
       <c r="D150" s="84"/>
     </row>
-    <row r="151" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B151" s="22"/>
       <c r="C151" s="18"/>
     </row>
-    <row r="153" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:18" x14ac:dyDescent="0.3">
       <c r="R153" s="9"/>
     </row>
-    <row r="156" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="B156" s="245"/>
-      <c r="C156" s="245"/>
-      <c r="D156" s="245"/>
-      <c r="E156" s="245"/>
+    <row r="156" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B156" s="247"/>
+      <c r="C156" s="247"/>
+      <c r="D156" s="247"/>
+      <c r="E156" s="247"/>
       <c r="F156" s="90"/>
       <c r="G156" s="90"/>
       <c r="H156" s="90"/>
       <c r="I156" s="90"/>
     </row>
-    <row r="157" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="B157" s="245"/>
-      <c r="C157" s="245"/>
-      <c r="D157" s="245"/>
-      <c r="E157" s="245"/>
+    <row r="157" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B157" s="247"/>
+      <c r="C157" s="247"/>
+      <c r="D157" s="247"/>
+      <c r="E157" s="247"/>
       <c r="F157" s="90"/>
       <c r="G157" s="90"/>
       <c r="H157" s="90"/>
       <c r="I157" s="90"/>
     </row>
-    <row r="158" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="B158" s="245"/>
-      <c r="C158" s="245"/>
-      <c r="D158" s="245"/>
-      <c r="E158" s="245"/>
+    <row r="158" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B158" s="247"/>
+      <c r="C158" s="247"/>
+      <c r="D158" s="247"/>
+      <c r="E158" s="247"/>
       <c r="F158" s="90"/>
       <c r="G158" s="90"/>
       <c r="H158" s="90"/>
       <c r="I158" s="90"/>
     </row>
-    <row r="159" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="B159" s="245"/>
-      <c r="C159" s="245"/>
-      <c r="D159" s="245"/>
-      <c r="E159" s="245"/>
+    <row r="159" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B159" s="247"/>
+      <c r="C159" s="247"/>
+      <c r="D159" s="247"/>
+      <c r="E159" s="247"/>
       <c r="F159" s="90"/>
       <c r="G159" s="90"/>
       <c r="H159" s="90"/>
       <c r="I159" s="90"/>
     </row>
-    <row r="160" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="B160" s="245"/>
-      <c r="C160" s="245"/>
-      <c r="D160" s="245"/>
-      <c r="E160" s="245"/>
+    <row r="160" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B160" s="247"/>
+      <c r="C160" s="247"/>
+      <c r="D160" s="247"/>
+      <c r="E160" s="247"/>
       <c r="F160" s="90"/>
       <c r="G160" s="90"/>
       <c r="H160" s="90"/>
@@ -5826,38 +5824,38 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:DI154"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.5703125" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="5.85546875" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="8.140625" customWidth="1"/>
-    <col min="4" max="4" width="42.7109375" customWidth="1"/>
-    <col min="5" max="5" width="25.5703125" customWidth="1"/>
-    <col min="6" max="6" width="9.42578125" customWidth="1"/>
-    <col min="7" max="7" width="13.28515625" customWidth="1"/>
+    <col min="1" max="1" width="4.5546875" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="5.88671875" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="8.109375" customWidth="1"/>
+    <col min="4" max="4" width="42.6640625" customWidth="1"/>
+    <col min="5" max="5" width="25.5546875" customWidth="1"/>
+    <col min="6" max="6" width="9.44140625" customWidth="1"/>
+    <col min="7" max="7" width="13.33203125" customWidth="1"/>
     <col min="8" max="8" width="13" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.85546875" customWidth="1"/>
-    <col min="10" max="10" width="13.7109375" customWidth="1"/>
-    <col min="11" max="11" width="13.28515625" customWidth="1"/>
-    <col min="12" max="12" width="10.42578125" customWidth="1"/>
-    <col min="13" max="13" width="15.42578125" customWidth="1"/>
-    <col min="14" max="14" width="13.7109375" customWidth="1"/>
-    <col min="15" max="15" width="11.42578125" customWidth="1"/>
-    <col min="16" max="16" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.88671875" customWidth="1"/>
+    <col min="10" max="10" width="13.6640625" customWidth="1"/>
+    <col min="11" max="11" width="13.33203125" customWidth="1"/>
+    <col min="12" max="12" width="10.44140625" customWidth="1"/>
+    <col min="13" max="13" width="15.44140625" customWidth="1"/>
+    <col min="14" max="14" width="13.6640625" customWidth="1"/>
+    <col min="15" max="15" width="11.44140625" customWidth="1"/>
+    <col min="16" max="16" width="14.5546875" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="13" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A1" s="291" t="s">
-        <v>365</v>
-      </c>
-      <c r="B1" s="292"/>
-      <c r="C1" s="292"/>
-      <c r="D1" s="292"/>
-      <c r="E1" s="292"/>
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A1" s="297" t="s">
+        <v>364</v>
+      </c>
+      <c r="B1" s="298"/>
+      <c r="C1" s="298"/>
+      <c r="D1" s="298"/>
+      <c r="E1" s="298"/>
       <c r="F1" s="158" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="G1" s="158"/>
       <c r="H1" s="158"/>
@@ -5866,22 +5864,22 @@
       <c r="K1" s="192" t="s">
         <v>41</v>
       </c>
-      <c r="L1" s="267">
+      <c r="L1" s="273">
         <f>RESUMEN!D110-RESUMEN!D108</f>
         <v>12343887.129999999</v>
       </c>
-      <c r="M1" s="268"/>
+      <c r="M1" s="274"/>
       <c r="N1" s="159"/>
       <c r="O1" s="59"/>
     </row>
-    <row r="2" spans="1:18" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="293"/>
-      <c r="B2" s="294"/>
-      <c r="C2" s="294"/>
-      <c r="D2" s="294"/>
-      <c r="E2" s="294"/>
+    <row r="2" spans="1:18" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="299"/>
+      <c r="B2" s="300"/>
+      <c r="C2" s="300"/>
+      <c r="D2" s="300"/>
+      <c r="E2" s="300"/>
       <c r="F2" s="7" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="G2" s="7"/>
       <c r="H2" s="7"/>
@@ -5897,14 +5895,14 @@
       <c r="N2" s="160"/>
       <c r="O2" s="59"/>
     </row>
-    <row r="3" spans="1:18" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="293"/>
-      <c r="B3" s="294"/>
-      <c r="C3" s="294"/>
-      <c r="D3" s="294"/>
-      <c r="E3" s="294"/>
+    <row r="3" spans="1:18" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="299"/>
+      <c r="B3" s="300"/>
+      <c r="C3" s="300"/>
+      <c r="D3" s="300"/>
+      <c r="E3" s="300"/>
       <c r="F3" s="7" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="G3" s="7"/>
       <c r="H3" s="7"/>
@@ -5916,12 +5914,12 @@
       <c r="N3" s="163"/>
       <c r="O3" s="15"/>
     </row>
-    <row r="4" spans="1:18" ht="2.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="295"/>
-      <c r="B4" s="296"/>
-      <c r="C4" s="296"/>
-      <c r="D4" s="296"/>
-      <c r="E4" s="296"/>
+    <row r="4" spans="1:18" ht="2.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="301"/>
+      <c r="B4" s="302"/>
+      <c r="C4" s="302"/>
+      <c r="D4" s="302"/>
+      <c r="E4" s="302"/>
       <c r="F4" s="164"/>
       <c r="G4" s="164"/>
       <c r="H4" s="164"/>
@@ -5933,93 +5931,93 @@
       <c r="N4" s="167"/>
       <c r="O4" s="15"/>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" s="7"/>
       <c r="B5" s="7"/>
-      <c r="C5" s="276" t="s">
-        <v>314</v>
-      </c>
-      <c r="D5" s="277"/>
-      <c r="E5" s="277"/>
-      <c r="F5" s="277"/>
-      <c r="G5" s="277"/>
-      <c r="H5" s="277"/>
-      <c r="I5" s="277"/>
-      <c r="J5" s="277"/>
-      <c r="K5" s="277"/>
-      <c r="L5" s="277"/>
-      <c r="M5" s="277"/>
-      <c r="N5" s="278"/>
+      <c r="C5" s="282" t="s">
+        <v>313</v>
+      </c>
+      <c r="D5" s="283"/>
+      <c r="E5" s="283"/>
+      <c r="F5" s="283"/>
+      <c r="G5" s="283"/>
+      <c r="H5" s="283"/>
+      <c r="I5" s="283"/>
+      <c r="J5" s="283"/>
+      <c r="K5" s="283"/>
+      <c r="L5" s="283"/>
+      <c r="M5" s="283"/>
+      <c r="N5" s="284"/>
       <c r="O5" s="15"/>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" s="7"/>
       <c r="B6" s="7"/>
-      <c r="C6" s="279"/>
-      <c r="D6" s="280"/>
-      <c r="E6" s="280"/>
-      <c r="F6" s="280"/>
-      <c r="G6" s="280"/>
-      <c r="H6" s="280"/>
-      <c r="I6" s="280"/>
-      <c r="J6" s="280"/>
-      <c r="K6" s="280"/>
-      <c r="L6" s="280"/>
-      <c r="M6" s="280"/>
-      <c r="N6" s="281"/>
+      <c r="C6" s="285"/>
+      <c r="D6" s="286"/>
+      <c r="E6" s="286"/>
+      <c r="F6" s="286"/>
+      <c r="G6" s="286"/>
+      <c r="H6" s="286"/>
+      <c r="I6" s="286"/>
+      <c r="J6" s="286"/>
+      <c r="K6" s="286"/>
+      <c r="L6" s="286"/>
+      <c r="M6" s="286"/>
+      <c r="N6" s="287"/>
       <c r="O6" s="15"/>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" s="7"/>
       <c r="B7" s="7"/>
-      <c r="C7" s="279"/>
-      <c r="D7" s="280"/>
-      <c r="E7" s="280"/>
-      <c r="F7" s="280"/>
-      <c r="G7" s="280"/>
-      <c r="H7" s="280"/>
-      <c r="I7" s="280"/>
-      <c r="J7" s="280"/>
-      <c r="K7" s="280"/>
-      <c r="L7" s="280"/>
-      <c r="M7" s="280"/>
-      <c r="N7" s="281"/>
+      <c r="C7" s="285"/>
+      <c r="D7" s="286"/>
+      <c r="E7" s="286"/>
+      <c r="F7" s="286"/>
+      <c r="G7" s="286"/>
+      <c r="H7" s="286"/>
+      <c r="I7" s="286"/>
+      <c r="J7" s="286"/>
+      <c r="K7" s="286"/>
+      <c r="L7" s="286"/>
+      <c r="M7" s="286"/>
+      <c r="N7" s="287"/>
       <c r="O7" s="15"/>
     </row>
-    <row r="8" spans="1:18" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="7"/>
       <c r="B8" s="7"/>
-      <c r="C8" s="282"/>
-      <c r="D8" s="283"/>
-      <c r="E8" s="283"/>
-      <c r="F8" s="283"/>
-      <c r="G8" s="283"/>
-      <c r="H8" s="283"/>
-      <c r="I8" s="283"/>
-      <c r="J8" s="283"/>
-      <c r="K8" s="283"/>
-      <c r="L8" s="283"/>
-      <c r="M8" s="283"/>
-      <c r="N8" s="284"/>
+      <c r="C8" s="288"/>
+      <c r="D8" s="289"/>
+      <c r="E8" s="289"/>
+      <c r="F8" s="289"/>
+      <c r="G8" s="289"/>
+      <c r="H8" s="289"/>
+      <c r="I8" s="289"/>
+      <c r="J8" s="289"/>
+      <c r="K8" s="289"/>
+      <c r="L8" s="289"/>
+      <c r="M8" s="289"/>
+      <c r="N8" s="290"/>
       <c r="P8" s="84"/>
     </row>
-    <row r="9" spans="1:18" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:18" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
-      <c r="C9" s="285" t="s">
-        <v>312</v>
-      </c>
-      <c r="D9" s="286"/>
-      <c r="E9" s="286"/>
-      <c r="F9" s="286"/>
-      <c r="G9" s="286"/>
-      <c r="H9" s="286"/>
-      <c r="I9" s="286"/>
-      <c r="J9" s="286"/>
-      <c r="K9" s="286"/>
-      <c r="L9" s="286"/>
-      <c r="M9" s="286"/>
-      <c r="N9" s="287"/>
+      <c r="C9" s="291" t="s">
+        <v>311</v>
+      </c>
+      <c r="D9" s="292"/>
+      <c r="E9" s="292"/>
+      <c r="F9" s="292"/>
+      <c r="G9" s="292"/>
+      <c r="H9" s="292"/>
+      <c r="I9" s="292"/>
+      <c r="J9" s="292"/>
+      <c r="K9" s="292"/>
+      <c r="L9" s="292"/>
+      <c r="M9" s="292"/>
+      <c r="N9" s="293"/>
       <c r="P9" t="s">
         <v>250</v>
       </c>
@@ -6028,21 +6026,21 @@
         <v>141730.21116000001</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="7"/>
       <c r="B10" s="7"/>
-      <c r="C10" s="288"/>
-      <c r="D10" s="289"/>
-      <c r="E10" s="289"/>
-      <c r="F10" s="289"/>
-      <c r="G10" s="289"/>
-      <c r="H10" s="289"/>
-      <c r="I10" s="289"/>
-      <c r="J10" s="289"/>
-      <c r="K10" s="289"/>
-      <c r="L10" s="289"/>
-      <c r="M10" s="289"/>
-      <c r="N10" s="290"/>
+      <c r="C10" s="294"/>
+      <c r="D10" s="295"/>
+      <c r="E10" s="295"/>
+      <c r="F10" s="295"/>
+      <c r="G10" s="295"/>
+      <c r="H10" s="295"/>
+      <c r="I10" s="295"/>
+      <c r="J10" s="295"/>
+      <c r="K10" s="295"/>
+      <c r="L10" s="295"/>
+      <c r="M10" s="295"/>
+      <c r="N10" s="296"/>
       <c r="P10" t="s">
         <v>251</v>
       </c>
@@ -6051,48 +6049,48 @@
         <v>167976.54656000002</v>
       </c>
     </row>
-    <row r="11" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="263" t="s">
+    <row r="11" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="264" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="297" t="s">
+      <c r="B11" s="266" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="263" t="s">
+      <c r="C11" s="264" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="299" t="s">
+      <c r="D11" s="268" t="s">
         <v>12</v>
       </c>
-      <c r="E11" s="299" t="s">
-        <v>269</v>
-      </c>
-      <c r="F11" s="263" t="s">
+      <c r="E11" s="268" t="s">
+        <v>268</v>
+      </c>
+      <c r="F11" s="264" t="s">
         <v>27</v>
       </c>
-      <c r="G11" s="263" t="s">
+      <c r="G11" s="264" t="s">
         <v>13</v>
       </c>
-      <c r="H11" s="263" t="s">
+      <c r="H11" s="264" t="s">
         <v>14</v>
       </c>
-      <c r="I11" s="269" t="s">
+      <c r="I11" s="275" t="s">
         <v>15</v>
       </c>
-      <c r="J11" s="271" t="s">
+      <c r="J11" s="277" t="s">
         <v>16</v>
       </c>
-      <c r="K11" s="271" t="s">
+      <c r="K11" s="277" t="s">
         <v>18</v>
       </c>
-      <c r="L11" s="274" t="s">
+      <c r="L11" s="280" t="s">
         <v>40</v>
       </c>
-      <c r="M11" s="271" t="s">
-        <v>280</v>
-      </c>
-      <c r="N11" s="271" t="s">
+      <c r="M11" s="277" t="s">
         <v>279</v>
+      </c>
+      <c r="N11" s="277" t="s">
+        <v>278</v>
       </c>
       <c r="P11" t="s">
         <v>252</v>
@@ -6102,21 +6100,21 @@
         <v>158790.32916999998</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="264"/>
-      <c r="B12" s="298"/>
-      <c r="C12" s="264"/>
-      <c r="D12" s="300"/>
-      <c r="E12" s="300"/>
-      <c r="F12" s="264"/>
-      <c r="G12" s="264"/>
-      <c r="H12" s="264"/>
-      <c r="I12" s="270"/>
-      <c r="J12" s="272"/>
-      <c r="K12" s="272"/>
-      <c r="L12" s="275"/>
-      <c r="M12" s="272"/>
-      <c r="N12" s="272"/>
+    <row r="12" spans="1:18" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="265"/>
+      <c r="B12" s="267"/>
+      <c r="C12" s="265"/>
+      <c r="D12" s="269"/>
+      <c r="E12" s="269"/>
+      <c r="F12" s="265"/>
+      <c r="G12" s="265"/>
+      <c r="H12" s="265"/>
+      <c r="I12" s="276"/>
+      <c r="J12" s="278"/>
+      <c r="K12" s="278"/>
+      <c r="L12" s="281"/>
+      <c r="M12" s="278"/>
+      <c r="N12" s="278"/>
       <c r="P12" t="s">
         <v>253</v>
       </c>
@@ -6125,19 +6123,19 @@
         <v>195535.19872999997</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="264"/>
-      <c r="B13" s="298"/>
-      <c r="C13" s="264"/>
-      <c r="D13" s="300"/>
-      <c r="E13" s="300"/>
-      <c r="F13" s="264"/>
-      <c r="G13" s="264"/>
-      <c r="H13" s="264"/>
-      <c r="I13" s="270"/>
-      <c r="J13" s="272"/>
-      <c r="K13" s="273"/>
-      <c r="L13" s="275"/>
+    <row r="13" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="265"/>
+      <c r="B13" s="267"/>
+      <c r="C13" s="265"/>
+      <c r="D13" s="269"/>
+      <c r="E13" s="269"/>
+      <c r="F13" s="265"/>
+      <c r="G13" s="265"/>
+      <c r="H13" s="265"/>
+      <c r="I13" s="276"/>
+      <c r="J13" s="278"/>
+      <c r="K13" s="279"/>
+      <c r="L13" s="281"/>
       <c r="M13" s="132" t="str">
         <f>RESUMEN!A20</f>
         <v>VTO 16/02</v>
@@ -6154,7 +6152,7 @@
         <v>228343.11798000001</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
         <v>118</v>
       </c>
@@ -6166,7 +6164,7 @@
         <v>175</v>
       </c>
       <c r="E14" s="108" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F14" s="143">
         <v>1.0800000000000001E-2</v>
@@ -6197,17 +6195,17 @@
         <v>441436.50630288007</v>
       </c>
       <c r="O14" s="115"/>
-      <c r="Q14" s="262"/>
-      <c r="R14" s="262"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="Q14" s="270"/>
+      <c r="R14" s="270"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" s="6"/>
       <c r="B15" s="6"/>
       <c r="C15" s="35" t="s">
         <v>117</v>
       </c>
       <c r="D15" s="108" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E15" s="190"/>
       <c r="F15" s="143">
@@ -6241,10 +6239,10 @@
         <v>307962.66747008008</v>
       </c>
       <c r="O15" s="115"/>
-      <c r="Q15" s="262"/>
-      <c r="R15" s="262"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="Q15" s="270"/>
+      <c r="R15" s="270"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
         <v>118</v>
       </c>
@@ -6253,10 +6251,10 @@
         <v>114</v>
       </c>
       <c r="D16" s="108" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E16" s="108" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F16" s="143">
         <v>1.21E-2</v>
@@ -6292,7 +6290,7 @@
       <c r="O16" s="115"/>
       <c r="R16" s="43"/>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
         <v>118</v>
       </c>
@@ -6335,7 +6333,7 @@
       <c r="O17" s="115"/>
       <c r="R17" s="43"/>
     </row>
-    <row r="18" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="6" t="s">
         <v>118</v>
       </c>
@@ -6344,7 +6342,7 @@
         <v>116</v>
       </c>
       <c r="D18" s="149" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E18" s="149"/>
       <c r="F18" s="150">
@@ -6381,7 +6379,7 @@
       <c r="O18" s="115"/>
       <c r="R18" s="43"/>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A19" s="57" t="s">
         <v>120</v>
       </c>
@@ -6430,11 +6428,11 @@
         <v>0.01</v>
       </c>
       <c r="P19" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="R19" s="43"/>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A20" s="57" t="s">
         <v>121</v>
       </c>
@@ -6485,7 +6483,7 @@
       </c>
       <c r="R20" s="43"/>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A21" s="57" t="s">
         <v>120</v>
       </c>
@@ -6535,7 +6533,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A22" s="57" t="s">
         <v>122</v>
       </c>
@@ -6547,7 +6545,7 @@
         <v>180</v>
       </c>
       <c r="E22" s="200" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="F22" s="201">
         <v>9.4000000000000004E-3</v>
@@ -6586,10 +6584,10 @@
         <v>0.04</v>
       </c>
       <c r="P22" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A23" s="57" t="s">
         <v>122</v>
       </c>
@@ -6601,7 +6599,7 @@
         <v>181</v>
       </c>
       <c r="E23" s="135" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F23" s="136">
         <v>8.6999999999999994E-3</v>
@@ -6639,7 +6637,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A24" s="57" t="s">
         <v>122</v>
       </c>
@@ -6651,7 +6649,7 @@
         <v>182</v>
       </c>
       <c r="E24" s="135" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F24" s="136">
         <v>9.4999999999999998E-3</v>
@@ -6691,7 +6689,7 @@
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A25" s="57" t="s">
         <v>120</v>
       </c>
@@ -6703,7 +6701,7 @@
         <v>182</v>
       </c>
       <c r="E25" s="135" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F25" s="136">
         <v>1.6500000000000001E-2</v>
@@ -6743,7 +6741,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A26" s="57" t="s">
         <v>121</v>
       </c>
@@ -6752,7 +6750,7 @@
         <v>51</v>
       </c>
       <c r="D26" s="108" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E26" s="135"/>
       <c r="F26" s="136">
@@ -6793,7 +6791,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A27" s="108" t="s">
         <v>120</v>
       </c>
@@ -6805,7 +6803,7 @@
         <v>182</v>
       </c>
       <c r="E27" s="200" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="F27" s="201">
         <v>1.78E-2</v>
@@ -6846,7 +6844,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A28" s="108" t="s">
         <v>122</v>
       </c>
@@ -6855,7 +6853,7 @@
         <v>53</v>
       </c>
       <c r="D28" s="108" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="E28" s="135"/>
       <c r="F28" s="136">
@@ -6896,7 +6894,7 @@
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A29" s="108" t="s">
         <v>122</v>
       </c>
@@ -6905,7 +6903,7 @@
         <v>54</v>
       </c>
       <c r="D29" s="108" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E29" s="135"/>
       <c r="F29" s="136">
@@ -6946,7 +6944,7 @@
         <v>0.10999999999999999</v>
       </c>
     </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A30" s="108" t="s">
         <v>122</v>
       </c>
@@ -6993,7 +6991,7 @@
         <v>0.11999999999999998</v>
       </c>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A31" s="108" t="s">
         <v>120</v>
       </c>
@@ -7043,7 +7041,7 @@
         <v>0.12999999999999998</v>
       </c>
     </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A32" s="57" t="s">
         <v>121</v>
       </c>
@@ -7055,7 +7053,7 @@
         <v>256</v>
       </c>
       <c r="E32" s="135" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="F32" s="136">
         <v>7.1999999999999998E-3</v>
@@ -7095,7 +7093,7 @@
         <v>0.13999999999999999</v>
       </c>
     </row>
-    <row r="33" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A33" s="57" t="s">
         <v>120</v>
       </c>
@@ -7145,7 +7143,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="34" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A34" s="139" t="s">
         <v>122</v>
       </c>
@@ -7154,7 +7152,7 @@
         <v>59</v>
       </c>
       <c r="D34" s="108" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E34" s="135"/>
       <c r="F34" s="136">
@@ -7195,10 +7193,10 @@
         <v>0.16</v>
       </c>
       <c r="P34" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="35" spans="1:113" x14ac:dyDescent="0.25">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="35" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A35" s="57" t="s">
         <v>122</v>
       </c>
@@ -7210,7 +7208,7 @@
         <v>183</v>
       </c>
       <c r="E35" s="135" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F35" s="136">
         <v>8.6999999999999994E-3</v>
@@ -7250,7 +7248,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="36" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A36" s="57" t="s">
         <v>122</v>
       </c>
@@ -7297,7 +7295,7 @@
         <v>0.18000000000000002</v>
       </c>
     </row>
-    <row r="37" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A37" s="57" t="s">
         <v>120</v>
       </c>
@@ -7309,7 +7307,7 @@
         <v>186</v>
       </c>
       <c r="E37" s="135" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F37" s="136">
         <v>1.6400000000000001E-2</v>
@@ -7347,10 +7345,10 @@
         <v>0.19000000000000003</v>
       </c>
       <c r="P37" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="38" spans="1:113" x14ac:dyDescent="0.25">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="38" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A38" s="57" t="s">
         <v>121</v>
       </c>
@@ -7400,7 +7398,7 @@
         <v>0.20000000000000004</v>
       </c>
     </row>
-    <row r="39" spans="1:113" s="140" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:113" s="140" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A39" s="108" t="s">
         <v>120</v>
       </c>
@@ -7547,7 +7545,7 @@
       <c r="DH39" s="73"/>
       <c r="DI39" s="73"/>
     </row>
-    <row r="40" spans="1:113" s="140" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:113" s="140" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A40" s="108" t="s">
         <v>122</v>
       </c>
@@ -7556,7 +7554,7 @@
         <v>65</v>
       </c>
       <c r="D40" s="108" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E40" s="135"/>
       <c r="F40" s="136">
@@ -7592,7 +7590,7 @@
         <v>0.22000000000000006</v>
       </c>
       <c r="P40" s="73" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="Q40" s="73"/>
       <c r="R40" s="73"/>
@@ -7692,7 +7690,7 @@
       <c r="DH40" s="73"/>
       <c r="DI40" s="73"/>
     </row>
-    <row r="41" spans="1:113" s="140" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:113" s="140" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A41" s="108" t="s">
         <v>122</v>
       </c>
@@ -7742,7 +7740,7 @@
         <v>0.23000000000000007</v>
       </c>
       <c r="P41" s="73" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="Q41" s="73"/>
       <c r="R41" s="73"/>
@@ -7842,7 +7840,7 @@
       <c r="DH41" s="73"/>
       <c r="DI41" s="73"/>
     </row>
-    <row r="42" spans="1:113" s="140" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:113" s="140" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A42" s="108" t="s">
         <v>122</v>
       </c>
@@ -7851,7 +7849,7 @@
         <v>67</v>
       </c>
       <c r="D42" s="108" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E42" s="135"/>
       <c r="F42" s="136">
@@ -7987,7 +7985,7 @@
       <c r="DH42" s="73"/>
       <c r="DI42" s="73"/>
     </row>
-    <row r="43" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A43" s="57" t="s">
         <v>120</v>
       </c>
@@ -8037,7 +8035,7 @@
         <v>0.25000000000000006</v>
       </c>
     </row>
-    <row r="44" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A44" s="57" t="s">
         <v>121</v>
       </c>
@@ -8049,7 +8047,7 @@
         <v>189</v>
       </c>
       <c r="E44" s="135" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F44" s="136">
         <v>7.1999999999999998E-3</v>
@@ -8089,7 +8087,7 @@
         <v>0.26000000000000006</v>
       </c>
     </row>
-    <row r="45" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A45" s="57" t="s">
         <v>120</v>
       </c>
@@ -8139,13 +8137,13 @@
         <v>0.27000000000000007</v>
       </c>
       <c r="P45" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="Q45" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="46" spans="1:113" x14ac:dyDescent="0.25">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="46" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A46" s="172" t="s">
         <v>122</v>
       </c>
@@ -8154,7 +8152,7 @@
         <v>71</v>
       </c>
       <c r="D46" s="108" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E46" s="135"/>
       <c r="F46" s="136">
@@ -8195,7 +8193,7 @@
         <v>0.28000000000000008</v>
       </c>
     </row>
-    <row r="47" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A47" s="57" t="s">
         <v>122</v>
       </c>
@@ -8207,7 +8205,7 @@
         <v>181</v>
       </c>
       <c r="E47" s="135" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="F47" s="136">
         <v>8.6999999999999994E-3</v>
@@ -8244,7 +8242,7 @@
         <v>0.29000000000000009</v>
       </c>
     </row>
-    <row r="48" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A48" s="57" t="s">
         <v>122</v>
       </c>
@@ -8294,7 +8292,7 @@
         <v>0.3000000000000001</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A49" s="57" t="s">
         <v>120</v>
       </c>
@@ -8344,7 +8342,7 @@
         <v>0.31000000000000011</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A50" s="57" t="s">
         <v>121</v>
       </c>
@@ -8393,7 +8391,7 @@
       </c>
       <c r="P50" s="43"/>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A51" s="57" t="s">
         <v>120</v>
       </c>
@@ -8444,7 +8442,7 @@
       </c>
       <c r="P51" s="43"/>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A52" s="57" t="s">
         <v>122</v>
       </c>
@@ -8453,7 +8451,7 @@
         <v>77</v>
       </c>
       <c r="D52" s="108" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E52" s="135"/>
       <c r="F52" s="136">
@@ -8492,10 +8490,10 @@
         <v>0.34000000000000014</v>
       </c>
       <c r="P52" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A53" s="57" t="s">
         <v>122</v>
       </c>
@@ -8545,7 +8543,7 @@
         <v>0.35000000000000014</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A54" s="57" t="s">
         <v>122</v>
       </c>
@@ -8595,7 +8593,7 @@
         <v>0.36000000000000015</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A55" s="57" t="s">
         <v>120</v>
       </c>
@@ -8646,7 +8644,7 @@
       </c>
       <c r="Q55" s="59"/>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A56" s="57" t="s">
         <v>121</v>
       </c>
@@ -8658,7 +8656,7 @@
         <v>196</v>
       </c>
       <c r="E56" s="135" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F56" s="136">
         <v>7.1999999999999998E-3</v>
@@ -8698,7 +8696,7 @@
         <v>0.38000000000000017</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A57" s="57" t="s">
         <v>120</v>
       </c>
@@ -8747,7 +8745,7 @@
         <v>0.39000000000000018</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A58" s="57" t="s">
         <v>122</v>
       </c>
@@ -8759,7 +8757,7 @@
         <v>198</v>
       </c>
       <c r="E58" s="135" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F58" s="136">
         <v>9.4000000000000004E-3</v>
@@ -8800,7 +8798,7 @@
         <v>0.40000000000000019</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A59" s="108" t="s">
         <v>122</v>
       </c>
@@ -8809,7 +8807,7 @@
         <v>84</v>
       </c>
       <c r="D59" s="108" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="E59" s="135"/>
       <c r="F59" s="136">
@@ -8853,7 +8851,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A60" s="108" t="s">
         <v>122</v>
       </c>
@@ -8901,10 +8899,10 @@
         <v>0.42000000000000021</v>
       </c>
       <c r="P60" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="61" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A61" s="108" t="s">
         <v>120</v>
       </c>
@@ -8954,7 +8952,7 @@
         <v>0.43000000000000022</v>
       </c>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A62" s="108" t="s">
         <v>121</v>
       </c>
@@ -9004,7 +9002,7 @@
         <v>0.44000000000000022</v>
       </c>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A63" s="57" t="s">
         <v>120</v>
       </c>
@@ -9054,7 +9052,7 @@
         <v>0.45000000000000023</v>
       </c>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A64" s="57" t="s">
         <v>122</v>
       </c>
@@ -9066,7 +9064,7 @@
         <v>202</v>
       </c>
       <c r="E64" s="135" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="F64" s="136">
         <v>9.4000000000000004E-3</v>
@@ -9106,7 +9104,7 @@
         <v>0.46000000000000024</v>
       </c>
     </row>
-    <row r="65" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A65" s="57" t="s">
         <v>122</v>
       </c>
@@ -9156,7 +9154,7 @@
         <v>0.47000000000000025</v>
       </c>
     </row>
-    <row r="66" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A66" s="57" t="s">
         <v>122</v>
       </c>
@@ -9206,7 +9204,7 @@
       </c>
       <c r="R66" s="183"/>
     </row>
-    <row r="67" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A67" s="57" t="s">
         <v>120</v>
       </c>
@@ -9255,7 +9253,7 @@
       </c>
       <c r="R67" s="43"/>
     </row>
-    <row r="68" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A68" s="139" t="s">
         <v>121</v>
       </c>
@@ -9302,7 +9300,7 @@
         <v>0.50000000000000022</v>
       </c>
     </row>
-    <row r="69" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A69" s="57" t="s">
         <v>120</v>
       </c>
@@ -9352,7 +9350,7 @@
         <v>0.51000000000000023</v>
       </c>
     </row>
-    <row r="70" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A70" s="57" t="s">
         <v>122</v>
       </c>
@@ -9402,7 +9400,7 @@
         <v>0.52000000000000024</v>
       </c>
     </row>
-    <row r="71" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A71" s="57" t="s">
         <v>122</v>
       </c>
@@ -9455,7 +9453,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="72" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A72" s="57" t="s">
         <v>122</v>
       </c>
@@ -9505,7 +9503,7 @@
         <v>0.54000000000000026</v>
       </c>
     </row>
-    <row r="73" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A73" s="57" t="s">
         <v>123</v>
       </c>
@@ -9554,7 +9552,7 @@
       </c>
       <c r="P73" s="73"/>
     </row>
-    <row r="74" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A74" s="57" t="s">
         <v>120</v>
       </c>
@@ -9604,7 +9602,7 @@
         <v>0.56000000000000028</v>
       </c>
     </row>
-    <row r="75" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A75" s="57" t="s">
         <v>122</v>
       </c>
@@ -9654,7 +9652,7 @@
         <v>0.57000000000000028</v>
       </c>
     </row>
-    <row r="76" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A76" s="57" t="s">
         <v>122</v>
       </c>
@@ -9666,7 +9664,7 @@
         <v>211</v>
       </c>
       <c r="E76" s="135" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F76" s="136">
         <v>8.6999999999999994E-3</v>
@@ -9703,7 +9701,7 @@
         <v>0.58000000000000029</v>
       </c>
     </row>
-    <row r="77" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A77" s="57" t="s">
         <v>122</v>
       </c>
@@ -9753,7 +9751,7 @@
         <v>0.5900000000000003</v>
       </c>
     </row>
-    <row r="78" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A78" s="57" t="s">
         <v>123</v>
       </c>
@@ -9803,7 +9801,7 @@
         <v>0.60000000000000031</v>
       </c>
     </row>
-    <row r="79" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A79" s="57" t="s">
         <v>120</v>
       </c>
@@ -9853,7 +9851,7 @@
         <v>0.61000000000000032</v>
       </c>
     </row>
-    <row r="80" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A80" s="57" t="s">
         <v>122</v>
       </c>
@@ -9900,7 +9898,7 @@
         <v>0.62000000000000033</v>
       </c>
     </row>
-    <row r="81" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A81" s="57" t="s">
         <v>122</v>
       </c>
@@ -9912,7 +9910,7 @@
         <v>216</v>
       </c>
       <c r="E81" s="200" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F81" s="201">
         <v>8.6999999999999994E-3</v>
@@ -9952,7 +9950,7 @@
         <v>0.63000000000000034</v>
       </c>
     </row>
-    <row r="82" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A82" s="57" t="s">
         <v>122</v>
       </c>
@@ -10002,10 +10000,10 @@
         <v>0.64000000000000035</v>
       </c>
       <c r="P82" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="83" spans="1:16" x14ac:dyDescent="0.25">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="83" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A83" s="57" t="s">
         <v>123</v>
       </c>
@@ -10014,7 +10012,7 @@
         <v>108</v>
       </c>
       <c r="D83" s="108" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E83" s="135"/>
       <c r="F83" s="136">
@@ -10055,7 +10053,7 @@
         <v>0.65000000000000036</v>
       </c>
     </row>
-    <row r="84" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A84" s="57" t="s">
         <v>120</v>
       </c>
@@ -10103,7 +10101,7 @@
         <v>0.66000000000000036</v>
       </c>
     </row>
-    <row r="85" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A85" s="57" t="s">
         <v>122</v>
       </c>
@@ -10151,7 +10149,7 @@
         <v>0.67000000000000037</v>
       </c>
     </row>
-    <row r="86" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A86" s="57" t="s">
         <v>122</v>
       </c>
@@ -10201,7 +10199,7 @@
         <v>0.68000000000000038</v>
       </c>
     </row>
-    <row r="87" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A87" s="108" t="s">
         <v>122</v>
       </c>
@@ -10251,7 +10249,7 @@
         <v>0.69000000000000039</v>
       </c>
     </row>
-    <row r="88" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A88" s="108"/>
       <c r="B88" s="35"/>
       <c r="C88" s="35" t="s">
@@ -10299,7 +10297,7 @@
         <v>0.7000000000000004</v>
       </c>
     </row>
-    <row r="89" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A89" s="108"/>
       <c r="B89" s="35"/>
       <c r="C89" s="35" t="s">
@@ -10347,7 +10345,7 @@
         <v>0.71000000000000041</v>
       </c>
     </row>
-    <row r="90" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A90" s="108"/>
       <c r="B90" s="35"/>
       <c r="C90" s="35" t="s">
@@ -10395,7 +10393,7 @@
         <v>0.72000000000000042</v>
       </c>
     </row>
-    <row r="91" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A91" s="108"/>
       <c r="B91" s="35"/>
       <c r="C91" s="35" t="s">
@@ -10443,7 +10441,7 @@
         <v>0.73000000000000043</v>
       </c>
     </row>
-    <row r="92" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A92" s="108"/>
       <c r="B92" s="35"/>
       <c r="C92" s="176" t="s">
@@ -10491,10 +10489,10 @@
         <v>0.74000000000000044</v>
       </c>
       <c r="P92" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="93" spans="1:16" x14ac:dyDescent="0.25">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="93" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A93" s="108"/>
       <c r="B93" s="35"/>
       <c r="C93" s="35" t="s">
@@ -10541,7 +10539,7 @@
         <v>0.75000000000000044</v>
       </c>
     </row>
-    <row r="94" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A94" s="108"/>
       <c r="B94" s="35"/>
       <c r="C94" s="35" t="s">
@@ -10589,7 +10587,7 @@
         <v>0.76000000000000045</v>
       </c>
     </row>
-    <row r="95" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A95" s="108"/>
       <c r="B95" s="35"/>
       <c r="C95" s="35" t="s">
@@ -10637,14 +10635,14 @@
         <v>0.77000000000000046</v>
       </c>
     </row>
-    <row r="96" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A96" s="108"/>
       <c r="B96" s="35"/>
       <c r="C96" s="35" t="s">
         <v>132</v>
       </c>
       <c r="D96" s="108" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E96" s="108"/>
       <c r="F96" s="143">
@@ -10685,7 +10683,7 @@
         <v>0.78000000000000047</v>
       </c>
     </row>
-    <row r="97" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A97" s="108"/>
       <c r="B97" s="35"/>
       <c r="C97" s="35" t="s">
@@ -10730,7 +10728,7 @@
         <v>0.79000000000000048</v>
       </c>
     </row>
-    <row r="98" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A98" s="108"/>
       <c r="B98" s="35"/>
       <c r="C98" s="35" t="s">
@@ -10778,7 +10776,7 @@
         <v>0.80000000000000049</v>
       </c>
     </row>
-    <row r="99" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A99" s="108"/>
       <c r="B99" s="35"/>
       <c r="C99" s="35" t="s">
@@ -10823,14 +10821,14 @@
         <v>0.8100000000000005</v>
       </c>
     </row>
-    <row r="100" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A100" s="108"/>
       <c r="B100" s="35"/>
       <c r="C100" s="35" t="s">
         <v>136</v>
       </c>
       <c r="D100" s="108" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="E100" s="108"/>
       <c r="F100" s="89">
@@ -10871,7 +10869,7 @@
         <v>0.82000000000000051</v>
       </c>
     </row>
-    <row r="101" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A101" s="108"/>
       <c r="B101" s="35"/>
       <c r="C101" s="35" t="s">
@@ -10919,7 +10917,7 @@
         <v>0.83000000000000052</v>
       </c>
     </row>
-    <row r="102" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="108"/>
       <c r="B102" s="35"/>
       <c r="C102" s="35" t="s">
@@ -10967,7 +10965,7 @@
         <v>0.84000000000000052</v>
       </c>
     </row>
-    <row r="103" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="108"/>
       <c r="B103" s="35"/>
       <c r="C103" s="35" t="s">
@@ -11015,7 +11013,7 @@
         <v>0.85000000000000053</v>
       </c>
     </row>
-    <row r="104" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="108"/>
       <c r="B104" s="35"/>
       <c r="C104" s="35" t="s">
@@ -11063,7 +11061,7 @@
         <v>0.86000000000000054</v>
       </c>
     </row>
-    <row r="105" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="108"/>
       <c r="B105" s="35"/>
       <c r="C105" s="35" t="s">
@@ -11111,7 +11109,7 @@
         <v>0.87000000000000055</v>
       </c>
     </row>
-    <row r="106" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="108"/>
       <c r="B106" s="35"/>
       <c r="C106" s="35" t="s">
@@ -11159,7 +11157,7 @@
         <v>0.88000000000000056</v>
       </c>
     </row>
-    <row r="107" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="108"/>
       <c r="B107" s="35"/>
       <c r="C107" s="35" t="s">
@@ -11206,7 +11204,7 @@
         <v>0.89000000000000057</v>
       </c>
     </row>
-    <row r="108" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="108"/>
       <c r="B108" s="35"/>
       <c r="C108" s="35" t="s">
@@ -11254,7 +11252,7 @@
         <v>0.90000000000000058</v>
       </c>
     </row>
-    <row r="109" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="108"/>
       <c r="B109" s="35"/>
       <c r="C109" s="35" t="s">
@@ -11302,7 +11300,7 @@
         <v>0.91000000000000059</v>
       </c>
     </row>
-    <row r="110" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="108"/>
       <c r="B110" s="35"/>
       <c r="C110" s="35" t="s">
@@ -11350,7 +11348,7 @@
         <v>0.9200000000000006</v>
       </c>
     </row>
-    <row r="111" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="108"/>
       <c r="B111" s="35"/>
       <c r="C111" s="35" t="s">
@@ -11398,7 +11396,7 @@
         <v>0.9300000000000006</v>
       </c>
     </row>
-    <row r="112" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A112" s="108"/>
       <c r="B112" s="35"/>
       <c r="C112" s="35" t="s">
@@ -11446,7 +11444,7 @@
         <v>0.94000000000000061</v>
       </c>
     </row>
-    <row r="113" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A113" s="108"/>
       <c r="B113" s="35"/>
       <c r="C113" s="35" t="s">
@@ -11494,7 +11492,7 @@
         <v>0.95000000000000062</v>
       </c>
     </row>
-    <row r="114" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A114" s="108"/>
       <c r="B114" s="35"/>
       <c r="C114" s="35" t="s">
@@ -11542,7 +11540,7 @@
         <v>0.96000000000000063</v>
       </c>
     </row>
-    <row r="115" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A115" s="108"/>
       <c r="B115" s="35"/>
       <c r="C115" s="35" t="s">
@@ -11590,7 +11588,7 @@
         <v>0.97000000000000064</v>
       </c>
     </row>
-    <row r="116" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A116" s="108"/>
       <c r="B116" s="35"/>
       <c r="C116" s="35" t="s">
@@ -11600,7 +11598,7 @@
         <v>182</v>
       </c>
       <c r="E116" s="108" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F116" s="143">
         <v>2.3E-3</v>
@@ -11640,7 +11638,7 @@
         <v>0.98000000000000065</v>
       </c>
     </row>
-    <row r="117" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A117" s="108"/>
       <c r="B117" s="35"/>
       <c r="C117" s="35" t="s">
@@ -11685,7 +11683,7 @@
         <v>0.99000000000000066</v>
       </c>
     </row>
-    <row r="118" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A118" s="108"/>
       <c r="B118" s="35"/>
       <c r="C118" s="35" t="s">
@@ -11733,17 +11731,17 @@
         <v>1.0000000000000007</v>
       </c>
       <c r="P118" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="119" spans="1:16" x14ac:dyDescent="0.25">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="119" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A119" s="127"/>
       <c r="B119" s="35"/>
       <c r="C119" s="35" t="s">
         <v>155</v>
       </c>
       <c r="D119" s="108" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="E119" s="108"/>
       <c r="F119" s="143">
@@ -11784,7 +11782,7 @@
         <v>1.0100000000000007</v>
       </c>
     </row>
-    <row r="120" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A120" s="127"/>
       <c r="B120" s="35"/>
       <c r="C120" s="35" t="s">
@@ -11832,7 +11830,7 @@
         <v>1.0200000000000007</v>
       </c>
     </row>
-    <row r="121" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A121" s="127"/>
       <c r="B121" s="35"/>
       <c r="C121" s="35" t="s">
@@ -11880,7 +11878,7 @@
         <v>1.0300000000000007</v>
       </c>
     </row>
-    <row r="122" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A122" s="127"/>
       <c r="B122" s="35"/>
       <c r="C122" s="35" t="s">
@@ -11928,7 +11926,7 @@
         <v>1.0400000000000007</v>
       </c>
     </row>
-    <row r="123" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A123" s="127"/>
       <c r="B123" s="35"/>
       <c r="C123" s="35" t="s">
@@ -11976,7 +11974,7 @@
         <v>1.0500000000000007</v>
       </c>
     </row>
-    <row r="124" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A124" s="127"/>
       <c r="B124" s="35"/>
       <c r="C124" s="35" t="s">
@@ -12024,10 +12022,10 @@
         <v>1.0600000000000007</v>
       </c>
       <c r="P124" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="125" spans="1:16" x14ac:dyDescent="0.25">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="125" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A125" s="175"/>
       <c r="B125" s="170"/>
       <c r="C125" s="35" t="s">
@@ -12037,7 +12035,7 @@
         <v>182</v>
       </c>
       <c r="E125" s="135" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F125" s="143">
         <v>2.3E-3</v>
@@ -12076,7 +12074,7 @@
         <v>1.0700000000000007</v>
       </c>
     </row>
-    <row r="126" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A126" s="175"/>
       <c r="B126" s="170"/>
       <c r="C126" s="35" t="s">
@@ -12124,7 +12122,7 @@
         <v>1.0800000000000007</v>
       </c>
     </row>
-    <row r="127" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A127" s="127"/>
       <c r="B127" s="35"/>
       <c r="C127" s="35" t="s">
@@ -12172,7 +12170,7 @@
         <v>1.0900000000000007</v>
       </c>
     </row>
-    <row r="128" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A128" s="127"/>
       <c r="B128" s="35"/>
       <c r="C128" s="35" t="s">
@@ -12220,7 +12218,7 @@
         <v>1.1000000000000008</v>
       </c>
     </row>
-    <row r="129" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A129" s="127"/>
       <c r="B129" s="35"/>
       <c r="C129" s="35" t="s">
@@ -12268,7 +12266,7 @@
         <v>1.1100000000000008</v>
       </c>
     </row>
-    <row r="130" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A130" s="127" t="s">
         <v>26</v>
       </c>
@@ -12318,7 +12316,7 @@
         <v>1.1200000000000008</v>
       </c>
     </row>
-    <row r="131" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A131" s="127" t="s">
         <v>26</v>
       </c>
@@ -12327,7 +12325,7 @@
         <v>167</v>
       </c>
       <c r="D131" s="108" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E131" s="108"/>
       <c r="F131" s="89">
@@ -12368,7 +12366,7 @@
         <v>1.1300000000000008</v>
       </c>
     </row>
-    <row r="132" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A132" s="53" t="s">
         <v>26</v>
       </c>
@@ -12386,7 +12384,7 @@
       <c r="M132" s="5"/>
       <c r="N132" s="8"/>
     </row>
-    <row r="133" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="27"/>
       <c r="B133" s="27"/>
       <c r="C133" s="27"/>
@@ -12427,41 +12425,41 @@
       </c>
       <c r="P133" s="59"/>
     </row>
-    <row r="134" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="K134" s="61">
         <f>K133-L1</f>
         <v>3118989.9373000227</v>
       </c>
     </row>
-    <row r="135" spans="1:16" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C135" s="266"/>
-      <c r="D135" s="266"/>
-      <c r="E135" s="266"/>
-      <c r="F135" s="266"/>
-      <c r="G135" s="266"/>
-      <c r="H135" s="266"/>
-      <c r="I135" s="266"/>
-      <c r="J135" s="266"/>
-      <c r="K135" s="266"/>
-      <c r="L135" s="266"/>
-      <c r="M135" s="266"/>
-      <c r="N135" s="266"/>
-    </row>
-    <row r="136" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C136" s="266"/>
-      <c r="D136" s="266"/>
-      <c r="E136" s="266"/>
-      <c r="F136" s="266"/>
-      <c r="G136" s="266"/>
-      <c r="H136" s="266"/>
-      <c r="I136" s="266"/>
-      <c r="J136" s="266"/>
-      <c r="K136" s="266"/>
-      <c r="L136" s="266"/>
-      <c r="M136" s="266"/>
-      <c r="N136" s="266"/>
-    </row>
-    <row r="137" spans="1:16" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:16" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C135" s="272"/>
+      <c r="D135" s="272"/>
+      <c r="E135" s="272"/>
+      <c r="F135" s="272"/>
+      <c r="G135" s="272"/>
+      <c r="H135" s="272"/>
+      <c r="I135" s="272"/>
+      <c r="J135" s="272"/>
+      <c r="K135" s="272"/>
+      <c r="L135" s="272"/>
+      <c r="M135" s="272"/>
+      <c r="N135" s="272"/>
+    </row>
+    <row r="136" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="C136" s="272"/>
+      <c r="D136" s="272"/>
+      <c r="E136" s="272"/>
+      <c r="F136" s="272"/>
+      <c r="G136" s="272"/>
+      <c r="H136" s="272"/>
+      <c r="I136" s="272"/>
+      <c r="J136" s="272"/>
+      <c r="K136" s="272"/>
+      <c r="L136" s="272"/>
+      <c r="M136" s="272"/>
+      <c r="N136" s="272"/>
+    </row>
+    <row r="137" spans="1:16" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C137" s="77"/>
       <c r="D137" s="77"/>
       <c r="E137" s="77"/>
@@ -12475,121 +12473,121 @@
       <c r="M137" s="77"/>
       <c r="N137" s="77"/>
     </row>
-    <row r="138" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C138" s="254" t="s">
+    <row r="138" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C138" s="256" t="s">
         <v>260</v>
       </c>
-      <c r="D138" s="254"/>
-      <c r="E138" s="254"/>
-      <c r="F138" s="254"/>
-      <c r="G138" s="254"/>
-      <c r="H138" s="254"/>
-      <c r="I138" s="254"/>
-      <c r="J138" s="254"/>
-      <c r="K138" s="254"/>
-      <c r="L138" s="254"/>
-      <c r="M138" s="254"/>
-      <c r="N138" s="254"/>
-    </row>
-    <row r="139" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C139" s="254"/>
-      <c r="D139" s="254"/>
-      <c r="E139" s="254"/>
-      <c r="F139" s="254"/>
-      <c r="G139" s="254"/>
-      <c r="H139" s="254"/>
-      <c r="I139" s="254"/>
-      <c r="J139" s="254"/>
-      <c r="K139" s="254"/>
-      <c r="L139" s="254"/>
-      <c r="M139" s="254"/>
-      <c r="N139" s="254"/>
-    </row>
-    <row r="140" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C140" s="254"/>
-      <c r="D140" s="254"/>
-      <c r="E140" s="254"/>
-      <c r="F140" s="254"/>
-      <c r="G140" s="254"/>
-      <c r="H140" s="254"/>
-      <c r="I140" s="254"/>
-      <c r="J140" s="254"/>
-      <c r="K140" s="254"/>
-      <c r="L140" s="254"/>
-      <c r="M140" s="254"/>
-      <c r="N140" s="254"/>
-    </row>
-    <row r="141" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C141" s="254"/>
-      <c r="D141" s="254"/>
-      <c r="E141" s="254"/>
-      <c r="F141" s="254"/>
-      <c r="G141" s="254"/>
-      <c r="H141" s="254"/>
-      <c r="I141" s="254"/>
-      <c r="J141" s="254"/>
-      <c r="K141" s="254"/>
-      <c r="L141" s="254"/>
-      <c r="M141" s="254"/>
-      <c r="N141" s="254"/>
-    </row>
-    <row r="142" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C142" s="254"/>
-      <c r="D142" s="254"/>
-      <c r="E142" s="254"/>
-      <c r="F142" s="254"/>
-      <c r="G142" s="254"/>
-      <c r="H142" s="254"/>
-      <c r="I142" s="254"/>
-      <c r="J142" s="254"/>
-      <c r="K142" s="254"/>
-      <c r="L142" s="254"/>
-      <c r="M142" s="254"/>
-      <c r="N142" s="254"/>
-    </row>
-    <row r="143" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C143" s="254"/>
-      <c r="D143" s="254"/>
-      <c r="E143" s="254"/>
-      <c r="F143" s="254"/>
-      <c r="G143" s="254"/>
-      <c r="H143" s="254"/>
-      <c r="I143" s="254"/>
-      <c r="J143" s="254"/>
-      <c r="K143" s="254"/>
-      <c r="L143" s="254"/>
-      <c r="M143" s="254"/>
-      <c r="N143" s="254"/>
-    </row>
-    <row r="144" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C144" s="254"/>
-      <c r="D144" s="254"/>
-      <c r="E144" s="254"/>
-      <c r="F144" s="254"/>
-      <c r="G144" s="254"/>
-      <c r="H144" s="254"/>
-      <c r="I144" s="254"/>
-      <c r="J144" s="254"/>
-      <c r="K144" s="254"/>
-      <c r="L144" s="254"/>
-      <c r="M144" s="254"/>
-      <c r="N144" s="254"/>
-    </row>
-    <row r="145" spans="3:16" x14ac:dyDescent="0.25">
-      <c r="C145" s="254"/>
-      <c r="D145" s="254"/>
-      <c r="E145" s="254"/>
-      <c r="F145" s="254"/>
-      <c r="G145" s="254"/>
-      <c r="H145" s="254"/>
-      <c r="I145" s="254"/>
-      <c r="J145" s="254"/>
-      <c r="K145" s="254"/>
-      <c r="L145" s="254"/>
-      <c r="M145" s="254"/>
-      <c r="N145" s="254"/>
-    </row>
-    <row r="146" spans="3:16" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D138" s="256"/>
+      <c r="E138" s="256"/>
+      <c r="F138" s="256"/>
+      <c r="G138" s="256"/>
+      <c r="H138" s="256"/>
+      <c r="I138" s="256"/>
+      <c r="J138" s="256"/>
+      <c r="K138" s="256"/>
+      <c r="L138" s="256"/>
+      <c r="M138" s="256"/>
+      <c r="N138" s="256"/>
+    </row>
+    <row r="139" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C139" s="256"/>
+      <c r="D139" s="256"/>
+      <c r="E139" s="256"/>
+      <c r="F139" s="256"/>
+      <c r="G139" s="256"/>
+      <c r="H139" s="256"/>
+      <c r="I139" s="256"/>
+      <c r="J139" s="256"/>
+      <c r="K139" s="256"/>
+      <c r="L139" s="256"/>
+      <c r="M139" s="256"/>
+      <c r="N139" s="256"/>
+    </row>
+    <row r="140" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C140" s="256"/>
+      <c r="D140" s="256"/>
+      <c r="E140" s="256"/>
+      <c r="F140" s="256"/>
+      <c r="G140" s="256"/>
+      <c r="H140" s="256"/>
+      <c r="I140" s="256"/>
+      <c r="J140" s="256"/>
+      <c r="K140" s="256"/>
+      <c r="L140" s="256"/>
+      <c r="M140" s="256"/>
+      <c r="N140" s="256"/>
+    </row>
+    <row r="141" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C141" s="256"/>
+      <c r="D141" s="256"/>
+      <c r="E141" s="256"/>
+      <c r="F141" s="256"/>
+      <c r="G141" s="256"/>
+      <c r="H141" s="256"/>
+      <c r="I141" s="256"/>
+      <c r="J141" s="256"/>
+      <c r="K141" s="256"/>
+      <c r="L141" s="256"/>
+      <c r="M141" s="256"/>
+      <c r="N141" s="256"/>
+    </row>
+    <row r="142" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C142" s="256"/>
+      <c r="D142" s="256"/>
+      <c r="E142" s="256"/>
+      <c r="F142" s="256"/>
+      <c r="G142" s="256"/>
+      <c r="H142" s="256"/>
+      <c r="I142" s="256"/>
+      <c r="J142" s="256"/>
+      <c r="K142" s="256"/>
+      <c r="L142" s="256"/>
+      <c r="M142" s="256"/>
+      <c r="N142" s="256"/>
+    </row>
+    <row r="143" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C143" s="256"/>
+      <c r="D143" s="256"/>
+      <c r="E143" s="256"/>
+      <c r="F143" s="256"/>
+      <c r="G143" s="256"/>
+      <c r="H143" s="256"/>
+      <c r="I143" s="256"/>
+      <c r="J143" s="256"/>
+      <c r="K143" s="256"/>
+      <c r="L143" s="256"/>
+      <c r="M143" s="256"/>
+      <c r="N143" s="256"/>
+    </row>
+    <row r="144" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C144" s="256"/>
+      <c r="D144" s="256"/>
+      <c r="E144" s="256"/>
+      <c r="F144" s="256"/>
+      <c r="G144" s="256"/>
+      <c r="H144" s="256"/>
+      <c r="I144" s="256"/>
+      <c r="J144" s="256"/>
+      <c r="K144" s="256"/>
+      <c r="L144" s="256"/>
+      <c r="M144" s="256"/>
+      <c r="N144" s="256"/>
+    </row>
+    <row r="145" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="C145" s="256"/>
+      <c r="D145" s="256"/>
+      <c r="E145" s="256"/>
+      <c r="F145" s="256"/>
+      <c r="G145" s="256"/>
+      <c r="H145" s="256"/>
+      <c r="I145" s="256"/>
+      <c r="J145" s="256"/>
+      <c r="K145" s="256"/>
+      <c r="L145" s="256"/>
+      <c r="M145" s="256"/>
+      <c r="N145" s="256"/>
+    </row>
+    <row r="146" spans="3:16" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C146" s="77"/>
       <c r="D146" s="77"/>
       <c r="E146" s="77"/>
@@ -12603,7 +12601,7 @@
       <c r="M146" s="77"/>
       <c r="N146" s="77"/>
     </row>
-    <row r="147" spans="3:16" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="3:16" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C147" s="77"/>
       <c r="D147" s="77"/>
       <c r="E147" s="77"/>
@@ -12617,118 +12615,112 @@
       <c r="M147" s="77"/>
       <c r="N147" s="77"/>
     </row>
-    <row r="148" spans="3:16" x14ac:dyDescent="0.25">
-      <c r="C148" s="265" t="s">
+    <row r="148" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="C148" s="271" t="s">
         <v>259</v>
       </c>
-      <c r="D148" s="265"/>
-      <c r="E148" s="265"/>
-      <c r="F148" s="265"/>
-      <c r="G148" s="265"/>
-      <c r="H148" s="265"/>
-      <c r="I148" s="265"/>
-      <c r="J148" s="265"/>
-      <c r="K148" s="265"/>
-      <c r="L148" s="265"/>
-      <c r="M148" s="265"/>
-      <c r="N148" s="265"/>
-    </row>
-    <row r="149" spans="3:16" x14ac:dyDescent="0.25">
-      <c r="C149" s="265"/>
-      <c r="D149" s="265"/>
-      <c r="E149" s="265"/>
-      <c r="F149" s="265"/>
-      <c r="G149" s="265"/>
-      <c r="H149" s="265"/>
-      <c r="I149" s="265"/>
-      <c r="J149" s="265"/>
-      <c r="K149" s="265"/>
-      <c r="L149" s="265"/>
-      <c r="M149" s="265"/>
-      <c r="N149" s="265"/>
-    </row>
-    <row r="150" spans="3:16" x14ac:dyDescent="0.25">
-      <c r="C150" s="265"/>
-      <c r="D150" s="265"/>
-      <c r="E150" s="265"/>
-      <c r="F150" s="265"/>
-      <c r="G150" s="265"/>
-      <c r="H150" s="265"/>
-      <c r="I150" s="265"/>
-      <c r="J150" s="265"/>
-      <c r="K150" s="265"/>
-      <c r="L150" s="265"/>
-      <c r="M150" s="265"/>
-      <c r="N150" s="265"/>
+      <c r="D148" s="271"/>
+      <c r="E148" s="271"/>
+      <c r="F148" s="271"/>
+      <c r="G148" s="271"/>
+      <c r="H148" s="271"/>
+      <c r="I148" s="271"/>
+      <c r="J148" s="271"/>
+      <c r="K148" s="271"/>
+      <c r="L148" s="271"/>
+      <c r="M148" s="271"/>
+      <c r="N148" s="271"/>
+    </row>
+    <row r="149" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="C149" s="271"/>
+      <c r="D149" s="271"/>
+      <c r="E149" s="271"/>
+      <c r="F149" s="271"/>
+      <c r="G149" s="271"/>
+      <c r="H149" s="271"/>
+      <c r="I149" s="271"/>
+      <c r="J149" s="271"/>
+      <c r="K149" s="271"/>
+      <c r="L149" s="271"/>
+      <c r="M149" s="271"/>
+      <c r="N149" s="271"/>
+    </row>
+    <row r="150" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="C150" s="271"/>
+      <c r="D150" s="271"/>
+      <c r="E150" s="271"/>
+      <c r="F150" s="271"/>
+      <c r="G150" s="271"/>
+      <c r="H150" s="271"/>
+      <c r="I150" s="271"/>
+      <c r="J150" s="271"/>
+      <c r="K150" s="271"/>
+      <c r="L150" s="271"/>
+      <c r="M150" s="271"/>
+      <c r="N150" s="271"/>
       <c r="P150" s="84">
         <f>L1-K133</f>
         <v>-3118989.9373000227</v>
       </c>
     </row>
-    <row r="151" spans="3:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C151" s="265"/>
-      <c r="D151" s="265"/>
-      <c r="E151" s="265"/>
-      <c r="F151" s="265"/>
-      <c r="G151" s="265"/>
-      <c r="H151" s="265"/>
-      <c r="I151" s="265"/>
-      <c r="J151" s="265"/>
-      <c r="K151" s="265"/>
-      <c r="L151" s="265"/>
-      <c r="M151" s="265"/>
-      <c r="N151" s="265"/>
-    </row>
-    <row r="152" spans="3:16" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C152" s="265"/>
-      <c r="D152" s="265"/>
-      <c r="E152" s="265"/>
-      <c r="F152" s="265"/>
-      <c r="G152" s="265"/>
-      <c r="H152" s="265"/>
-      <c r="I152" s="265"/>
-      <c r="J152" s="265"/>
-      <c r="K152" s="265"/>
-      <c r="L152" s="265"/>
-      <c r="M152" s="265"/>
-      <c r="N152" s="265"/>
-    </row>
-    <row r="153" spans="3:16" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C153" s="265"/>
-      <c r="D153" s="265"/>
-      <c r="E153" s="265"/>
-      <c r="F153" s="265"/>
-      <c r="G153" s="265"/>
-      <c r="H153" s="265"/>
-      <c r="I153" s="265"/>
-      <c r="J153" s="265"/>
-      <c r="K153" s="265"/>
-      <c r="L153" s="265"/>
-      <c r="M153" s="265"/>
-      <c r="N153" s="265"/>
-    </row>
-    <row r="154" spans="3:16" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C154" s="265"/>
-      <c r="D154" s="265"/>
-      <c r="E154" s="265"/>
-      <c r="F154" s="265"/>
-      <c r="G154" s="265"/>
-      <c r="H154" s="265"/>
-      <c r="I154" s="265"/>
-      <c r="J154" s="265"/>
-      <c r="K154" s="265"/>
-      <c r="L154" s="265"/>
-      <c r="M154" s="265"/>
-      <c r="N154" s="265"/>
+    <row r="151" spans="3:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C151" s="271"/>
+      <c r="D151" s="271"/>
+      <c r="E151" s="271"/>
+      <c r="F151" s="271"/>
+      <c r="G151" s="271"/>
+      <c r="H151" s="271"/>
+      <c r="I151" s="271"/>
+      <c r="J151" s="271"/>
+      <c r="K151" s="271"/>
+      <c r="L151" s="271"/>
+      <c r="M151" s="271"/>
+      <c r="N151" s="271"/>
+    </row>
+    <row r="152" spans="3:16" ht="5.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C152" s="271"/>
+      <c r="D152" s="271"/>
+      <c r="E152" s="271"/>
+      <c r="F152" s="271"/>
+      <c r="G152" s="271"/>
+      <c r="H152" s="271"/>
+      <c r="I152" s="271"/>
+      <c r="J152" s="271"/>
+      <c r="K152" s="271"/>
+      <c r="L152" s="271"/>
+      <c r="M152" s="271"/>
+      <c r="N152" s="271"/>
+    </row>
+    <row r="153" spans="3:16" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C153" s="271"/>
+      <c r="D153" s="271"/>
+      <c r="E153" s="271"/>
+      <c r="F153" s="271"/>
+      <c r="G153" s="271"/>
+      <c r="H153" s="271"/>
+      <c r="I153" s="271"/>
+      <c r="J153" s="271"/>
+      <c r="K153" s="271"/>
+      <c r="L153" s="271"/>
+      <c r="M153" s="271"/>
+      <c r="N153" s="271"/>
+    </row>
+    <row r="154" spans="3:16" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C154" s="271"/>
+      <c r="D154" s="271"/>
+      <c r="E154" s="271"/>
+      <c r="F154" s="271"/>
+      <c r="G154" s="271"/>
+      <c r="H154" s="271"/>
+      <c r="I154" s="271"/>
+      <c r="J154" s="271"/>
+      <c r="K154" s="271"/>
+      <c r="L154" s="271"/>
+      <c r="M154" s="271"/>
+      <c r="N154" s="271"/>
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="A11:A13"/>
-    <mergeCell ref="B11:B13"/>
-    <mergeCell ref="C11:C13"/>
-    <mergeCell ref="D11:D13"/>
-    <mergeCell ref="F11:F13"/>
-    <mergeCell ref="E11:E13"/>
     <mergeCell ref="Q14:R15"/>
     <mergeCell ref="G11:G13"/>
     <mergeCell ref="C148:N154"/>
@@ -12745,6 +12737,12 @@
     <mergeCell ref="C5:N8"/>
     <mergeCell ref="C9:N10"/>
     <mergeCell ref="A1:E4"/>
+    <mergeCell ref="A11:A13"/>
+    <mergeCell ref="B11:B13"/>
+    <mergeCell ref="C11:C13"/>
+    <mergeCell ref="D11:D13"/>
+    <mergeCell ref="F11:F13"/>
+    <mergeCell ref="E11:E13"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12755,118 +12753,118 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7AB47CA-548A-40FB-AC1D-01E96423736C}">
   <dimension ref="A1:DF81"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.140625" customWidth="1"/>
-    <col min="2" max="2" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="47.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.28515625" customWidth="1"/>
-    <col min="5" max="5" width="14.140625" customWidth="1"/>
-    <col min="6" max="6" width="13.42578125" customWidth="1"/>
-    <col min="7" max="7" width="15.140625" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="7.109375" customWidth="1"/>
+    <col min="2" max="2" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="47.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.33203125" customWidth="1"/>
+    <col min="5" max="5" width="14.109375" customWidth="1"/>
+    <col min="6" max="6" width="13.44140625" customWidth="1"/>
+    <col min="7" max="7" width="15.109375" hidden="1" customWidth="1"/>
     <col min="8" max="8" width="15" customWidth="1"/>
-    <col min="9" max="9" width="15.140625" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="15.140625" customWidth="1"/>
-    <col min="11" max="11" width="19.5703125" customWidth="1"/>
-    <col min="12" max="12" width="5.5703125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="43.28515625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.109375" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="15.109375" customWidth="1"/>
+    <col min="11" max="11" width="19.5546875" customWidth="1"/>
+    <col min="12" max="12" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="43.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="17.88671875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="303" t="s">
+    <row r="1" spans="1:15" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="308" t="s">
+        <v>366</v>
+      </c>
+      <c r="B1" s="308"/>
+      <c r="C1" s="308"/>
+      <c r="D1" s="308"/>
+      <c r="E1" s="308"/>
+      <c r="F1" s="308"/>
+      <c r="G1" s="308"/>
+      <c r="H1" s="308"/>
+      <c r="I1" s="308"/>
+      <c r="J1" s="308"/>
+      <c r="K1" s="309"/>
+      <c r="N1" s="43"/>
+    </row>
+    <row r="2" spans="1:15" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="310"/>
+      <c r="B2" s="310"/>
+      <c r="C2" s="310"/>
+      <c r="D2" s="310"/>
+      <c r="E2" s="310"/>
+      <c r="F2" s="310"/>
+      <c r="G2" s="310"/>
+      <c r="H2" s="310"/>
+      <c r="I2" s="310"/>
+      <c r="J2" s="310"/>
+      <c r="K2" s="311"/>
+      <c r="N2" s="43"/>
+    </row>
+    <row r="3" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="264" t="s">
         <v>367</v>
       </c>
-      <c r="B1" s="303"/>
-      <c r="C1" s="303"/>
-      <c r="D1" s="303"/>
-      <c r="E1" s="303"/>
-      <c r="F1" s="303"/>
-      <c r="G1" s="303"/>
-      <c r="H1" s="303"/>
-      <c r="I1" s="303"/>
-      <c r="J1" s="303"/>
-      <c r="K1" s="304"/>
-      <c r="N1" s="43"/>
-    </row>
-    <row r="2" spans="1:15" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="305"/>
-      <c r="B2" s="305"/>
-      <c r="C2" s="305"/>
-      <c r="D2" s="305"/>
-      <c r="E2" s="305"/>
-      <c r="F2" s="305"/>
-      <c r="G2" s="305"/>
-      <c r="H2" s="305"/>
-      <c r="I2" s="305"/>
-      <c r="J2" s="305"/>
-      <c r="K2" s="306"/>
-      <c r="N2" s="43"/>
-    </row>
-    <row r="3" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="263" t="s">
+      <c r="B3" s="264" t="s">
         <v>368</v>
       </c>
-      <c r="B3" s="263" t="s">
-        <v>369</v>
-      </c>
-      <c r="C3" s="263" t="s">
+      <c r="C3" s="264" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="263" t="s">
+      <c r="D3" s="264" t="s">
         <v>27</v>
       </c>
-      <c r="E3" s="271" t="s">
+      <c r="E3" s="277" t="s">
+        <v>395</v>
+      </c>
+      <c r="F3" s="277" t="s">
         <v>396</v>
       </c>
-      <c r="F3" s="271" t="s">
+      <c r="G3" s="277" t="s">
+        <v>279</v>
+      </c>
+      <c r="H3" s="305" t="s">
         <v>397</v>
       </c>
-      <c r="G3" s="271" t="s">
-        <v>280</v>
-      </c>
-      <c r="H3" s="311" t="s">
+      <c r="I3" s="226"/>
+      <c r="J3" s="277" t="s">
         <v>398</v>
       </c>
-      <c r="I3" s="226"/>
-      <c r="J3" s="271" t="s">
-        <v>399</v>
-      </c>
-      <c r="K3" s="271" t="s">
+      <c r="K3" s="277" t="s">
         <v>17</v>
       </c>
       <c r="N3" s="43"/>
     </row>
-    <row r="4" spans="1:15" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="264"/>
-      <c r="B4" s="264"/>
-      <c r="C4" s="264"/>
-      <c r="D4" s="264"/>
-      <c r="E4" s="272"/>
-      <c r="F4" s="272"/>
-      <c r="G4" s="272"/>
-      <c r="H4" s="312"/>
+    <row r="4" spans="1:15" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="265"/>
+      <c r="B4" s="265"/>
+      <c r="C4" s="265"/>
+      <c r="D4" s="265"/>
+      <c r="E4" s="278"/>
+      <c r="F4" s="278"/>
+      <c r="G4" s="278"/>
+      <c r="H4" s="306"/>
       <c r="I4" s="131"/>
-      <c r="J4" s="272"/>
-      <c r="K4" s="272"/>
+      <c r="J4" s="278"/>
+      <c r="K4" s="278"/>
       <c r="N4" s="43"/>
     </row>
-    <row r="5" spans="1:15" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="301"/>
-      <c r="B5" s="301"/>
-      <c r="C5" s="301"/>
-      <c r="D5" s="301"/>
-      <c r="E5" s="302"/>
-      <c r="F5" s="302"/>
-      <c r="G5" s="302"/>
-      <c r="H5" s="313"/>
+    <row r="5" spans="1:15" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="304"/>
+      <c r="B5" s="304"/>
+      <c r="C5" s="304"/>
+      <c r="D5" s="304"/>
+      <c r="E5" s="303"/>
+      <c r="F5" s="303"/>
+      <c r="G5" s="303"/>
+      <c r="H5" s="307"/>
       <c r="I5" s="227"/>
-      <c r="J5" s="302"/>
-      <c r="K5" s="302"/>
+      <c r="J5" s="303"/>
+      <c r="K5" s="303"/>
       <c r="N5" s="43"/>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" s="228" t="s">
         <v>113</v>
       </c>
@@ -12886,7 +12884,7 @@
       <c r="G6" s="243">
         <v>-197064.48265741928</v>
       </c>
-      <c r="H6" s="309">
+      <c r="H6" s="244">
         <f>ROUND((-G6),0)+L6</f>
         <v>197064.7</v>
       </c>
@@ -12897,23 +12895,23 @@
         <f>-I6</f>
         <v>85849.897062580741</v>
       </c>
-      <c r="K6" s="307">
+      <c r="K6" s="189">
         <f>ROUND((H6+J6),0) + L6</f>
         <v>282915.7</v>
       </c>
       <c r="L6" s="115">
         <v>0.7</v>
       </c>
-      <c r="N6" s="262"/>
-      <c r="O6" s="262"/>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="N6" s="270"/>
+      <c r="O6" s="270"/>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" s="228" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B7" s="229"/>
       <c r="C7" s="35" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="D7" s="143">
         <v>1.2800000000000001E-2</v>
@@ -12927,7 +12925,7 @@
       <c r="G7" s="146">
         <v>-34751.379392876712</v>
       </c>
-      <c r="H7" s="309">
+      <c r="H7" s="244">
         <f t="shared" ref="H7:H70" si="0">ROUND((-G7),0)+L7</f>
         <v>34751.71</v>
       </c>
@@ -12938,7 +12936,7 @@
         <f t="shared" ref="J7:J10" si="1">-I7</f>
         <v>300554.55212712329</v>
       </c>
-      <c r="K7" s="307">
+      <c r="K7" s="189">
         <f t="shared" ref="K7:K10" si="2">ROUND((H7+J7),0) + L7</f>
         <v>335306.71000000002</v>
       </c>
@@ -12946,16 +12944,16 @@
         <f>L6+0.01</f>
         <v>0.71</v>
       </c>
-      <c r="N7" s="262"/>
-      <c r="O7" s="262"/>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="N7" s="270"/>
+      <c r="O7" s="270"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" s="228" t="s">
         <v>114</v>
       </c>
       <c r="B8" s="229"/>
       <c r="C8" s="231" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="D8" s="143">
         <v>1.21E-2</v>
@@ -12969,7 +12967,7 @@
       <c r="G8" s="146">
         <v>-220785.20742173825</v>
       </c>
-      <c r="H8" s="309">
+      <c r="H8" s="244">
         <f t="shared" si="0"/>
         <v>220785.72</v>
       </c>
@@ -12980,7 +12978,7 @@
         <f t="shared" si="1"/>
         <v>96183.680968261731</v>
       </c>
-      <c r="K8" s="307">
+      <c r="K8" s="189">
         <f t="shared" si="2"/>
         <v>316969.71999999997</v>
       </c>
@@ -12990,7 +12988,7 @@
       </c>
       <c r="O8" s="43"/>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" s="228" t="s">
         <v>115</v>
       </c>
@@ -13010,7 +13008,7 @@
       <c r="G9" s="146">
         <v>-271875.99922180991</v>
       </c>
-      <c r="H9" s="309">
+      <c r="H9" s="244">
         <f t="shared" si="0"/>
         <v>271876.73</v>
       </c>
@@ -13021,7 +13019,7 @@
         <f t="shared" si="1"/>
         <v>118441.06168819009</v>
       </c>
-      <c r="K9" s="307">
+      <c r="K9" s="189">
         <f t="shared" si="2"/>
         <v>390318.73</v>
       </c>
@@ -13031,13 +13029,13 @@
       </c>
       <c r="O9" s="43"/>
     </row>
-    <row r="10" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="232" t="s">
         <v>116</v>
       </c>
       <c r="B10" s="233"/>
       <c r="C10" s="234" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="D10" s="150">
         <v>1.7500000000000002E-2</v>
@@ -13051,7 +13049,7 @@
       <c r="G10" s="154">
         <v>-319317.44875044789</v>
       </c>
-      <c r="H10" s="310">
+      <c r="H10" s="245">
         <f t="shared" si="0"/>
         <v>319317.74</v>
       </c>
@@ -13062,7 +13060,7 @@
         <f t="shared" si="1"/>
         <v>139108.62949955213</v>
       </c>
-      <c r="K10" s="308">
+      <c r="K10" s="155">
         <f t="shared" si="2"/>
         <v>458426.74</v>
       </c>
@@ -13072,7 +13070,7 @@
       </c>
       <c r="O10" s="43"/>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" s="235" t="s">
         <v>44</v>
       </c>
@@ -13094,7 +13092,7 @@
       <c r="G11" s="189">
         <v>-519626.96981144731</v>
       </c>
-      <c r="H11" s="309">
+      <c r="H11" s="244">
         <f t="shared" si="0"/>
         <v>519627.01</v>
       </c>
@@ -13105,7 +13103,7 @@
         <f>-I11</f>
         <v>35723.479268552619</v>
       </c>
-      <c r="K11" s="307">
+      <c r="K11" s="189">
         <f>ROUND((H11+J11),0) + L11</f>
         <v>555350.01</v>
       </c>
@@ -13114,7 +13112,7 @@
       </c>
       <c r="O11" s="43"/>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" s="228" t="s">
         <v>45</v>
       </c>
@@ -13134,7 +13132,7 @@
       <c r="G12" s="147">
         <v>-206492.25424856588</v>
       </c>
-      <c r="H12" s="309">
+      <c r="H12" s="244">
         <f t="shared" si="0"/>
         <v>206492.02</v>
       </c>
@@ -13145,7 +13143,7 @@
         <f t="shared" ref="J12:J75" si="4">-I12</f>
         <v>13552.263311434101</v>
       </c>
-      <c r="K12" s="307">
+      <c r="K12" s="189">
         <f t="shared" ref="K12:K75" si="5">ROUND((H12+J12),0) + L12</f>
         <v>220044.02</v>
       </c>
@@ -13155,7 +13153,7 @@
       </c>
       <c r="O12" s="43"/>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" s="228" t="s">
         <v>46</v>
       </c>
@@ -13177,7 +13175,7 @@
       <c r="G13" s="147">
         <v>-557137.66415134736</v>
       </c>
-      <c r="H13" s="309">
+      <c r="H13" s="244">
         <f t="shared" si="0"/>
         <v>557138.03</v>
       </c>
@@ -13188,7 +13186,7 @@
         <f t="shared" si="4"/>
         <v>32267.293598652584</v>
       </c>
-      <c r="K13" s="307">
+      <c r="K13" s="189">
         <f t="shared" si="5"/>
         <v>589405.03</v>
       </c>
@@ -13197,12 +13195,12 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" s="228" t="s">
         <v>47</v>
       </c>
       <c r="B14" s="229" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C14" s="108" t="s">
         <v>180</v>
@@ -13219,7 +13217,7 @@
       <c r="G14" s="147">
         <v>-327282.74303127197</v>
       </c>
-      <c r="H14" s="309">
+      <c r="H14" s="244">
         <f t="shared" si="0"/>
         <v>327283.03999999998</v>
       </c>
@@ -13230,7 +13228,7 @@
         <f t="shared" si="4"/>
         <v>39458.119568728027</v>
       </c>
-      <c r="K14" s="307">
+      <c r="K14" s="189">
         <f t="shared" si="5"/>
         <v>366741.04</v>
       </c>
@@ -13239,7 +13237,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" s="228" t="s">
         <v>48</v>
       </c>
@@ -13259,7 +13257,7 @@
       <c r="G15" s="147">
         <v>-206069.04832824506</v>
       </c>
-      <c r="H15" s="309">
+      <c r="H15" s="244">
         <f t="shared" si="0"/>
         <v>206069.05</v>
       </c>
@@ -13270,7 +13268,7 @@
         <f t="shared" si="4"/>
         <v>21834.202001754922</v>
       </c>
-      <c r="K15" s="307">
+      <c r="K15" s="189">
         <f t="shared" si="5"/>
         <v>227903.05</v>
       </c>
@@ -13279,12 +13277,12 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" s="228" t="s">
         <v>49</v>
       </c>
       <c r="B16" s="229" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C16" s="108" t="s">
         <v>182</v>
@@ -13301,7 +13299,7 @@
       <c r="G16" s="147">
         <v>-329620.47691006673</v>
       </c>
-      <c r="H16" s="309">
+      <c r="H16" s="244">
         <f t="shared" si="0"/>
         <v>329620.06</v>
       </c>
@@ -13312,7 +13310,7 @@
         <f t="shared" si="4"/>
         <v>39739.963279933261</v>
       </c>
-      <c r="K16" s="307">
+      <c r="K16" s="189">
         <f t="shared" si="5"/>
         <v>369360.06</v>
       </c>
@@ -13321,15 +13319,15 @@
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:110" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:110" x14ac:dyDescent="0.3">
       <c r="A17" s="228" t="s">
         <v>50</v>
       </c>
       <c r="B17" s="229" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C17" s="108" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="D17" s="136">
         <v>2.1100000000000001E-2</v>
@@ -13343,7 +13341,7 @@
       <c r="G17" s="147">
         <v>-493261.84842570277</v>
       </c>
-      <c r="H17" s="309">
+      <c r="H17" s="244">
         <f t="shared" si="0"/>
         <v>493262.07</v>
       </c>
@@ -13354,7 +13352,7 @@
         <f t="shared" si="4"/>
         <v>59469.023064297158</v>
       </c>
-      <c r="K17" s="307">
+      <c r="K17" s="189">
         <f t="shared" si="5"/>
         <v>552731.06999999995</v>
       </c>
@@ -13363,13 +13361,13 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:110" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:110" x14ac:dyDescent="0.3">
       <c r="A18" s="228" t="s">
         <v>51</v>
       </c>
       <c r="B18" s="229"/>
       <c r="C18" s="108" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="D18" s="136">
         <v>7.4000000000000003E-3</v>
@@ -13383,7 +13381,7 @@
       <c r="G18" s="147">
         <v>-147681.21170563609</v>
       </c>
-      <c r="H18" s="309">
+      <c r="H18" s="244">
         <f t="shared" si="0"/>
         <v>147681.07999999999</v>
       </c>
@@ -13394,7 +13392,7 @@
         <f t="shared" si="4"/>
         <v>46167.529954363912</v>
       </c>
-      <c r="K18" s="307">
+      <c r="K18" s="189">
         <f t="shared" si="5"/>
         <v>193849.08</v>
       </c>
@@ -13403,7 +13401,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="19" spans="1:110" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:110" x14ac:dyDescent="0.3">
       <c r="A19" s="228" t="s">
         <v>52</v>
       </c>
@@ -13423,7 +13421,7 @@
       <c r="G19" s="147">
         <v>-418454.36430426914</v>
       </c>
-      <c r="H19" s="309">
+      <c r="H19" s="244">
         <f t="shared" si="0"/>
         <v>418454.09</v>
       </c>
@@ -13434,7 +13432,7 @@
         <f t="shared" si="4"/>
         <v>50450.024305730825</v>
       </c>
-      <c r="K19" s="307">
+      <c r="K19" s="189">
         <f t="shared" si="5"/>
         <v>468904.09</v>
       </c>
@@ -13443,7 +13441,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="20" spans="1:110" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:110" x14ac:dyDescent="0.3">
       <c r="A20" s="228" t="s">
         <v>53</v>
       </c>
@@ -13463,7 +13461,7 @@
       <c r="G20" s="147">
         <v>-187595.05270715937</v>
       </c>
-      <c r="H20" s="309">
+      <c r="H20" s="244">
         <f t="shared" si="0"/>
         <v>187595.1</v>
       </c>
@@ -13474,7 +13472,7 @@
         <f t="shared" si="4"/>
         <v>58645.240752840618</v>
       </c>
-      <c r="K20" s="307">
+      <c r="K20" s="189">
         <f t="shared" si="5"/>
         <v>246240.1</v>
       </c>
@@ -13483,13 +13481,13 @@
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:110" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:110" x14ac:dyDescent="0.3">
       <c r="A21" s="228" t="s">
         <v>54</v>
       </c>
       <c r="B21" s="229"/>
       <c r="C21" s="108" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D21" s="136">
         <v>8.6999999999999994E-3</v>
@@ -13503,7 +13501,7 @@
       <c r="G21" s="147">
         <v>-173625.20835662619</v>
       </c>
-      <c r="H21" s="309">
+      <c r="H21" s="244">
         <f t="shared" si="0"/>
         <v>173625.11</v>
       </c>
@@ -13514,7 +13512,7 @@
         <f t="shared" si="4"/>
         <v>54278.041973373794</v>
       </c>
-      <c r="K21" s="307">
+      <c r="K21" s="189">
         <f t="shared" si="5"/>
         <v>227903.11</v>
       </c>
@@ -13523,7 +13521,7 @@
         <v>0.10999999999999999</v>
       </c>
     </row>
-    <row r="22" spans="1:110" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:110" x14ac:dyDescent="0.3">
       <c r="A22" s="228" t="s">
         <v>55</v>
       </c>
@@ -13543,7 +13541,7 @@
       <c r="G22" s="147">
         <v>-189590.74475723552</v>
       </c>
-      <c r="H22" s="309">
+      <c r="H22" s="244">
         <f t="shared" si="0"/>
         <v>189591.12</v>
       </c>
@@ -13554,7 +13552,7 @@
         <f t="shared" si="4"/>
         <v>59269.126292764471</v>
       </c>
-      <c r="K22" s="307">
+      <c r="K22" s="189">
         <f t="shared" si="5"/>
         <v>248860.12</v>
       </c>
@@ -13563,7 +13561,7 @@
         <v>0.11999999999999998</v>
       </c>
     </row>
-    <row r="23" spans="1:110" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:110" x14ac:dyDescent="0.3">
       <c r="A23" s="228" t="s">
         <v>56</v>
       </c>
@@ -13583,7 +13581,7 @@
       <c r="G23" s="147">
         <v>-403151.54400910489</v>
       </c>
-      <c r="H23" s="309">
+      <c r="H23" s="244">
         <f t="shared" si="0"/>
         <v>403152.13</v>
       </c>
@@ -13594,7 +13592,7 @@
         <f t="shared" si="4"/>
         <v>26459.180750895117</v>
       </c>
-      <c r="K23" s="307">
+      <c r="K23" s="189">
         <f t="shared" si="5"/>
         <v>429611.13</v>
       </c>
@@ -13603,13 +13601,13 @@
         <v>0.12999999999999998</v>
       </c>
     </row>
-    <row r="24" spans="1:110" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:110" x14ac:dyDescent="0.3">
       <c r="A24" s="228" t="s">
         <v>57</v>
       </c>
       <c r="B24" s="229"/>
       <c r="C24" s="108" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="D24" s="136">
         <v>7.3000000000000001E-3</v>
@@ -13623,7 +13621,7 @@
       <c r="G24" s="147">
         <v>-172908.51181565388</v>
       </c>
-      <c r="H24" s="309">
+      <c r="H24" s="244">
         <f t="shared" si="0"/>
         <v>172909.14</v>
       </c>
@@ -13634,7 +13632,7 @@
         <f t="shared" si="4"/>
         <v>18320.652254346118</v>
       </c>
-      <c r="K24" s="307">
+      <c r="K24" s="189">
         <f t="shared" si="5"/>
         <v>191230.14</v>
       </c>
@@ -13643,12 +13641,12 @@
         <v>0.13999999999999999</v>
       </c>
     </row>
-    <row r="25" spans="1:110" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:110" x14ac:dyDescent="0.3">
       <c r="A25" s="228" t="s">
         <v>58</v>
       </c>
       <c r="B25" s="237" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C25" s="108" t="s">
         <v>185</v>
@@ -13665,7 +13663,7 @@
       <c r="G25" s="147">
         <v>-540813.04684148217</v>
       </c>
-      <c r="H25" s="309">
+      <c r="H25" s="244">
         <f t="shared" si="0"/>
         <v>540813.15</v>
       </c>
@@ -13676,7 +13674,7 @@
         <f t="shared" si="4"/>
         <v>35494.022958517773</v>
       </c>
-      <c r="K25" s="307">
+      <c r="K25" s="189">
         <f t="shared" si="5"/>
         <v>576307.15</v>
       </c>
@@ -13685,7 +13683,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="26" spans="1:110" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:110" x14ac:dyDescent="0.3">
       <c r="A26" s="228" t="s">
         <v>59</v>
       </c>
@@ -13705,7 +13703,7 @@
       <c r="G26" s="147">
         <v>-187595.05270715937</v>
       </c>
-      <c r="H26" s="309">
+      <c r="H26" s="244">
         <f t="shared" si="0"/>
         <v>187595.16</v>
       </c>
@@ -13716,7 +13714,7 @@
         <f t="shared" si="4"/>
         <v>58645.240752840618</v>
       </c>
-      <c r="K26" s="307">
+      <c r="K26" s="189">
         <f t="shared" si="5"/>
         <v>246240.16</v>
       </c>
@@ -13725,16 +13723,16 @@
         <v>0.16</v>
       </c>
       <c r="M26" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="27" spans="1:110" x14ac:dyDescent="0.25">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="27" spans="1:110" x14ac:dyDescent="0.3">
       <c r="A27" s="228" t="s">
         <v>60</v>
       </c>
       <c r="B27" s="229"/>
       <c r="C27" s="108" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D27" s="136">
         <v>8.6999999999999994E-3</v>
@@ -13748,7 +13746,7 @@
       <c r="G27" s="147">
         <v>-173625.20835662619</v>
       </c>
-      <c r="H27" s="309">
+      <c r="H27" s="244">
         <f t="shared" si="0"/>
         <v>173625.17</v>
       </c>
@@ -13759,7 +13757,7 @@
         <f t="shared" si="4"/>
         <v>54278.041973373794</v>
       </c>
-      <c r="K27" s="307">
+      <c r="K27" s="189">
         <f t="shared" si="5"/>
         <v>227903.17</v>
       </c>
@@ -13768,7 +13766,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="28" spans="1:110" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:110" x14ac:dyDescent="0.3">
       <c r="A28" s="228" t="s">
         <v>61</v>
       </c>
@@ -13788,7 +13786,7 @@
       <c r="G28" s="147">
         <v>-189590.74475723552</v>
       </c>
-      <c r="H28" s="309">
+      <c r="H28" s="244">
         <f t="shared" si="0"/>
         <v>189591.18</v>
       </c>
@@ -13799,7 +13797,7 @@
         <f t="shared" si="4"/>
         <v>59269.126292764471</v>
       </c>
-      <c r="K28" s="307">
+      <c r="K28" s="189">
         <f t="shared" si="5"/>
         <v>248860.18</v>
       </c>
@@ -13808,7 +13806,7 @@
         <v>0.18000000000000002</v>
       </c>
     </row>
-    <row r="29" spans="1:110" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:110" x14ac:dyDescent="0.3">
       <c r="A29" s="228" t="s">
         <v>62</v>
       </c>
@@ -13828,7 +13826,7 @@
       <c r="G29" s="147">
         <v>-388451.99914749648</v>
       </c>
-      <c r="H29" s="309">
+      <c r="H29" s="244">
         <f t="shared" si="0"/>
         <v>388452.19</v>
       </c>
@@ -13839,7 +13837,7 @@
         <f t="shared" si="4"/>
         <v>41158.725612503535</v>
       </c>
-      <c r="K29" s="307">
+      <c r="K29" s="189">
         <f t="shared" si="5"/>
         <v>429611.19</v>
       </c>
@@ -13848,10 +13846,10 @@
         <v>0.19000000000000003</v>
       </c>
       <c r="M29" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="30" spans="1:110" x14ac:dyDescent="0.25">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="30" spans="1:110" x14ac:dyDescent="0.3">
       <c r="A30" s="228" t="s">
         <v>63</v>
       </c>
@@ -13873,7 +13871,7 @@
       <c r="G30" s="147">
         <v>-224422.45236430079</v>
       </c>
-      <c r="H30" s="309">
+      <c r="H30" s="244">
         <f t="shared" si="0"/>
         <v>224422.2</v>
       </c>
@@ -13884,7 +13882,7 @@
         <f t="shared" si="4"/>
         <v>27056.996275699232</v>
       </c>
-      <c r="K30" s="307">
+      <c r="K30" s="189">
         <f t="shared" si="5"/>
         <v>251479.2</v>
       </c>
@@ -13893,7 +13891,7 @@
         <v>0.20000000000000004</v>
       </c>
     </row>
-    <row r="31" spans="1:110" s="140" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:110" s="140" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A31" s="228" t="s">
         <v>64</v>
       </c>
@@ -13915,7 +13913,7 @@
       <c r="G31" s="147">
         <v>-460533.57412257558</v>
       </c>
-      <c r="H31" s="309">
+      <c r="H31" s="244">
         <f t="shared" si="0"/>
         <v>460534.21</v>
       </c>
@@ -13926,7 +13924,7 @@
         <f t="shared" si="4"/>
         <v>55523.211107424344</v>
       </c>
-      <c r="K31" s="307">
+      <c r="K31" s="189">
         <f t="shared" si="5"/>
         <v>516057.21</v>
       </c>
@@ -14033,7 +14031,7 @@
       <c r="DE31" s="73"/>
       <c r="DF31" s="73"/>
     </row>
-    <row r="32" spans="1:110" s="140" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:110" s="140" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A32" s="228" t="s">
         <v>65</v>
       </c>
@@ -14053,7 +14051,7 @@
       <c r="G32" s="147">
         <v>-187595.05270715937</v>
       </c>
-      <c r="H32" s="309">
+      <c r="H32" s="244">
         <f t="shared" si="0"/>
         <v>187595.22</v>
       </c>
@@ -14064,7 +14062,7 @@
         <f t="shared" si="4"/>
         <v>58645.240752840618</v>
       </c>
-      <c r="K32" s="307">
+      <c r="K32" s="189">
         <f t="shared" si="5"/>
         <v>246240.22</v>
       </c>
@@ -14073,7 +14071,7 @@
         <v>0.22000000000000006</v>
       </c>
       <c r="M32" s="73" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="N32" s="73"/>
       <c r="O32" s="73"/>
@@ -14173,7 +14171,7 @@
       <c r="DE32" s="73"/>
       <c r="DF32" s="73"/>
     </row>
-    <row r="33" spans="1:110" s="140" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:110" s="140" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A33" s="228" t="s">
         <v>66</v>
       </c>
@@ -14181,7 +14179,7 @@
         <v>31</v>
       </c>
       <c r="C33" s="108" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D33" s="136">
         <v>1.0999999999999999E-2</v>
@@ -14195,7 +14193,7 @@
       <c r="G33" s="147">
         <v>-219526.12550837794</v>
       </c>
-      <c r="H33" s="309">
+      <c r="H33" s="244">
         <f t="shared" si="0"/>
         <v>219526.23</v>
       </c>
@@ -14206,7 +14204,7 @@
         <f t="shared" si="4"/>
         <v>68627.40939162203</v>
       </c>
-      <c r="K33" s="307">
+      <c r="K33" s="189">
         <f t="shared" si="5"/>
         <v>288154.23</v>
       </c>
@@ -14215,7 +14213,7 @@
         <v>0.23000000000000007</v>
       </c>
       <c r="M33" s="73" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="N33" s="73"/>
       <c r="O33" s="73"/>
@@ -14315,7 +14313,7 @@
       <c r="DE33" s="73"/>
       <c r="DF33" s="73"/>
     </row>
-    <row r="34" spans="1:110" s="140" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:110" s="140" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A34" s="228" t="s">
         <v>67</v>
       </c>
@@ -14335,7 +14333,7 @@
       <c r="G34" s="147">
         <v>-189590.74475723552</v>
       </c>
-      <c r="H34" s="309">
+      <c r="H34" s="244">
         <f t="shared" si="0"/>
         <v>189591.24</v>
       </c>
@@ -14346,7 +14344,7 @@
         <f t="shared" si="4"/>
         <v>59269.126292764471</v>
       </c>
-      <c r="K34" s="307">
+      <c r="K34" s="189">
         <f t="shared" si="5"/>
         <v>248860.24</v>
       </c>
@@ -14453,7 +14451,7 @@
       <c r="DE34" s="73"/>
       <c r="DF34" s="73"/>
     </row>
-    <row r="35" spans="1:110" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:110" x14ac:dyDescent="0.3">
       <c r="A35" s="228" t="s">
         <v>68</v>
       </c>
@@ -14475,7 +14473,7 @@
       <c r="G35" s="147">
         <v>-452316.22060054552</v>
       </c>
-      <c r="H35" s="309">
+      <c r="H35" s="244">
         <f t="shared" si="0"/>
         <v>452316.25</v>
       </c>
@@ -14486,7 +14484,7 @@
         <f t="shared" si="4"/>
         <v>37544.788729454507</v>
       </c>
-      <c r="K35" s="307">
+      <c r="K35" s="189">
         <f t="shared" si="5"/>
         <v>489861.25</v>
       </c>
@@ -14495,13 +14493,13 @@
         <v>0.25000000000000006</v>
       </c>
     </row>
-    <row r="36" spans="1:110" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:110" x14ac:dyDescent="0.3">
       <c r="A36" s="228" t="s">
         <v>69</v>
       </c>
       <c r="B36" s="229"/>
       <c r="C36" s="108" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D36" s="136">
         <v>7.3000000000000001E-3</v>
@@ -14515,7 +14513,7 @@
       <c r="G36" s="147">
         <v>-175787.47145562258</v>
       </c>
-      <c r="H36" s="309">
+      <c r="H36" s="244">
         <f t="shared" si="0"/>
         <v>175787.26</v>
       </c>
@@ -14526,7 +14524,7 @@
         <f t="shared" si="4"/>
         <v>15441.692614377418</v>
       </c>
-      <c r="K36" s="307">
+      <c r="K36" s="189">
         <f t="shared" si="5"/>
         <v>191229.26</v>
       </c>
@@ -14535,7 +14533,7 @@
         <v>0.26000000000000006</v>
       </c>
     </row>
-    <row r="37" spans="1:110" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:110" x14ac:dyDescent="0.3">
       <c r="A37" s="228" t="s">
         <v>70</v>
       </c>
@@ -14557,7 +14555,7 @@
       <c r="G37" s="147">
         <v>-471560.18735745805</v>
       </c>
-      <c r="H37" s="309">
+      <c r="H37" s="244">
         <f t="shared" si="0"/>
         <v>471560.27</v>
       </c>
@@ -14568,7 +14566,7 @@
         <f t="shared" si="4"/>
         <v>44496.597872541868</v>
       </c>
-      <c r="K37" s="307">
+      <c r="K37" s="189">
         <f t="shared" si="5"/>
         <v>516057.27</v>
       </c>
@@ -14577,13 +14575,13 @@
         <v>0.27000000000000007</v>
       </c>
       <c r="M37" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="N37" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="38" spans="1:110" x14ac:dyDescent="0.25">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="38" spans="1:110" x14ac:dyDescent="0.3">
       <c r="A38" s="228" t="s">
         <v>71</v>
       </c>
@@ -14591,7 +14589,7 @@
         <v>44</v>
       </c>
       <c r="C38" s="108" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="D38" s="136">
         <v>1.17E-2</v>
@@ -14605,7 +14603,7 @@
       <c r="G38" s="147">
         <v>-277127.3408552261</v>
       </c>
-      <c r="H38" s="309">
+      <c r="H38" s="244">
         <f t="shared" si="0"/>
         <v>277127.28000000003</v>
       </c>
@@ -14616,7 +14614,7 @@
         <f t="shared" si="4"/>
         <v>29363.23717477388</v>
       </c>
-      <c r="K38" s="307">
+      <c r="K38" s="189">
         <f t="shared" si="5"/>
         <v>306491.28000000003</v>
       </c>
@@ -14625,7 +14623,7 @@
         <v>0.28000000000000008</v>
       </c>
     </row>
-    <row r="39" spans="1:110" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:110" x14ac:dyDescent="0.3">
       <c r="A39" s="228" t="s">
         <v>72</v>
       </c>
@@ -14645,7 +14643,7 @@
       <c r="G39" s="147">
         <v>-206069.04832824506</v>
       </c>
-      <c r="H39" s="309">
+      <c r="H39" s="244">
         <f t="shared" si="0"/>
         <v>206069.29</v>
       </c>
@@ -14656,7 +14654,7 @@
         <f t="shared" si="4"/>
         <v>21834.202001754922</v>
       </c>
-      <c r="K39" s="307">
+      <c r="K39" s="189">
         <f t="shared" si="5"/>
         <v>227903.29</v>
       </c>
@@ -14665,13 +14663,13 @@
         <v>0.29000000000000009</v>
       </c>
     </row>
-    <row r="40" spans="1:110" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:110" x14ac:dyDescent="0.3">
       <c r="A40" s="228" t="s">
         <v>73</v>
       </c>
       <c r="B40" s="229"/>
       <c r="C40" s="108" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="D40" s="136">
         <v>9.4999999999999998E-3</v>
@@ -14685,7 +14683,7 @@
       <c r="G40" s="147">
         <v>-225017.92633544002</v>
       </c>
-      <c r="H40" s="309">
+      <c r="H40" s="244">
         <f t="shared" si="0"/>
         <v>225018.3</v>
       </c>
@@ -14696,7 +14694,7 @@
         <f t="shared" si="4"/>
         <v>23841.94471455997</v>
       </c>
-      <c r="K40" s="307">
+      <c r="K40" s="189">
         <f t="shared" si="5"/>
         <v>248860.3</v>
       </c>
@@ -14705,7 +14703,7 @@
         <v>0.3000000000000001</v>
       </c>
     </row>
-    <row r="41" spans="1:110" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:110" x14ac:dyDescent="0.3">
       <c r="A41" s="228" t="s">
         <v>74</v>
       </c>
@@ -14727,7 +14725,7 @@
       <c r="G41" s="147">
         <v>-435275.0052766751</v>
       </c>
-      <c r="H41" s="309">
+      <c r="H41" s="244">
         <f t="shared" si="0"/>
         <v>435275.31</v>
       </c>
@@ -14738,7 +14736,7 @@
         <f t="shared" si="4"/>
         <v>54586.004053324927</v>
       </c>
-      <c r="K41" s="307">
+      <c r="K41" s="189">
         <f t="shared" si="5"/>
         <v>489861.31</v>
       </c>
@@ -14747,7 +14745,7 @@
         <v>0.31000000000000011</v>
       </c>
     </row>
-    <row r="42" spans="1:110" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:110" x14ac:dyDescent="0.3">
       <c r="A42" s="228" t="s">
         <v>75</v>
       </c>
@@ -14769,7 +14767,7 @@
       <c r="G42" s="147">
         <v>-235991.14771264675</v>
       </c>
-      <c r="H42" s="309">
+      <c r="H42" s="244">
         <f t="shared" si="0"/>
         <v>235991.32</v>
       </c>
@@ -14780,7 +14778,7 @@
         <f t="shared" si="4"/>
         <v>15488.300927353266</v>
       </c>
-      <c r="K42" s="307">
+      <c r="K42" s="189">
         <f t="shared" si="5"/>
         <v>251480.32000000001</v>
       </c>
@@ -14790,7 +14788,7 @@
       </c>
       <c r="M42" s="43"/>
     </row>
-    <row r="43" spans="1:110" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:110" x14ac:dyDescent="0.3">
       <c r="A43" s="228" t="s">
         <v>76</v>
       </c>
@@ -14812,7 +14810,7 @@
       <c r="G43" s="147">
         <v>-471560.18735745805</v>
       </c>
-      <c r="H43" s="309">
+      <c r="H43" s="244">
         <f t="shared" si="0"/>
         <v>471560.33</v>
       </c>
@@ -14823,7 +14821,7 @@
         <f t="shared" si="4"/>
         <v>44496.597872541868</v>
       </c>
-      <c r="K43" s="307">
+      <c r="K43" s="189">
         <f t="shared" si="5"/>
         <v>516057.33</v>
       </c>
@@ -14833,13 +14831,13 @@
       </c>
       <c r="M43" s="43"/>
     </row>
-    <row r="44" spans="1:110" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:110" x14ac:dyDescent="0.3">
       <c r="A44" s="228" t="s">
         <v>77</v>
       </c>
       <c r="B44" s="229"/>
       <c r="C44" s="108" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D44" s="136">
         <v>9.4000000000000004E-3</v>
@@ -14853,7 +14851,7 @@
       <c r="G44" s="147">
         <v>-227367.51195963251</v>
       </c>
-      <c r="H44" s="309">
+      <c r="H44" s="244">
         <f t="shared" si="0"/>
         <v>227368.34</v>
       </c>
@@ -14864,7 +14862,7 @@
         <f t="shared" si="4"/>
         <v>18872.781500367477</v>
       </c>
-      <c r="K44" s="307">
+      <c r="K44" s="189">
         <f t="shared" si="5"/>
         <v>246241.34</v>
       </c>
@@ -14873,16 +14871,16 @@
         <v>0.34000000000000014</v>
       </c>
       <c r="M44" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="45" spans="1:110" x14ac:dyDescent="0.25">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="45" spans="1:110" x14ac:dyDescent="0.3">
       <c r="A45" s="228" t="s">
         <v>78</v>
       </c>
       <c r="B45" s="229"/>
       <c r="C45" s="108" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="D45" s="136">
         <v>8.6999999999999994E-3</v>
@@ -14896,7 +14894,7 @@
       <c r="G45" s="147">
         <v>-201632.39809641102</v>
       </c>
-      <c r="H45" s="309">
+      <c r="H45" s="244">
         <f t="shared" si="0"/>
         <v>201632.35</v>
       </c>
@@ -14907,7 +14905,7 @@
         <f t="shared" si="4"/>
         <v>26270.852233588957</v>
       </c>
-      <c r="K45" s="307">
+      <c r="K45" s="189">
         <f t="shared" si="5"/>
         <v>227903.35</v>
       </c>
@@ -14916,7 +14914,7 @@
         <v>0.35000000000000014</v>
       </c>
     </row>
-    <row r="46" spans="1:110" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:110" x14ac:dyDescent="0.3">
       <c r="A46" s="228" t="s">
         <v>79</v>
       </c>
@@ -14936,7 +14934,7 @@
       <c r="G46" s="147">
         <v>-229786.31527835201</v>
       </c>
-      <c r="H46" s="309">
+      <c r="H46" s="244">
         <f t="shared" si="0"/>
         <v>229786.36</v>
       </c>
@@ -14947,7 +14945,7 @@
         <f t="shared" si="4"/>
         <v>19073.555771647982</v>
       </c>
-      <c r="K46" s="307">
+      <c r="K46" s="189">
         <f t="shared" si="5"/>
         <v>248860.36</v>
       </c>
@@ -14956,7 +14954,7 @@
         <v>0.36000000000000015</v>
       </c>
     </row>
-    <row r="47" spans="1:110" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:110" x14ac:dyDescent="0.3">
       <c r="A47" s="228" t="s">
         <v>80</v>
       </c>
@@ -14978,7 +14976,7 @@
       <c r="G47" s="147">
         <v>-447623.12200936372</v>
       </c>
-      <c r="H47" s="309">
+      <c r="H47" s="244">
         <f t="shared" si="0"/>
         <v>447623.37</v>
       </c>
@@ -14989,7 +14987,7 @@
         <f t="shared" si="4"/>
         <v>42237.887320636306</v>
       </c>
-      <c r="K47" s="307">
+      <c r="K47" s="189">
         <f t="shared" si="5"/>
         <v>489861.37</v>
       </c>
@@ -14999,7 +14997,7 @@
       </c>
       <c r="N47" s="59"/>
     </row>
-    <row r="48" spans="1:110" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:110" x14ac:dyDescent="0.3">
       <c r="A48" s="228" t="s">
         <v>81</v>
       </c>
@@ -15019,7 +15017,7 @@
       <c r="G48" s="147">
         <v>-170654.57315202037</v>
       </c>
-      <c r="H48" s="309">
+      <c r="H48" s="244">
         <f t="shared" si="0"/>
         <v>170655.38</v>
       </c>
@@ -15030,7 +15028,7 @@
         <f t="shared" si="4"/>
         <v>20574.590917979629</v>
       </c>
-      <c r="K48" s="307">
+      <c r="K48" s="189">
         <f t="shared" si="5"/>
         <v>191230.38</v>
       </c>
@@ -15039,7 +15037,7 @@
         <v>0.38000000000000017</v>
       </c>
     </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A49" s="228" t="s">
         <v>82</v>
       </c>
@@ -15061,7 +15059,7 @@
       <c r="G49" s="147">
         <v>-460533.57412257558</v>
       </c>
-      <c r="H49" s="309">
+      <c r="H49" s="244">
         <f t="shared" si="0"/>
         <v>460534.39</v>
       </c>
@@ -15072,7 +15070,7 @@
         <f t="shared" si="4"/>
         <v>55523.211107424344</v>
       </c>
-      <c r="K49" s="307">
+      <c r="K49" s="189">
         <f t="shared" si="5"/>
         <v>516058.39</v>
       </c>
@@ -15081,7 +15079,7 @@
         <v>0.39000000000000018</v>
       </c>
     </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A50" s="228" t="s">
         <v>83</v>
       </c>
@@ -15101,7 +15099,7 @@
       <c r="G50" s="147">
         <v>-225008.41427208658</v>
       </c>
-      <c r="H50" s="309">
+      <c r="H50" s="244">
         <f t="shared" si="0"/>
         <v>225008.4</v>
       </c>
@@ -15112,7 +15110,7 @@
         <f t="shared" si="4"/>
         <v>21231.879187913408</v>
       </c>
-      <c r="K50" s="307">
+      <c r="K50" s="189">
         <f t="shared" si="5"/>
         <v>246240.4</v>
       </c>
@@ -15121,13 +15119,13 @@
         <v>0.40000000000000019</v>
       </c>
     </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A51" s="228" t="s">
         <v>84</v>
       </c>
       <c r="B51" s="229"/>
       <c r="C51" s="108" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="D51" s="136">
         <v>8.6999999999999994E-3</v>
@@ -15141,7 +15139,7 @@
       <c r="G51" s="147">
         <v>-206069.04832824506</v>
       </c>
-      <c r="H51" s="309">
+      <c r="H51" s="244">
         <f t="shared" si="0"/>
         <v>206069.41</v>
       </c>
@@ -15152,7 +15150,7 @@
         <f t="shared" si="4"/>
         <v>21834.202001754922</v>
       </c>
-      <c r="K51" s="307">
+      <c r="K51" s="189">
         <f t="shared" si="5"/>
         <v>227904.41</v>
       </c>
@@ -15164,7 +15162,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A52" s="228" t="s">
         <v>85</v>
       </c>
@@ -15186,7 +15184,7 @@
       <c r="G52" s="147">
         <v>-282457.37110751297</v>
       </c>
-      <c r="H52" s="309">
+      <c r="H52" s="244">
         <f t="shared" si="0"/>
         <v>282457.42</v>
       </c>
@@ -15197,7 +15195,7 @@
         <f t="shared" si="4"/>
         <v>26652.784512487007</v>
       </c>
-      <c r="K52" s="307">
+      <c r="K52" s="189">
         <f t="shared" si="5"/>
         <v>309110.42</v>
       </c>
@@ -15206,10 +15204,10 @@
         <v>0.42000000000000021</v>
       </c>
       <c r="M52" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A53" s="228" t="s">
         <v>86</v>
       </c>
@@ -15231,7 +15229,7 @@
       <c r="G53" s="147">
         <v>-447623.12200936372</v>
       </c>
-      <c r="H53" s="309">
+      <c r="H53" s="244">
         <f t="shared" si="0"/>
         <v>447623.43</v>
       </c>
@@ -15242,7 +15240,7 @@
         <f t="shared" si="4"/>
         <v>42237.887320636306</v>
       </c>
-      <c r="K53" s="307">
+      <c r="K53" s="189">
         <f t="shared" si="5"/>
         <v>489861.43</v>
       </c>
@@ -15251,7 +15249,7 @@
         <v>0.43000000000000022</v>
       </c>
     </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A54" s="228" t="s">
         <v>87</v>
       </c>
@@ -15271,7 +15269,7 @@
       <c r="G54" s="147">
         <v>-174740.57704108849</v>
       </c>
-      <c r="H54" s="309">
+      <c r="H54" s="244">
         <f t="shared" si="0"/>
         <v>174741.44</v>
       </c>
@@ -15282,7 +15280,7 @@
         <f t="shared" si="4"/>
         <v>16488.587028911512</v>
       </c>
-      <c r="K54" s="307">
+      <c r="K54" s="189">
         <f t="shared" si="5"/>
         <v>191230.44</v>
       </c>
@@ -15291,7 +15289,7 @@
         <v>0.44000000000000022</v>
       </c>
     </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A55" s="228" t="s">
         <v>88</v>
       </c>
@@ -15313,7 +15311,7 @@
       <c r="G55" s="147">
         <v>-487804.97705695755</v>
       </c>
-      <c r="H55" s="309">
+      <c r="H55" s="244">
         <f t="shared" si="0"/>
         <v>487805.45</v>
       </c>
@@ -15324,7 +15322,7 @@
         <f t="shared" si="4"/>
         <v>28251.808173042373</v>
       </c>
-      <c r="K55" s="307">
+      <c r="K55" s="189">
         <f t="shared" si="5"/>
         <v>516057.45</v>
       </c>
@@ -15333,7 +15331,7 @@
         <v>0.45000000000000023</v>
       </c>
     </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A56" s="228" t="s">
         <v>89</v>
       </c>
@@ -15355,7 +15353,7 @@
       <c r="G56" s="147">
         <v>-280063.66457270354</v>
       </c>
-      <c r="H56" s="309">
+      <c r="H56" s="244">
         <f t="shared" si="0"/>
         <v>280064.46000000002</v>
       </c>
@@ -15366,7 +15364,7 @@
         <f t="shared" si="4"/>
         <v>26426.913457296439</v>
       </c>
-      <c r="K56" s="307">
+      <c r="K56" s="189">
         <f t="shared" si="5"/>
         <v>306491.46000000002</v>
       </c>
@@ -15375,7 +15373,7 @@
         <v>0.46000000000000024</v>
       </c>
     </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A57" s="228" t="s">
         <v>90</v>
       </c>
@@ -15397,7 +15395,7 @@
       <c r="G57" s="147">
         <v>-260547.07259893051</v>
       </c>
-      <c r="H57" s="309">
+      <c r="H57" s="244">
         <f t="shared" si="0"/>
         <v>260547.47</v>
       </c>
@@ -15408,7 +15406,7 @@
         <f t="shared" si="4"/>
         <v>27606.462301069463</v>
       </c>
-      <c r="K57" s="307">
+      <c r="K57" s="189">
         <f t="shared" si="5"/>
         <v>288154.46999999997</v>
       </c>
@@ -15417,7 +15415,7 @@
         <v>0.47000000000000025</v>
       </c>
     </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A58" s="228" t="s">
         <v>91</v>
       </c>
@@ -15439,7 +15437,7 @@
       <c r="G58" s="147">
         <v>-275852.5976977864</v>
       </c>
-      <c r="H58" s="309">
+      <c r="H58" s="244">
         <f t="shared" si="0"/>
         <v>275853.48</v>
       </c>
@@ -15450,7 +15448,7 @@
         <f t="shared" si="4"/>
         <v>33257.557922213571</v>
       </c>
-      <c r="K58" s="307">
+      <c r="K58" s="189">
         <f t="shared" si="5"/>
         <v>309111.48</v>
       </c>
@@ -15460,7 +15458,7 @@
       </c>
       <c r="O58" s="183"/>
     </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A59" s="228" t="s">
         <v>92</v>
       </c>
@@ -15468,7 +15466,7 @@
         <v>4</v>
       </c>
       <c r="C59" s="108" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="D59" s="136">
         <v>1.8700000000000001E-2</v>
@@ -15482,7 +15480,7 @@
       <c r="G59" s="147">
         <v>-447623.12200936372</v>
       </c>
-      <c r="H59" s="309">
+      <c r="H59" s="244">
         <f t="shared" si="0"/>
         <v>447623.49</v>
       </c>
@@ -15493,7 +15491,7 @@
         <f t="shared" si="4"/>
         <v>42237.887320636306</v>
       </c>
-      <c r="K59" s="307">
+      <c r="K59" s="189">
         <f t="shared" si="5"/>
         <v>489861.49</v>
       </c>
@@ -15503,7 +15501,7 @@
       </c>
       <c r="O59" s="43"/>
     </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A60" s="228" t="s">
         <v>93</v>
       </c>
@@ -15523,7 +15521,7 @@
       <c r="G60" s="147">
         <v>-174740.57704108849</v>
       </c>
-      <c r="H60" s="309">
+      <c r="H60" s="244">
         <f t="shared" si="0"/>
         <v>174741.5</v>
       </c>
@@ -15534,7 +15532,7 @@
         <f t="shared" si="4"/>
         <v>16488.587028911512</v>
       </c>
-      <c r="K60" s="307">
+      <c r="K60" s="189">
         <f t="shared" si="5"/>
         <v>191230.5</v>
       </c>
@@ -15543,7 +15541,7 @@
         <v>0.50000000000000022</v>
       </c>
     </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A61" s="228" t="s">
         <v>94</v>
       </c>
@@ -15565,7 +15563,7 @@
       <c r="G61" s="147">
         <v>-469441.3017444798</v>
       </c>
-      <c r="H61" s="309">
+      <c r="H61" s="244">
         <f t="shared" si="0"/>
         <v>469441.51</v>
       </c>
@@ -15576,7 +15574,7 @@
         <f t="shared" si="4"/>
         <v>46615.483485520119</v>
       </c>
-      <c r="K61" s="307">
+      <c r="K61" s="189">
         <f t="shared" si="5"/>
         <v>516057.51</v>
       </c>
@@ -15585,7 +15583,7 @@
         <v>0.51000000000000023</v>
       </c>
     </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A62" s="228" t="s">
         <v>95</v>
       </c>
@@ -15605,7 +15603,7 @@
       <c r="G62" s="147">
         <v>-164899.57136629923</v>
       </c>
-      <c r="H62" s="309">
+      <c r="H62" s="244">
         <f t="shared" si="0"/>
         <v>164900.51999999999</v>
       </c>
@@ -15616,7 +15614,7 @@
         <f t="shared" si="4"/>
         <v>81340.722093700751</v>
       </c>
-      <c r="K62" s="307">
+      <c r="K62" s="189">
         <f t="shared" si="5"/>
         <v>246241.52</v>
       </c>
@@ -15625,13 +15623,13 @@
         <v>0.52000000000000024</v>
       </c>
     </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A63" s="228" t="s">
         <v>96</v>
       </c>
       <c r="B63" s="229"/>
       <c r="C63" s="108" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D63" s="136">
         <v>8.6999999999999994E-3</v>
@@ -15645,7 +15643,7 @@
       <c r="G63" s="147">
         <v>-206069.04832824506</v>
       </c>
-      <c r="H63" s="309">
+      <c r="H63" s="244">
         <f t="shared" si="0"/>
         <v>206069.53</v>
       </c>
@@ -15656,7 +15654,7 @@
         <f t="shared" si="4"/>
         <v>21834.202001754922</v>
       </c>
-      <c r="K63" s="307">
+      <c r="K63" s="189">
         <f t="shared" si="5"/>
         <v>227904.53</v>
       </c>
@@ -15668,7 +15666,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A64" s="228" t="s">
         <v>97</v>
       </c>
@@ -15690,7 +15688,7 @@
       <c r="G64" s="147">
         <v>-285418.79160890041</v>
       </c>
-      <c r="H64" s="309">
+      <c r="H64" s="244">
         <f t="shared" si="0"/>
         <v>285419.53999999998</v>
       </c>
@@ -15701,7 +15699,7 @@
         <f t="shared" si="4"/>
         <v>23691.364011099562</v>
       </c>
-      <c r="K64" s="307">
+      <c r="K64" s="189">
         <f t="shared" si="5"/>
         <v>309111.53999999998</v>
       </c>
@@ -15710,7 +15708,7 @@
         <v>0.54000000000000026</v>
       </c>
     </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A65" s="228" t="s">
         <v>98</v>
       </c>
@@ -15732,7 +15730,7 @@
       <c r="G65" s="147">
         <v>-634226.20947773824</v>
       </c>
-      <c r="H65" s="309">
+      <c r="H65" s="244">
         <f t="shared" si="0"/>
         <v>634226.55000000005</v>
       </c>
@@ -15743,7 +15741,7 @@
         <f t="shared" si="4"/>
         <v>41624.808742261725</v>
       </c>
-      <c r="K65" s="307">
+      <c r="K65" s="189">
         <f t="shared" si="5"/>
         <v>675851.55</v>
       </c>
@@ -15753,7 +15751,7 @@
       </c>
       <c r="M65" s="73"/>
     </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A66" s="228" t="s">
         <v>99</v>
       </c>
@@ -15761,7 +15759,7 @@
         <v>41</v>
       </c>
       <c r="C66" s="108" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="D66" s="136">
         <v>1.9699999999999999E-2</v>
@@ -15775,7 +15773,7 @@
       <c r="G66" s="147">
         <v>-473679.07297043619</v>
       </c>
-      <c r="H66" s="309">
+      <c r="H66" s="244">
         <f t="shared" si="0"/>
         <v>473679.56</v>
       </c>
@@ -15786,7 +15784,7 @@
         <f t="shared" si="4"/>
         <v>42377.712259563734</v>
       </c>
-      <c r="K66" s="307">
+      <c r="K66" s="189">
         <f t="shared" si="5"/>
         <v>516057.56</v>
       </c>
@@ -15795,7 +15793,7 @@
         <v>0.56000000000000028</v>
       </c>
     </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A67" s="228" t="s">
         <v>100</v>
       </c>
@@ -15803,7 +15801,7 @@
         <v>2</v>
       </c>
       <c r="C67" s="108" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="D67" s="136">
         <v>1.17E-2</v>
@@ -15815,7 +15813,7 @@
       <c r="G67" s="147">
         <v>0</v>
       </c>
-      <c r="H67" s="309"/>
+      <c r="H67" s="244"/>
       <c r="I67" s="147">
         <v>-306490.57802999998</v>
       </c>
@@ -15823,7 +15821,7 @@
         <f t="shared" si="4"/>
         <v>306490.57802999998</v>
       </c>
-      <c r="K67" s="307">
+      <c r="K67" s="189">
         <f t="shared" si="5"/>
         <v>306491.57</v>
       </c>
@@ -15832,7 +15830,7 @@
         <v>0.57000000000000028</v>
       </c>
     </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A68" s="228" t="s">
         <v>101</v>
       </c>
@@ -15852,7 +15850,7 @@
       <c r="G68" s="147">
         <v>-213866.97761458607</v>
       </c>
-      <c r="H68" s="309">
+      <c r="H68" s="244">
         <f t="shared" si="0"/>
         <v>213867.58</v>
       </c>
@@ -15863,7 +15861,7 @@
         <f t="shared" si="4"/>
         <v>14036.272715413914</v>
       </c>
-      <c r="K68" s="307">
+      <c r="K68" s="189">
         <f t="shared" si="5"/>
         <v>227904.58</v>
       </c>
@@ -15872,7 +15870,7 @@
         <v>0.58000000000000029</v>
       </c>
     </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A69" s="228" t="s">
         <v>102</v>
       </c>
@@ -15894,7 +15892,7 @@
       <c r="G69" s="147">
         <v>-256859.2161501162</v>
       </c>
-      <c r="H69" s="309">
+      <c r="H69" s="244">
         <f t="shared" si="0"/>
         <v>256859.59</v>
       </c>
@@ -15905,7 +15903,7 @@
         <f t="shared" si="4"/>
         <v>52250.939469883771</v>
       </c>
-      <c r="K69" s="307">
+      <c r="K69" s="189">
         <f t="shared" si="5"/>
         <v>309111.59000000003</v>
       </c>
@@ -15914,7 +15912,7 @@
         <v>0.5900000000000003</v>
       </c>
     </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A70" s="228" t="s">
         <v>103</v>
       </c>
@@ -15936,7 +15934,7 @@
       <c r="G70" s="147">
         <v>-382821.80090465758</v>
       </c>
-      <c r="H70" s="309">
+      <c r="H70" s="244">
         <f t="shared" si="0"/>
         <v>382822.6</v>
       </c>
@@ -15947,7 +15945,7 @@
         <f t="shared" si="4"/>
         <v>293029.21731534239</v>
       </c>
-      <c r="K70" s="307">
+      <c r="K70" s="189">
         <f t="shared" si="5"/>
         <v>675852.6</v>
       </c>
@@ -15956,7 +15954,7 @@
         <v>0.60000000000000031</v>
       </c>
     </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A71" s="228" t="s">
         <v>104</v>
       </c>
@@ -15978,7 +15976,7 @@
       <c r="G71" s="147">
         <v>-466616.12092717562</v>
       </c>
-      <c r="H71" s="309">
+      <c r="H71" s="244">
         <f t="shared" ref="H71:H79" si="7">ROUND((-G71),0)+L71</f>
         <v>466616.61</v>
       </c>
@@ -15989,7 +15987,7 @@
         <f t="shared" si="4"/>
         <v>49440.664302824298</v>
       </c>
-      <c r="K71" s="307">
+      <c r="K71" s="189">
         <f t="shared" si="5"/>
         <v>516057.61</v>
       </c>
@@ -15998,7 +15996,7 @@
         <v>0.61000000000000032</v>
       </c>
     </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A72" s="228" t="s">
         <v>105</v>
       </c>
@@ -16018,7 +16016,7 @@
       <c r="G72" s="147">
         <v>-228041.53987035993</v>
       </c>
-      <c r="H72" s="309">
+      <c r="H72" s="244">
         <f t="shared" si="7"/>
         <v>228042.62</v>
       </c>
@@ -16029,7 +16027,7 @@
         <f t="shared" si="4"/>
         <v>18198.753589640051</v>
       </c>
-      <c r="K72" s="307">
+      <c r="K72" s="189">
         <f t="shared" si="5"/>
         <v>246241.62</v>
       </c>
@@ -16038,7 +16036,7 @@
         <v>0.62000000000000033</v>
       </c>
     </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A73" s="228" t="s">
         <v>106</v>
       </c>
@@ -16060,7 +16058,7 @@
       <c r="G73" s="147">
         <v>-266857.12112488924</v>
       </c>
-      <c r="H73" s="309">
+      <c r="H73" s="244">
         <f t="shared" si="7"/>
         <v>266857.63</v>
       </c>
@@ -16071,7 +16069,7 @@
         <f t="shared" si="4"/>
         <v>21296.413775110734</v>
       </c>
-      <c r="K73" s="307">
+      <c r="K73" s="189">
         <f t="shared" si="5"/>
         <v>288154.63</v>
       </c>
@@ -16080,7 +16078,7 @@
         <v>0.63000000000000034</v>
       </c>
     </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A74" s="228" t="s">
         <v>107</v>
       </c>
@@ -16100,7 +16098,7 @@
       <c r="G74" s="147">
         <v>-229786.31527835201</v>
       </c>
-      <c r="H74" s="309">
+      <c r="H74" s="244">
         <f t="shared" si="7"/>
         <v>229786.64</v>
       </c>
@@ -16111,7 +16109,7 @@
         <f t="shared" si="4"/>
         <v>19073.555771647982</v>
       </c>
-      <c r="K74" s="307">
+      <c r="K74" s="189">
         <f t="shared" si="5"/>
         <v>248860.64</v>
       </c>
@@ -16120,7 +16118,7 @@
         <v>0.64000000000000035</v>
       </c>
     </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A75" s="228" t="s">
         <v>108</v>
       </c>
@@ -16128,7 +16126,7 @@
         <v>9</v>
       </c>
       <c r="C75" s="108" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="D75" s="136">
         <v>2.58E-2</v>
@@ -16142,7 +16140,7 @@
       <c r="G75" s="147">
         <v>-525270.52442663931</v>
       </c>
-      <c r="H75" s="309">
+      <c r="H75" s="244">
         <f t="shared" si="7"/>
         <v>525271.65</v>
       </c>
@@ -16153,7 +16151,7 @@
         <f t="shared" si="4"/>
         <v>150580.49379336066</v>
       </c>
-      <c r="K75" s="307">
+      <c r="K75" s="189">
         <f t="shared" si="5"/>
         <v>675852.65</v>
       </c>
@@ -16162,7 +16160,7 @@
         <v>0.65000000000000036</v>
       </c>
     </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A76" s="228" t="s">
         <v>109</v>
       </c>
@@ -16184,7 +16182,7 @@
       <c r="G76" s="147">
         <v>-477916.84419639257</v>
       </c>
-      <c r="H76" s="309">
+      <c r="H76" s="244">
         <f t="shared" si="7"/>
         <v>477917.66</v>
       </c>
@@ -16195,7 +16193,7 @@
         <f t="shared" ref="J76:J79" si="8">-I76</f>
         <v>38139.941033607349</v>
       </c>
-      <c r="K76" s="307">
+      <c r="K76" s="189">
         <f t="shared" ref="K76:K79" si="9">ROUND((H76+J76),0) + L76</f>
         <v>516058.66</v>
       </c>
@@ -16204,12 +16202,12 @@
         <v>0.66000000000000036</v>
       </c>
     </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A77" s="228" t="s">
         <v>110</v>
       </c>
       <c r="B77" s="229" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C77" s="108" t="s">
         <v>219</v>
@@ -16226,7 +16224,7 @@
       <c r="G77" s="147">
         <v>-338632.46462072933</v>
       </c>
-      <c r="H77" s="309">
+      <c r="H77" s="244">
         <f t="shared" si="7"/>
         <v>338632.67</v>
       </c>
@@ -16237,7 +16235,7 @@
         <f t="shared" si="8"/>
         <v>28108.397979270667</v>
       </c>
-      <c r="K77" s="307">
+      <c r="K77" s="189">
         <f t="shared" si="9"/>
         <v>366741.67</v>
       </c>
@@ -16246,7 +16244,7 @@
         <v>0.67000000000000037</v>
       </c>
     </row>
-    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A78" s="228" t="s">
         <v>111</v>
       </c>
@@ -16268,7 +16266,7 @@
       <c r="G78" s="147">
         <v>-269617.76735499618</v>
       </c>
-      <c r="H78" s="309">
+      <c r="H78" s="244">
         <f t="shared" si="7"/>
         <v>269618.68</v>
       </c>
@@ -16279,7 +16277,7 @@
         <f t="shared" si="8"/>
         <v>18535.767545003793</v>
       </c>
-      <c r="K78" s="307">
+      <c r="K78" s="189">
         <f t="shared" si="9"/>
         <v>288154.68</v>
       </c>
@@ -16288,7 +16286,7 @@
         <v>0.68000000000000038</v>
       </c>
     </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A79" s="228" t="s">
         <v>112</v>
       </c>
@@ -16310,7 +16308,7 @@
       <c r="G79" s="147">
         <v>-279495.95060612552</v>
       </c>
-      <c r="H79" s="309">
+      <c r="H79" s="244">
         <f t="shared" si="7"/>
         <v>279496.69</v>
       </c>
@@ -16321,7 +16319,7 @@
         <f t="shared" si="8"/>
         <v>29614.205013874453</v>
       </c>
-      <c r="K79" s="307">
+      <c r="K79" s="189">
         <f t="shared" si="9"/>
         <v>309111.69</v>
       </c>
@@ -16330,7 +16328,7 @@
         <v>0.69000000000000039</v>
       </c>
     </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A80" s="35"/>
       <c r="B80" s="35"/>
       <c r="C80" s="108"/>
@@ -16343,7 +16341,7 @@
       <c r="J80" s="146"/>
       <c r="K80" s="147"/>
     </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A81" s="27"/>
       <c r="B81" s="27"/>
       <c r="C81" s="27"/>
@@ -16374,18 +16372,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A1:K2"/>
+    <mergeCell ref="N6:O7"/>
+    <mergeCell ref="H3:H5"/>
+    <mergeCell ref="J3:J5"/>
+    <mergeCell ref="A3:A5"/>
+    <mergeCell ref="G3:G5"/>
+    <mergeCell ref="K3:K5"/>
     <mergeCell ref="E3:E5"/>
     <mergeCell ref="F3:F5"/>
     <mergeCell ref="B3:B5"/>
     <mergeCell ref="C3:C5"/>
     <mergeCell ref="D3:D5"/>
-    <mergeCell ref="H3:H5"/>
-    <mergeCell ref="J3:J5"/>
-    <mergeCell ref="A3:A5"/>
-    <mergeCell ref="G3:G5"/>
-    <mergeCell ref="K3:K5"/>
-    <mergeCell ref="A1:K2"/>
-    <mergeCell ref="N6:O7"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="3" scale="110" orientation="landscape" r:id="rId1"/>
@@ -16395,9 +16393,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7365EFC1-5C09-4380-B9A2-A73102AE2F7A}">
   <dimension ref="A13"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="13" ht="15.6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/2026/EL MIRADOR/Febrero/Febrero - EL MIRADOR.xlsx
+++ b/2026/EL MIRADOR/Febrero/Febrero - EL MIRADOR.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\EL MIRADOR\Febrero\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{679AAA98-AFE3-491A-BBF5-4F51FF505FA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31BBF0E1-339D-4BF1-A25E-CC3CFC1F7C4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -962,9 +962,6 @@
     <t>Julieta Damiano/Damiani</t>
   </si>
   <si>
-    <t>Heredia, Christian</t>
-  </si>
-  <si>
     <t>0CTtubr3</t>
   </si>
   <si>
@@ -1237,6 +1234,9 @@
   </si>
   <si>
     <t>HORARIOS DE ATENCION: LUNES A VIERNES - 10 A 15HS - EMERGENCIAS 24HS</t>
+  </si>
+  <si>
+    <t>Fernandez, Christian Norberto</t>
   </si>
 </sst>
 </file>
@@ -2270,26 +2270,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -2387,10 +2375,28 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="23" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="23" fillId="9" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="23" fillId="9" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="23" fillId="9" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="12" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2402,16 +2408,10 @@
     <xf numFmtId="0" fontId="2" fillId="12" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="23" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="23" fillId="9" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="23" fillId="9" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="23" fillId="9" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2860,11 +2860,11 @@
       <c r="A5" s="117"/>
       <c r="B5" s="122"/>
       <c r="C5" s="122" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D5" s="122"/>
       <c r="E5" s="122" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="F5" s="122"/>
       <c r="G5" s="122"/>
@@ -2970,7 +2970,7 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" s="255" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B20" s="255"/>
       <c r="C20" s="255"/>
@@ -3148,7 +3148,7 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" s="6" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B32" s="6"/>
       <c r="C32" s="6"/>
@@ -3295,7 +3295,7 @@
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41" s="6" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B41" s="6"/>
       <c r="C41" s="6"/>
@@ -3371,7 +3371,7 @@
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A44" s="32" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B44" s="6"/>
       <c r="C44" s="6"/>
@@ -3462,7 +3462,7 @@
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A48" s="6" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B48" s="6"/>
       <c r="C48" s="195">
@@ -3484,7 +3484,7 @@
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A49" s="6" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B49" s="6"/>
       <c r="C49" s="195">
@@ -3506,7 +3506,7 @@
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A50" s="6" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B50" s="6"/>
       <c r="C50" s="195">
@@ -3528,7 +3528,7 @@
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A51" s="6" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B51" s="6"/>
       <c r="C51" s="195">
@@ -3550,7 +3550,7 @@
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A52" s="6" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B52" s="6"/>
       <c r="C52" s="195">
@@ -3646,10 +3646,10 @@
         <v>248</v>
       </c>
       <c r="B57" s="35" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C57" s="35" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D57" s="213">
         <v>249469</v>
@@ -3667,10 +3667,10 @@
         <v>248</v>
       </c>
       <c r="B58" s="35" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C58" s="35" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D58" s="213">
         <v>249469</v>
@@ -3747,7 +3747,7 @@
       </c>
       <c r="B61" s="6"/>
       <c r="C61" s="6" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D61" s="208">
         <v>56231.41</v>
@@ -3766,7 +3766,7 @@
       </c>
       <c r="B62" s="6"/>
       <c r="C62" s="6" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D62" s="208">
         <v>64941</v>
@@ -3784,10 +3784,10 @@
         <v>281</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C63" s="184" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D63" s="208">
         <v>64941</v>
@@ -3864,7 +3864,7 @@
       </c>
       <c r="B66" s="6"/>
       <c r="C66" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="D66" s="208">
         <v>160913</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="B67" s="258"/>
       <c r="C67" s="35" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="D67" s="208">
         <v>7907</v>
@@ -3939,7 +3939,7 @@
         <v>7907</v>
       </c>
       <c r="L67" s="207" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="68" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
@@ -3948,7 +3948,7 @@
       </c>
       <c r="B68" s="258"/>
       <c r="C68" s="35" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="D68" s="208">
         <v>7907</v>
@@ -4047,7 +4047,7 @@
       </c>
       <c r="B71" s="6"/>
       <c r="C71" s="35" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D71" s="220">
         <v>1469353.32</v>
@@ -4093,7 +4093,7 @@
       </c>
       <c r="B72" s="6"/>
       <c r="C72" s="35" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D72" s="220">
         <v>2331402.6</v>
@@ -4139,7 +4139,7 @@
       </c>
       <c r="B73" s="6"/>
       <c r="C73" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="D73" s="208">
         <v>124753.28</v>
@@ -4172,11 +4172,11 @@
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A74" s="6" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B74" s="6"/>
       <c r="C74" s="6" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="D74" s="208">
         <v>352314.06</v>
@@ -4203,11 +4203,11 @@
     </row>
     <row r="75" spans="1:14" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="253" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B75" s="259"/>
       <c r="C75" s="35" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D75" s="208">
         <v>40000</v>
@@ -4240,11 +4240,11 @@
     </row>
     <row r="76" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="253" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B76" s="259"/>
       <c r="C76" s="184" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D76" s="208">
         <v>130000</v>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="B77" s="35"/>
       <c r="C77" s="184" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D77" s="208">
         <v>993952.65</v>
@@ -4324,7 +4324,7 @@
       </c>
       <c r="B78" s="35"/>
       <c r="C78" s="184" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D78" s="208">
         <v>5460.69</v>
@@ -4376,7 +4376,7 @@
       </c>
       <c r="B79" s="141"/>
       <c r="C79" s="6" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D79" s="208">
         <v>100000</v>
@@ -4512,11 +4512,11 @@
     </row>
     <row r="84" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A84" s="6" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B84" s="35"/>
       <c r="C84" s="35" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D84" s="208">
         <v>606800</v>
@@ -4549,11 +4549,11 @@
     </row>
     <row r="85" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A85" s="6" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B85" s="35"/>
       <c r="C85" s="35" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D85" s="208">
         <v>216800</v>
@@ -4571,11 +4571,11 @@
     </row>
     <row r="86" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A86" s="6" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B86" s="35"/>
       <c r="C86" s="35" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D86" s="208">
         <v>1300</v>
@@ -4608,11 +4608,11 @@
     </row>
     <row r="87" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="71" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B87" s="35"/>
       <c r="C87" s="196" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D87" s="208">
         <v>350000</v>
@@ -4630,11 +4630,11 @@
     </row>
     <row r="88" spans="1:14" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="262" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B88" s="263"/>
       <c r="C88" s="35" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D88" s="208">
         <v>250000</v>
@@ -4652,11 +4652,11 @@
     </row>
     <row r="89" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A89" s="6" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B89" s="35"/>
       <c r="C89" s="35" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D89" s="208">
         <v>32800</v>
@@ -4674,11 +4674,11 @@
     </row>
     <row r="90" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A90" s="6" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B90" s="35"/>
       <c r="C90" s="35" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D90" s="208">
         <v>50000</v>
@@ -4696,11 +4696,11 @@
     </row>
     <row r="91" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A91" s="45" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B91" s="197"/>
       <c r="C91" s="35" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D91" s="208">
         <v>60000</v>
@@ -4718,11 +4718,11 @@
     </row>
     <row r="92" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A92" s="45" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B92" s="197"/>
       <c r="C92" s="35" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D92" s="208">
         <v>50000</v>
@@ -4740,11 +4740,11 @@
     </row>
     <row r="93" spans="1:14" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="257" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B93" s="258"/>
       <c r="C93" s="137" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="D93" s="208">
         <v>307200</v>
@@ -4762,11 +4762,11 @@
     </row>
     <row r="94" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="257" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B94" s="258"/>
       <c r="C94" s="137" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="D94" s="208">
         <v>191400</v>
@@ -4784,11 +4784,11 @@
     </row>
     <row r="95" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="260" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B95" s="261"/>
       <c r="C95" s="137" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="D95" s="208">
         <v>95700</v>
@@ -4926,7 +4926,7 @@
         <v>13114.38</v>
       </c>
       <c r="L100" s="69" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="101" spans="1:14" x14ac:dyDescent="0.3">
@@ -5128,7 +5128,7 @@
     </row>
     <row r="108" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A108" s="100" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B108" s="101"/>
       <c r="C108" s="101"/>
@@ -5252,10 +5252,10 @@
     </row>
     <row r="113" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A113" s="1" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B113" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C113" s="128">
         <v>25000</v>
@@ -5544,7 +5544,7 @@
     </row>
     <row r="134" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="224" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B134" s="30">
         <v>426600</v>
@@ -5641,7 +5641,7 @@
     </row>
     <row r="141" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" s="19" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B141" s="30">
         <v>143267</v>
@@ -5712,7 +5712,7 @@
     </row>
     <row r="148" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A148" s="19" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B148" s="83">
         <v>-20000</v>
@@ -5847,13 +5847,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A1" s="297" t="s">
-        <v>364</v>
-      </c>
-      <c r="B1" s="298"/>
-      <c r="C1" s="298"/>
-      <c r="D1" s="298"/>
-      <c r="E1" s="298"/>
+      <c r="A1" s="293" t="s">
+        <v>363</v>
+      </c>
+      <c r="B1" s="294"/>
+      <c r="C1" s="294"/>
+      <c r="D1" s="294"/>
+      <c r="E1" s="294"/>
       <c r="F1" s="158" t="s">
         <v>295</v>
       </c>
@@ -5864,20 +5864,20 @@
       <c r="K1" s="192" t="s">
         <v>41</v>
       </c>
-      <c r="L1" s="273">
+      <c r="L1" s="269">
         <f>RESUMEN!D110-RESUMEN!D108</f>
         <v>12343887.129999999</v>
       </c>
-      <c r="M1" s="274"/>
+      <c r="M1" s="270"/>
       <c r="N1" s="159"/>
       <c r="O1" s="59"/>
     </row>
     <row r="2" spans="1:18" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="299"/>
-      <c r="B2" s="300"/>
-      <c r="C2" s="300"/>
-      <c r="D2" s="300"/>
-      <c r="E2" s="300"/>
+      <c r="A2" s="295"/>
+      <c r="B2" s="296"/>
+      <c r="C2" s="296"/>
+      <c r="D2" s="296"/>
+      <c r="E2" s="296"/>
       <c r="F2" s="7" t="s">
         <v>294</v>
       </c>
@@ -5896,11 +5896,11 @@
       <c r="O2" s="59"/>
     </row>
     <row r="3" spans="1:18" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="299"/>
-      <c r="B3" s="300"/>
-      <c r="C3" s="300"/>
-      <c r="D3" s="300"/>
-      <c r="E3" s="300"/>
+      <c r="A3" s="295"/>
+      <c r="B3" s="296"/>
+      <c r="C3" s="296"/>
+      <c r="D3" s="296"/>
+      <c r="E3" s="296"/>
       <c r="F3" s="7" t="s">
         <v>296</v>
       </c>
@@ -5915,11 +5915,11 @@
       <c r="O3" s="15"/>
     </row>
     <row r="4" spans="1:18" ht="2.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="301"/>
-      <c r="B4" s="302"/>
-      <c r="C4" s="302"/>
-      <c r="D4" s="302"/>
-      <c r="E4" s="302"/>
+      <c r="A4" s="297"/>
+      <c r="B4" s="298"/>
+      <c r="C4" s="298"/>
+      <c r="D4" s="298"/>
+      <c r="E4" s="298"/>
       <c r="F4" s="164"/>
       <c r="G4" s="164"/>
       <c r="H4" s="164"/>
@@ -5934,90 +5934,90 @@
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" s="7"/>
       <c r="B5" s="7"/>
-      <c r="C5" s="282" t="s">
-        <v>313</v>
-      </c>
-      <c r="D5" s="283"/>
-      <c r="E5" s="283"/>
-      <c r="F5" s="283"/>
-      <c r="G5" s="283"/>
-      <c r="H5" s="283"/>
-      <c r="I5" s="283"/>
-      <c r="J5" s="283"/>
-      <c r="K5" s="283"/>
-      <c r="L5" s="283"/>
-      <c r="M5" s="283"/>
-      <c r="N5" s="284"/>
+      <c r="C5" s="278" t="s">
+        <v>312</v>
+      </c>
+      <c r="D5" s="279"/>
+      <c r="E5" s="279"/>
+      <c r="F5" s="279"/>
+      <c r="G5" s="279"/>
+      <c r="H5" s="279"/>
+      <c r="I5" s="279"/>
+      <c r="J5" s="279"/>
+      <c r="K5" s="279"/>
+      <c r="L5" s="279"/>
+      <c r="M5" s="279"/>
+      <c r="N5" s="280"/>
       <c r="O5" s="15"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" s="7"/>
       <c r="B6" s="7"/>
-      <c r="C6" s="285"/>
-      <c r="D6" s="286"/>
-      <c r="E6" s="286"/>
-      <c r="F6" s="286"/>
-      <c r="G6" s="286"/>
-      <c r="H6" s="286"/>
-      <c r="I6" s="286"/>
-      <c r="J6" s="286"/>
-      <c r="K6" s="286"/>
-      <c r="L6" s="286"/>
-      <c r="M6" s="286"/>
-      <c r="N6" s="287"/>
+      <c r="C6" s="281"/>
+      <c r="D6" s="282"/>
+      <c r="E6" s="282"/>
+      <c r="F6" s="282"/>
+      <c r="G6" s="282"/>
+      <c r="H6" s="282"/>
+      <c r="I6" s="282"/>
+      <c r="J6" s="282"/>
+      <c r="K6" s="282"/>
+      <c r="L6" s="282"/>
+      <c r="M6" s="282"/>
+      <c r="N6" s="283"/>
       <c r="O6" s="15"/>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" s="7"/>
       <c r="B7" s="7"/>
-      <c r="C7" s="285"/>
-      <c r="D7" s="286"/>
-      <c r="E7" s="286"/>
-      <c r="F7" s="286"/>
-      <c r="G7" s="286"/>
-      <c r="H7" s="286"/>
-      <c r="I7" s="286"/>
-      <c r="J7" s="286"/>
-      <c r="K7" s="286"/>
-      <c r="L7" s="286"/>
-      <c r="M7" s="286"/>
-      <c r="N7" s="287"/>
+      <c r="C7" s="281"/>
+      <c r="D7" s="282"/>
+      <c r="E7" s="282"/>
+      <c r="F7" s="282"/>
+      <c r="G7" s="282"/>
+      <c r="H7" s="282"/>
+      <c r="I7" s="282"/>
+      <c r="J7" s="282"/>
+      <c r="K7" s="282"/>
+      <c r="L7" s="282"/>
+      <c r="M7" s="282"/>
+      <c r="N7" s="283"/>
       <c r="O7" s="15"/>
     </row>
     <row r="8" spans="1:18" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="7"/>
       <c r="B8" s="7"/>
-      <c r="C8" s="288"/>
-      <c r="D8" s="289"/>
-      <c r="E8" s="289"/>
-      <c r="F8" s="289"/>
-      <c r="G8" s="289"/>
-      <c r="H8" s="289"/>
-      <c r="I8" s="289"/>
-      <c r="J8" s="289"/>
-      <c r="K8" s="289"/>
-      <c r="L8" s="289"/>
-      <c r="M8" s="289"/>
-      <c r="N8" s="290"/>
+      <c r="C8" s="284"/>
+      <c r="D8" s="285"/>
+      <c r="E8" s="285"/>
+      <c r="F8" s="285"/>
+      <c r="G8" s="285"/>
+      <c r="H8" s="285"/>
+      <c r="I8" s="285"/>
+      <c r="J8" s="285"/>
+      <c r="K8" s="285"/>
+      <c r="L8" s="285"/>
+      <c r="M8" s="285"/>
+      <c r="N8" s="286"/>
       <c r="P8" s="84"/>
     </row>
     <row r="9" spans="1:18" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
-      <c r="C9" s="291" t="s">
-        <v>311</v>
-      </c>
-      <c r="D9" s="292"/>
-      <c r="E9" s="292"/>
-      <c r="F9" s="292"/>
-      <c r="G9" s="292"/>
-      <c r="H9" s="292"/>
-      <c r="I9" s="292"/>
-      <c r="J9" s="292"/>
-      <c r="K9" s="292"/>
-      <c r="L9" s="292"/>
-      <c r="M9" s="292"/>
-      <c r="N9" s="293"/>
+      <c r="C9" s="287" t="s">
+        <v>310</v>
+      </c>
+      <c r="D9" s="288"/>
+      <c r="E9" s="288"/>
+      <c r="F9" s="288"/>
+      <c r="G9" s="288"/>
+      <c r="H9" s="288"/>
+      <c r="I9" s="288"/>
+      <c r="J9" s="288"/>
+      <c r="K9" s="288"/>
+      <c r="L9" s="288"/>
+      <c r="M9" s="288"/>
+      <c r="N9" s="289"/>
       <c r="P9" t="s">
         <v>250</v>
       </c>
@@ -6029,18 +6029,18 @@
     <row r="10" spans="1:18" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="7"/>
       <c r="B10" s="7"/>
-      <c r="C10" s="294"/>
-      <c r="D10" s="295"/>
-      <c r="E10" s="295"/>
-      <c r="F10" s="295"/>
-      <c r="G10" s="295"/>
-      <c r="H10" s="295"/>
-      <c r="I10" s="295"/>
-      <c r="J10" s="295"/>
-      <c r="K10" s="295"/>
-      <c r="L10" s="295"/>
-      <c r="M10" s="295"/>
-      <c r="N10" s="296"/>
+      <c r="C10" s="290"/>
+      <c r="D10" s="291"/>
+      <c r="E10" s="291"/>
+      <c r="F10" s="291"/>
+      <c r="G10" s="291"/>
+      <c r="H10" s="291"/>
+      <c r="I10" s="291"/>
+      <c r="J10" s="291"/>
+      <c r="K10" s="291"/>
+      <c r="L10" s="291"/>
+      <c r="M10" s="291"/>
+      <c r="N10" s="292"/>
       <c r="P10" t="s">
         <v>251</v>
       </c>
@@ -6050,46 +6050,46 @@
       </c>
     </row>
     <row r="11" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="264" t="s">
+      <c r="A11" s="265" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="266" t="s">
+      <c r="B11" s="299" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="264" t="s">
+      <c r="C11" s="265" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="268" t="s">
+      <c r="D11" s="301" t="s">
         <v>12</v>
       </c>
-      <c r="E11" s="268" t="s">
+      <c r="E11" s="301" t="s">
         <v>268</v>
       </c>
-      <c r="F11" s="264" t="s">
+      <c r="F11" s="265" t="s">
         <v>27</v>
       </c>
-      <c r="G11" s="264" t="s">
+      <c r="G11" s="265" t="s">
         <v>13</v>
       </c>
-      <c r="H11" s="264" t="s">
+      <c r="H11" s="265" t="s">
         <v>14</v>
       </c>
-      <c r="I11" s="275" t="s">
+      <c r="I11" s="271" t="s">
         <v>15</v>
       </c>
-      <c r="J11" s="277" t="s">
+      <c r="J11" s="273" t="s">
         <v>16</v>
       </c>
-      <c r="K11" s="277" t="s">
+      <c r="K11" s="273" t="s">
         <v>18</v>
       </c>
-      <c r="L11" s="280" t="s">
+      <c r="L11" s="276" t="s">
         <v>40</v>
       </c>
-      <c r="M11" s="277" t="s">
+      <c r="M11" s="273" t="s">
         <v>279</v>
       </c>
-      <c r="N11" s="277" t="s">
+      <c r="N11" s="273" t="s">
         <v>278</v>
       </c>
       <c r="P11" t="s">
@@ -6101,20 +6101,20 @@
       </c>
     </row>
     <row r="12" spans="1:18" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="265"/>
-      <c r="B12" s="267"/>
-      <c r="C12" s="265"/>
-      <c r="D12" s="269"/>
-      <c r="E12" s="269"/>
-      <c r="F12" s="265"/>
-      <c r="G12" s="265"/>
-      <c r="H12" s="265"/>
-      <c r="I12" s="276"/>
-      <c r="J12" s="278"/>
-      <c r="K12" s="278"/>
-      <c r="L12" s="281"/>
-      <c r="M12" s="278"/>
-      <c r="N12" s="278"/>
+      <c r="A12" s="266"/>
+      <c r="B12" s="300"/>
+      <c r="C12" s="266"/>
+      <c r="D12" s="302"/>
+      <c r="E12" s="302"/>
+      <c r="F12" s="266"/>
+      <c r="G12" s="266"/>
+      <c r="H12" s="266"/>
+      <c r="I12" s="272"/>
+      <c r="J12" s="274"/>
+      <c r="K12" s="274"/>
+      <c r="L12" s="277"/>
+      <c r="M12" s="274"/>
+      <c r="N12" s="274"/>
       <c r="P12" t="s">
         <v>253</v>
       </c>
@@ -6124,18 +6124,18 @@
       </c>
     </row>
     <row r="13" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="265"/>
-      <c r="B13" s="267"/>
-      <c r="C13" s="265"/>
-      <c r="D13" s="269"/>
-      <c r="E13" s="269"/>
-      <c r="F13" s="265"/>
-      <c r="G13" s="265"/>
-      <c r="H13" s="265"/>
-      <c r="I13" s="276"/>
-      <c r="J13" s="278"/>
-      <c r="K13" s="279"/>
-      <c r="L13" s="281"/>
+      <c r="A13" s="266"/>
+      <c r="B13" s="300"/>
+      <c r="C13" s="266"/>
+      <c r="D13" s="302"/>
+      <c r="E13" s="302"/>
+      <c r="F13" s="266"/>
+      <c r="G13" s="266"/>
+      <c r="H13" s="266"/>
+      <c r="I13" s="272"/>
+      <c r="J13" s="274"/>
+      <c r="K13" s="275"/>
+      <c r="L13" s="277"/>
       <c r="M13" s="132" t="str">
         <f>RESUMEN!A20</f>
         <v>VTO 16/02</v>
@@ -6195,8 +6195,8 @@
         <v>441436.50630288007</v>
       </c>
       <c r="O14" s="115"/>
-      <c r="Q14" s="270"/>
-      <c r="R14" s="270"/>
+      <c r="Q14" s="264"/>
+      <c r="R14" s="264"/>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" s="6"/>
@@ -6205,7 +6205,7 @@
         <v>117</v>
       </c>
       <c r="D15" s="108" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="E15" s="190"/>
       <c r="F15" s="143">
@@ -6239,8 +6239,8 @@
         <v>307962.66747008008</v>
       </c>
       <c r="O15" s="115"/>
-      <c r="Q15" s="270"/>
-      <c r="R15" s="270"/>
+      <c r="Q15" s="264"/>
+      <c r="R15" s="264"/>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
@@ -6254,7 +6254,7 @@
         <v>266</v>
       </c>
       <c r="E16" s="108" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="F16" s="143">
         <v>1.21E-2</v>
@@ -6428,7 +6428,7 @@
         <v>0.01</v>
       </c>
       <c r="P19" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="R19" s="43"/>
     </row>
@@ -6584,7 +6584,7 @@
         <v>0.04</v>
       </c>
       <c r="P22" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.3">
@@ -6701,7 +6701,7 @@
         <v>182</v>
       </c>
       <c r="E25" s="135" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F25" s="136">
         <v>1.6500000000000001E-2</v>
@@ -6803,7 +6803,7 @@
         <v>182</v>
       </c>
       <c r="E27" s="200" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="F27" s="201">
         <v>1.78E-2</v>
@@ -6853,7 +6853,7 @@
         <v>53</v>
       </c>
       <c r="D28" s="108" t="s">
-        <v>308</v>
+        <v>399</v>
       </c>
       <c r="E28" s="135"/>
       <c r="F28" s="136">
@@ -7193,7 +7193,7 @@
         <v>0.16</v>
       </c>
       <c r="P34" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="35" spans="1:113" x14ac:dyDescent="0.3">
@@ -7345,7 +7345,7 @@
         <v>0.19000000000000003</v>
       </c>
       <c r="P37" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="38" spans="1:113" x14ac:dyDescent="0.3">
@@ -7590,7 +7590,7 @@
         <v>0.22000000000000006</v>
       </c>
       <c r="P40" s="73" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="Q40" s="73"/>
       <c r="R40" s="73"/>
@@ -8152,7 +8152,7 @@
         <v>71</v>
       </c>
       <c r="D46" s="108" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E46" s="135"/>
       <c r="F46" s="136">
@@ -8757,7 +8757,7 @@
         <v>198</v>
       </c>
       <c r="E58" s="135" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="F58" s="136">
         <v>9.4000000000000004E-3</v>
@@ -8807,7 +8807,7 @@
         <v>84</v>
       </c>
       <c r="D59" s="108" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="E59" s="135"/>
       <c r="F59" s="136">
@@ -11598,7 +11598,7 @@
         <v>182</v>
       </c>
       <c r="E116" s="108" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F116" s="143">
         <v>2.3E-3</v>
@@ -12022,7 +12022,7 @@
         <v>1.0600000000000007</v>
       </c>
       <c r="P124" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="125" spans="1:16" x14ac:dyDescent="0.3">
@@ -12325,7 +12325,7 @@
         <v>167</v>
       </c>
       <c r="D131" s="108" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E131" s="108"/>
       <c r="F131" s="89">
@@ -12432,32 +12432,32 @@
       </c>
     </row>
     <row r="135" spans="1:16" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C135" s="272"/>
-      <c r="D135" s="272"/>
-      <c r="E135" s="272"/>
-      <c r="F135" s="272"/>
-      <c r="G135" s="272"/>
-      <c r="H135" s="272"/>
-      <c r="I135" s="272"/>
-      <c r="J135" s="272"/>
-      <c r="K135" s="272"/>
-      <c r="L135" s="272"/>
-      <c r="M135" s="272"/>
-      <c r="N135" s="272"/>
+      <c r="C135" s="268"/>
+      <c r="D135" s="268"/>
+      <c r="E135" s="268"/>
+      <c r="F135" s="268"/>
+      <c r="G135" s="268"/>
+      <c r="H135" s="268"/>
+      <c r="I135" s="268"/>
+      <c r="J135" s="268"/>
+      <c r="K135" s="268"/>
+      <c r="L135" s="268"/>
+      <c r="M135" s="268"/>
+      <c r="N135" s="268"/>
     </row>
     <row r="136" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
-      <c r="C136" s="272"/>
-      <c r="D136" s="272"/>
-      <c r="E136" s="272"/>
-      <c r="F136" s="272"/>
-      <c r="G136" s="272"/>
-      <c r="H136" s="272"/>
-      <c r="I136" s="272"/>
-      <c r="J136" s="272"/>
-      <c r="K136" s="272"/>
-      <c r="L136" s="272"/>
-      <c r="M136" s="272"/>
-      <c r="N136" s="272"/>
+      <c r="C136" s="268"/>
+      <c r="D136" s="268"/>
+      <c r="E136" s="268"/>
+      <c r="F136" s="268"/>
+      <c r="G136" s="268"/>
+      <c r="H136" s="268"/>
+      <c r="I136" s="268"/>
+      <c r="J136" s="268"/>
+      <c r="K136" s="268"/>
+      <c r="L136" s="268"/>
+      <c r="M136" s="268"/>
+      <c r="N136" s="268"/>
     </row>
     <row r="137" spans="1:16" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C137" s="77"/>
@@ -12616,111 +12616,117 @@
       <c r="N147" s="77"/>
     </row>
     <row r="148" spans="3:16" x14ac:dyDescent="0.3">
-      <c r="C148" s="271" t="s">
+      <c r="C148" s="267" t="s">
         <v>259</v>
       </c>
-      <c r="D148" s="271"/>
-      <c r="E148" s="271"/>
-      <c r="F148" s="271"/>
-      <c r="G148" s="271"/>
-      <c r="H148" s="271"/>
-      <c r="I148" s="271"/>
-      <c r="J148" s="271"/>
-      <c r="K148" s="271"/>
-      <c r="L148" s="271"/>
-      <c r="M148" s="271"/>
-      <c r="N148" s="271"/>
+      <c r="D148" s="267"/>
+      <c r="E148" s="267"/>
+      <c r="F148" s="267"/>
+      <c r="G148" s="267"/>
+      <c r="H148" s="267"/>
+      <c r="I148" s="267"/>
+      <c r="J148" s="267"/>
+      <c r="K148" s="267"/>
+      <c r="L148" s="267"/>
+      <c r="M148" s="267"/>
+      <c r="N148" s="267"/>
     </row>
     <row r="149" spans="3:16" x14ac:dyDescent="0.3">
-      <c r="C149" s="271"/>
-      <c r="D149" s="271"/>
-      <c r="E149" s="271"/>
-      <c r="F149" s="271"/>
-      <c r="G149" s="271"/>
-      <c r="H149" s="271"/>
-      <c r="I149" s="271"/>
-      <c r="J149" s="271"/>
-      <c r="K149" s="271"/>
-      <c r="L149" s="271"/>
-      <c r="M149" s="271"/>
-      <c r="N149" s="271"/>
+      <c r="C149" s="267"/>
+      <c r="D149" s="267"/>
+      <c r="E149" s="267"/>
+      <c r="F149" s="267"/>
+      <c r="G149" s="267"/>
+      <c r="H149" s="267"/>
+      <c r="I149" s="267"/>
+      <c r="J149" s="267"/>
+      <c r="K149" s="267"/>
+      <c r="L149" s="267"/>
+      <c r="M149" s="267"/>
+      <c r="N149" s="267"/>
     </row>
     <row r="150" spans="3:16" x14ac:dyDescent="0.3">
-      <c r="C150" s="271"/>
-      <c r="D150" s="271"/>
-      <c r="E150" s="271"/>
-      <c r="F150" s="271"/>
-      <c r="G150" s="271"/>
-      <c r="H150" s="271"/>
-      <c r="I150" s="271"/>
-      <c r="J150" s="271"/>
-      <c r="K150" s="271"/>
-      <c r="L150" s="271"/>
-      <c r="M150" s="271"/>
-      <c r="N150" s="271"/>
+      <c r="C150" s="267"/>
+      <c r="D150" s="267"/>
+      <c r="E150" s="267"/>
+      <c r="F150" s="267"/>
+      <c r="G150" s="267"/>
+      <c r="H150" s="267"/>
+      <c r="I150" s="267"/>
+      <c r="J150" s="267"/>
+      <c r="K150" s="267"/>
+      <c r="L150" s="267"/>
+      <c r="M150" s="267"/>
+      <c r="N150" s="267"/>
       <c r="P150" s="84">
         <f>L1-K133</f>
         <v>-3118989.9373000227</v>
       </c>
     </row>
     <row r="151" spans="3:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C151" s="271"/>
-      <c r="D151" s="271"/>
-      <c r="E151" s="271"/>
-      <c r="F151" s="271"/>
-      <c r="G151" s="271"/>
-      <c r="H151" s="271"/>
-      <c r="I151" s="271"/>
-      <c r="J151" s="271"/>
-      <c r="K151" s="271"/>
-      <c r="L151" s="271"/>
-      <c r="M151" s="271"/>
-      <c r="N151" s="271"/>
+      <c r="C151" s="267"/>
+      <c r="D151" s="267"/>
+      <c r="E151" s="267"/>
+      <c r="F151" s="267"/>
+      <c r="G151" s="267"/>
+      <c r="H151" s="267"/>
+      <c r="I151" s="267"/>
+      <c r="J151" s="267"/>
+      <c r="K151" s="267"/>
+      <c r="L151" s="267"/>
+      <c r="M151" s="267"/>
+      <c r="N151" s="267"/>
     </row>
     <row r="152" spans="3:16" ht="5.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C152" s="271"/>
-      <c r="D152" s="271"/>
-      <c r="E152" s="271"/>
-      <c r="F152" s="271"/>
-      <c r="G152" s="271"/>
-      <c r="H152" s="271"/>
-      <c r="I152" s="271"/>
-      <c r="J152" s="271"/>
-      <c r="K152" s="271"/>
-      <c r="L152" s="271"/>
-      <c r="M152" s="271"/>
-      <c r="N152" s="271"/>
+      <c r="C152" s="267"/>
+      <c r="D152" s="267"/>
+      <c r="E152" s="267"/>
+      <c r="F152" s="267"/>
+      <c r="G152" s="267"/>
+      <c r="H152" s="267"/>
+      <c r="I152" s="267"/>
+      <c r="J152" s="267"/>
+      <c r="K152" s="267"/>
+      <c r="L152" s="267"/>
+      <c r="M152" s="267"/>
+      <c r="N152" s="267"/>
     </row>
     <row r="153" spans="3:16" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C153" s="271"/>
-      <c r="D153" s="271"/>
-      <c r="E153" s="271"/>
-      <c r="F153" s="271"/>
-      <c r="G153" s="271"/>
-      <c r="H153" s="271"/>
-      <c r="I153" s="271"/>
-      <c r="J153" s="271"/>
-      <c r="K153" s="271"/>
-      <c r="L153" s="271"/>
-      <c r="M153" s="271"/>
-      <c r="N153" s="271"/>
+      <c r="C153" s="267"/>
+      <c r="D153" s="267"/>
+      <c r="E153" s="267"/>
+      <c r="F153" s="267"/>
+      <c r="G153" s="267"/>
+      <c r="H153" s="267"/>
+      <c r="I153" s="267"/>
+      <c r="J153" s="267"/>
+      <c r="K153" s="267"/>
+      <c r="L153" s="267"/>
+      <c r="M153" s="267"/>
+      <c r="N153" s="267"/>
     </row>
     <row r="154" spans="3:16" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C154" s="271"/>
-      <c r="D154" s="271"/>
-      <c r="E154" s="271"/>
-      <c r="F154" s="271"/>
-      <c r="G154" s="271"/>
-      <c r="H154" s="271"/>
-      <c r="I154" s="271"/>
-      <c r="J154" s="271"/>
-      <c r="K154" s="271"/>
-      <c r="L154" s="271"/>
-      <c r="M154" s="271"/>
-      <c r="N154" s="271"/>
+      <c r="C154" s="267"/>
+      <c r="D154" s="267"/>
+      <c r="E154" s="267"/>
+      <c r="F154" s="267"/>
+      <c r="G154" s="267"/>
+      <c r="H154" s="267"/>
+      <c r="I154" s="267"/>
+      <c r="J154" s="267"/>
+      <c r="K154" s="267"/>
+      <c r="L154" s="267"/>
+      <c r="M154" s="267"/>
+      <c r="N154" s="267"/>
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="A11:A13"/>
+    <mergeCell ref="B11:B13"/>
+    <mergeCell ref="C11:C13"/>
+    <mergeCell ref="D11:D13"/>
+    <mergeCell ref="F11:F13"/>
+    <mergeCell ref="E11:E13"/>
     <mergeCell ref="Q14:R15"/>
     <mergeCell ref="G11:G13"/>
     <mergeCell ref="C148:N154"/>
@@ -12737,12 +12743,6 @@
     <mergeCell ref="C5:N8"/>
     <mergeCell ref="C9:N10"/>
     <mergeCell ref="A1:E4"/>
-    <mergeCell ref="A11:A13"/>
-    <mergeCell ref="B11:B13"/>
-    <mergeCell ref="C11:C13"/>
-    <mergeCell ref="D11:D13"/>
-    <mergeCell ref="F11:F13"/>
-    <mergeCell ref="E11:E13"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12773,95 +12773,95 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="308" t="s">
+      <c r="A1" s="303" t="s">
+        <v>365</v>
+      </c>
+      <c r="B1" s="303"/>
+      <c r="C1" s="303"/>
+      <c r="D1" s="303"/>
+      <c r="E1" s="303"/>
+      <c r="F1" s="303"/>
+      <c r="G1" s="303"/>
+      <c r="H1" s="303"/>
+      <c r="I1" s="303"/>
+      <c r="J1" s="303"/>
+      <c r="K1" s="304"/>
+      <c r="N1" s="43"/>
+    </row>
+    <row r="2" spans="1:15" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="305"/>
+      <c r="B2" s="305"/>
+      <c r="C2" s="305"/>
+      <c r="D2" s="305"/>
+      <c r="E2" s="305"/>
+      <c r="F2" s="305"/>
+      <c r="G2" s="305"/>
+      <c r="H2" s="305"/>
+      <c r="I2" s="305"/>
+      <c r="J2" s="305"/>
+      <c r="K2" s="306"/>
+      <c r="N2" s="43"/>
+    </row>
+    <row r="3" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="265" t="s">
         <v>366</v>
       </c>
-      <c r="B1" s="308"/>
-      <c r="C1" s="308"/>
-      <c r="D1" s="308"/>
-      <c r="E1" s="308"/>
-      <c r="F1" s="308"/>
-      <c r="G1" s="308"/>
-      <c r="H1" s="308"/>
-      <c r="I1" s="308"/>
-      <c r="J1" s="308"/>
-      <c r="K1" s="309"/>
-      <c r="N1" s="43"/>
-    </row>
-    <row r="2" spans="1:15" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="310"/>
-      <c r="B2" s="310"/>
-      <c r="C2" s="310"/>
-      <c r="D2" s="310"/>
-      <c r="E2" s="310"/>
-      <c r="F2" s="310"/>
-      <c r="G2" s="310"/>
-      <c r="H2" s="310"/>
-      <c r="I2" s="310"/>
-      <c r="J2" s="310"/>
-      <c r="K2" s="311"/>
-      <c r="N2" s="43"/>
-    </row>
-    <row r="3" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="264" t="s">
+      <c r="B3" s="265" t="s">
         <v>367</v>
       </c>
-      <c r="B3" s="264" t="s">
-        <v>368</v>
-      </c>
-      <c r="C3" s="264" t="s">
+      <c r="C3" s="265" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="264" t="s">
+      <c r="D3" s="265" t="s">
         <v>27</v>
       </c>
-      <c r="E3" s="277" t="s">
+      <c r="E3" s="273" t="s">
+        <v>394</v>
+      </c>
+      <c r="F3" s="273" t="s">
         <v>395</v>
       </c>
-      <c r="F3" s="277" t="s">
+      <c r="G3" s="273" t="s">
+        <v>279</v>
+      </c>
+      <c r="H3" s="307" t="s">
         <v>396</v>
       </c>
-      <c r="G3" s="277" t="s">
-        <v>279</v>
-      </c>
-      <c r="H3" s="305" t="s">
+      <c r="I3" s="226"/>
+      <c r="J3" s="273" t="s">
         <v>397</v>
       </c>
-      <c r="I3" s="226"/>
-      <c r="J3" s="277" t="s">
-        <v>398</v>
-      </c>
-      <c r="K3" s="277" t="s">
+      <c r="K3" s="273" t="s">
         <v>17</v>
       </c>
       <c r="N3" s="43"/>
     </row>
     <row r="4" spans="1:15" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="265"/>
-      <c r="B4" s="265"/>
-      <c r="C4" s="265"/>
-      <c r="D4" s="265"/>
-      <c r="E4" s="278"/>
-      <c r="F4" s="278"/>
-      <c r="G4" s="278"/>
-      <c r="H4" s="306"/>
+      <c r="A4" s="266"/>
+      <c r="B4" s="266"/>
+      <c r="C4" s="266"/>
+      <c r="D4" s="266"/>
+      <c r="E4" s="274"/>
+      <c r="F4" s="274"/>
+      <c r="G4" s="274"/>
+      <c r="H4" s="308"/>
       <c r="I4" s="131"/>
-      <c r="J4" s="278"/>
-      <c r="K4" s="278"/>
+      <c r="J4" s="274"/>
+      <c r="K4" s="274"/>
       <c r="N4" s="43"/>
     </row>
     <row r="5" spans="1:15" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="304"/>
-      <c r="B5" s="304"/>
-      <c r="C5" s="304"/>
-      <c r="D5" s="304"/>
-      <c r="E5" s="303"/>
-      <c r="F5" s="303"/>
-      <c r="G5" s="303"/>
-      <c r="H5" s="307"/>
+      <c r="A5" s="311"/>
+      <c r="B5" s="311"/>
+      <c r="C5" s="311"/>
+      <c r="D5" s="311"/>
+      <c r="E5" s="310"/>
+      <c r="F5" s="310"/>
+      <c r="G5" s="310"/>
+      <c r="H5" s="309"/>
       <c r="I5" s="227"/>
-      <c r="J5" s="303"/>
-      <c r="K5" s="303"/>
+      <c r="J5" s="310"/>
+      <c r="K5" s="310"/>
       <c r="N5" s="43"/>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
@@ -12902,16 +12902,16 @@
       <c r="L6" s="115">
         <v>0.7</v>
       </c>
-      <c r="N6" s="270"/>
-      <c r="O6" s="270"/>
+      <c r="N6" s="264"/>
+      <c r="O6" s="264"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" s="228" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B7" s="229"/>
       <c r="C7" s="35" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="D7" s="143">
         <v>1.2800000000000001E-2</v>
@@ -12944,8 +12944,8 @@
         <f>L6+0.01</f>
         <v>0.71</v>
       </c>
-      <c r="N7" s="270"/>
-      <c r="O7" s="270"/>
+      <c r="N7" s="264"/>
+      <c r="O7" s="264"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" s="228" t="s">
@@ -12953,7 +12953,7 @@
       </c>
       <c r="B8" s="229"/>
       <c r="C8" s="231" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="D8" s="143">
         <v>1.21E-2</v>
@@ -13035,7 +13035,7 @@
       </c>
       <c r="B10" s="233"/>
       <c r="C10" s="234" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="D10" s="150">
         <v>1.7500000000000002E-2</v>
@@ -13200,7 +13200,7 @@
         <v>47</v>
       </c>
       <c r="B14" s="229" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C14" s="108" t="s">
         <v>180</v>
@@ -13282,7 +13282,7 @@
         <v>49</v>
       </c>
       <c r="B16" s="229" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C16" s="108" t="s">
         <v>182</v>
@@ -13324,10 +13324,10 @@
         <v>50</v>
       </c>
       <c r="B17" s="229" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C17" s="108" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="D17" s="136">
         <v>2.1100000000000001E-2</v>
@@ -13367,7 +13367,7 @@
       </c>
       <c r="B18" s="229"/>
       <c r="C18" s="108" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="D18" s="136">
         <v>7.4000000000000003E-3</v>
@@ -13487,7 +13487,7 @@
       </c>
       <c r="B21" s="229"/>
       <c r="C21" s="108" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="D21" s="136">
         <v>8.6999999999999994E-3</v>
@@ -13607,7 +13607,7 @@
       </c>
       <c r="B24" s="229"/>
       <c r="C24" s="108" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D24" s="136">
         <v>7.3000000000000001E-3</v>
@@ -13646,7 +13646,7 @@
         <v>58</v>
       </c>
       <c r="B25" s="237" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C25" s="108" t="s">
         <v>185</v>
@@ -13723,7 +13723,7 @@
         <v>0.16</v>
       </c>
       <c r="M26" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="27" spans="1:110" x14ac:dyDescent="0.3">
@@ -13732,7 +13732,7 @@
       </c>
       <c r="B27" s="229"/>
       <c r="C27" s="108" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="D27" s="136">
         <v>8.6999999999999994E-3</v>
@@ -13846,7 +13846,7 @@
         <v>0.19000000000000003</v>
       </c>
       <c r="M29" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="30" spans="1:110" x14ac:dyDescent="0.3">
@@ -14071,7 +14071,7 @@
         <v>0.22000000000000006</v>
       </c>
       <c r="M32" s="73" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="N32" s="73"/>
       <c r="O32" s="73"/>
@@ -14179,7 +14179,7 @@
         <v>31</v>
       </c>
       <c r="C33" s="108" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D33" s="136">
         <v>1.0999999999999999E-2</v>
@@ -14499,7 +14499,7 @@
       </c>
       <c r="B36" s="229"/>
       <c r="C36" s="108" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D36" s="136">
         <v>7.3000000000000001E-3</v>
@@ -14589,7 +14589,7 @@
         <v>44</v>
       </c>
       <c r="C38" s="108" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D38" s="136">
         <v>1.17E-2</v>
@@ -14669,7 +14669,7 @@
       </c>
       <c r="B40" s="229"/>
       <c r="C40" s="108" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="D40" s="136">
         <v>9.4999999999999998E-3</v>
@@ -14837,7 +14837,7 @@
       </c>
       <c r="B44" s="229"/>
       <c r="C44" s="108" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="D44" s="136">
         <v>9.4000000000000004E-3</v>
@@ -14880,7 +14880,7 @@
       </c>
       <c r="B45" s="229"/>
       <c r="C45" s="108" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D45" s="136">
         <v>8.6999999999999994E-3</v>
@@ -15125,7 +15125,7 @@
       </c>
       <c r="B51" s="229"/>
       <c r="C51" s="108" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="D51" s="136">
         <v>8.6999999999999994E-3</v>
@@ -15466,7 +15466,7 @@
         <v>4</v>
       </c>
       <c r="C59" s="108" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="D59" s="136">
         <v>1.8700000000000001E-2</v>
@@ -15629,7 +15629,7 @@
       </c>
       <c r="B63" s="229"/>
       <c r="C63" s="108" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="D63" s="136">
         <v>8.6999999999999994E-3</v>
@@ -15759,7 +15759,7 @@
         <v>41</v>
       </c>
       <c r="C66" s="108" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D66" s="136">
         <v>1.9699999999999999E-2</v>
@@ -15801,7 +15801,7 @@
         <v>2</v>
       </c>
       <c r="C67" s="108" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="D67" s="136">
         <v>1.17E-2</v>
@@ -16126,7 +16126,7 @@
         <v>9</v>
       </c>
       <c r="C75" s="108" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="D75" s="136">
         <v>2.58E-2</v>
@@ -16207,7 +16207,7 @@
         <v>110</v>
       </c>
       <c r="B77" s="229" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C77" s="108" t="s">
         <v>219</v>

--- a/2026/EL MIRADOR/Febrero/Febrero - EL MIRADOR.xlsx
+++ b/2026/EL MIRADOR/Febrero/Febrero - EL MIRADOR.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\EL MIRADOR\Febrero\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87127A66-1251-4F9F-A9BE-442137190BFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63891412-D89D-4CDD-BF2E-8BF57FA9359D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -2177,6 +2177,14 @@
     <xf numFmtId="44" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="4" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="14" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="0" fillId="14" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="14" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2222,14 +2230,35 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -2248,15 +2277,6 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2327,18 +2347,6 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="1" fontId="23" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2365,14 +2373,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="14" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="0" fillId="14" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="14" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -2897,108 +2897,108 @@
     <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="239" t="s">
+      <c r="A14" s="245" t="s">
         <v>258</v>
       </c>
-      <c r="B14" s="239"/>
-      <c r="C14" s="239"/>
-      <c r="D14" s="239"/>
-      <c r="E14" s="239"/>
-      <c r="F14" s="239"/>
-      <c r="G14" s="239"/>
-      <c r="H14" s="239"/>
-      <c r="I14" s="239"/>
-      <c r="J14" s="239"/>
+      <c r="B14" s="245"/>
+      <c r="C14" s="245"/>
+      <c r="D14" s="245"/>
+      <c r="E14" s="245"/>
+      <c r="F14" s="245"/>
+      <c r="G14" s="245"/>
+      <c r="H14" s="245"/>
+      <c r="I14" s="245"/>
+      <c r="J14" s="245"/>
     </row>
     <row r="15" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="239"/>
-      <c r="B15" s="239"/>
-      <c r="C15" s="239"/>
-      <c r="D15" s="239"/>
-      <c r="E15" s="239"/>
-      <c r="F15" s="239"/>
-      <c r="G15" s="239"/>
-      <c r="H15" s="239"/>
-      <c r="I15" s="239"/>
-      <c r="J15" s="239"/>
+      <c r="A15" s="245"/>
+      <c r="B15" s="245"/>
+      <c r="C15" s="245"/>
+      <c r="D15" s="245"/>
+      <c r="E15" s="245"/>
+      <c r="F15" s="245"/>
+      <c r="G15" s="245"/>
+      <c r="H15" s="245"/>
+      <c r="I15" s="245"/>
+      <c r="J15" s="245"/>
     </row>
     <row r="16" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="239"/>
-      <c r="B16" s="239"/>
-      <c r="C16" s="239"/>
-      <c r="D16" s="239"/>
-      <c r="E16" s="239"/>
-      <c r="F16" s="239"/>
-      <c r="G16" s="239"/>
-      <c r="H16" s="239"/>
-      <c r="I16" s="239"/>
-      <c r="J16" s="239"/>
+      <c r="A16" s="245"/>
+      <c r="B16" s="245"/>
+      <c r="C16" s="245"/>
+      <c r="D16" s="245"/>
+      <c r="E16" s="245"/>
+      <c r="F16" s="245"/>
+      <c r="G16" s="245"/>
+      <c r="H16" s="245"/>
+      <c r="I16" s="245"/>
+      <c r="J16" s="245"/>
     </row>
     <row r="17" spans="1:10" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="239"/>
-      <c r="B17" s="239"/>
-      <c r="C17" s="239"/>
-      <c r="D17" s="239"/>
-      <c r="E17" s="239"/>
-      <c r="F17" s="239"/>
-      <c r="G17" s="239"/>
-      <c r="H17" s="239"/>
-      <c r="I17" s="239"/>
-      <c r="J17" s="239"/>
+      <c r="A17" s="245"/>
+      <c r="B17" s="245"/>
+      <c r="C17" s="245"/>
+      <c r="D17" s="245"/>
+      <c r="E17" s="245"/>
+      <c r="F17" s="245"/>
+      <c r="G17" s="245"/>
+      <c r="H17" s="245"/>
+      <c r="I17" s="245"/>
+      <c r="J17" s="245"/>
     </row>
     <row r="18" spans="1:10" ht="47.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="239"/>
-      <c r="B18" s="239"/>
-      <c r="C18" s="239"/>
-      <c r="D18" s="239"/>
-      <c r="E18" s="239"/>
-      <c r="F18" s="239"/>
-      <c r="G18" s="239"/>
-      <c r="H18" s="239"/>
-      <c r="I18" s="239"/>
-      <c r="J18" s="239"/>
+      <c r="A18" s="245"/>
+      <c r="B18" s="245"/>
+      <c r="C18" s="245"/>
+      <c r="D18" s="245"/>
+      <c r="E18" s="245"/>
+      <c r="F18" s="245"/>
+      <c r="G18" s="245"/>
+      <c r="H18" s="245"/>
+      <c r="I18" s="245"/>
+      <c r="J18" s="245"/>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
       <c r="H19" s="94"/>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A20" s="248" t="s">
+      <c r="A20" s="254" t="s">
         <v>364</v>
       </c>
-      <c r="B20" s="248"/>
-      <c r="C20" s="248"/>
-      <c r="D20" s="248"/>
-      <c r="E20" s="248"/>
-      <c r="F20" s="248"/>
-      <c r="G20" s="248"/>
-      <c r="H20" s="248"/>
-      <c r="I20" s="248"/>
-      <c r="J20" s="248"/>
+      <c r="B20" s="254"/>
+      <c r="C20" s="254"/>
+      <c r="D20" s="254"/>
+      <c r="E20" s="254"/>
+      <c r="F20" s="254"/>
+      <c r="G20" s="254"/>
+      <c r="H20" s="254"/>
+      <c r="I20" s="254"/>
+      <c r="J20" s="254"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21" s="248"/>
-      <c r="B21" s="248"/>
-      <c r="C21" s="248"/>
-      <c r="D21" s="248"/>
-      <c r="E21" s="248"/>
-      <c r="F21" s="248"/>
-      <c r="G21" s="248"/>
-      <c r="H21" s="248"/>
-      <c r="I21" s="248"/>
-      <c r="J21" s="248"/>
+      <c r="A21" s="254"/>
+      <c r="B21" s="254"/>
+      <c r="C21" s="254"/>
+      <c r="D21" s="254"/>
+      <c r="E21" s="254"/>
+      <c r="F21" s="254"/>
+      <c r="G21" s="254"/>
+      <c r="H21" s="254"/>
+      <c r="I21" s="254"/>
+      <c r="J21" s="254"/>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A22" s="248"/>
-      <c r="B22" s="248"/>
-      <c r="C22" s="248"/>
-      <c r="D22" s="248"/>
-      <c r="E22" s="248"/>
-      <c r="F22" s="248"/>
-      <c r="G22" s="248"/>
-      <c r="H22" s="248"/>
-      <c r="I22" s="248"/>
-      <c r="J22" s="248"/>
+      <c r="A22" s="254"/>
+      <c r="B22" s="254"/>
+      <c r="C22" s="254"/>
+      <c r="D22" s="254"/>
+      <c r="E22" s="254"/>
+      <c r="F22" s="254"/>
+      <c r="G22" s="254"/>
+      <c r="H22" s="254"/>
+      <c r="I22" s="254"/>
+      <c r="J22" s="254"/>
     </row>
     <row r="23" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="H23" s="94"/>
@@ -3801,10 +3801,10 @@
       <c r="L62" s="69"/>
     </row>
     <row r="63" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="250" t="s">
+      <c r="A63" s="256" t="s">
         <v>232</v>
       </c>
-      <c r="B63" s="251"/>
+      <c r="B63" s="257"/>
       <c r="C63" s="35" t="s">
         <v>311</v>
       </c>
@@ -3844,10 +3844,10 @@
       </c>
     </row>
     <row r="64" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="250" t="s">
+      <c r="A64" s="256" t="s">
         <v>233</v>
       </c>
-      <c r="B64" s="251"/>
+      <c r="B64" s="257"/>
       <c r="C64" s="6" t="s">
         <v>381</v>
       </c>
@@ -4103,10 +4103,10 @@
       <c r="N70" s="84"/>
     </row>
     <row r="71" spans="1:14" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="246" t="s">
+      <c r="A71" s="252" t="s">
         <v>368</v>
       </c>
-      <c r="B71" s="252"/>
+      <c r="B71" s="258"/>
       <c r="C71" s="35"/>
       <c r="D71" s="44"/>
       <c r="E71" s="68">
@@ -4422,10 +4422,10 @@
       <c r="L80" s="69"/>
     </row>
     <row r="81" spans="1:14" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="250" t="s">
+      <c r="A81" s="256" t="s">
         <v>375</v>
       </c>
-      <c r="B81" s="251"/>
+      <c r="B81" s="257"/>
       <c r="C81" s="137" t="s">
         <v>376</v>
       </c>
@@ -4444,10 +4444,10 @@
       <c r="L81" s="69"/>
     </row>
     <row r="82" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="250" t="s">
+      <c r="A82" s="256" t="s">
         <v>377</v>
       </c>
-      <c r="B82" s="251"/>
+      <c r="B82" s="257"/>
       <c r="C82" s="137" t="s">
         <v>376</v>
       </c>
@@ -4481,10 +4481,10 @@
       <c r="L82" s="69"/>
     </row>
     <row r="83" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="250" t="s">
+      <c r="A83" s="256" t="s">
         <v>378</v>
       </c>
-      <c r="B83" s="251"/>
+      <c r="B83" s="257"/>
       <c r="C83" s="137" t="s">
         <v>318</v>
       </c>
@@ -5007,12 +5007,12 @@
       <c r="I105" s="60"/>
     </row>
     <row r="106" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A106" s="244" t="s">
+      <c r="A106" s="250" t="s">
         <v>34</v>
       </c>
-      <c r="B106" s="245"/>
-      <c r="C106" s="245"/>
-      <c r="D106" s="245"/>
+      <c r="B106" s="251"/>
+      <c r="C106" s="251"/>
+      <c r="D106" s="251"/>
       <c r="E106" s="80" t="s">
         <v>11</v>
       </c>
@@ -5033,8 +5033,8 @@
       </c>
     </row>
     <row r="107" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="246"/>
-      <c r="B107" s="247"/>
+      <c r="A107" s="252"/>
+      <c r="B107" s="253"/>
       <c r="C107" s="82"/>
       <c r="D107" s="44"/>
       <c r="E107" s="68">
@@ -5048,8 +5048,8 @@
       <c r="J107" s="58"/>
     </row>
     <row r="108" spans="1:13" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A108" s="246"/>
-      <c r="B108" s="247"/>
+      <c r="A108" s="252"/>
+      <c r="B108" s="253"/>
       <c r="C108" s="82"/>
       <c r="D108" s="44"/>
       <c r="E108" s="68"/>
@@ -5060,11 +5060,11 @@
       <c r="J108" s="58"/>
     </row>
     <row r="109" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A109" s="241" t="s">
+      <c r="A109" s="247" t="s">
         <v>17</v>
       </c>
-      <c r="B109" s="242"/>
-      <c r="C109" s="243"/>
+      <c r="B109" s="248"/>
+      <c r="C109" s="249"/>
       <c r="D109" s="79">
         <f>SUM(D107:D108)</f>
         <v>0</v>
@@ -5114,92 +5114,92 @@
         <f>D98-D96</f>
         <v>14242326.569999998</v>
       </c>
-      <c r="D113" s="249" t="s">
+      <c r="D113" s="255" t="s">
         <v>302</v>
       </c>
-      <c r="E113" s="249"/>
-      <c r="F113" s="249"/>
-      <c r="G113" s="249"/>
-      <c r="H113" s="249"/>
-      <c r="I113" s="249"/>
+      <c r="E113" s="255"/>
+      <c r="F113" s="255"/>
+      <c r="G113" s="255"/>
+      <c r="H113" s="255"/>
+      <c r="I113" s="255"/>
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="D114" s="249"/>
-      <c r="E114" s="249"/>
-      <c r="F114" s="249"/>
-      <c r="G114" s="249"/>
-      <c r="H114" s="249"/>
-      <c r="I114" s="249"/>
+      <c r="D114" s="255"/>
+      <c r="E114" s="255"/>
+      <c r="F114" s="255"/>
+      <c r="G114" s="255"/>
+      <c r="H114" s="255"/>
+      <c r="I114" s="255"/>
     </row>
     <row r="115" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A115" s="238" t="s">
+      <c r="A115" s="244" t="s">
         <v>384</v>
       </c>
-      <c r="B115" s="238"/>
-      <c r="D115" s="249"/>
-      <c r="E115" s="249"/>
-      <c r="F115" s="249"/>
-      <c r="G115" s="249"/>
-      <c r="H115" s="249"/>
-      <c r="I115" s="249"/>
+      <c r="B115" s="244"/>
+      <c r="D115" s="255"/>
+      <c r="E115" s="255"/>
+      <c r="F115" s="255"/>
+      <c r="G115" s="255"/>
+      <c r="H115" s="255"/>
+      <c r="I115" s="255"/>
     </row>
     <row r="116" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A116" s="238"/>
-      <c r="B116" s="238"/>
-      <c r="D116" s="249"/>
-      <c r="E116" s="249"/>
-      <c r="F116" s="249"/>
-      <c r="G116" s="249"/>
-      <c r="H116" s="249"/>
-      <c r="I116" s="249"/>
+      <c r="A116" s="244"/>
+      <c r="B116" s="244"/>
+      <c r="D116" s="255"/>
+      <c r="E116" s="255"/>
+      <c r="F116" s="255"/>
+      <c r="G116" s="255"/>
+      <c r="H116" s="255"/>
+      <c r="I116" s="255"/>
     </row>
     <row r="117" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A117" s="238"/>
-      <c r="B117" s="238"/>
-      <c r="D117" s="249"/>
-      <c r="E117" s="249"/>
-      <c r="F117" s="249"/>
-      <c r="G117" s="249"/>
-      <c r="H117" s="249"/>
-      <c r="I117" s="249"/>
+      <c r="A117" s="244"/>
+      <c r="B117" s="244"/>
+      <c r="D117" s="255"/>
+      <c r="E117" s="255"/>
+      <c r="F117" s="255"/>
+      <c r="G117" s="255"/>
+      <c r="H117" s="255"/>
+      <c r="I117" s="255"/>
     </row>
     <row r="118" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A118" s="238"/>
-      <c r="B118" s="238"/>
-      <c r="D118" s="249"/>
-      <c r="E118" s="249"/>
-      <c r="F118" s="249"/>
-      <c r="G118" s="249"/>
-      <c r="H118" s="249"/>
-      <c r="I118" s="249"/>
+      <c r="A118" s="244"/>
+      <c r="B118" s="244"/>
+      <c r="D118" s="255"/>
+      <c r="E118" s="255"/>
+      <c r="F118" s="255"/>
+      <c r="G118" s="255"/>
+      <c r="H118" s="255"/>
+      <c r="I118" s="255"/>
     </row>
     <row r="119" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A119" s="238"/>
-      <c r="B119" s="238"/>
-      <c r="D119" s="249"/>
-      <c r="E119" s="249"/>
-      <c r="F119" s="249"/>
-      <c r="G119" s="249"/>
-      <c r="H119" s="249"/>
-      <c r="I119" s="249"/>
+      <c r="A119" s="244"/>
+      <c r="B119" s="244"/>
+      <c r="D119" s="255"/>
+      <c r="E119" s="255"/>
+      <c r="F119" s="255"/>
+      <c r="G119" s="255"/>
+      <c r="H119" s="255"/>
+      <c r="I119" s="255"/>
     </row>
     <row r="120" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A120" s="238"/>
-      <c r="B120" s="238"/>
-      <c r="D120" s="249"/>
-      <c r="E120" s="249"/>
-      <c r="F120" s="249"/>
-      <c r="G120" s="249"/>
-      <c r="H120" s="249"/>
-      <c r="I120" s="249"/>
+      <c r="A120" s="244"/>
+      <c r="B120" s="244"/>
+      <c r="D120" s="255"/>
+      <c r="E120" s="255"/>
+      <c r="F120" s="255"/>
+      <c r="G120" s="255"/>
+      <c r="H120" s="255"/>
+      <c r="I120" s="255"/>
     </row>
     <row r="121" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="D121" s="249"/>
-      <c r="E121" s="249"/>
-      <c r="F121" s="249"/>
-      <c r="G121" s="249"/>
-      <c r="H121" s="249"/>
-      <c r="I121" s="249"/>
+      <c r="D121" s="255"/>
+      <c r="E121" s="255"/>
+      <c r="F121" s="255"/>
+      <c r="G121" s="255"/>
+      <c r="H121" s="255"/>
+      <c r="I121" s="255"/>
     </row>
     <row r="122" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A122" s="16" t="s">
@@ -5207,12 +5207,12 @@
       </c>
       <c r="B122" s="17"/>
       <c r="C122" s="18"/>
-      <c r="D122" s="249"/>
-      <c r="E122" s="249"/>
-      <c r="F122" s="249"/>
-      <c r="G122" s="249"/>
-      <c r="H122" s="249"/>
-      <c r="I122" s="249"/>
+      <c r="D122" s="255"/>
+      <c r="E122" s="255"/>
+      <c r="F122" s="255"/>
+      <c r="G122" s="255"/>
+      <c r="H122" s="255"/>
+      <c r="I122" s="255"/>
     </row>
     <row r="123" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A123" s="19" t="s">
@@ -5222,12 +5222,12 @@
         <v>1767072.6013971008</v>
       </c>
       <c r="C123" s="20"/>
-      <c r="D123" s="249"/>
-      <c r="E123" s="249"/>
-      <c r="F123" s="249"/>
-      <c r="G123" s="249"/>
-      <c r="H123" s="249"/>
-      <c r="I123" s="249"/>
+      <c r="D123" s="255"/>
+      <c r="E123" s="255"/>
+      <c r="F123" s="255"/>
+      <c r="G123" s="255"/>
+      <c r="H123" s="255"/>
+      <c r="I123" s="255"/>
     </row>
     <row r="124" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A124" s="21" t="s">
@@ -5240,12 +5240,12 @@
       <c r="C124" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="D124" s="249"/>
-      <c r="E124" s="249"/>
-      <c r="F124" s="249"/>
-      <c r="G124" s="249"/>
-      <c r="H124" s="249"/>
-      <c r="I124" s="249"/>
+      <c r="D124" s="255"/>
+      <c r="E124" s="255"/>
+      <c r="F124" s="255"/>
+      <c r="G124" s="255"/>
+      <c r="H124" s="255"/>
+      <c r="I124" s="255"/>
     </row>
     <row r="125" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A125" s="21" t="s">
@@ -5256,12 +5256,12 @@
         <v>-14242326.569999998</v>
       </c>
       <c r="C125" s="18"/>
-      <c r="D125" s="249"/>
-      <c r="E125" s="249"/>
-      <c r="F125" s="249"/>
-      <c r="G125" s="249"/>
-      <c r="H125" s="249"/>
-      <c r="I125" s="249"/>
+      <c r="D125" s="255"/>
+      <c r="E125" s="255"/>
+      <c r="F125" s="255"/>
+      <c r="G125" s="255"/>
+      <c r="H125" s="255"/>
+      <c r="I125" s="255"/>
       <c r="K125" s="44"/>
     </row>
     <row r="126" spans="1:11" x14ac:dyDescent="0.25">
@@ -5273,12 +5273,12 @@
         <v>0</v>
       </c>
       <c r="C126" s="18"/>
-      <c r="D126" s="249"/>
-      <c r="E126" s="249"/>
-      <c r="F126" s="249"/>
-      <c r="G126" s="249"/>
-      <c r="H126" s="249"/>
-      <c r="I126" s="249"/>
+      <c r="D126" s="255"/>
+      <c r="E126" s="255"/>
+      <c r="F126" s="255"/>
+      <c r="G126" s="255"/>
+      <c r="H126" s="255"/>
+      <c r="I126" s="255"/>
       <c r="K126" s="52"/>
     </row>
     <row r="127" spans="1:11" x14ac:dyDescent="0.25">
@@ -5290,12 +5290,12 @@
         <v>141730</v>
       </c>
       <c r="C127" s="18"/>
-      <c r="D127" s="249"/>
-      <c r="E127" s="249"/>
-      <c r="F127" s="249"/>
-      <c r="G127" s="249"/>
-      <c r="H127" s="249"/>
-      <c r="I127" s="249"/>
+      <c r="D127" s="255"/>
+      <c r="E127" s="255"/>
+      <c r="F127" s="255"/>
+      <c r="G127" s="255"/>
+      <c r="H127" s="255"/>
+      <c r="I127" s="255"/>
       <c r="K127" s="52"/>
     </row>
     <row r="128" spans="1:11" x14ac:dyDescent="0.25">
@@ -5307,12 +5307,12 @@
         <v>-145000</v>
       </c>
       <c r="C128" s="22"/>
-      <c r="D128" s="249"/>
-      <c r="E128" s="249"/>
-      <c r="F128" s="249"/>
-      <c r="G128" s="249"/>
-      <c r="H128" s="249"/>
-      <c r="I128" s="249"/>
+      <c r="D128" s="255"/>
+      <c r="E128" s="255"/>
+      <c r="F128" s="255"/>
+      <c r="G128" s="255"/>
+      <c r="H128" s="255"/>
+      <c r="I128" s="255"/>
     </row>
     <row r="129" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A129" s="21" t="s">
@@ -5323,12 +5323,12 @@
         <v>-87300</v>
       </c>
       <c r="C129" s="22"/>
-      <c r="D129" s="249"/>
-      <c r="E129" s="249"/>
-      <c r="F129" s="249"/>
-      <c r="G129" s="249"/>
-      <c r="H129" s="249"/>
-      <c r="I129" s="249"/>
+      <c r="D129" s="255"/>
+      <c r="E129" s="255"/>
+      <c r="F129" s="255"/>
+      <c r="G129" s="255"/>
+      <c r="H129" s="255"/>
+      <c r="I129" s="255"/>
     </row>
     <row r="130" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A130" s="21" t="s">
@@ -5339,23 +5339,23 @@
         <v>0</v>
       </c>
       <c r="C130" s="22"/>
-      <c r="D130" s="249"/>
-      <c r="E130" s="249"/>
-      <c r="F130" s="249"/>
-      <c r="G130" s="249"/>
-      <c r="H130" s="249"/>
-      <c r="I130" s="249"/>
+      <c r="D130" s="255"/>
+      <c r="E130" s="255"/>
+      <c r="F130" s="255"/>
+      <c r="G130" s="255"/>
+      <c r="H130" s="255"/>
+      <c r="I130" s="255"/>
     </row>
     <row r="131" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A131" s="21"/>
       <c r="B131" s="168"/>
       <c r="C131" s="22"/>
-      <c r="D131" s="249"/>
-      <c r="E131" s="249"/>
-      <c r="F131" s="249"/>
-      <c r="G131" s="249"/>
-      <c r="H131" s="249"/>
-      <c r="I131" s="249"/>
+      <c r="D131" s="255"/>
+      <c r="E131" s="255"/>
+      <c r="F131" s="255"/>
+      <c r="G131" s="255"/>
+      <c r="H131" s="255"/>
+      <c r="I131" s="255"/>
     </row>
     <row r="132" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A132" s="19" t="s">
@@ -5366,22 +5366,22 @@
         <v>1499395.7189351022</v>
       </c>
       <c r="C132" s="70"/>
-      <c r="D132" s="249"/>
-      <c r="E132" s="249"/>
-      <c r="F132" s="249"/>
-      <c r="G132" s="249"/>
-      <c r="H132" s="249"/>
-      <c r="I132" s="249"/>
+      <c r="D132" s="255"/>
+      <c r="E132" s="255"/>
+      <c r="F132" s="255"/>
+      <c r="G132" s="255"/>
+      <c r="H132" s="255"/>
+      <c r="I132" s="255"/>
     </row>
     <row r="133" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A133" s="22"/>
       <c r="C133" s="18"/>
-      <c r="D133" s="249"/>
-      <c r="E133" s="249"/>
-      <c r="F133" s="249"/>
-      <c r="G133" s="249"/>
-      <c r="H133" s="249"/>
-      <c r="I133" s="249"/>
+      <c r="D133" s="255"/>
+      <c r="E133" s="255"/>
+      <c r="F133" s="255"/>
+      <c r="G133" s="255"/>
+      <c r="H133" s="255"/>
+      <c r="I133" s="255"/>
     </row>
     <row r="134" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A134" s="16" t="s">
@@ -5389,12 +5389,12 @@
       </c>
       <c r="B134" s="8"/>
       <c r="C134" s="18"/>
-      <c r="D134" s="249"/>
-      <c r="E134" s="249"/>
-      <c r="F134" s="249"/>
-      <c r="G134" s="249"/>
-      <c r="H134" s="249"/>
-      <c r="I134" s="249"/>
+      <c r="D134" s="255"/>
+      <c r="E134" s="255"/>
+      <c r="F134" s="255"/>
+      <c r="G134" s="255"/>
+      <c r="H134" s="255"/>
+      <c r="I134" s="255"/>
     </row>
     <row r="135" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="19" t="s">
@@ -5500,50 +5500,50 @@
       <c r="R147" s="9"/>
     </row>
     <row r="150" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B150" s="240"/>
-      <c r="C150" s="240"/>
-      <c r="D150" s="240"/>
-      <c r="E150" s="240"/>
+      <c r="B150" s="246"/>
+      <c r="C150" s="246"/>
+      <c r="D150" s="246"/>
+      <c r="E150" s="246"/>
       <c r="F150" s="90"/>
       <c r="G150" s="90"/>
       <c r="H150" s="90"/>
       <c r="I150" s="90"/>
     </row>
     <row r="151" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B151" s="240"/>
-      <c r="C151" s="240"/>
-      <c r="D151" s="240"/>
-      <c r="E151" s="240"/>
+      <c r="B151" s="246"/>
+      <c r="C151" s="246"/>
+      <c r="D151" s="246"/>
+      <c r="E151" s="246"/>
       <c r="F151" s="90"/>
       <c r="G151" s="90"/>
       <c r="H151" s="90"/>
       <c r="I151" s="90"/>
     </row>
     <row r="152" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B152" s="240"/>
-      <c r="C152" s="240"/>
-      <c r="D152" s="240"/>
-      <c r="E152" s="240"/>
+      <c r="B152" s="246"/>
+      <c r="C152" s="246"/>
+      <c r="D152" s="246"/>
+      <c r="E152" s="246"/>
       <c r="F152" s="90"/>
       <c r="G152" s="90"/>
       <c r="H152" s="90"/>
       <c r="I152" s="90"/>
     </row>
     <row r="153" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B153" s="240"/>
-      <c r="C153" s="240"/>
-      <c r="D153" s="240"/>
-      <c r="E153" s="240"/>
+      <c r="B153" s="246"/>
+      <c r="C153" s="246"/>
+      <c r="D153" s="246"/>
+      <c r="E153" s="246"/>
       <c r="F153" s="90"/>
       <c r="G153" s="90"/>
       <c r="H153" s="90"/>
       <c r="I153" s="90"/>
     </row>
     <row r="154" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B154" s="240"/>
-      <c r="C154" s="240"/>
-      <c r="D154" s="240"/>
-      <c r="E154" s="240"/>
+      <c r="B154" s="246"/>
+      <c r="C154" s="246"/>
+      <c r="D154" s="246"/>
+      <c r="E154" s="246"/>
       <c r="F154" s="90"/>
       <c r="G154" s="90"/>
       <c r="H154" s="90"/>
@@ -5599,13 +5599,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A1" s="282" t="s">
+      <c r="A1" s="292" t="s">
         <v>327</v>
       </c>
-      <c r="B1" s="283"/>
-      <c r="C1" s="283"/>
-      <c r="D1" s="283"/>
-      <c r="E1" s="283"/>
+      <c r="B1" s="293"/>
+      <c r="C1" s="293"/>
+      <c r="D1" s="293"/>
+      <c r="E1" s="293"/>
       <c r="F1" s="158" t="s">
         <v>293</v>
       </c>
@@ -5617,20 +5617,20 @@
       <c r="L1" s="190" t="s">
         <v>41</v>
       </c>
-      <c r="M1" s="258">
+      <c r="M1" s="271">
         <f>RESUMEN!D98-RESUMEN!D96</f>
         <v>14242326.569999998</v>
       </c>
-      <c r="N1" s="259"/>
+      <c r="N1" s="272"/>
       <c r="O1" s="159"/>
       <c r="P1" s="59"/>
     </row>
     <row r="2" spans="1:19" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="284"/>
-      <c r="B2" s="285"/>
-      <c r="C2" s="285"/>
-      <c r="D2" s="285"/>
-      <c r="E2" s="285"/>
+      <c r="A2" s="294"/>
+      <c r="B2" s="295"/>
+      <c r="C2" s="295"/>
+      <c r="D2" s="295"/>
+      <c r="E2" s="295"/>
       <c r="F2" s="7" t="s">
         <v>292</v>
       </c>
@@ -5650,11 +5650,11 @@
       <c r="P2" s="59"/>
     </row>
     <row r="3" spans="1:19" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="284"/>
-      <c r="B3" s="285"/>
-      <c r="C3" s="285"/>
-      <c r="D3" s="285"/>
-      <c r="E3" s="285"/>
+      <c r="A3" s="294"/>
+      <c r="B3" s="295"/>
+      <c r="C3" s="295"/>
+      <c r="D3" s="295"/>
+      <c r="E3" s="295"/>
       <c r="F3" s="7" t="s">
         <v>294</v>
       </c>
@@ -5667,7 +5667,7 @@
         <v>390</v>
       </c>
       <c r="M3" s="7"/>
-      <c r="N3" s="306">
+      <c r="N3" s="243">
         <f>5359814.2</f>
         <v>5359814.2</v>
       </c>
@@ -5675,11 +5675,11 @@
       <c r="P3" s="15"/>
     </row>
     <row r="4" spans="1:19" ht="2.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="286"/>
-      <c r="B4" s="287"/>
-      <c r="C4" s="287"/>
-      <c r="D4" s="287"/>
-      <c r="E4" s="287"/>
+      <c r="A4" s="296"/>
+      <c r="B4" s="297"/>
+      <c r="C4" s="297"/>
+      <c r="D4" s="297"/>
+      <c r="E4" s="297"/>
       <c r="F4" s="163"/>
       <c r="G4" s="163"/>
       <c r="H4" s="163"/>
@@ -5695,95 +5695,95 @@
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="7"/>
       <c r="B5" s="7"/>
-      <c r="C5" s="267" t="s">
+      <c r="C5" s="277" t="s">
         <v>310</v>
       </c>
-      <c r="D5" s="268"/>
-      <c r="E5" s="268"/>
-      <c r="F5" s="268"/>
-      <c r="G5" s="268"/>
-      <c r="H5" s="268"/>
-      <c r="I5" s="268"/>
-      <c r="J5" s="268"/>
-      <c r="K5" s="268"/>
-      <c r="L5" s="268"/>
-      <c r="M5" s="268"/>
-      <c r="N5" s="268"/>
-      <c r="O5" s="269"/>
+      <c r="D5" s="278"/>
+      <c r="E5" s="278"/>
+      <c r="F5" s="278"/>
+      <c r="G5" s="278"/>
+      <c r="H5" s="278"/>
+      <c r="I5" s="278"/>
+      <c r="J5" s="278"/>
+      <c r="K5" s="278"/>
+      <c r="L5" s="278"/>
+      <c r="M5" s="278"/>
+      <c r="N5" s="278"/>
+      <c r="O5" s="279"/>
       <c r="P5" s="15"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="7"/>
       <c r="B6" s="7"/>
-      <c r="C6" s="270"/>
-      <c r="D6" s="271"/>
-      <c r="E6" s="271"/>
-      <c r="F6" s="271"/>
-      <c r="G6" s="271"/>
-      <c r="H6" s="271"/>
-      <c r="I6" s="271"/>
-      <c r="J6" s="271"/>
-      <c r="K6" s="271"/>
-      <c r="L6" s="271"/>
-      <c r="M6" s="271"/>
-      <c r="N6" s="271"/>
-      <c r="O6" s="272"/>
+      <c r="C6" s="280"/>
+      <c r="D6" s="281"/>
+      <c r="E6" s="281"/>
+      <c r="F6" s="281"/>
+      <c r="G6" s="281"/>
+      <c r="H6" s="281"/>
+      <c r="I6" s="281"/>
+      <c r="J6" s="281"/>
+      <c r="K6" s="281"/>
+      <c r="L6" s="281"/>
+      <c r="M6" s="281"/>
+      <c r="N6" s="281"/>
+      <c r="O6" s="282"/>
       <c r="P6" s="15"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="7"/>
       <c r="B7" s="7"/>
-      <c r="C7" s="270"/>
-      <c r="D7" s="271"/>
-      <c r="E7" s="271"/>
-      <c r="F7" s="271"/>
-      <c r="G7" s="271"/>
-      <c r="H7" s="271"/>
-      <c r="I7" s="271"/>
-      <c r="J7" s="271"/>
-      <c r="K7" s="271"/>
-      <c r="L7" s="271"/>
-      <c r="M7" s="271"/>
-      <c r="N7" s="271"/>
-      <c r="O7" s="272"/>
+      <c r="C7" s="280"/>
+      <c r="D7" s="281"/>
+      <c r="E7" s="281"/>
+      <c r="F7" s="281"/>
+      <c r="G7" s="281"/>
+      <c r="H7" s="281"/>
+      <c r="I7" s="281"/>
+      <c r="J7" s="281"/>
+      <c r="K7" s="281"/>
+      <c r="L7" s="281"/>
+      <c r="M7" s="281"/>
+      <c r="N7" s="281"/>
+      <c r="O7" s="282"/>
       <c r="P7" s="15"/>
     </row>
     <row r="8" spans="1:19" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="7"/>
       <c r="B8" s="7"/>
-      <c r="C8" s="273"/>
-      <c r="D8" s="274"/>
-      <c r="E8" s="274"/>
-      <c r="F8" s="274"/>
-      <c r="G8" s="274"/>
-      <c r="H8" s="274"/>
-      <c r="I8" s="274"/>
-      <c r="J8" s="274"/>
-      <c r="K8" s="274"/>
-      <c r="L8" s="274"/>
-      <c r="M8" s="274"/>
-      <c r="N8" s="274"/>
-      <c r="O8" s="275"/>
+      <c r="C8" s="283"/>
+      <c r="D8" s="284"/>
+      <c r="E8" s="284"/>
+      <c r="F8" s="284"/>
+      <c r="G8" s="284"/>
+      <c r="H8" s="284"/>
+      <c r="I8" s="284"/>
+      <c r="J8" s="284"/>
+      <c r="K8" s="284"/>
+      <c r="L8" s="284"/>
+      <c r="M8" s="284"/>
+      <c r="N8" s="284"/>
+      <c r="O8" s="285"/>
       <c r="Q8" s="84"/>
     </row>
     <row r="9" spans="1:19" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
-      <c r="C9" s="276" t="s">
+      <c r="C9" s="286" t="s">
         <v>308</v>
       </c>
-      <c r="D9" s="277"/>
-      <c r="E9" s="277"/>
-      <c r="F9" s="277"/>
-      <c r="G9" s="277"/>
-      <c r="H9" s="277"/>
-      <c r="I9" s="277"/>
-      <c r="J9" s="277"/>
-      <c r="K9" s="277"/>
-      <c r="L9" s="277"/>
-      <c r="M9" s="277"/>
-      <c r="N9" s="277"/>
-      <c r="O9" s="278"/>
+      <c r="D9" s="287"/>
+      <c r="E9" s="287"/>
+      <c r="F9" s="287"/>
+      <c r="G9" s="287"/>
+      <c r="H9" s="287"/>
+      <c r="I9" s="287"/>
+      <c r="J9" s="287"/>
+      <c r="K9" s="287"/>
+      <c r="L9" s="287"/>
+      <c r="M9" s="287"/>
+      <c r="N9" s="287"/>
+      <c r="O9" s="288"/>
       <c r="Q9" t="s">
         <v>248</v>
       </c>
@@ -5795,19 +5795,19 @@
     <row r="10" spans="1:19" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="7"/>
       <c r="B10" s="7"/>
-      <c r="C10" s="279"/>
-      <c r="D10" s="280"/>
-      <c r="E10" s="280"/>
-      <c r="F10" s="280"/>
-      <c r="G10" s="280"/>
-      <c r="H10" s="280"/>
-      <c r="I10" s="280"/>
-      <c r="J10" s="280"/>
-      <c r="K10" s="280"/>
-      <c r="L10" s="280"/>
-      <c r="M10" s="280"/>
-      <c r="N10" s="280"/>
-      <c r="O10" s="281"/>
+      <c r="C10" s="289"/>
+      <c r="D10" s="290"/>
+      <c r="E10" s="290"/>
+      <c r="F10" s="290"/>
+      <c r="G10" s="290"/>
+      <c r="H10" s="290"/>
+      <c r="I10" s="290"/>
+      <c r="J10" s="290"/>
+      <c r="K10" s="290"/>
+      <c r="L10" s="290"/>
+      <c r="M10" s="290"/>
+      <c r="N10" s="290"/>
+      <c r="O10" s="291"/>
       <c r="Q10" t="s">
         <v>249</v>
       </c>
@@ -5817,49 +5817,49 @@
       </c>
     </row>
     <row r="11" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="254" t="s">
+      <c r="A11" s="262" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="288" t="s">
+      <c r="B11" s="264" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="254" t="s">
+      <c r="C11" s="262" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="290" t="s">
+      <c r="D11" s="266" t="s">
         <v>12</v>
       </c>
-      <c r="E11" s="290" t="s">
+      <c r="E11" s="266" t="s">
         <v>266</v>
       </c>
-      <c r="F11" s="254" t="s">
+      <c r="F11" s="262" t="s">
         <v>27</v>
       </c>
-      <c r="G11" s="254" t="s">
+      <c r="G11" s="262" t="s">
         <v>13</v>
       </c>
-      <c r="H11" s="254" t="s">
+      <c r="H11" s="262" t="s">
         <v>14</v>
       </c>
-      <c r="I11" s="260" t="s">
+      <c r="I11" s="273" t="s">
         <v>15</v>
       </c>
-      <c r="J11" s="262" t="s">
+      <c r="J11" s="259" t="s">
         <v>16</v>
       </c>
-      <c r="K11" s="262" t="s">
+      <c r="K11" s="259" t="s">
         <v>391</v>
       </c>
-      <c r="L11" s="262" t="s">
+      <c r="L11" s="259" t="s">
         <v>18</v>
       </c>
-      <c r="M11" s="265" t="s">
+      <c r="M11" s="275" t="s">
         <v>40</v>
       </c>
-      <c r="N11" s="262" t="s">
+      <c r="N11" s="259" t="s">
         <v>277</v>
       </c>
-      <c r="O11" s="262" t="s">
+      <c r="O11" s="259" t="s">
         <v>276</v>
       </c>
       <c r="Q11" t="s">
@@ -5871,21 +5871,21 @@
       </c>
     </row>
     <row r="12" spans="1:19" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="255"/>
-      <c r="B12" s="289"/>
-      <c r="C12" s="255"/>
-      <c r="D12" s="291"/>
-      <c r="E12" s="291"/>
-      <c r="F12" s="255"/>
-      <c r="G12" s="255"/>
-      <c r="H12" s="255"/>
-      <c r="I12" s="261"/>
-      <c r="J12" s="263"/>
-      <c r="K12" s="263"/>
-      <c r="L12" s="263"/>
-      <c r="M12" s="266"/>
-      <c r="N12" s="263"/>
-      <c r="O12" s="263"/>
+      <c r="A12" s="263"/>
+      <c r="B12" s="265"/>
+      <c r="C12" s="263"/>
+      <c r="D12" s="267"/>
+      <c r="E12" s="267"/>
+      <c r="F12" s="263"/>
+      <c r="G12" s="263"/>
+      <c r="H12" s="263"/>
+      <c r="I12" s="274"/>
+      <c r="J12" s="260"/>
+      <c r="K12" s="260"/>
+      <c r="L12" s="260"/>
+      <c r="M12" s="276"/>
+      <c r="N12" s="260"/>
+      <c r="O12" s="260"/>
       <c r="Q12" t="s">
         <v>251</v>
       </c>
@@ -5895,19 +5895,19 @@
       </c>
     </row>
     <row r="13" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="255"/>
-      <c r="B13" s="289"/>
-      <c r="C13" s="255"/>
-      <c r="D13" s="291"/>
-      <c r="E13" s="291"/>
-      <c r="F13" s="255"/>
-      <c r="G13" s="255"/>
-      <c r="H13" s="255"/>
-      <c r="I13" s="261"/>
-      <c r="J13" s="263"/>
-      <c r="K13" s="264"/>
-      <c r="L13" s="264"/>
-      <c r="M13" s="266"/>
+      <c r="A13" s="263"/>
+      <c r="B13" s="265"/>
+      <c r="C13" s="263"/>
+      <c r="D13" s="267"/>
+      <c r="E13" s="267"/>
+      <c r="F13" s="263"/>
+      <c r="G13" s="263"/>
+      <c r="H13" s="263"/>
+      <c r="I13" s="274"/>
+      <c r="J13" s="260"/>
+      <c r="K13" s="261"/>
+      <c r="L13" s="261"/>
+      <c r="M13" s="276"/>
       <c r="N13" s="132" t="str">
         <f>RESUMEN!A20</f>
         <v>VTO 13/03</v>
@@ -5971,8 +5971,8 @@
         <v>594272.46717576019</v>
       </c>
       <c r="P14" s="115"/>
-      <c r="R14" s="253"/>
-      <c r="S14" s="253"/>
+      <c r="R14" s="268"/>
+      <c r="S14" s="268"/>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15" s="6"/>
@@ -6020,8 +6020,8 @@
         <v>181138.91659008001</v>
       </c>
       <c r="P15" s="115"/>
-      <c r="R15" s="253"/>
-      <c r="S15" s="253"/>
+      <c r="R15" s="268"/>
+      <c r="S15" s="268"/>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
@@ -6140,7 +6140,7 @@
       <c r="G18" s="151">
         <v>228343.11798000001</v>
       </c>
-      <c r="H18" s="303"/>
+      <c r="H18" s="240"/>
       <c r="I18" s="152">
         <f t="shared" si="1"/>
         <v>228343.11798000001</v>
@@ -6187,7 +6187,7 @@
       <c r="G19" s="184">
         <v>294543.01</v>
       </c>
-      <c r="H19" s="304">
+      <c r="H19" s="241">
         <v>312216.01</v>
       </c>
       <c r="I19" s="185">
@@ -6351,7 +6351,7 @@
       <c r="G22" s="198">
         <v>146494.04</v>
       </c>
-      <c r="H22" s="305">
+      <c r="H22" s="242">
         <v>147272</v>
       </c>
       <c r="I22" s="199">
@@ -6362,7 +6362,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="K22" s="301">
+      <c r="K22" s="238">
         <f t="shared" si="7"/>
         <v>50382.253480000007</v>
       </c>
@@ -6373,7 +6373,7 @@
       <c r="M22" s="201">
         <v>0</v>
       </c>
-      <c r="N22" s="302">
+      <c r="N22" s="239">
         <f t="shared" si="9"/>
         <v>143604.04</v>
       </c>
@@ -6628,7 +6628,7 @@
       <c r="G27" s="198">
         <v>316248.09000000003</v>
       </c>
-      <c r="H27" s="305"/>
+      <c r="H27" s="242"/>
       <c r="I27" s="199">
         <f t="shared" si="1"/>
         <v>316248.09000000003</v>
@@ -6637,7 +6637,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="K27" s="301">
+      <c r="K27" s="238">
         <f t="shared" si="7"/>
         <v>95404.692760000005</v>
       </c>
@@ -6648,7 +6648,7 @@
       <c r="M27" s="201">
         <v>0</v>
       </c>
-      <c r="N27" s="302">
+      <c r="N27" s="239">
         <f t="shared" si="9"/>
         <v>589653.09</v>
       </c>
@@ -8652,7 +8652,7 @@
       <c r="G57" s="198">
         <v>271043.39</v>
       </c>
-      <c r="H57" s="305"/>
+      <c r="H57" s="242"/>
       <c r="I57" s="199">
         <f t="shared" si="1"/>
         <v>271043.39</v>
@@ -8661,7 +8661,7 @@
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="K57" s="301">
+      <c r="K57" s="238">
         <f t="shared" si="7"/>
         <v>92724.785659999994</v>
       </c>
@@ -8672,7 +8672,7 @@
       <c r="M57" s="201">
         <v>0</v>
       </c>
-      <c r="N57" s="302">
+      <c r="N57" s="239">
         <f t="shared" si="9"/>
         <v>536768.39</v>
       </c>
@@ -9960,7 +9960,7 @@
       <c r="G81" s="198">
         <v>156305.63</v>
       </c>
-      <c r="H81" s="305">
+      <c r="H81" s="242">
         <f t="shared" ref="H81:H82" si="29">G81</f>
         <v>156305.63</v>
       </c>
@@ -9972,7 +9972,7 @@
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="K81" s="301">
+      <c r="K81" s="238">
         <f t="shared" si="7"/>
         <v>46630.383539999995</v>
       </c>
@@ -9983,7 +9983,7 @@
       <c r="M81" s="201">
         <v>0</v>
       </c>
-      <c r="N81" s="302">
+      <c r="N81" s="239">
         <f t="shared" si="9"/>
         <v>133630.63</v>
       </c>
@@ -11889,7 +11889,7 @@
       <c r="G118" s="198">
         <v>36036</v>
       </c>
-      <c r="H118" s="305">
+      <c r="H118" s="242">
         <f t="shared" ref="H118:H120" si="48">G118</f>
         <v>36036</v>
       </c>
@@ -11901,7 +11901,7 @@
         <f t="shared" si="46"/>
         <v>0</v>
       </c>
-      <c r="K118" s="301">
+      <c r="K118" s="238">
         <f t="shared" si="33"/>
         <v>12327.57266</v>
       </c>
@@ -11912,7 +11912,7 @@
       <c r="M118" s="201">
         <v>0</v>
       </c>
-      <c r="N118" s="302">
+      <c r="N118" s="239">
         <f t="shared" si="34"/>
         <v>35329</v>
       </c>
@@ -12675,34 +12675,34 @@
       </c>
     </row>
     <row r="135" spans="1:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C135" s="257"/>
-      <c r="D135" s="257"/>
-      <c r="E135" s="257"/>
-      <c r="F135" s="257"/>
-      <c r="G135" s="257"/>
-      <c r="H135" s="257"/>
-      <c r="I135" s="257"/>
-      <c r="J135" s="257"/>
-      <c r="K135" s="257"/>
-      <c r="L135" s="257"/>
-      <c r="M135" s="257"/>
-      <c r="N135" s="257"/>
-      <c r="O135" s="257"/>
+      <c r="C135" s="270"/>
+      <c r="D135" s="270"/>
+      <c r="E135" s="270"/>
+      <c r="F135" s="270"/>
+      <c r="G135" s="270"/>
+      <c r="H135" s="270"/>
+      <c r="I135" s="270"/>
+      <c r="J135" s="270"/>
+      <c r="K135" s="270"/>
+      <c r="L135" s="270"/>
+      <c r="M135" s="270"/>
+      <c r="N135" s="270"/>
+      <c r="O135" s="270"/>
     </row>
     <row r="136" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C136" s="257"/>
-      <c r="D136" s="257"/>
-      <c r="E136" s="257"/>
-      <c r="F136" s="257"/>
-      <c r="G136" s="257"/>
-      <c r="H136" s="257"/>
-      <c r="I136" s="257"/>
-      <c r="J136" s="257"/>
-      <c r="K136" s="257"/>
-      <c r="L136" s="257"/>
-      <c r="M136" s="257"/>
-      <c r="N136" s="257"/>
-      <c r="O136" s="257"/>
+      <c r="C136" s="270"/>
+      <c r="D136" s="270"/>
+      <c r="E136" s="270"/>
+      <c r="F136" s="270"/>
+      <c r="G136" s="270"/>
+      <c r="H136" s="270"/>
+      <c r="I136" s="270"/>
+      <c r="J136" s="270"/>
+      <c r="K136" s="270"/>
+      <c r="L136" s="270"/>
+      <c r="M136" s="270"/>
+      <c r="N136" s="270"/>
+      <c r="O136" s="270"/>
     </row>
     <row r="137" spans="1:17" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C137" s="77"/>
@@ -12720,126 +12720,126 @@
       <c r="O137" s="77"/>
     </row>
     <row r="138" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="C138" s="238" t="s">
+      <c r="C138" s="244" t="s">
         <v>258</v>
       </c>
-      <c r="D138" s="238"/>
-      <c r="E138" s="238"/>
-      <c r="F138" s="238"/>
-      <c r="G138" s="238"/>
-      <c r="H138" s="238"/>
-      <c r="I138" s="238"/>
-      <c r="J138" s="238"/>
-      <c r="K138" s="238"/>
-      <c r="L138" s="238"/>
-      <c r="M138" s="238"/>
-      <c r="N138" s="238"/>
-      <c r="O138" s="238"/>
+      <c r="D138" s="244"/>
+      <c r="E138" s="244"/>
+      <c r="F138" s="244"/>
+      <c r="G138" s="244"/>
+      <c r="H138" s="244"/>
+      <c r="I138" s="244"/>
+      <c r="J138" s="244"/>
+      <c r="K138" s="244"/>
+      <c r="L138" s="244"/>
+      <c r="M138" s="244"/>
+      <c r="N138" s="244"/>
+      <c r="O138" s="244"/>
     </row>
     <row r="139" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="C139" s="238"/>
-      <c r="D139" s="238"/>
-      <c r="E139" s="238"/>
-      <c r="F139" s="238"/>
-      <c r="G139" s="238"/>
-      <c r="H139" s="238"/>
-      <c r="I139" s="238"/>
-      <c r="J139" s="238"/>
-      <c r="K139" s="238"/>
-      <c r="L139" s="238"/>
-      <c r="M139" s="238"/>
-      <c r="N139" s="238"/>
-      <c r="O139" s="238"/>
+      <c r="C139" s="244"/>
+      <c r="D139" s="244"/>
+      <c r="E139" s="244"/>
+      <c r="F139" s="244"/>
+      <c r="G139" s="244"/>
+      <c r="H139" s="244"/>
+      <c r="I139" s="244"/>
+      <c r="J139" s="244"/>
+      <c r="K139" s="244"/>
+      <c r="L139" s="244"/>
+      <c r="M139" s="244"/>
+      <c r="N139" s="244"/>
+      <c r="O139" s="244"/>
     </row>
     <row r="140" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="C140" s="238"/>
-      <c r="D140" s="238"/>
-      <c r="E140" s="238"/>
-      <c r="F140" s="238"/>
-      <c r="G140" s="238"/>
-      <c r="H140" s="238"/>
-      <c r="I140" s="238"/>
-      <c r="J140" s="238"/>
-      <c r="K140" s="238"/>
-      <c r="L140" s="238"/>
-      <c r="M140" s="238"/>
-      <c r="N140" s="238"/>
-      <c r="O140" s="238"/>
+      <c r="C140" s="244"/>
+      <c r="D140" s="244"/>
+      <c r="E140" s="244"/>
+      <c r="F140" s="244"/>
+      <c r="G140" s="244"/>
+      <c r="H140" s="244"/>
+      <c r="I140" s="244"/>
+      <c r="J140" s="244"/>
+      <c r="K140" s="244"/>
+      <c r="L140" s="244"/>
+      <c r="M140" s="244"/>
+      <c r="N140" s="244"/>
+      <c r="O140" s="244"/>
     </row>
     <row r="141" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="C141" s="238"/>
-      <c r="D141" s="238"/>
-      <c r="E141" s="238"/>
-      <c r="F141" s="238"/>
-      <c r="G141" s="238"/>
-      <c r="H141" s="238"/>
-      <c r="I141" s="238"/>
-      <c r="J141" s="238"/>
-      <c r="K141" s="238"/>
-      <c r="L141" s="238"/>
-      <c r="M141" s="238"/>
-      <c r="N141" s="238"/>
-      <c r="O141" s="238"/>
+      <c r="C141" s="244"/>
+      <c r="D141" s="244"/>
+      <c r="E141" s="244"/>
+      <c r="F141" s="244"/>
+      <c r="G141" s="244"/>
+      <c r="H141" s="244"/>
+      <c r="I141" s="244"/>
+      <c r="J141" s="244"/>
+      <c r="K141" s="244"/>
+      <c r="L141" s="244"/>
+      <c r="M141" s="244"/>
+      <c r="N141" s="244"/>
+      <c r="O141" s="244"/>
     </row>
     <row r="142" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="C142" s="238"/>
-      <c r="D142" s="238"/>
-      <c r="E142" s="238"/>
-      <c r="F142" s="238"/>
-      <c r="G142" s="238"/>
-      <c r="H142" s="238"/>
-      <c r="I142" s="238"/>
-      <c r="J142" s="238"/>
-      <c r="K142" s="238"/>
-      <c r="L142" s="238"/>
-      <c r="M142" s="238"/>
-      <c r="N142" s="238"/>
-      <c r="O142" s="238"/>
+      <c r="C142" s="244"/>
+      <c r="D142" s="244"/>
+      <c r="E142" s="244"/>
+      <c r="F142" s="244"/>
+      <c r="G142" s="244"/>
+      <c r="H142" s="244"/>
+      <c r="I142" s="244"/>
+      <c r="J142" s="244"/>
+      <c r="K142" s="244"/>
+      <c r="L142" s="244"/>
+      <c r="M142" s="244"/>
+      <c r="N142" s="244"/>
+      <c r="O142" s="244"/>
     </row>
     <row r="143" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="C143" s="238"/>
-      <c r="D143" s="238"/>
-      <c r="E143" s="238"/>
-      <c r="F143" s="238"/>
-      <c r="G143" s="238"/>
-      <c r="H143" s="238"/>
-      <c r="I143" s="238"/>
-      <c r="J143" s="238"/>
-      <c r="K143" s="238"/>
-      <c r="L143" s="238"/>
-      <c r="M143" s="238"/>
-      <c r="N143" s="238"/>
-      <c r="O143" s="238"/>
+      <c r="C143" s="244"/>
+      <c r="D143" s="244"/>
+      <c r="E143" s="244"/>
+      <c r="F143" s="244"/>
+      <c r="G143" s="244"/>
+      <c r="H143" s="244"/>
+      <c r="I143" s="244"/>
+      <c r="J143" s="244"/>
+      <c r="K143" s="244"/>
+      <c r="L143" s="244"/>
+      <c r="M143" s="244"/>
+      <c r="N143" s="244"/>
+      <c r="O143" s="244"/>
     </row>
     <row r="144" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="C144" s="238"/>
-      <c r="D144" s="238"/>
-      <c r="E144" s="238"/>
-      <c r="F144" s="238"/>
-      <c r="G144" s="238"/>
-      <c r="H144" s="238"/>
-      <c r="I144" s="238"/>
-      <c r="J144" s="238"/>
-      <c r="K144" s="238"/>
-      <c r="L144" s="238"/>
-      <c r="M144" s="238"/>
-      <c r="N144" s="238"/>
-      <c r="O144" s="238"/>
+      <c r="C144" s="244"/>
+      <c r="D144" s="244"/>
+      <c r="E144" s="244"/>
+      <c r="F144" s="244"/>
+      <c r="G144" s="244"/>
+      <c r="H144" s="244"/>
+      <c r="I144" s="244"/>
+      <c r="J144" s="244"/>
+      <c r="K144" s="244"/>
+      <c r="L144" s="244"/>
+      <c r="M144" s="244"/>
+      <c r="N144" s="244"/>
+      <c r="O144" s="244"/>
     </row>
     <row r="145" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C145" s="238"/>
-      <c r="D145" s="238"/>
-      <c r="E145" s="238"/>
-      <c r="F145" s="238"/>
-      <c r="G145" s="238"/>
-      <c r="H145" s="238"/>
-      <c r="I145" s="238"/>
-      <c r="J145" s="238"/>
-      <c r="K145" s="238"/>
-      <c r="L145" s="238"/>
-      <c r="M145" s="238"/>
-      <c r="N145" s="238"/>
-      <c r="O145" s="238"/>
+      <c r="C145" s="244"/>
+      <c r="D145" s="244"/>
+      <c r="E145" s="244"/>
+      <c r="F145" s="244"/>
+      <c r="G145" s="244"/>
+      <c r="H145" s="244"/>
+      <c r="I145" s="244"/>
+      <c r="J145" s="244"/>
+      <c r="K145" s="244"/>
+      <c r="L145" s="244"/>
+      <c r="M145" s="244"/>
+      <c r="N145" s="244"/>
+      <c r="O145" s="244"/>
     </row>
     <row r="146" spans="3:17" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C146" s="77"/>
@@ -12872,125 +12872,118 @@
       <c r="O147" s="77"/>
     </row>
     <row r="148" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C148" s="256" t="s">
+      <c r="C148" s="269" t="s">
         <v>257</v>
       </c>
-      <c r="D148" s="256"/>
-      <c r="E148" s="256"/>
-      <c r="F148" s="256"/>
-      <c r="G148" s="256"/>
-      <c r="H148" s="256"/>
-      <c r="I148" s="256"/>
-      <c r="J148" s="256"/>
-      <c r="K148" s="256"/>
-      <c r="L148" s="256"/>
-      <c r="M148" s="256"/>
-      <c r="N148" s="256"/>
-      <c r="O148" s="256"/>
+      <c r="D148" s="269"/>
+      <c r="E148" s="269"/>
+      <c r="F148" s="269"/>
+      <c r="G148" s="269"/>
+      <c r="H148" s="269"/>
+      <c r="I148" s="269"/>
+      <c r="J148" s="269"/>
+      <c r="K148" s="269"/>
+      <c r="L148" s="269"/>
+      <c r="M148" s="269"/>
+      <c r="N148" s="269"/>
+      <c r="O148" s="269"/>
     </row>
     <row r="149" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C149" s="256"/>
-      <c r="D149" s="256"/>
-      <c r="E149" s="256"/>
-      <c r="F149" s="256"/>
-      <c r="G149" s="256"/>
-      <c r="H149" s="256"/>
-      <c r="I149" s="256"/>
-      <c r="J149" s="256"/>
-      <c r="K149" s="256"/>
-      <c r="L149" s="256"/>
-      <c r="M149" s="256"/>
-      <c r="N149" s="256"/>
-      <c r="O149" s="256"/>
+      <c r="C149" s="269"/>
+      <c r="D149" s="269"/>
+      <c r="E149" s="269"/>
+      <c r="F149" s="269"/>
+      <c r="G149" s="269"/>
+      <c r="H149" s="269"/>
+      <c r="I149" s="269"/>
+      <c r="J149" s="269"/>
+      <c r="K149" s="269"/>
+      <c r="L149" s="269"/>
+      <c r="M149" s="269"/>
+      <c r="N149" s="269"/>
+      <c r="O149" s="269"/>
     </row>
     <row r="150" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C150" s="256"/>
-      <c r="D150" s="256"/>
-      <c r="E150" s="256"/>
-      <c r="F150" s="256"/>
-      <c r="G150" s="256"/>
-      <c r="H150" s="256"/>
-      <c r="I150" s="256"/>
-      <c r="J150" s="256"/>
-      <c r="K150" s="256"/>
-      <c r="L150" s="256"/>
-      <c r="M150" s="256"/>
-      <c r="N150" s="256"/>
-      <c r="O150" s="256"/>
+      <c r="C150" s="269"/>
+      <c r="D150" s="269"/>
+      <c r="E150" s="269"/>
+      <c r="F150" s="269"/>
+      <c r="G150" s="269"/>
+      <c r="H150" s="269"/>
+      <c r="I150" s="269"/>
+      <c r="J150" s="269"/>
+      <c r="K150" s="269"/>
+      <c r="L150" s="269"/>
+      <c r="M150" s="269"/>
+      <c r="N150" s="269"/>
+      <c r="O150" s="269"/>
       <c r="Q150" s="84">
         <f>M1-L133</f>
         <v>4034495.9149199985</v>
       </c>
     </row>
     <row r="151" spans="3:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C151" s="256"/>
-      <c r="D151" s="256"/>
-      <c r="E151" s="256"/>
-      <c r="F151" s="256"/>
-      <c r="G151" s="256"/>
-      <c r="H151" s="256"/>
-      <c r="I151" s="256"/>
-      <c r="J151" s="256"/>
-      <c r="K151" s="256"/>
-      <c r="L151" s="256"/>
-      <c r="M151" s="256"/>
-      <c r="N151" s="256"/>
-      <c r="O151" s="256"/>
+      <c r="C151" s="269"/>
+      <c r="D151" s="269"/>
+      <c r="E151" s="269"/>
+      <c r="F151" s="269"/>
+      <c r="G151" s="269"/>
+      <c r="H151" s="269"/>
+      <c r="I151" s="269"/>
+      <c r="J151" s="269"/>
+      <c r="K151" s="269"/>
+      <c r="L151" s="269"/>
+      <c r="M151" s="269"/>
+      <c r="N151" s="269"/>
+      <c r="O151" s="269"/>
     </row>
     <row r="152" spans="3:17" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C152" s="256"/>
-      <c r="D152" s="256"/>
-      <c r="E152" s="256"/>
-      <c r="F152" s="256"/>
-      <c r="G152" s="256"/>
-      <c r="H152" s="256"/>
-      <c r="I152" s="256"/>
-      <c r="J152" s="256"/>
-      <c r="K152" s="256"/>
-      <c r="L152" s="256"/>
-      <c r="M152" s="256"/>
-      <c r="N152" s="256"/>
-      <c r="O152" s="256"/>
+      <c r="C152" s="269"/>
+      <c r="D152" s="269"/>
+      <c r="E152" s="269"/>
+      <c r="F152" s="269"/>
+      <c r="G152" s="269"/>
+      <c r="H152" s="269"/>
+      <c r="I152" s="269"/>
+      <c r="J152" s="269"/>
+      <c r="K152" s="269"/>
+      <c r="L152" s="269"/>
+      <c r="M152" s="269"/>
+      <c r="N152" s="269"/>
+      <c r="O152" s="269"/>
     </row>
     <row r="153" spans="3:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C153" s="256"/>
-      <c r="D153" s="256"/>
-      <c r="E153" s="256"/>
-      <c r="F153" s="256"/>
-      <c r="G153" s="256"/>
-      <c r="H153" s="256"/>
-      <c r="I153" s="256"/>
-      <c r="J153" s="256"/>
-      <c r="K153" s="256"/>
-      <c r="L153" s="256"/>
-      <c r="M153" s="256"/>
-      <c r="N153" s="256"/>
-      <c r="O153" s="256"/>
+      <c r="C153" s="269"/>
+      <c r="D153" s="269"/>
+      <c r="E153" s="269"/>
+      <c r="F153" s="269"/>
+      <c r="G153" s="269"/>
+      <c r="H153" s="269"/>
+      <c r="I153" s="269"/>
+      <c r="J153" s="269"/>
+      <c r="K153" s="269"/>
+      <c r="L153" s="269"/>
+      <c r="M153" s="269"/>
+      <c r="N153" s="269"/>
+      <c r="O153" s="269"/>
     </row>
     <row r="154" spans="3:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C154" s="256"/>
-      <c r="D154" s="256"/>
-      <c r="E154" s="256"/>
-      <c r="F154" s="256"/>
-      <c r="G154" s="256"/>
-      <c r="H154" s="256"/>
-      <c r="I154" s="256"/>
-      <c r="J154" s="256"/>
-      <c r="K154" s="256"/>
-      <c r="L154" s="256"/>
-      <c r="M154" s="256"/>
-      <c r="N154" s="256"/>
-      <c r="O154" s="256"/>
+      <c r="C154" s="269"/>
+      <c r="D154" s="269"/>
+      <c r="E154" s="269"/>
+      <c r="F154" s="269"/>
+      <c r="G154" s="269"/>
+      <c r="H154" s="269"/>
+      <c r="I154" s="269"/>
+      <c r="J154" s="269"/>
+      <c r="K154" s="269"/>
+      <c r="L154" s="269"/>
+      <c r="M154" s="269"/>
+      <c r="N154" s="269"/>
+      <c r="O154" s="269"/>
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="K11:K13"/>
-    <mergeCell ref="A11:A13"/>
-    <mergeCell ref="B11:B13"/>
-    <mergeCell ref="C11:C13"/>
-    <mergeCell ref="D11:D13"/>
-    <mergeCell ref="F11:F13"/>
-    <mergeCell ref="E11:E13"/>
     <mergeCell ref="R14:S15"/>
     <mergeCell ref="G11:G13"/>
     <mergeCell ref="C148:O154"/>
@@ -13007,6 +13000,13 @@
     <mergeCell ref="C5:O8"/>
     <mergeCell ref="C9:O10"/>
     <mergeCell ref="A1:E4"/>
+    <mergeCell ref="K11:K13"/>
+    <mergeCell ref="A11:A13"/>
+    <mergeCell ref="B11:B13"/>
+    <mergeCell ref="C11:C13"/>
+    <mergeCell ref="D11:D13"/>
+    <mergeCell ref="F11:F13"/>
+    <mergeCell ref="E11:E13"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13037,95 +13037,95 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="292" t="s">
+      <c r="A1" s="298" t="s">
         <v>329</v>
       </c>
-      <c r="B1" s="292"/>
-      <c r="C1" s="292"/>
-      <c r="D1" s="292"/>
-      <c r="E1" s="292"/>
-      <c r="F1" s="292"/>
-      <c r="G1" s="292"/>
-      <c r="H1" s="292"/>
-      <c r="I1" s="292"/>
-      <c r="J1" s="292"/>
-      <c r="K1" s="293"/>
+      <c r="B1" s="298"/>
+      <c r="C1" s="298"/>
+      <c r="D1" s="298"/>
+      <c r="E1" s="298"/>
+      <c r="F1" s="298"/>
+      <c r="G1" s="298"/>
+      <c r="H1" s="298"/>
+      <c r="I1" s="298"/>
+      <c r="J1" s="298"/>
+      <c r="K1" s="299"/>
       <c r="N1" s="43"/>
     </row>
     <row r="2" spans="1:15" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="294"/>
-      <c r="B2" s="294"/>
-      <c r="C2" s="294"/>
-      <c r="D2" s="294"/>
-      <c r="E2" s="294"/>
-      <c r="F2" s="294"/>
-      <c r="G2" s="294"/>
-      <c r="H2" s="294"/>
-      <c r="I2" s="294"/>
-      <c r="J2" s="294"/>
-      <c r="K2" s="295"/>
+      <c r="A2" s="300"/>
+      <c r="B2" s="300"/>
+      <c r="C2" s="300"/>
+      <c r="D2" s="300"/>
+      <c r="E2" s="300"/>
+      <c r="F2" s="300"/>
+      <c r="G2" s="300"/>
+      <c r="H2" s="300"/>
+      <c r="I2" s="300"/>
+      <c r="J2" s="300"/>
+      <c r="K2" s="301"/>
       <c r="N2" s="43"/>
     </row>
     <row r="3" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="254" t="s">
+      <c r="A3" s="262" t="s">
         <v>330</v>
       </c>
-      <c r="B3" s="254" t="s">
+      <c r="B3" s="262" t="s">
         <v>331</v>
       </c>
-      <c r="C3" s="254" t="s">
+      <c r="C3" s="262" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="254" t="s">
+      <c r="D3" s="262" t="s">
         <v>27</v>
       </c>
-      <c r="E3" s="262" t="s">
+      <c r="E3" s="259" t="s">
         <v>358</v>
       </c>
-      <c r="F3" s="262" t="s">
+      <c r="F3" s="259" t="s">
         <v>359</v>
       </c>
-      <c r="G3" s="262" t="s">
+      <c r="G3" s="259" t="s">
         <v>277</v>
       </c>
-      <c r="H3" s="296" t="s">
+      <c r="H3" s="302" t="s">
         <v>360</v>
       </c>
       <c r="I3" s="209"/>
-      <c r="J3" s="262" t="s">
+      <c r="J3" s="259" t="s">
         <v>361</v>
       </c>
-      <c r="K3" s="262" t="s">
+      <c r="K3" s="259" t="s">
         <v>17</v>
       </c>
       <c r="N3" s="43"/>
     </row>
     <row r="4" spans="1:15" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="255"/>
-      <c r="B4" s="255"/>
-      <c r="C4" s="255"/>
-      <c r="D4" s="255"/>
-      <c r="E4" s="263"/>
-      <c r="F4" s="263"/>
-      <c r="G4" s="263"/>
-      <c r="H4" s="297"/>
+      <c r="A4" s="263"/>
+      <c r="B4" s="263"/>
+      <c r="C4" s="263"/>
+      <c r="D4" s="263"/>
+      <c r="E4" s="260"/>
+      <c r="F4" s="260"/>
+      <c r="G4" s="260"/>
+      <c r="H4" s="303"/>
       <c r="I4" s="131"/>
-      <c r="J4" s="263"/>
-      <c r="K4" s="263"/>
+      <c r="J4" s="260"/>
+      <c r="K4" s="260"/>
       <c r="N4" s="43"/>
     </row>
     <row r="5" spans="1:15" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="300"/>
-      <c r="B5" s="300"/>
-      <c r="C5" s="300"/>
-      <c r="D5" s="300"/>
-      <c r="E5" s="299"/>
-      <c r="F5" s="299"/>
-      <c r="G5" s="299"/>
-      <c r="H5" s="298"/>
+      <c r="A5" s="306"/>
+      <c r="B5" s="306"/>
+      <c r="C5" s="306"/>
+      <c r="D5" s="306"/>
+      <c r="E5" s="305"/>
+      <c r="F5" s="305"/>
+      <c r="G5" s="305"/>
+      <c r="H5" s="304"/>
       <c r="I5" s="210"/>
-      <c r="J5" s="299"/>
-      <c r="K5" s="299"/>
+      <c r="J5" s="305"/>
+      <c r="K5" s="305"/>
       <c r="N5" s="43"/>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
@@ -13166,8 +13166,8 @@
       <c r="L6" s="115">
         <v>0.7</v>
       </c>
-      <c r="N6" s="253"/>
-      <c r="O6" s="253"/>
+      <c r="N6" s="268"/>
+      <c r="O6" s="268"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="211" t="s">
@@ -13208,8 +13208,8 @@
         <f>L6+0.01</f>
         <v>0.71</v>
       </c>
-      <c r="N7" s="253"/>
-      <c r="O7" s="253"/>
+      <c r="N7" s="268"/>
+      <c r="O7" s="268"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="211" t="s">

--- a/2026/EL MIRADOR/Febrero/Febrero - EL MIRADOR.xlsx
+++ b/2026/EL MIRADOR/Febrero/Febrero - EL MIRADOR.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\EL MIRADOR\Febrero\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\EL MIRADOR\Febrero\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F412C450-D6C4-4C83-92FC-52A3FB2915B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30E2F71E-F286-4BA9-B1BD-5E0423414185}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -24,6 +24,11 @@
     <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$J$144</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -2201,6 +2206,18 @@
     <xf numFmtId="8" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
+    <xf numFmtId="3" fontId="0" fillId="15" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="15" borderId="28" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="0" fillId="15" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="5" borderId="28" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="0" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="23" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="23" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2246,14 +2263,35 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -2272,15 +2310,6 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2351,17 +2380,23 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="1" fontId="26" fillId="15" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="1" fontId="26" fillId="15" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="1" fontId="26" fillId="15" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="1" fontId="26" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="26" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="26" fillId="5" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="23" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2389,36 +2424,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="15" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="0" fillId="15" borderId="28" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="0" fillId="15" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="0" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="0" fillId="5" borderId="28" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="0" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="23" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="23" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="26" fillId="15" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="26" fillId="15" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="26" fillId="15" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="26" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="26" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="26" fillId="5" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -2500,9 +2505,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2540,9 +2545,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2575,9 +2580,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2610,9 +2632,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2787,24 +2826,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:R154"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="33.44140625" customWidth="1"/>
-    <col min="2" max="2" width="36.88671875" customWidth="1"/>
-    <col min="3" max="3" width="17.44140625" customWidth="1"/>
-    <col min="4" max="4" width="21.6640625" customWidth="1"/>
+    <col min="1" max="1" width="33.42578125" customWidth="1"/>
+    <col min="2" max="2" width="36.85546875" customWidth="1"/>
+    <col min="3" max="3" width="17.42578125" customWidth="1"/>
+    <col min="4" max="4" width="21.7109375" customWidth="1"/>
     <col min="5" max="5" width="18" customWidth="1"/>
-    <col min="6" max="9" width="15.6640625" customWidth="1"/>
-    <col min="10" max="10" width="14.6640625" customWidth="1"/>
-    <col min="11" max="11" width="15.88671875" customWidth="1"/>
-    <col min="12" max="12" width="16.109375" customWidth="1"/>
+    <col min="6" max="9" width="15.7109375" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.85546875" customWidth="1"/>
+    <col min="12" max="12" width="16.140625" customWidth="1"/>
     <col min="13" max="13" width="13" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="18" customWidth="1"/>
-    <col min="17" max="17" width="18.33203125" customWidth="1"/>
+    <col min="17" max="17" width="18.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="18" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="112"/>
       <c r="B1" s="121"/>
       <c r="C1" s="129" t="s">
@@ -2818,7 +2857,7 @@
       <c r="I1" s="110"/>
       <c r="J1" s="111"/>
     </row>
-    <row r="2" spans="1:10" ht="18" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A2" s="113"/>
       <c r="B2" s="122"/>
       <c r="C2" s="122" t="s">
@@ -2832,7 +2871,7 @@
       <c r="I2" s="123"/>
       <c r="J2" s="109"/>
     </row>
-    <row r="3" spans="1:10" ht="18" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A3" s="113"/>
       <c r="B3" s="122"/>
       <c r="C3" s="122" t="s">
@@ -2848,7 +2887,7 @@
       <c r="I3" s="123"/>
       <c r="J3" s="109"/>
     </row>
-    <row r="4" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="113"/>
       <c r="B4" s="122"/>
       <c r="C4" s="122" t="s">
@@ -2862,7 +2901,7 @@
       <c r="I4" s="123"/>
       <c r="J4" s="109"/>
     </row>
-    <row r="5" spans="1:10" ht="18" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A5" s="117"/>
       <c r="B5" s="122"/>
       <c r="C5" s="122" t="s">
@@ -2878,7 +2917,7 @@
       <c r="I5" s="122"/>
       <c r="J5" s="118"/>
     </row>
-    <row r="6" spans="1:10" ht="18" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A6" s="117"/>
       <c r="B6" s="122"/>
       <c r="C6" s="122" t="s">
@@ -2892,7 +2931,7 @@
       <c r="I6" s="122"/>
       <c r="J6" s="118"/>
     </row>
-    <row r="7" spans="1:10" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="119"/>
       <c r="B7" s="120"/>
       <c r="C7" s="120"/>
@@ -2904,118 +2943,118 @@
       <c r="I7" s="120"/>
       <c r="J7" s="124"/>
     </row>
-    <row r="9" spans="1:10" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="10" spans="1:10" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="14" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="243" t="s">
+    <row r="9" spans="1:10" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="10" spans="1:10" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="251" t="s">
         <v>258</v>
       </c>
-      <c r="B14" s="243"/>
-      <c r="C14" s="243"/>
-      <c r="D14" s="243"/>
-      <c r="E14" s="243"/>
-      <c r="F14" s="243"/>
-      <c r="G14" s="243"/>
-      <c r="H14" s="243"/>
-      <c r="I14" s="243"/>
-      <c r="J14" s="243"/>
-    </row>
-    <row r="15" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="243"/>
-      <c r="B15" s="243"/>
-      <c r="C15" s="243"/>
-      <c r="D15" s="243"/>
-      <c r="E15" s="243"/>
-      <c r="F15" s="243"/>
-      <c r="G15" s="243"/>
-      <c r="H15" s="243"/>
-      <c r="I15" s="243"/>
-      <c r="J15" s="243"/>
-    </row>
-    <row r="16" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="243"/>
-      <c r="B16" s="243"/>
-      <c r="C16" s="243"/>
-      <c r="D16" s="243"/>
-      <c r="E16" s="243"/>
-      <c r="F16" s="243"/>
-      <c r="G16" s="243"/>
-      <c r="H16" s="243"/>
-      <c r="I16" s="243"/>
-      <c r="J16" s="243"/>
-    </row>
-    <row r="17" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="243"/>
-      <c r="B17" s="243"/>
-      <c r="C17" s="243"/>
-      <c r="D17" s="243"/>
-      <c r="E17" s="243"/>
-      <c r="F17" s="243"/>
-      <c r="G17" s="243"/>
-      <c r="H17" s="243"/>
-      <c r="I17" s="243"/>
-      <c r="J17" s="243"/>
-    </row>
-    <row r="18" spans="1:10" ht="47.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="243"/>
-      <c r="B18" s="243"/>
-      <c r="C18" s="243"/>
-      <c r="D18" s="243"/>
-      <c r="E18" s="243"/>
-      <c r="F18" s="243"/>
-      <c r="G18" s="243"/>
-      <c r="H18" s="243"/>
-      <c r="I18" s="243"/>
-      <c r="J18" s="243"/>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B14" s="251"/>
+      <c r="C14" s="251"/>
+      <c r="D14" s="251"/>
+      <c r="E14" s="251"/>
+      <c r="F14" s="251"/>
+      <c r="G14" s="251"/>
+      <c r="H14" s="251"/>
+      <c r="I14" s="251"/>
+      <c r="J14" s="251"/>
+    </row>
+    <row r="15" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="251"/>
+      <c r="B15" s="251"/>
+      <c r="C15" s="251"/>
+      <c r="D15" s="251"/>
+      <c r="E15" s="251"/>
+      <c r="F15" s="251"/>
+      <c r="G15" s="251"/>
+      <c r="H15" s="251"/>
+      <c r="I15" s="251"/>
+      <c r="J15" s="251"/>
+    </row>
+    <row r="16" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="251"/>
+      <c r="B16" s="251"/>
+      <c r="C16" s="251"/>
+      <c r="D16" s="251"/>
+      <c r="E16" s="251"/>
+      <c r="F16" s="251"/>
+      <c r="G16" s="251"/>
+      <c r="H16" s="251"/>
+      <c r="I16" s="251"/>
+      <c r="J16" s="251"/>
+    </row>
+    <row r="17" spans="1:10" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="251"/>
+      <c r="B17" s="251"/>
+      <c r="C17" s="251"/>
+      <c r="D17" s="251"/>
+      <c r="E17" s="251"/>
+      <c r="F17" s="251"/>
+      <c r="G17" s="251"/>
+      <c r="H17" s="251"/>
+      <c r="I17" s="251"/>
+      <c r="J17" s="251"/>
+    </row>
+    <row r="18" spans="1:10" ht="47.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="251"/>
+      <c r="B18" s="251"/>
+      <c r="C18" s="251"/>
+      <c r="D18" s="251"/>
+      <c r="E18" s="251"/>
+      <c r="F18" s="251"/>
+      <c r="G18" s="251"/>
+      <c r="H18" s="251"/>
+      <c r="I18" s="251"/>
+      <c r="J18" s="251"/>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
       <c r="H19" s="94"/>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A20" s="252" t="s">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" s="260" t="s">
         <v>395</v>
       </c>
-      <c r="B20" s="252"/>
-      <c r="C20" s="252"/>
-      <c r="D20" s="252"/>
-      <c r="E20" s="252"/>
-      <c r="F20" s="252"/>
-      <c r="G20" s="252"/>
-      <c r="H20" s="252"/>
-      <c r="I20" s="252"/>
-      <c r="J20" s="252"/>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A21" s="252"/>
-      <c r="B21" s="252"/>
-      <c r="C21" s="252"/>
-      <c r="D21" s="252"/>
-      <c r="E21" s="252"/>
-      <c r="F21" s="252"/>
-      <c r="G21" s="252"/>
-      <c r="H21" s="252"/>
-      <c r="I21" s="252"/>
-      <c r="J21" s="252"/>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A22" s="252"/>
-      <c r="B22" s="252"/>
-      <c r="C22" s="252"/>
-      <c r="D22" s="252"/>
-      <c r="E22" s="252"/>
-      <c r="F22" s="252"/>
-      <c r="G22" s="252"/>
-      <c r="H22" s="252"/>
-      <c r="I22" s="252"/>
-      <c r="J22" s="252"/>
-    </row>
-    <row r="23" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B20" s="260"/>
+      <c r="C20" s="260"/>
+      <c r="D20" s="260"/>
+      <c r="E20" s="260"/>
+      <c r="F20" s="260"/>
+      <c r="G20" s="260"/>
+      <c r="H20" s="260"/>
+      <c r="I20" s="260"/>
+      <c r="J20" s="260"/>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A21" s="260"/>
+      <c r="B21" s="260"/>
+      <c r="C21" s="260"/>
+      <c r="D21" s="260"/>
+      <c r="E21" s="260"/>
+      <c r="F21" s="260"/>
+      <c r="G21" s="260"/>
+      <c r="H21" s="260"/>
+      <c r="I21" s="260"/>
+      <c r="J21" s="260"/>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A22" s="260"/>
+      <c r="B22" s="260"/>
+      <c r="C22" s="260"/>
+      <c r="D22" s="260"/>
+      <c r="E22" s="260"/>
+      <c r="F22" s="260"/>
+      <c r="G22" s="260"/>
+      <c r="H22" s="260"/>
+      <c r="I22" s="260"/>
+      <c r="J22" s="260"/>
+    </row>
+    <row r="23" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="H23" s="94"/>
     </row>
-    <row r="24" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="12" t="s">
         <v>19</v>
       </c>
@@ -3041,7 +3080,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="50" t="s">
         <v>387</v>
       </c>
@@ -3055,7 +3094,7 @@
       <c r="I25" s="95"/>
       <c r="J25" s="95"/>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
         <v>43</v>
       </c>
@@ -3071,7 +3110,7 @@
       <c r="I26" s="58"/>
       <c r="J26" s="58"/>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
         <v>237</v>
       </c>
@@ -3087,7 +3126,7 @@
       <c r="I27" s="58"/>
       <c r="J27" s="58"/>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
         <v>235</v>
       </c>
@@ -3104,7 +3143,7 @@
       <c r="I28" s="58"/>
       <c r="J28" s="58"/>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
         <v>236</v>
       </c>
@@ -3120,7 +3159,7 @@
       <c r="I29" s="58"/>
       <c r="J29" s="58"/>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
         <v>295</v>
       </c>
@@ -3136,7 +3175,7 @@
       <c r="I30" s="58"/>
       <c r="J30" s="58"/>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
         <v>238</v>
       </c>
@@ -3152,7 +3191,7 @@
       <c r="I31" s="58"/>
       <c r="J31" s="58"/>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
         <v>384</v>
       </c>
@@ -3168,7 +3207,7 @@
       <c r="I32" s="58"/>
       <c r="J32" s="58"/>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" s="93" t="s">
         <v>168</v>
       </c>
@@ -3185,7 +3224,7 @@
       <c r="I33" s="92"/>
       <c r="J33" s="92"/>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" s="50" t="s">
         <v>234</v>
       </c>
@@ -3199,7 +3238,7 @@
       <c r="I34" s="6"/>
       <c r="J34" s="6"/>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" s="6" t="s">
         <v>43</v>
       </c>
@@ -3215,7 +3254,7 @@
       <c r="I35" s="58"/>
       <c r="J35" s="58"/>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
         <v>237</v>
       </c>
@@ -3232,7 +3271,7 @@
       <c r="I36" s="58"/>
       <c r="J36" s="58"/>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" s="6" t="s">
         <v>235</v>
       </c>
@@ -3249,7 +3288,7 @@
       <c r="I37" s="58"/>
       <c r="J37" s="58"/>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
         <v>236</v>
       </c>
@@ -3266,7 +3305,7 @@
       <c r="I38" s="58"/>
       <c r="J38" s="58"/>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" s="6" t="s">
         <v>295</v>
       </c>
@@ -3283,7 +3322,7 @@
       <c r="I39" s="58"/>
       <c r="J39" s="58"/>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" s="6" t="s">
         <v>238</v>
       </c>
@@ -3299,7 +3338,7 @@
       <c r="I40" s="58"/>
       <c r="J40" s="58"/>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" s="6" t="s">
         <v>385</v>
       </c>
@@ -3315,7 +3354,7 @@
       <c r="I41" s="58"/>
       <c r="J41" s="58"/>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" s="6" t="s">
         <v>386</v>
       </c>
@@ -3331,7 +3370,7 @@
       <c r="I42" s="58"/>
       <c r="J42" s="58"/>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" s="93" t="s">
         <v>168</v>
       </c>
@@ -3348,7 +3387,7 @@
       <c r="I43" s="92"/>
       <c r="J43" s="92"/>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" s="33" t="s">
         <v>1</v>
       </c>
@@ -3391,7 +3430,7 @@
         <v/>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" s="32" t="s">
         <v>388</v>
       </c>
@@ -3408,7 +3447,7 @@
       <c r="J45" s="58"/>
       <c r="L45" s="69"/>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46" s="32" t="s">
         <v>379</v>
       </c>
@@ -3427,7 +3466,7 @@
       <c r="J46" s="6"/>
       <c r="L46" s="69"/>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A47" s="33" t="s">
         <v>38</v>
       </c>
@@ -3470,7 +3509,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" s="32" t="s">
         <v>247</v>
       </c>
@@ -3488,7 +3527,7 @@
       <c r="J48" s="58"/>
       <c r="L48" s="69"/>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" s="6"/>
       <c r="B49" s="6"/>
       <c r="C49" s="6"/>
@@ -3501,7 +3540,7 @@
       <c r="J49" s="58"/>
       <c r="L49" s="69"/>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50" s="33" t="s">
         <v>17</v>
       </c>
@@ -3529,7 +3568,7 @@
         <v/>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51" s="32" t="s">
         <v>243</v>
       </c>
@@ -3544,7 +3583,7 @@
       <c r="J51" s="49"/>
       <c r="L51" s="69"/>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52" s="35" t="s">
         <v>381</v>
       </c>
@@ -3561,7 +3600,7 @@
       <c r="J52" s="49"/>
       <c r="L52" s="69"/>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A53" s="35" t="s">
         <v>246</v>
       </c>
@@ -3582,7 +3621,7 @@
       <c r="J53" s="49"/>
       <c r="L53" s="69"/>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A54" s="35" t="s">
         <v>246</v>
       </c>
@@ -3604,7 +3643,7 @@
       <c r="J54" s="49"/>
       <c r="L54" s="69"/>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A55" s="33" t="s">
         <v>245</v>
       </c>
@@ -3647,7 +3686,7 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A56" s="32" t="s">
         <v>2</v>
       </c>
@@ -3662,7 +3701,7 @@
       <c r="J56" s="6"/>
       <c r="L56" s="69"/>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A57" s="6" t="s">
         <v>239</v>
       </c>
@@ -3681,7 +3720,7 @@
       <c r="J57" s="6"/>
       <c r="L57" s="69"/>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A58" s="6" t="s">
         <v>279</v>
       </c>
@@ -3700,7 +3739,7 @@
       <c r="J58" s="6"/>
       <c r="L58" s="69"/>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A59" s="6"/>
       <c r="B59" s="6"/>
       <c r="C59" s="182"/>
@@ -3713,7 +3752,7 @@
       <c r="J59" s="6"/>
       <c r="L59" s="69"/>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A60" s="33" t="s">
         <v>244</v>
       </c>
@@ -3756,7 +3795,7 @@
         <v/>
       </c>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A61" s="32" t="s">
         <v>227</v>
       </c>
@@ -3771,7 +3810,7 @@
       <c r="J61" s="36"/>
       <c r="L61" s="69"/>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A62" s="6" t="s">
         <v>231</v>
       </c>
@@ -3812,11 +3851,11 @@
       </c>
       <c r="L62" s="69"/>
     </row>
-    <row r="63" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="254" t="s">
+    <row r="63" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="262" t="s">
         <v>232</v>
       </c>
-      <c r="B63" s="255"/>
+      <c r="B63" s="263"/>
       <c r="C63" s="35" t="s">
         <v>311</v>
       </c>
@@ -3855,11 +3894,11 @@
         <v>326</v>
       </c>
     </row>
-    <row r="64" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="254" t="s">
+    <row r="64" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="262" t="s">
         <v>233</v>
       </c>
-      <c r="B64" s="255"/>
+      <c r="B64" s="263"/>
       <c r="C64" s="6" t="s">
         <v>380</v>
       </c>
@@ -3896,7 +3935,7 @@
       </c>
       <c r="L64" s="69"/>
     </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A65" s="33" t="s">
         <v>3</v>
       </c>
@@ -3939,7 +3978,7 @@
         <v/>
       </c>
     </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A66" s="32" t="s">
         <v>4</v>
       </c>
@@ -3954,7 +3993,7 @@
       <c r="J66" s="6"/>
       <c r="L66" s="69"/>
     </row>
-    <row r="67" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="71" t="s">
         <v>240</v>
       </c>
@@ -4000,7 +4039,7 @@
       <c r="M67" s="84"/>
       <c r="N67" s="84"/>
     </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A68" s="6" t="s">
         <v>241</v>
       </c>
@@ -4046,7 +4085,7 @@
       <c r="M68" s="84"/>
       <c r="N68" s="84"/>
     </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A69" s="6" t="s">
         <v>242</v>
       </c>
@@ -4083,7 +4122,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A70" s="6" t="s">
         <v>366</v>
       </c>
@@ -4114,11 +4153,11 @@
       <c r="M70" s="84"/>
       <c r="N70" s="84"/>
     </row>
-    <row r="71" spans="1:14" ht="33" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="250" t="s">
+    <row r="71" spans="1:14" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="258" t="s">
         <v>367</v>
       </c>
-      <c r="B71" s="256"/>
+      <c r="B71" s="264"/>
       <c r="C71" s="35"/>
       <c r="D71" s="44"/>
       <c r="E71" s="68">
@@ -4147,7 +4186,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A72" s="35" t="s">
         <v>274</v>
       </c>
@@ -4199,7 +4238,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A73" s="35" t="s">
         <v>275</v>
       </c>
@@ -4251,7 +4290,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A74" s="142" t="s">
         <v>273</v>
       </c>
@@ -4301,7 +4340,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="33" t="s">
         <v>5</v>
       </c>
@@ -4348,7 +4387,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" s="6"/>
       <c r="B76" s="6"/>
       <c r="C76" s="6"/>
@@ -4361,7 +4400,7 @@
       <c r="J76" s="6"/>
       <c r="L76" s="69"/>
     </row>
-    <row r="77" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" s="6"/>
       <c r="B77" s="6"/>
       <c r="C77" s="6"/>
@@ -4374,7 +4413,7 @@
       <c r="J77" s="6"/>
       <c r="L77" s="69"/>
     </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A78" s="32" t="s">
         <v>228</v>
       </c>
@@ -4389,7 +4428,7 @@
       <c r="J78" s="6"/>
       <c r="L78" s="69"/>
     </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A79" s="45" t="s">
         <v>319</v>
       </c>
@@ -4411,7 +4450,7 @@
       <c r="J79" s="58"/>
       <c r="L79" s="69"/>
     </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A80" s="45" t="s">
         <v>369</v>
       </c>
@@ -4433,11 +4472,11 @@
       <c r="J80" s="58"/>
       <c r="L80" s="69"/>
     </row>
-    <row r="81" spans="1:14" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="254" t="s">
+    <row r="81" spans="1:14" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="262" t="s">
         <v>374</v>
       </c>
-      <c r="B81" s="255"/>
+      <c r="B81" s="263"/>
       <c r="C81" s="137" t="s">
         <v>375</v>
       </c>
@@ -4455,11 +4494,11 @@
       <c r="J81" s="58"/>
       <c r="L81" s="69"/>
     </row>
-    <row r="82" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="254" t="s">
+    <row r="82" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="262" t="s">
         <v>376</v>
       </c>
-      <c r="B82" s="255"/>
+      <c r="B82" s="263"/>
       <c r="C82" s="137" t="s">
         <v>375</v>
       </c>
@@ -4492,11 +4531,11 @@
       </c>
       <c r="L82" s="69"/>
     </row>
-    <row r="83" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="254" t="s">
+    <row r="83" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="262" t="s">
         <v>377</v>
       </c>
-      <c r="B83" s="255"/>
+      <c r="B83" s="263"/>
       <c r="C83" s="137" t="s">
         <v>318</v>
       </c>
@@ -4530,7 +4569,7 @@
       <c r="L83" s="69"/>
       <c r="M83" s="43"/>
     </row>
-    <row r="84" spans="1:14" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:14" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="33" t="s">
         <v>229</v>
       </c>
@@ -4574,7 +4613,7 @@
       </c>
       <c r="N84" s="43"/>
     </row>
-    <row r="85" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" s="6"/>
       <c r="B85" s="6"/>
       <c r="C85" s="6"/>
@@ -4587,7 +4626,7 @@
       <c r="J85" s="6"/>
       <c r="L85" s="69"/>
     </row>
-    <row r="86" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" s="6"/>
       <c r="B86" s="6"/>
       <c r="C86" s="6"/>
@@ -4600,7 +4639,7 @@
       <c r="J86" s="6"/>
       <c r="L86" s="69"/>
     </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A87" s="32" t="s">
         <v>6</v>
       </c>
@@ -4615,7 +4654,7 @@
       <c r="J87" s="6"/>
       <c r="L87" s="69"/>
     </row>
-    <row r="88" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="6" t="s">
         <v>7</v>
       </c>
@@ -4654,7 +4693,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A89" s="32"/>
       <c r="B89" s="6"/>
       <c r="C89" s="6"/>
@@ -4668,7 +4707,7 @@
       <c r="L89" s="69"/>
       <c r="N89" s="44"/>
     </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A90" s="6"/>
       <c r="B90" s="6"/>
       <c r="C90" s="6"/>
@@ -4682,7 +4721,7 @@
       <c r="L90" s="69"/>
       <c r="N90" s="43"/>
     </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A91" s="33" t="s">
         <v>8</v>
       </c>
@@ -4726,7 +4765,7 @@
       </c>
       <c r="N91" s="43"/>
     </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A92" s="6" t="s">
         <v>28</v>
       </c>
@@ -4761,7 +4800,7 @@
       </c>
       <c r="L92" s="69"/>
     </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A93" s="6" t="s">
         <v>29</v>
       </c>
@@ -4794,7 +4833,7 @@
       </c>
       <c r="L93" s="69"/>
     </row>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A94" s="33" t="s">
         <v>230</v>
       </c>
@@ -4837,7 +4876,7 @@
         <v/>
       </c>
     </row>
-    <row r="95" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A95" s="98"/>
       <c r="B95" s="98"/>
       <c r="C95" s="98"/>
@@ -4850,7 +4889,7 @@
       <c r="J95" s="98"/>
       <c r="L95" s="69"/>
     </row>
-    <row r="96" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A96" s="100" t="s">
         <v>312</v>
       </c>
@@ -4890,7 +4929,7 @@
         <v/>
       </c>
     </row>
-    <row r="97" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A97" s="103"/>
       <c r="B97" s="104"/>
       <c r="C97" s="104"/>
@@ -4904,7 +4943,7 @@
       <c r="K97" s="43"/>
       <c r="L97" s="69"/>
     </row>
-    <row r="98" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A98" s="3" t="s">
         <v>30</v>
       </c>
@@ -4951,7 +4990,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D99" s="85"/>
       <c r="E99" s="43"/>
       <c r="F99" s="43"/>
@@ -4959,7 +4998,7 @@
       <c r="H99" s="43"/>
       <c r="I99" s="43"/>
     </row>
-    <row r="100" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A100" s="64" t="s">
         <v>39</v>
       </c>
@@ -4971,7 +5010,7 @@
       <c r="H100" s="43"/>
       <c r="I100" s="43"/>
     </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A101" s="1"/>
       <c r="C101" s="128"/>
       <c r="E101" s="43"/>
@@ -4980,7 +5019,7 @@
       <c r="H101" s="43"/>
       <c r="I101" s="43"/>
     </row>
-    <row r="102" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A102" s="1"/>
       <c r="C102" s="128"/>
       <c r="E102" s="43"/>
@@ -4989,7 +5028,7 @@
       <c r="H102" s="43"/>
       <c r="I102" s="43"/>
     </row>
-    <row r="103" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A103" s="65" t="s">
         <v>17</v>
       </c>
@@ -5004,27 +5043,27 @@
       <c r="H103" s="43"/>
       <c r="I103" s="43"/>
     </row>
-    <row r="104" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:13" x14ac:dyDescent="0.25">
       <c r="E104" s="43"/>
       <c r="F104" s="43"/>
       <c r="G104" s="43"/>
       <c r="H104" s="43"/>
       <c r="I104" s="43"/>
     </row>
-    <row r="105" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:13" x14ac:dyDescent="0.25">
       <c r="E105" s="60"/>
       <c r="F105" s="60"/>
       <c r="G105" s="60"/>
       <c r="H105" s="60"/>
       <c r="I105" s="60"/>
     </row>
-    <row r="106" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A106" s="248" t="s">
+    <row r="106" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A106" s="256" t="s">
         <v>34</v>
       </c>
-      <c r="B106" s="249"/>
-      <c r="C106" s="249"/>
-      <c r="D106" s="249"/>
+      <c r="B106" s="257"/>
+      <c r="C106" s="257"/>
+      <c r="D106" s="257"/>
       <c r="E106" s="80" t="s">
         <v>11</v>
       </c>
@@ -5044,9 +5083,9 @@
         <v>174</v>
       </c>
     </row>
-    <row r="107" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A107" s="250"/>
-      <c r="B107" s="251"/>
+    <row r="107" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A107" s="258"/>
+      <c r="B107" s="259"/>
       <c r="C107" s="82"/>
       <c r="D107" s="44"/>
       <c r="E107" s="68">
@@ -5059,9 +5098,9 @@
       <c r="I107" s="68"/>
       <c r="J107" s="58"/>
     </row>
-    <row r="108" spans="1:13" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A108" s="250"/>
-      <c r="B108" s="251"/>
+    <row r="108" spans="1:13" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A108" s="258"/>
+      <c r="B108" s="259"/>
       <c r="C108" s="82"/>
       <c r="D108" s="44"/>
       <c r="E108" s="68"/>
@@ -5071,12 +5110,12 @@
       <c r="I108" s="68"/>
       <c r="J108" s="58"/>
     </row>
-    <row r="109" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A109" s="245" t="s">
+    <row r="109" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A109" s="253" t="s">
         <v>17</v>
       </c>
-      <c r="B109" s="246"/>
-      <c r="C109" s="247"/>
+      <c r="B109" s="254"/>
+      <c r="C109" s="255"/>
       <c r="D109" s="79">
         <f>SUM(D107:D108)</f>
         <v>0</v>
@@ -5102,14 +5141,14 @@
         <v/>
       </c>
     </row>
-    <row r="111" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E111" s="43"/>
       <c r="F111" s="43"/>
       <c r="G111" s="43"/>
       <c r="H111" s="43"/>
       <c r="I111" s="43"/>
     </row>
-    <row r="112" spans="1:13" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:13" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A112" s="38" t="s">
         <v>31</v>
       </c>
@@ -5118,7 +5157,7 @@
         <v>14242326.569999998</v>
       </c>
     </row>
-    <row r="113" spans="1:11" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:11" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A113" s="40" t="s">
         <v>33</v>
       </c>
@@ -5126,107 +5165,107 @@
         <f>D98-D96</f>
         <v>14242326.569999998</v>
       </c>
-      <c r="D113" s="253" t="s">
+      <c r="D113" s="261" t="s">
         <v>302</v>
       </c>
-      <c r="E113" s="253"/>
-      <c r="F113" s="253"/>
-      <c r="G113" s="253"/>
-      <c r="H113" s="253"/>
-      <c r="I113" s="253"/>
-    </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="D114" s="253"/>
-      <c r="E114" s="253"/>
-      <c r="F114" s="253"/>
-      <c r="G114" s="253"/>
-      <c r="H114" s="253"/>
-      <c r="I114" s="253"/>
-    </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A115" s="242" t="s">
+      <c r="E113" s="261"/>
+      <c r="F113" s="261"/>
+      <c r="G113" s="261"/>
+      <c r="H113" s="261"/>
+      <c r="I113" s="261"/>
+    </row>
+    <row r="114" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D114" s="261"/>
+      <c r="E114" s="261"/>
+      <c r="F114" s="261"/>
+      <c r="G114" s="261"/>
+      <c r="H114" s="261"/>
+      <c r="I114" s="261"/>
+    </row>
+    <row r="115" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A115" s="250" t="s">
         <v>383</v>
       </c>
-      <c r="B115" s="242"/>
-      <c r="D115" s="253"/>
-      <c r="E115" s="253"/>
-      <c r="F115" s="253"/>
-      <c r="G115" s="253"/>
-      <c r="H115" s="253"/>
-      <c r="I115" s="253"/>
-    </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A116" s="242"/>
-      <c r="B116" s="242"/>
-      <c r="D116" s="253"/>
-      <c r="E116" s="253"/>
-      <c r="F116" s="253"/>
-      <c r="G116" s="253"/>
-      <c r="H116" s="253"/>
-      <c r="I116" s="253"/>
-    </row>
-    <row r="117" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A117" s="242"/>
-      <c r="B117" s="242"/>
-      <c r="D117" s="253"/>
-      <c r="E117" s="253"/>
-      <c r="F117" s="253"/>
-      <c r="G117" s="253"/>
-      <c r="H117" s="253"/>
-      <c r="I117" s="253"/>
-    </row>
-    <row r="118" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A118" s="242"/>
-      <c r="B118" s="242"/>
-      <c r="D118" s="253"/>
-      <c r="E118" s="253"/>
-      <c r="F118" s="253"/>
-      <c r="G118" s="253"/>
-      <c r="H118" s="253"/>
-      <c r="I118" s="253"/>
-    </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A119" s="242"/>
-      <c r="B119" s="242"/>
-      <c r="D119" s="253"/>
-      <c r="E119" s="253"/>
-      <c r="F119" s="253"/>
-      <c r="G119" s="253"/>
-      <c r="H119" s="253"/>
-      <c r="I119" s="253"/>
-    </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A120" s="242"/>
-      <c r="B120" s="242"/>
-      <c r="D120" s="253"/>
-      <c r="E120" s="253"/>
-      <c r="F120" s="253"/>
-      <c r="G120" s="253"/>
-      <c r="H120" s="253"/>
-      <c r="I120" s="253"/>
-    </row>
-    <row r="121" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="D121" s="253"/>
-      <c r="E121" s="253"/>
-      <c r="F121" s="253"/>
-      <c r="G121" s="253"/>
-      <c r="H121" s="253"/>
-      <c r="I121" s="253"/>
-    </row>
-    <row r="122" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B115" s="250"/>
+      <c r="D115" s="261"/>
+      <c r="E115" s="261"/>
+      <c r="F115" s="261"/>
+      <c r="G115" s="261"/>
+      <c r="H115" s="261"/>
+      <c r="I115" s="261"/>
+    </row>
+    <row r="116" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A116" s="250"/>
+      <c r="B116" s="250"/>
+      <c r="D116" s="261"/>
+      <c r="E116" s="261"/>
+      <c r="F116" s="261"/>
+      <c r="G116" s="261"/>
+      <c r="H116" s="261"/>
+      <c r="I116" s="261"/>
+    </row>
+    <row r="117" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A117" s="250"/>
+      <c r="B117" s="250"/>
+      <c r="D117" s="261"/>
+      <c r="E117" s="261"/>
+      <c r="F117" s="261"/>
+      <c r="G117" s="261"/>
+      <c r="H117" s="261"/>
+      <c r="I117" s="261"/>
+    </row>
+    <row r="118" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A118" s="250"/>
+      <c r="B118" s="250"/>
+      <c r="D118" s="261"/>
+      <c r="E118" s="261"/>
+      <c r="F118" s="261"/>
+      <c r="G118" s="261"/>
+      <c r="H118" s="261"/>
+      <c r="I118" s="261"/>
+    </row>
+    <row r="119" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A119" s="250"/>
+      <c r="B119" s="250"/>
+      <c r="D119" s="261"/>
+      <c r="E119" s="261"/>
+      <c r="F119" s="261"/>
+      <c r="G119" s="261"/>
+      <c r="H119" s="261"/>
+      <c r="I119" s="261"/>
+    </row>
+    <row r="120" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A120" s="250"/>
+      <c r="B120" s="250"/>
+      <c r="D120" s="261"/>
+      <c r="E120" s="261"/>
+      <c r="F120" s="261"/>
+      <c r="G120" s="261"/>
+      <c r="H120" s="261"/>
+      <c r="I120" s="261"/>
+    </row>
+    <row r="121" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D121" s="261"/>
+      <c r="E121" s="261"/>
+      <c r="F121" s="261"/>
+      <c r="G121" s="261"/>
+      <c r="H121" s="261"/>
+      <c r="I121" s="261"/>
+    </row>
+    <row r="122" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A122" s="16" t="s">
         <v>20</v>
       </c>
       <c r="B122" s="17"/>
       <c r="C122" s="18"/>
-      <c r="D122" s="253"/>
-      <c r="E122" s="253"/>
-      <c r="F122" s="253"/>
-      <c r="G122" s="253"/>
-      <c r="H122" s="253"/>
-      <c r="I122" s="253"/>
-    </row>
-    <row r="123" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="D122" s="261"/>
+      <c r="E122" s="261"/>
+      <c r="F122" s="261"/>
+      <c r="G122" s="261"/>
+      <c r="H122" s="261"/>
+      <c r="I122" s="261"/>
+    </row>
+    <row r="123" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A123" s="19" t="s">
         <v>21</v>
       </c>
@@ -5234,14 +5273,14 @@
         <v>1767072.6013971008</v>
       </c>
       <c r="C123" s="20"/>
-      <c r="D123" s="253"/>
-      <c r="E123" s="253"/>
-      <c r="F123" s="253"/>
-      <c r="G123" s="253"/>
-      <c r="H123" s="253"/>
-      <c r="I123" s="253"/>
-    </row>
-    <row r="124" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="D123" s="261"/>
+      <c r="E123" s="261"/>
+      <c r="F123" s="261"/>
+      <c r="G123" s="261"/>
+      <c r="H123" s="261"/>
+      <c r="I123" s="261"/>
+    </row>
+    <row r="124" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A124" s="21" t="s">
         <v>22</v>
       </c>
@@ -5252,14 +5291,14 @@
       <c r="C124" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="D124" s="253"/>
-      <c r="E124" s="253"/>
-      <c r="F124" s="253"/>
-      <c r="G124" s="253"/>
-      <c r="H124" s="253"/>
-      <c r="I124" s="253"/>
-    </row>
-    <row r="125" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="D124" s="261"/>
+      <c r="E124" s="261"/>
+      <c r="F124" s="261"/>
+      <c r="G124" s="261"/>
+      <c r="H124" s="261"/>
+      <c r="I124" s="261"/>
+    </row>
+    <row r="125" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A125" s="21" t="s">
         <v>36</v>
       </c>
@@ -5268,15 +5307,15 @@
         <v>-14242326.569999998</v>
       </c>
       <c r="C125" s="18"/>
-      <c r="D125" s="253"/>
-      <c r="E125" s="253"/>
-      <c r="F125" s="253"/>
-      <c r="G125" s="253"/>
-      <c r="H125" s="253"/>
-      <c r="I125" s="253"/>
+      <c r="D125" s="261"/>
+      <c r="E125" s="261"/>
+      <c r="F125" s="261"/>
+      <c r="G125" s="261"/>
+      <c r="H125" s="261"/>
+      <c r="I125" s="261"/>
       <c r="K125" s="44"/>
     </row>
-    <row r="126" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A126" s="21" t="s">
         <v>35</v>
       </c>
@@ -5285,15 +5324,15 @@
         <v>0</v>
       </c>
       <c r="C126" s="18"/>
-      <c r="D126" s="253"/>
-      <c r="E126" s="253"/>
-      <c r="F126" s="253"/>
-      <c r="G126" s="253"/>
-      <c r="H126" s="253"/>
-      <c r="I126" s="253"/>
+      <c r="D126" s="261"/>
+      <c r="E126" s="261"/>
+      <c r="F126" s="261"/>
+      <c r="G126" s="261"/>
+      <c r="H126" s="261"/>
+      <c r="I126" s="261"/>
       <c r="K126" s="52"/>
     </row>
-    <row r="127" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A127" s="21" t="s">
         <v>291</v>
       </c>
@@ -5302,15 +5341,15 @@
         <v>141730</v>
       </c>
       <c r="C127" s="18"/>
-      <c r="D127" s="253"/>
-      <c r="E127" s="253"/>
-      <c r="F127" s="253"/>
-      <c r="G127" s="253"/>
-      <c r="H127" s="253"/>
-      <c r="I127" s="253"/>
+      <c r="D127" s="261"/>
+      <c r="E127" s="261"/>
+      <c r="F127" s="261"/>
+      <c r="G127" s="261"/>
+      <c r="H127" s="261"/>
+      <c r="I127" s="261"/>
       <c r="K127" s="52"/>
     </row>
-    <row r="128" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A128" s="21" t="s">
         <v>32</v>
       </c>
@@ -5319,14 +5358,14 @@
         <v>-145000</v>
       </c>
       <c r="C128" s="22"/>
-      <c r="D128" s="253"/>
-      <c r="E128" s="253"/>
-      <c r="F128" s="253"/>
-      <c r="G128" s="253"/>
-      <c r="H128" s="253"/>
-      <c r="I128" s="253"/>
-    </row>
-    <row r="129" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="D128" s="261"/>
+      <c r="E128" s="261"/>
+      <c r="F128" s="261"/>
+      <c r="G128" s="261"/>
+      <c r="H128" s="261"/>
+      <c r="I128" s="261"/>
+    </row>
+    <row r="129" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A129" s="21" t="s">
         <v>289</v>
       </c>
@@ -5335,14 +5374,14 @@
         <v>-87300</v>
       </c>
       <c r="C129" s="22"/>
-      <c r="D129" s="253"/>
-      <c r="E129" s="253"/>
-      <c r="F129" s="253"/>
-      <c r="G129" s="253"/>
-      <c r="H129" s="253"/>
-      <c r="I129" s="253"/>
-    </row>
-    <row r="130" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="D129" s="261"/>
+      <c r="E129" s="261"/>
+      <c r="F129" s="261"/>
+      <c r="G129" s="261"/>
+      <c r="H129" s="261"/>
+      <c r="I129" s="261"/>
+    </row>
+    <row r="130" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A130" s="21" t="s">
         <v>39</v>
       </c>
@@ -5351,25 +5390,25 @@
         <v>0</v>
       </c>
       <c r="C130" s="22"/>
-      <c r="D130" s="253"/>
-      <c r="E130" s="253"/>
-      <c r="F130" s="253"/>
-      <c r="G130" s="253"/>
-      <c r="H130" s="253"/>
-      <c r="I130" s="253"/>
-    </row>
-    <row r="131" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="D130" s="261"/>
+      <c r="E130" s="261"/>
+      <c r="F130" s="261"/>
+      <c r="G130" s="261"/>
+      <c r="H130" s="261"/>
+      <c r="I130" s="261"/>
+    </row>
+    <row r="131" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A131" s="21"/>
       <c r="B131" s="168"/>
       <c r="C131" s="22"/>
-      <c r="D131" s="253"/>
-      <c r="E131" s="253"/>
-      <c r="F131" s="253"/>
-      <c r="G131" s="253"/>
-      <c r="H131" s="253"/>
-      <c r="I131" s="253"/>
-    </row>
-    <row r="132" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="D131" s="261"/>
+      <c r="E131" s="261"/>
+      <c r="F131" s="261"/>
+      <c r="G131" s="261"/>
+      <c r="H131" s="261"/>
+      <c r="I131" s="261"/>
+    </row>
+    <row r="132" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A132" s="19" t="s">
         <v>24</v>
       </c>
@@ -5378,37 +5417,37 @@
         <v>1499395.7189351022</v>
       </c>
       <c r="C132" s="70"/>
-      <c r="D132" s="253"/>
-      <c r="E132" s="253"/>
-      <c r="F132" s="253"/>
-      <c r="G132" s="253"/>
-      <c r="H132" s="253"/>
-      <c r="I132" s="253"/>
-    </row>
-    <row r="133" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="D132" s="261"/>
+      <c r="E132" s="261"/>
+      <c r="F132" s="261"/>
+      <c r="G132" s="261"/>
+      <c r="H132" s="261"/>
+      <c r="I132" s="261"/>
+    </row>
+    <row r="133" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A133" s="22"/>
       <c r="C133" s="18"/>
-      <c r="D133" s="253"/>
-      <c r="E133" s="253"/>
-      <c r="F133" s="253"/>
-      <c r="G133" s="253"/>
-      <c r="H133" s="253"/>
-      <c r="I133" s="253"/>
-    </row>
-    <row r="134" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="D133" s="261"/>
+      <c r="E133" s="261"/>
+      <c r="F133" s="261"/>
+      <c r="G133" s="261"/>
+      <c r="H133" s="261"/>
+      <c r="I133" s="261"/>
+    </row>
+    <row r="134" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A134" s="16" t="s">
         <v>290</v>
       </c>
       <c r="B134" s="8"/>
       <c r="C134" s="18"/>
-      <c r="D134" s="253"/>
-      <c r="E134" s="253"/>
-      <c r="F134" s="253"/>
-      <c r="G134" s="253"/>
-      <c r="H134" s="253"/>
-      <c r="I134" s="253"/>
-    </row>
-    <row r="135" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D134" s="261"/>
+      <c r="E134" s="261"/>
+      <c r="F134" s="261"/>
+      <c r="G134" s="261"/>
+      <c r="H134" s="261"/>
+      <c r="I134" s="261"/>
+    </row>
+    <row r="135" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="19" t="s">
         <v>325</v>
       </c>
@@ -5418,7 +5457,7 @@
       <c r="C135" s="18"/>
       <c r="D135" s="25"/>
     </row>
-    <row r="136" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A136" s="36" t="s">
         <v>17</v>
       </c>
@@ -5429,17 +5468,17 @@
       <c r="C136" s="18"/>
       <c r="D136" s="25"/>
     </row>
-    <row r="137" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A137" s="22"/>
       <c r="C137" s="18"/>
       <c r="D137" s="25"/>
     </row>
-    <row r="138" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A138" s="22"/>
       <c r="C138" s="18"/>
       <c r="D138" s="25"/>
     </row>
-    <row r="139" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:10" x14ac:dyDescent="0.25">
       <c r="C139" s="18"/>
       <c r="D139" s="43"/>
       <c r="E139" s="84"/>
@@ -5448,7 +5487,7 @@
       <c r="H139" s="84"/>
       <c r="I139" s="84"/>
     </row>
-    <row r="140" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A140" s="16" t="s">
         <v>25</v>
       </c>
@@ -5464,7 +5503,7 @@
       <c r="I140" s="84"/>
       <c r="J140" s="84"/>
     </row>
-    <row r="141" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="19" t="s">
         <v>253</v>
       </c>
@@ -5479,7 +5518,7 @@
       <c r="H141" s="88"/>
       <c r="I141" s="88"/>
     </row>
-    <row r="142" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A142" s="19"/>
       <c r="B142" s="83"/>
       <c r="C142" s="24"/>
@@ -5490,7 +5529,7 @@
       <c r="H142" s="43"/>
       <c r="I142" s="43"/>
     </row>
-    <row r="143" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A143" s="36" t="s">
         <v>17</v>
       </c>
@@ -5500,62 +5539,62 @@
       </c>
       <c r="C143" s="24"/>
     </row>
-    <row r="144" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:10" x14ac:dyDescent="0.25">
       <c r="C144" s="25"/>
       <c r="D144" s="84"/>
     </row>
-    <row r="145" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="145" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B145" s="22"/>
       <c r="C145" s="18"/>
     </row>
-    <row r="147" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="147" spans="2:18" x14ac:dyDescent="0.25">
       <c r="R147" s="9"/>
     </row>
-    <row r="150" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B150" s="244"/>
-      <c r="C150" s="244"/>
-      <c r="D150" s="244"/>
-      <c r="E150" s="244"/>
+    <row r="150" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B150" s="252"/>
+      <c r="C150" s="252"/>
+      <c r="D150" s="252"/>
+      <c r="E150" s="252"/>
       <c r="F150" s="90"/>
       <c r="G150" s="90"/>
       <c r="H150" s="90"/>
       <c r="I150" s="90"/>
     </row>
-    <row r="151" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B151" s="244"/>
-      <c r="C151" s="244"/>
-      <c r="D151" s="244"/>
-      <c r="E151" s="244"/>
+    <row r="151" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B151" s="252"/>
+      <c r="C151" s="252"/>
+      <c r="D151" s="252"/>
+      <c r="E151" s="252"/>
       <c r="F151" s="90"/>
       <c r="G151" s="90"/>
       <c r="H151" s="90"/>
       <c r="I151" s="90"/>
     </row>
-    <row r="152" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B152" s="244"/>
-      <c r="C152" s="244"/>
-      <c r="D152" s="244"/>
-      <c r="E152" s="244"/>
+    <row r="152" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B152" s="252"/>
+      <c r="C152" s="252"/>
+      <c r="D152" s="252"/>
+      <c r="E152" s="252"/>
       <c r="F152" s="90"/>
       <c r="G152" s="90"/>
       <c r="H152" s="90"/>
       <c r="I152" s="90"/>
     </row>
-    <row r="153" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B153" s="244"/>
-      <c r="C153" s="244"/>
-      <c r="D153" s="244"/>
-      <c r="E153" s="244"/>
+    <row r="153" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B153" s="252"/>
+      <c r="C153" s="252"/>
+      <c r="D153" s="252"/>
+      <c r="E153" s="252"/>
       <c r="F153" s="90"/>
       <c r="G153" s="90"/>
       <c r="H153" s="90"/>
       <c r="I153" s="90"/>
     </row>
-    <row r="154" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B154" s="244"/>
-      <c r="C154" s="244"/>
-      <c r="D154" s="244"/>
-      <c r="E154" s="244"/>
+    <row r="154" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B154" s="252"/>
+      <c r="C154" s="252"/>
+      <c r="D154" s="252"/>
+      <c r="E154" s="252"/>
       <c r="F154" s="90"/>
       <c r="G154" s="90"/>
       <c r="H154" s="90"/>
@@ -5588,36 +5627,36 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:DJ154"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.5546875" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="5.88671875" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="8.109375" customWidth="1"/>
-    <col min="4" max="4" width="42.6640625" customWidth="1"/>
-    <col min="5" max="5" width="25.5546875" customWidth="1"/>
-    <col min="6" max="6" width="9.44140625" customWidth="1"/>
-    <col min="7" max="7" width="13.33203125" customWidth="1"/>
+    <col min="1" max="1" width="4.5703125" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="5.85546875" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="8.140625" customWidth="1"/>
+    <col min="4" max="4" width="42.7109375" customWidth="1"/>
+    <col min="5" max="5" width="25.5703125" customWidth="1"/>
+    <col min="6" max="6" width="9.42578125" customWidth="1"/>
+    <col min="7" max="7" width="13.28515625" customWidth="1"/>
     <col min="8" max="8" width="13" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.88671875" customWidth="1"/>
-    <col min="10" max="11" width="13.6640625" customWidth="1"/>
-    <col min="12" max="12" width="13.33203125" customWidth="1"/>
-    <col min="13" max="13" width="10.44140625" customWidth="1"/>
-    <col min="14" max="14" width="15.44140625" customWidth="1"/>
-    <col min="15" max="15" width="13.6640625" customWidth="1"/>
-    <col min="16" max="16" width="11.44140625" customWidth="1"/>
-    <col min="17" max="17" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.85546875" customWidth="1"/>
+    <col min="10" max="11" width="13.7109375" customWidth="1"/>
+    <col min="12" max="12" width="13.28515625" customWidth="1"/>
+    <col min="13" max="13" width="10.42578125" customWidth="1"/>
+    <col min="14" max="14" width="15.42578125" customWidth="1"/>
+    <col min="15" max="15" width="13.7109375" customWidth="1"/>
+    <col min="16" max="16" width="11.42578125" customWidth="1"/>
+    <col min="17" max="17" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="13" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A1" s="286" t="s">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A1" s="298" t="s">
         <v>327</v>
       </c>
-      <c r="B1" s="287"/>
-      <c r="C1" s="287"/>
-      <c r="D1" s="287"/>
-      <c r="E1" s="287"/>
+      <c r="B1" s="299"/>
+      <c r="C1" s="299"/>
+      <c r="D1" s="299"/>
+      <c r="E1" s="299"/>
       <c r="F1" s="158" t="s">
         <v>293</v>
       </c>
@@ -5629,20 +5668,20 @@
       <c r="L1" s="190" t="s">
         <v>41</v>
       </c>
-      <c r="M1" s="262">
+      <c r="M1" s="277">
         <f>RESUMEN!D98-RESUMEN!D96</f>
         <v>14242326.569999998</v>
       </c>
-      <c r="N1" s="263"/>
+      <c r="N1" s="278"/>
       <c r="O1" s="159"/>
       <c r="P1" s="59"/>
     </row>
-    <row r="2" spans="1:19" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="288"/>
-      <c r="B2" s="289"/>
-      <c r="C2" s="289"/>
-      <c r="D2" s="289"/>
-      <c r="E2" s="289"/>
+    <row r="2" spans="1:19" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="300"/>
+      <c r="B2" s="301"/>
+      <c r="C2" s="301"/>
+      <c r="D2" s="301"/>
+      <c r="E2" s="301"/>
       <c r="F2" s="7" t="s">
         <v>292</v>
       </c>
@@ -5661,12 +5700,12 @@
       <c r="O2" s="160"/>
       <c r="P2" s="59"/>
     </row>
-    <row r="3" spans="1:19" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="288"/>
-      <c r="B3" s="289"/>
-      <c r="C3" s="289"/>
-      <c r="D3" s="289"/>
-      <c r="E3" s="289"/>
+    <row r="3" spans="1:19" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="300"/>
+      <c r="B3" s="301"/>
+      <c r="C3" s="301"/>
+      <c r="D3" s="301"/>
+      <c r="E3" s="301"/>
       <c r="F3" s="7" t="s">
         <v>294</v>
       </c>
@@ -5686,12 +5725,12 @@
       <c r="O3" s="162"/>
       <c r="P3" s="15"/>
     </row>
-    <row r="4" spans="1:19" ht="2.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="290"/>
-      <c r="B4" s="291"/>
-      <c r="C4" s="291"/>
-      <c r="D4" s="291"/>
-      <c r="E4" s="291"/>
+    <row r="4" spans="1:19" ht="2.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="302"/>
+      <c r="B4" s="303"/>
+      <c r="C4" s="303"/>
+      <c r="D4" s="303"/>
+      <c r="E4" s="303"/>
       <c r="F4" s="163"/>
       <c r="G4" s="163"/>
       <c r="H4" s="163"/>
@@ -5704,98 +5743,98 @@
       <c r="O4" s="166"/>
       <c r="P4" s="15"/>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="7"/>
       <c r="B5" s="7"/>
-      <c r="C5" s="271" t="s">
+      <c r="C5" s="283" t="s">
         <v>310</v>
       </c>
-      <c r="D5" s="272"/>
-      <c r="E5" s="272"/>
-      <c r="F5" s="272"/>
-      <c r="G5" s="272"/>
-      <c r="H5" s="272"/>
-      <c r="I5" s="272"/>
-      <c r="J5" s="272"/>
-      <c r="K5" s="272"/>
-      <c r="L5" s="272"/>
-      <c r="M5" s="272"/>
-      <c r="N5" s="272"/>
-      <c r="O5" s="273"/>
+      <c r="D5" s="284"/>
+      <c r="E5" s="284"/>
+      <c r="F5" s="284"/>
+      <c r="G5" s="284"/>
+      <c r="H5" s="284"/>
+      <c r="I5" s="284"/>
+      <c r="J5" s="284"/>
+      <c r="K5" s="284"/>
+      <c r="L5" s="284"/>
+      <c r="M5" s="284"/>
+      <c r="N5" s="284"/>
+      <c r="O5" s="285"/>
       <c r="P5" s="15"/>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="7"/>
       <c r="B6" s="7"/>
-      <c r="C6" s="274"/>
-      <c r="D6" s="275"/>
-      <c r="E6" s="275"/>
-      <c r="F6" s="275"/>
-      <c r="G6" s="275"/>
-      <c r="H6" s="275"/>
-      <c r="I6" s="275"/>
-      <c r="J6" s="275"/>
-      <c r="K6" s="275"/>
-      <c r="L6" s="275"/>
-      <c r="M6" s="275"/>
-      <c r="N6" s="275"/>
-      <c r="O6" s="276"/>
+      <c r="C6" s="286"/>
+      <c r="D6" s="287"/>
+      <c r="E6" s="287"/>
+      <c r="F6" s="287"/>
+      <c r="G6" s="287"/>
+      <c r="H6" s="287"/>
+      <c r="I6" s="287"/>
+      <c r="J6" s="287"/>
+      <c r="K6" s="287"/>
+      <c r="L6" s="287"/>
+      <c r="M6" s="287"/>
+      <c r="N6" s="287"/>
+      <c r="O6" s="288"/>
       <c r="P6" s="15"/>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="7"/>
       <c r="B7" s="7"/>
-      <c r="C7" s="274"/>
-      <c r="D7" s="275"/>
-      <c r="E7" s="275"/>
-      <c r="F7" s="275"/>
-      <c r="G7" s="275"/>
-      <c r="H7" s="275"/>
-      <c r="I7" s="275"/>
-      <c r="J7" s="275"/>
-      <c r="K7" s="275"/>
-      <c r="L7" s="275"/>
-      <c r="M7" s="275"/>
-      <c r="N7" s="275"/>
-      <c r="O7" s="276"/>
+      <c r="C7" s="286"/>
+      <c r="D7" s="287"/>
+      <c r="E7" s="287"/>
+      <c r="F7" s="287"/>
+      <c r="G7" s="287"/>
+      <c r="H7" s="287"/>
+      <c r="I7" s="287"/>
+      <c r="J7" s="287"/>
+      <c r="K7" s="287"/>
+      <c r="L7" s="287"/>
+      <c r="M7" s="287"/>
+      <c r="N7" s="287"/>
+      <c r="O7" s="288"/>
       <c r="P7" s="15"/>
     </row>
-    <row r="8" spans="1:19" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:19" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="7"/>
       <c r="B8" s="7"/>
-      <c r="C8" s="277"/>
-      <c r="D8" s="278"/>
-      <c r="E8" s="278"/>
-      <c r="F8" s="278"/>
-      <c r="G8" s="278"/>
-      <c r="H8" s="278"/>
-      <c r="I8" s="278"/>
-      <c r="J8" s="278"/>
-      <c r="K8" s="278"/>
-      <c r="L8" s="278"/>
-      <c r="M8" s="278"/>
-      <c r="N8" s="278"/>
-      <c r="O8" s="279"/>
+      <c r="C8" s="289"/>
+      <c r="D8" s="290"/>
+      <c r="E8" s="290"/>
+      <c r="F8" s="290"/>
+      <c r="G8" s="290"/>
+      <c r="H8" s="290"/>
+      <c r="I8" s="290"/>
+      <c r="J8" s="290"/>
+      <c r="K8" s="290"/>
+      <c r="L8" s="290"/>
+      <c r="M8" s="290"/>
+      <c r="N8" s="290"/>
+      <c r="O8" s="291"/>
       <c r="Q8" s="84"/>
     </row>
-    <row r="9" spans="1:19" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:19" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
-      <c r="C9" s="280" t="s">
+      <c r="C9" s="292" t="s">
         <v>308</v>
       </c>
-      <c r="D9" s="281"/>
-      <c r="E9" s="281"/>
-      <c r="F9" s="281"/>
-      <c r="G9" s="281"/>
-      <c r="H9" s="281"/>
-      <c r="I9" s="281"/>
-      <c r="J9" s="281"/>
-      <c r="K9" s="281"/>
-      <c r="L9" s="281"/>
-      <c r="M9" s="281"/>
-      <c r="N9" s="281"/>
-      <c r="O9" s="282"/>
+      <c r="D9" s="293"/>
+      <c r="E9" s="293"/>
+      <c r="F9" s="293"/>
+      <c r="G9" s="293"/>
+      <c r="H9" s="293"/>
+      <c r="I9" s="293"/>
+      <c r="J9" s="293"/>
+      <c r="K9" s="293"/>
+      <c r="L9" s="293"/>
+      <c r="M9" s="293"/>
+      <c r="N9" s="293"/>
+      <c r="O9" s="294"/>
       <c r="Q9" t="s">
         <v>248</v>
       </c>
@@ -5804,22 +5843,22 @@
         <v>144184.86874800001</v>
       </c>
     </row>
-    <row r="10" spans="1:19" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:19" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="7"/>
       <c r="B10" s="7"/>
-      <c r="C10" s="283"/>
-      <c r="D10" s="284"/>
-      <c r="E10" s="284"/>
-      <c r="F10" s="284"/>
-      <c r="G10" s="284"/>
-      <c r="H10" s="284"/>
-      <c r="I10" s="284"/>
-      <c r="J10" s="284"/>
-      <c r="K10" s="284"/>
-      <c r="L10" s="284"/>
-      <c r="M10" s="284"/>
-      <c r="N10" s="284"/>
-      <c r="O10" s="285"/>
+      <c r="C10" s="295"/>
+      <c r="D10" s="296"/>
+      <c r="E10" s="296"/>
+      <c r="F10" s="296"/>
+      <c r="G10" s="296"/>
+      <c r="H10" s="296"/>
+      <c r="I10" s="296"/>
+      <c r="J10" s="296"/>
+      <c r="K10" s="296"/>
+      <c r="L10" s="296"/>
+      <c r="M10" s="296"/>
+      <c r="N10" s="296"/>
+      <c r="O10" s="297"/>
       <c r="Q10" t="s">
         <v>249</v>
       </c>
@@ -5828,50 +5867,50 @@
         <v>170885.77036800003</v>
       </c>
     </row>
-    <row r="11" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="258" t="s">
+    <row r="11" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="268" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="292" t="s">
+      <c r="B11" s="270" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="258" t="s">
+      <c r="C11" s="268" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="294" t="s">
+      <c r="D11" s="272" t="s">
         <v>12</v>
       </c>
-      <c r="E11" s="294" t="s">
+      <c r="E11" s="272" t="s">
         <v>266</v>
       </c>
-      <c r="F11" s="258" t="s">
+      <c r="F11" s="268" t="s">
         <v>27</v>
       </c>
-      <c r="G11" s="258" t="s">
+      <c r="G11" s="268" t="s">
         <v>13</v>
       </c>
-      <c r="H11" s="258" t="s">
+      <c r="H11" s="268" t="s">
         <v>14</v>
       </c>
-      <c r="I11" s="264" t="s">
+      <c r="I11" s="279" t="s">
         <v>15</v>
       </c>
-      <c r="J11" s="266" t="s">
+      <c r="J11" s="265" t="s">
         <v>16</v>
       </c>
-      <c r="K11" s="266" t="s">
+      <c r="K11" s="265" t="s">
         <v>390</v>
       </c>
-      <c r="L11" s="266" t="s">
+      <c r="L11" s="265" t="s">
         <v>18</v>
       </c>
-      <c r="M11" s="269" t="s">
+      <c r="M11" s="281" t="s">
         <v>40</v>
       </c>
-      <c r="N11" s="266" t="s">
+      <c r="N11" s="265" t="s">
         <v>277</v>
       </c>
-      <c r="O11" s="266" t="s">
+      <c r="O11" s="265" t="s">
         <v>276</v>
       </c>
       <c r="Q11" t="s">
@@ -5882,22 +5921,22 @@
         <v>161540.45480100001</v>
       </c>
     </row>
-    <row r="12" spans="1:19" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="259"/>
-      <c r="B12" s="293"/>
-      <c r="C12" s="259"/>
-      <c r="D12" s="295"/>
-      <c r="E12" s="295"/>
-      <c r="F12" s="259"/>
-      <c r="G12" s="259"/>
-      <c r="H12" s="259"/>
-      <c r="I12" s="265"/>
-      <c r="J12" s="267"/>
-      <c r="K12" s="267"/>
-      <c r="L12" s="267"/>
-      <c r="M12" s="270"/>
-      <c r="N12" s="267"/>
-      <c r="O12" s="267"/>
+    <row r="12" spans="1:19" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="269"/>
+      <c r="B12" s="271"/>
+      <c r="C12" s="269"/>
+      <c r="D12" s="273"/>
+      <c r="E12" s="273"/>
+      <c r="F12" s="269"/>
+      <c r="G12" s="269"/>
+      <c r="H12" s="269"/>
+      <c r="I12" s="280"/>
+      <c r="J12" s="266"/>
+      <c r="K12" s="266"/>
+      <c r="L12" s="266"/>
+      <c r="M12" s="282"/>
+      <c r="N12" s="266"/>
+      <c r="O12" s="266"/>
       <c r="Q12" t="s">
         <v>251</v>
       </c>
@@ -5906,20 +5945,20 @@
         <v>198921.71706900001</v>
       </c>
     </row>
-    <row r="13" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="259"/>
-      <c r="B13" s="293"/>
-      <c r="C13" s="259"/>
-      <c r="D13" s="295"/>
-      <c r="E13" s="295"/>
-      <c r="F13" s="259"/>
-      <c r="G13" s="259"/>
-      <c r="H13" s="259"/>
-      <c r="I13" s="265"/>
-      <c r="J13" s="267"/>
-      <c r="K13" s="268"/>
-      <c r="L13" s="268"/>
-      <c r="M13" s="270"/>
+    <row r="13" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="269"/>
+      <c r="B13" s="271"/>
+      <c r="C13" s="269"/>
+      <c r="D13" s="273"/>
+      <c r="E13" s="273"/>
+      <c r="F13" s="269"/>
+      <c r="G13" s="269"/>
+      <c r="H13" s="269"/>
+      <c r="I13" s="280"/>
+      <c r="J13" s="266"/>
+      <c r="K13" s="267"/>
+      <c r="L13" s="267"/>
+      <c r="M13" s="282"/>
       <c r="N13" s="132" t="str">
         <f>RESUMEN!A20</f>
         <v>VTO 16/03</v>
@@ -5936,7 +5975,7 @@
         <v>232297.84409400003</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
         <v>118</v>
       </c>
@@ -5975,18 +6014,18 @@
         <v>0</v>
       </c>
       <c r="N14" s="146">
-        <f>L14+J14+I14+M14</f>
-        <v>560634.40299600014</v>
+        <f>L14+J14+I14+M14+K14</f>
+        <v>618520.3963560001</v>
       </c>
       <c r="O14" s="147">
         <f>N14*6% + N14</f>
-        <v>594272.46717576019</v>
+        <v>655631.62013736006</v>
       </c>
       <c r="P14" s="115"/>
-      <c r="R14" s="257"/>
-      <c r="S14" s="257"/>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="R14" s="274"/>
+      <c r="S14" s="274"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15" s="6"/>
       <c r="B15" s="6"/>
       <c r="C15" s="35" t="s">
@@ -6024,18 +6063,18 @@
         <v>0</v>
       </c>
       <c r="N15" s="146">
-        <f t="shared" ref="N15:N18" si="3">L15+J15+I15+M15</f>
-        <v>170885.77036800003</v>
+        <f t="shared" ref="N15:N18" si="3">L15+J15+I15+M15+K15</f>
+        <v>240563.35496800003</v>
       </c>
       <c r="O15" s="147">
         <f t="shared" ref="O15:O18" si="4">N15*6% + N15</f>
-        <v>181138.91659008001</v>
+        <v>254997.15626608004</v>
       </c>
       <c r="P15" s="115"/>
-      <c r="R15" s="257"/>
-      <c r="S15" s="257"/>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="R15" s="274"/>
+      <c r="S15" s="274"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
         <v>118</v>
       </c>
@@ -6078,16 +6117,16 @@
       </c>
       <c r="N16" s="146">
         <f t="shared" si="3"/>
-        <v>161540.45480100001</v>
+        <v>226394.20662100002</v>
       </c>
       <c r="O16" s="147">
         <f t="shared" si="4"/>
-        <v>171232.88208906</v>
+        <v>239977.85901826003</v>
       </c>
       <c r="P16" s="115"/>
       <c r="S16" s="43"/>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
         <v>118</v>
       </c>
@@ -6125,16 +6164,16 @@
       </c>
       <c r="N17" s="146">
         <f t="shared" si="3"/>
-        <v>945509.83376299997</v>
+        <v>1025371.065343</v>
       </c>
       <c r="O17" s="147">
         <f t="shared" si="4"/>
-        <v>1002240.42378878</v>
+        <v>1086893.32926358</v>
       </c>
       <c r="P17" s="115"/>
       <c r="S17" s="43"/>
     </row>
-    <row r="18" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="6" t="s">
         <v>118</v>
       </c>
@@ -6170,18 +6209,18 @@
       <c r="M18" s="208">
         <v>0</v>
       </c>
-      <c r="N18" s="154">
+      <c r="N18" s="146">
         <f t="shared" si="3"/>
-        <v>460640.96207400004</v>
+        <v>553901.72915400006</v>
       </c>
       <c r="O18" s="155">
         <f t="shared" si="4"/>
-        <v>488279.41979844007</v>
+        <v>587135.83290324011</v>
       </c>
       <c r="P18" s="115"/>
       <c r="S18" s="43"/>
     </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A19" s="57" t="s">
         <v>120</v>
       </c>
@@ -6234,7 +6273,7 @@
       </c>
       <c r="S19" s="43"/>
     </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A20" s="57" t="s">
         <v>121</v>
       </c>
@@ -6289,7 +6328,7 @@
       </c>
       <c r="S20" s="43"/>
     </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A21" s="57" t="s">
         <v>120</v>
       </c>
@@ -6343,7 +6382,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A22" s="57" t="s">
         <v>122</v>
       </c>
@@ -6401,7 +6440,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A23" s="57" t="s">
         <v>122</v>
       </c>
@@ -6457,7 +6496,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A24" s="57" t="s">
         <v>122</v>
       </c>
@@ -6513,7 +6552,7 @@
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A25" s="57" t="s">
         <v>120</v>
       </c>
@@ -6566,7 +6605,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A26" s="57" t="s">
         <v>121</v>
       </c>
@@ -6620,7 +6659,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A27" s="108" t="s">
         <v>120</v>
       </c>
@@ -6673,7 +6712,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A28" s="108" t="s">
         <v>122</v>
       </c>
@@ -6727,7 +6766,7 @@
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A29" s="108" t="s">
         <v>122</v>
       </c>
@@ -6781,7 +6820,7 @@
         <v>0.10999999999999999</v>
       </c>
     </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A30" s="108" t="s">
         <v>122</v>
       </c>
@@ -6832,7 +6871,7 @@
         <v>0.11999999999999998</v>
       </c>
     </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A31" s="108" t="s">
         <v>120</v>
       </c>
@@ -6886,7 +6925,7 @@
         <v>0.12999999999999998</v>
       </c>
     </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A32" s="57" t="s">
         <v>121</v>
       </c>
@@ -6942,7 +6981,7 @@
         <v>0.13999999999999999</v>
       </c>
     </row>
-    <row r="33" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A33" s="57" t="s">
         <v>120</v>
       </c>
@@ -6996,7 +7035,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="34" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A34" s="139" t="s">
         <v>122</v>
       </c>
@@ -7053,7 +7092,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="35" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A35" s="57" t="s">
         <v>122</v>
       </c>
@@ -7109,7 +7148,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="36" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A36" s="57" t="s">
         <v>122</v>
       </c>
@@ -7160,7 +7199,7 @@
         <v>0.18000000000000002</v>
       </c>
     </row>
-    <row r="37" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A37" s="57" t="s">
         <v>120</v>
       </c>
@@ -7216,7 +7255,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="38" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A38" s="57" t="s">
         <v>121</v>
       </c>
@@ -7270,7 +7309,7 @@
         <v>0.20000000000000004</v>
       </c>
     </row>
-    <row r="39" spans="1:114" s="140" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:114" s="140" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="108" t="s">
         <v>120</v>
       </c>
@@ -7419,7 +7458,7 @@
       <c r="DI39" s="73"/>
       <c r="DJ39" s="73"/>
     </row>
-    <row r="40" spans="1:114" s="140" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:114" s="140" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="108" t="s">
         <v>122</v>
       </c>
@@ -7570,7 +7609,7 @@
       <c r="DI40" s="73"/>
       <c r="DJ40" s="73"/>
     </row>
-    <row r="41" spans="1:114" s="140" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:114" s="140" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="108" t="s">
         <v>122</v>
       </c>
@@ -7724,7 +7763,7 @@
       <c r="DI41" s="73"/>
       <c r="DJ41" s="73"/>
     </row>
-    <row r="42" spans="1:114" s="140" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:114" s="140" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="108" t="s">
         <v>122</v>
       </c>
@@ -7875,7 +7914,7 @@
       <c r="DI42" s="73"/>
       <c r="DJ42" s="73"/>
     </row>
-    <row r="43" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A43" s="57" t="s">
         <v>120</v>
       </c>
@@ -7929,7 +7968,7 @@
         <v>0.25000000000000006</v>
       </c>
     </row>
-    <row r="44" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A44" s="57" t="s">
         <v>121</v>
       </c>
@@ -7985,7 +8024,7 @@
         <v>0.26000000000000006</v>
       </c>
     </row>
-    <row r="45" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A45" s="57" t="s">
         <v>120</v>
       </c>
@@ -8045,7 +8084,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="46" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A46" s="171" t="s">
         <v>122</v>
       </c>
@@ -8099,7 +8138,7 @@
         <v>0.28000000000000008</v>
       </c>
     </row>
-    <row r="47" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A47" s="57" t="s">
         <v>122</v>
       </c>
@@ -8155,7 +8194,7 @@
         <v>0.29000000000000009</v>
       </c>
     </row>
-    <row r="48" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A48" s="57" t="s">
         <v>122</v>
       </c>
@@ -8209,7 +8248,7 @@
         <v>0.3000000000000001</v>
       </c>
     </row>
-    <row r="49" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A49" s="57" t="s">
         <v>120</v>
       </c>
@@ -8263,7 +8302,7 @@
         <v>0.31000000000000011</v>
       </c>
     </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A50" s="57" t="s">
         <v>121</v>
       </c>
@@ -8318,7 +8357,7 @@
       </c>
       <c r="Q50" s="43"/>
     </row>
-    <row r="51" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A51" s="57" t="s">
         <v>120</v>
       </c>
@@ -8373,7 +8412,7 @@
       </c>
       <c r="Q51" s="43"/>
     </row>
-    <row r="52" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A52" s="57" t="s">
         <v>122</v>
       </c>
@@ -8430,7 +8469,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="53" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A53" s="57" t="s">
         <v>122</v>
       </c>
@@ -8484,7 +8523,7 @@
         <v>0.35000000000000014</v>
       </c>
     </row>
-    <row r="54" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A54" s="57" t="s">
         <v>122</v>
       </c>
@@ -8535,7 +8574,7 @@
         <v>0.36000000000000015</v>
       </c>
     </row>
-    <row r="55" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A55" s="57" t="s">
         <v>120</v>
       </c>
@@ -8590,7 +8629,7 @@
       </c>
       <c r="R55" s="59"/>
     </row>
-    <row r="56" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A56" s="57" t="s">
         <v>121</v>
       </c>
@@ -8646,7 +8685,7 @@
         <v>0.38000000000000017</v>
       </c>
     </row>
-    <row r="57" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A57" s="57" t="s">
         <v>120</v>
       </c>
@@ -8697,7 +8736,7 @@
         <v>0.39000000000000018</v>
       </c>
     </row>
-    <row r="58" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A58" s="57" t="s">
         <v>122</v>
       </c>
@@ -8752,7 +8791,7 @@
         <v>0.40000000000000019</v>
       </c>
     </row>
-    <row r="59" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A59" s="108" t="s">
         <v>122</v>
       </c>
@@ -8809,7 +8848,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="60" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A60" s="108" t="s">
         <v>122</v>
       </c>
@@ -8866,7 +8905,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="61" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A61" s="108" t="s">
         <v>120</v>
       </c>
@@ -8920,7 +8959,7 @@
         <v>0.43000000000000022</v>
       </c>
     </row>
-    <row r="62" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A62" s="108" t="s">
         <v>121</v>
       </c>
@@ -8974,7 +9013,7 @@
         <v>0.44000000000000022</v>
       </c>
     </row>
-    <row r="63" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A63" s="57" t="s">
         <v>120</v>
       </c>
@@ -9028,7 +9067,7 @@
         <v>0.45000000000000023</v>
       </c>
     </row>
-    <row r="64" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A64" s="57" t="s">
         <v>122</v>
       </c>
@@ -9084,7 +9123,7 @@
         <v>0.46000000000000024</v>
       </c>
     </row>
-    <row r="65" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A65" s="57" t="s">
         <v>122</v>
       </c>
@@ -9138,7 +9177,7 @@
         <v>0.47000000000000025</v>
       </c>
     </row>
-    <row r="66" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A66" s="57" t="s">
         <v>122</v>
       </c>
@@ -9193,7 +9232,7 @@
       </c>
       <c r="S66" s="181"/>
     </row>
-    <row r="67" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A67" s="57" t="s">
         <v>120</v>
       </c>
@@ -9248,7 +9287,7 @@
       </c>
       <c r="S67" s="43"/>
     </row>
-    <row r="68" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A68" s="139" t="s">
         <v>121</v>
       </c>
@@ -9302,7 +9341,7 @@
         <v>0.50000000000000022</v>
       </c>
     </row>
-    <row r="69" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A69" s="57" t="s">
         <v>120</v>
       </c>
@@ -9356,7 +9395,7 @@
         <v>0.51000000000000023</v>
       </c>
     </row>
-    <row r="70" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A70" s="57" t="s">
         <v>122</v>
       </c>
@@ -9410,7 +9449,7 @@
         <v>0.52000000000000024</v>
       </c>
     </row>
-    <row r="71" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A71" s="57" t="s">
         <v>122</v>
       </c>
@@ -9467,7 +9506,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="72" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A72" s="57" t="s">
         <v>122</v>
       </c>
@@ -9521,7 +9560,7 @@
         <v>0.54000000000000026</v>
       </c>
     </row>
-    <row r="73" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A73" s="57" t="s">
         <v>123</v>
       </c>
@@ -9576,7 +9615,7 @@
       </c>
       <c r="Q73" s="73"/>
     </row>
-    <row r="74" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A74" s="57" t="s">
         <v>120</v>
       </c>
@@ -9630,7 +9669,7 @@
         <v>0.56000000000000028</v>
       </c>
     </row>
-    <row r="75" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A75" s="57" t="s">
         <v>122</v>
       </c>
@@ -9683,7 +9722,7 @@
         <v>0.57000000000000028</v>
       </c>
     </row>
-    <row r="76" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A76" s="57" t="s">
         <v>122</v>
       </c>
@@ -9736,7 +9775,7 @@
         <v>0.58000000000000029</v>
       </c>
     </row>
-    <row r="77" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A77" s="57" t="s">
         <v>122</v>
       </c>
@@ -9790,7 +9829,7 @@
         <v>0.5900000000000003</v>
       </c>
     </row>
-    <row r="78" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A78" s="57" t="s">
         <v>123</v>
       </c>
@@ -9844,7 +9883,7 @@
         <v>0.60000000000000031</v>
       </c>
     </row>
-    <row r="79" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A79" s="57" t="s">
         <v>120</v>
       </c>
@@ -9898,7 +9937,7 @@
         <v>0.61000000000000032</v>
       </c>
     </row>
-    <row r="80" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A80" s="57" t="s">
         <v>122</v>
       </c>
@@ -9952,7 +9991,7 @@
         <v>0.62000000000000033</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A81" s="57" t="s">
         <v>122</v>
       </c>
@@ -10008,7 +10047,7 @@
         <v>0.63000000000000034</v>
       </c>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A82" s="57" t="s">
         <v>122</v>
       </c>
@@ -10065,7 +10104,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A83" s="57" t="s">
         <v>123</v>
       </c>
@@ -10119,7 +10158,7 @@
         <v>0.65000000000000036</v>
       </c>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A84" s="57" t="s">
         <v>120</v>
       </c>
@@ -10173,7 +10212,7 @@
         <v>0.66000000000000036</v>
       </c>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A85" s="57" t="s">
         <v>122</v>
       </c>
@@ -10227,7 +10266,7 @@
         <v>0.67000000000000037</v>
       </c>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A86" s="57" t="s">
         <v>122</v>
       </c>
@@ -10281,7 +10320,7 @@
         <v>0.68000000000000038</v>
       </c>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A87" s="108" t="s">
         <v>122</v>
       </c>
@@ -10335,7 +10374,7 @@
         <v>0.69000000000000039</v>
       </c>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A88" s="108"/>
       <c r="B88" s="35"/>
       <c r="C88" s="35" t="s">
@@ -10387,7 +10426,7 @@
         <v>0.7000000000000004</v>
       </c>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A89" s="108"/>
       <c r="B89" s="35"/>
       <c r="C89" s="35" t="s">
@@ -10439,7 +10478,7 @@
         <v>0.71000000000000041</v>
       </c>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A90" s="108"/>
       <c r="B90" s="35"/>
       <c r="C90" s="35" t="s">
@@ -10491,7 +10530,7 @@
         <v>0.72000000000000042</v>
       </c>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A91" s="108"/>
       <c r="B91" s="35"/>
       <c r="C91" s="35" t="s">
@@ -10542,7 +10581,7 @@
         <v>0.73000000000000043</v>
       </c>
     </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A92" s="108"/>
       <c r="B92" s="35"/>
       <c r="C92" s="175" t="s">
@@ -10597,7 +10636,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A93" s="108"/>
       <c r="B93" s="35"/>
       <c r="C93" s="35" t="s">
@@ -10649,7 +10688,7 @@
         <v>0.75000000000000044</v>
       </c>
     </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A94" s="108"/>
       <c r="B94" s="35"/>
       <c r="C94" s="35" t="s">
@@ -10701,7 +10740,7 @@
         <v>0.76000000000000045</v>
       </c>
     </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A95" s="108"/>
       <c r="B95" s="35"/>
       <c r="C95" s="35" t="s">
@@ -10753,7 +10792,7 @@
         <v>0.77000000000000046</v>
       </c>
     </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A96" s="108"/>
       <c r="B96" s="35"/>
       <c r="C96" s="35" t="s">
@@ -10805,7 +10844,7 @@
         <v>0.78000000000000047</v>
       </c>
     </row>
-    <row r="97" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A97" s="108"/>
       <c r="B97" s="35"/>
       <c r="C97" s="35" t="s">
@@ -10854,7 +10893,7 @@
         <v>0.79000000000000048</v>
       </c>
     </row>
-    <row r="98" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A98" s="108"/>
       <c r="B98" s="35"/>
       <c r="C98" s="35" t="s">
@@ -10906,7 +10945,7 @@
         <v>0.80000000000000049</v>
       </c>
     </row>
-    <row r="99" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A99" s="108"/>
       <c r="B99" s="35"/>
       <c r="C99" s="35" t="s">
@@ -10958,7 +10997,7 @@
         <v>0.8100000000000005</v>
       </c>
     </row>
-    <row r="100" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A100" s="108"/>
       <c r="B100" s="35"/>
       <c r="C100" s="35" t="s">
@@ -11010,7 +11049,7 @@
         <v>0.82000000000000051</v>
       </c>
     </row>
-    <row r="101" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A101" s="108"/>
       <c r="B101" s="35"/>
       <c r="C101" s="35" t="s">
@@ -11059,7 +11098,7 @@
         <v>0.83000000000000052</v>
       </c>
     </row>
-    <row r="102" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="108"/>
       <c r="B102" s="35"/>
       <c r="C102" s="35" t="s">
@@ -11111,7 +11150,7 @@
         <v>0.84000000000000052</v>
       </c>
     </row>
-    <row r="103" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="108"/>
       <c r="B103" s="35"/>
       <c r="C103" s="35" t="s">
@@ -11163,7 +11202,7 @@
         <v>0.85000000000000053</v>
       </c>
     </row>
-    <row r="104" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="108"/>
       <c r="B104" s="35"/>
       <c r="C104" s="35" t="s">
@@ -11215,7 +11254,7 @@
         <v>0.86000000000000054</v>
       </c>
     </row>
-    <row r="105" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="108"/>
       <c r="B105" s="35"/>
       <c r="C105" s="35" t="s">
@@ -11267,7 +11306,7 @@
         <v>0.87000000000000055</v>
       </c>
     </row>
-    <row r="106" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="108"/>
       <c r="B106" s="35"/>
       <c r="C106" s="35" t="s">
@@ -11319,7 +11358,7 @@
         <v>0.88000000000000056</v>
       </c>
     </row>
-    <row r="107" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="108"/>
       <c r="B107" s="35"/>
       <c r="C107" s="35" t="s">
@@ -11370,7 +11409,7 @@
         <v>0.89000000000000057</v>
       </c>
     </row>
-    <row r="108" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="108"/>
       <c r="B108" s="35"/>
       <c r="C108" s="35" t="s">
@@ -11422,7 +11461,7 @@
         <v>0.90000000000000058</v>
       </c>
     </row>
-    <row r="109" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="108"/>
       <c r="B109" s="35"/>
       <c r="C109" s="35" t="s">
@@ -11474,7 +11513,7 @@
         <v>0.91000000000000059</v>
       </c>
     </row>
-    <row r="110" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="108"/>
       <c r="B110" s="35"/>
       <c r="C110" s="35" t="s">
@@ -11526,7 +11565,7 @@
         <v>0.9200000000000006</v>
       </c>
     </row>
-    <row r="111" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="108"/>
       <c r="B111" s="35"/>
       <c r="C111" s="35" t="s">
@@ -11578,7 +11617,7 @@
         <v>0.9300000000000006</v>
       </c>
     </row>
-    <row r="112" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A112" s="108"/>
       <c r="B112" s="35"/>
       <c r="C112" s="35" t="s">
@@ -11629,7 +11668,7 @@
         <v>0.94000000000000061</v>
       </c>
     </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A113" s="108"/>
       <c r="B113" s="35"/>
       <c r="C113" s="35" t="s">
@@ -11681,7 +11720,7 @@
         <v>0.95000000000000062</v>
       </c>
     </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A114" s="108"/>
       <c r="B114" s="35"/>
       <c r="C114" s="35" t="s">
@@ -11733,7 +11772,7 @@
         <v>0.96000000000000063</v>
       </c>
     </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A115" s="108"/>
       <c r="B115" s="35"/>
       <c r="C115" s="35" t="s">
@@ -11785,7 +11824,7 @@
         <v>0.97000000000000064</v>
       </c>
     </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A116" s="108"/>
       <c r="B116" s="35"/>
       <c r="C116" s="35" t="s">
@@ -11836,7 +11875,7 @@
         <v>0.98000000000000065</v>
       </c>
     </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A117" s="108"/>
       <c r="B117" s="35"/>
       <c r="C117" s="35" t="s">
@@ -11885,7 +11924,7 @@
         <v>0.99000000000000066</v>
       </c>
     </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A118" s="108"/>
       <c r="B118" s="35"/>
       <c r="C118" s="194" t="s">
@@ -11940,7 +11979,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A119" s="127"/>
       <c r="B119" s="35"/>
       <c r="C119" s="35" t="s">
@@ -11992,7 +12031,7 @@
         <v>1.0100000000000007</v>
       </c>
     </row>
-    <row r="120" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A120" s="127"/>
       <c r="B120" s="35"/>
       <c r="C120" s="35" t="s">
@@ -12044,7 +12083,7 @@
         <v>1.0200000000000007</v>
       </c>
     </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A121" s="127"/>
       <c r="B121" s="35"/>
       <c r="C121" s="35" t="s">
@@ -12093,7 +12132,7 @@
         <v>1.0300000000000007</v>
       </c>
     </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A122" s="127"/>
       <c r="B122" s="35"/>
       <c r="C122" s="35" t="s">
@@ -12145,7 +12184,7 @@
         <v>1.0400000000000007</v>
       </c>
     </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A123" s="127"/>
       <c r="B123" s="35"/>
       <c r="C123" s="35" t="s">
@@ -12197,7 +12236,7 @@
         <v>1.0500000000000007</v>
       </c>
     </row>
-    <row r="124" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A124" s="127"/>
       <c r="B124" s="35"/>
       <c r="C124" s="35" t="s">
@@ -12252,7 +12291,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="125" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A125" s="174"/>
       <c r="B125" s="169"/>
       <c r="C125" s="35" t="s">
@@ -12303,7 +12342,7 @@
         <v>1.0700000000000007</v>
       </c>
     </row>
-    <row r="126" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A126" s="174"/>
       <c r="B126" s="169"/>
       <c r="C126" s="35" t="s">
@@ -12355,7 +12394,7 @@
         <v>1.0800000000000007</v>
       </c>
     </row>
-    <row r="127" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A127" s="127"/>
       <c r="B127" s="35"/>
       <c r="C127" s="35" t="s">
@@ -12407,7 +12446,7 @@
         <v>1.0900000000000007</v>
       </c>
     </row>
-    <row r="128" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A128" s="127"/>
       <c r="B128" s="35"/>
       <c r="C128" s="35" t="s">
@@ -12459,7 +12498,7 @@
         <v>1.1000000000000008</v>
       </c>
     </row>
-    <row r="129" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A129" s="127"/>
       <c r="B129" s="35"/>
       <c r="C129" s="35" t="s">
@@ -12511,7 +12550,7 @@
         <v>1.1100000000000008</v>
       </c>
     </row>
-    <row r="130" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A130" s="127" t="s">
         <v>26</v>
       </c>
@@ -12565,7 +12604,7 @@
         <v>1.1200000000000008</v>
       </c>
     </row>
-    <row r="131" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A131" s="127" t="s">
         <v>26</v>
       </c>
@@ -12619,7 +12658,7 @@
         <v>1.1300000000000008</v>
       </c>
     </row>
-    <row r="132" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A132" s="53" t="s">
         <v>26</v>
       </c>
@@ -12638,7 +12677,7 @@
       <c r="N132" s="5"/>
       <c r="O132" s="8"/>
     </row>
-    <row r="133" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="27"/>
       <c r="B133" s="27"/>
       <c r="C133" s="27"/>
@@ -12672,51 +12711,51 @@
       </c>
       <c r="N133" s="29">
         <f>SUM(N14:N132)</f>
-        <v>20755218.834001999</v>
+        <v>21120758.162442002</v>
       </c>
       <c r="O133" s="28">
         <f>SUM(O14:O132)</f>
-        <v>22000604.519442119</v>
+        <v>22388076.207588516</v>
       </c>
       <c r="Q133" s="59"/>
     </row>
-    <row r="134" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="L134" s="61">
         <f>L133-M1</f>
         <v>-4034495.9149199985</v>
       </c>
     </row>
-    <row r="135" spans="1:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C135" s="261"/>
-      <c r="D135" s="261"/>
-      <c r="E135" s="261"/>
-      <c r="F135" s="261"/>
-      <c r="G135" s="261"/>
-      <c r="H135" s="261"/>
-      <c r="I135" s="261"/>
-      <c r="J135" s="261"/>
-      <c r="K135" s="261"/>
-      <c r="L135" s="261"/>
-      <c r="M135" s="261"/>
-      <c r="N135" s="261"/>
-      <c r="O135" s="261"/>
-    </row>
-    <row r="136" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
-      <c r="C136" s="261"/>
-      <c r="D136" s="261"/>
-      <c r="E136" s="261"/>
-      <c r="F136" s="261"/>
-      <c r="G136" s="261"/>
-      <c r="H136" s="261"/>
-      <c r="I136" s="261"/>
-      <c r="J136" s="261"/>
-      <c r="K136" s="261"/>
-      <c r="L136" s="261"/>
-      <c r="M136" s="261"/>
-      <c r="N136" s="261"/>
-      <c r="O136" s="261"/>
-    </row>
-    <row r="137" spans="1:17" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C135" s="276"/>
+      <c r="D135" s="276"/>
+      <c r="E135" s="276"/>
+      <c r="F135" s="276"/>
+      <c r="G135" s="276"/>
+      <c r="H135" s="276"/>
+      <c r="I135" s="276"/>
+      <c r="J135" s="276"/>
+      <c r="K135" s="276"/>
+      <c r="L135" s="276"/>
+      <c r="M135" s="276"/>
+      <c r="N135" s="276"/>
+      <c r="O135" s="276"/>
+    </row>
+    <row r="136" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="C136" s="276"/>
+      <c r="D136" s="276"/>
+      <c r="E136" s="276"/>
+      <c r="F136" s="276"/>
+      <c r="G136" s="276"/>
+      <c r="H136" s="276"/>
+      <c r="I136" s="276"/>
+      <c r="J136" s="276"/>
+      <c r="K136" s="276"/>
+      <c r="L136" s="276"/>
+      <c r="M136" s="276"/>
+      <c r="N136" s="276"/>
+      <c r="O136" s="276"/>
+    </row>
+    <row r="137" spans="1:17" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C137" s="77"/>
       <c r="D137" s="77"/>
       <c r="E137" s="77"/>
@@ -12731,129 +12770,129 @@
       <c r="N137" s="77"/>
       <c r="O137" s="77"/>
     </row>
-    <row r="138" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="C138" s="242" t="s">
+    <row r="138" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="C138" s="250" t="s">
         <v>258</v>
       </c>
-      <c r="D138" s="242"/>
-      <c r="E138" s="242"/>
-      <c r="F138" s="242"/>
-      <c r="G138" s="242"/>
-      <c r="H138" s="242"/>
-      <c r="I138" s="242"/>
-      <c r="J138" s="242"/>
-      <c r="K138" s="242"/>
-      <c r="L138" s="242"/>
-      <c r="M138" s="242"/>
-      <c r="N138" s="242"/>
-      <c r="O138" s="242"/>
-    </row>
-    <row r="139" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="C139" s="242"/>
-      <c r="D139" s="242"/>
-      <c r="E139" s="242"/>
-      <c r="F139" s="242"/>
-      <c r="G139" s="242"/>
-      <c r="H139" s="242"/>
-      <c r="I139" s="242"/>
-      <c r="J139" s="242"/>
-      <c r="K139" s="242"/>
-      <c r="L139" s="242"/>
-      <c r="M139" s="242"/>
-      <c r="N139" s="242"/>
-      <c r="O139" s="242"/>
-    </row>
-    <row r="140" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="C140" s="242"/>
-      <c r="D140" s="242"/>
-      <c r="E140" s="242"/>
-      <c r="F140" s="242"/>
-      <c r="G140" s="242"/>
-      <c r="H140" s="242"/>
-      <c r="I140" s="242"/>
-      <c r="J140" s="242"/>
-      <c r="K140" s="242"/>
-      <c r="L140" s="242"/>
-      <c r="M140" s="242"/>
-      <c r="N140" s="242"/>
-      <c r="O140" s="242"/>
-    </row>
-    <row r="141" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="C141" s="242"/>
-      <c r="D141" s="242"/>
-      <c r="E141" s="242"/>
-      <c r="F141" s="242"/>
-      <c r="G141" s="242"/>
-      <c r="H141" s="242"/>
-      <c r="I141" s="242"/>
-      <c r="J141" s="242"/>
-      <c r="K141" s="242"/>
-      <c r="L141" s="242"/>
-      <c r="M141" s="242"/>
-      <c r="N141" s="242"/>
-      <c r="O141" s="242"/>
-    </row>
-    <row r="142" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="C142" s="242"/>
-      <c r="D142" s="242"/>
-      <c r="E142" s="242"/>
-      <c r="F142" s="242"/>
-      <c r="G142" s="242"/>
-      <c r="H142" s="242"/>
-      <c r="I142" s="242"/>
-      <c r="J142" s="242"/>
-      <c r="K142" s="242"/>
-      <c r="L142" s="242"/>
-      <c r="M142" s="242"/>
-      <c r="N142" s="242"/>
-      <c r="O142" s="242"/>
-    </row>
-    <row r="143" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="C143" s="242"/>
-      <c r="D143" s="242"/>
-      <c r="E143" s="242"/>
-      <c r="F143" s="242"/>
-      <c r="G143" s="242"/>
-      <c r="H143" s="242"/>
-      <c r="I143" s="242"/>
-      <c r="J143" s="242"/>
-      <c r="K143" s="242"/>
-      <c r="L143" s="242"/>
-      <c r="M143" s="242"/>
-      <c r="N143" s="242"/>
-      <c r="O143" s="242"/>
-    </row>
-    <row r="144" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="C144" s="242"/>
-      <c r="D144" s="242"/>
-      <c r="E144" s="242"/>
-      <c r="F144" s="242"/>
-      <c r="G144" s="242"/>
-      <c r="H144" s="242"/>
-      <c r="I144" s="242"/>
-      <c r="J144" s="242"/>
-      <c r="K144" s="242"/>
-      <c r="L144" s="242"/>
-      <c r="M144" s="242"/>
-      <c r="N144" s="242"/>
-      <c r="O144" s="242"/>
-    </row>
-    <row r="145" spans="3:17" x14ac:dyDescent="0.3">
-      <c r="C145" s="242"/>
-      <c r="D145" s="242"/>
-      <c r="E145" s="242"/>
-      <c r="F145" s="242"/>
-      <c r="G145" s="242"/>
-      <c r="H145" s="242"/>
-      <c r="I145" s="242"/>
-      <c r="J145" s="242"/>
-      <c r="K145" s="242"/>
-      <c r="L145" s="242"/>
-      <c r="M145" s="242"/>
-      <c r="N145" s="242"/>
-      <c r="O145" s="242"/>
-    </row>
-    <row r="146" spans="3:17" ht="6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D138" s="250"/>
+      <c r="E138" s="250"/>
+      <c r="F138" s="250"/>
+      <c r="G138" s="250"/>
+      <c r="H138" s="250"/>
+      <c r="I138" s="250"/>
+      <c r="J138" s="250"/>
+      <c r="K138" s="250"/>
+      <c r="L138" s="250"/>
+      <c r="M138" s="250"/>
+      <c r="N138" s="250"/>
+      <c r="O138" s="250"/>
+    </row>
+    <row r="139" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="C139" s="250"/>
+      <c r="D139" s="250"/>
+      <c r="E139" s="250"/>
+      <c r="F139" s="250"/>
+      <c r="G139" s="250"/>
+      <c r="H139" s="250"/>
+      <c r="I139" s="250"/>
+      <c r="J139" s="250"/>
+      <c r="K139" s="250"/>
+      <c r="L139" s="250"/>
+      <c r="M139" s="250"/>
+      <c r="N139" s="250"/>
+      <c r="O139" s="250"/>
+    </row>
+    <row r="140" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="C140" s="250"/>
+      <c r="D140" s="250"/>
+      <c r="E140" s="250"/>
+      <c r="F140" s="250"/>
+      <c r="G140" s="250"/>
+      <c r="H140" s="250"/>
+      <c r="I140" s="250"/>
+      <c r="J140" s="250"/>
+      <c r="K140" s="250"/>
+      <c r="L140" s="250"/>
+      <c r="M140" s="250"/>
+      <c r="N140" s="250"/>
+      <c r="O140" s="250"/>
+    </row>
+    <row r="141" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="C141" s="250"/>
+      <c r="D141" s="250"/>
+      <c r="E141" s="250"/>
+      <c r="F141" s="250"/>
+      <c r="G141" s="250"/>
+      <c r="H141" s="250"/>
+      <c r="I141" s="250"/>
+      <c r="J141" s="250"/>
+      <c r="K141" s="250"/>
+      <c r="L141" s="250"/>
+      <c r="M141" s="250"/>
+      <c r="N141" s="250"/>
+      <c r="O141" s="250"/>
+    </row>
+    <row r="142" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="C142" s="250"/>
+      <c r="D142" s="250"/>
+      <c r="E142" s="250"/>
+      <c r="F142" s="250"/>
+      <c r="G142" s="250"/>
+      <c r="H142" s="250"/>
+      <c r="I142" s="250"/>
+      <c r="J142" s="250"/>
+      <c r="K142" s="250"/>
+      <c r="L142" s="250"/>
+      <c r="M142" s="250"/>
+      <c r="N142" s="250"/>
+      <c r="O142" s="250"/>
+    </row>
+    <row r="143" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="C143" s="250"/>
+      <c r="D143" s="250"/>
+      <c r="E143" s="250"/>
+      <c r="F143" s="250"/>
+      <c r="G143" s="250"/>
+      <c r="H143" s="250"/>
+      <c r="I143" s="250"/>
+      <c r="J143" s="250"/>
+      <c r="K143" s="250"/>
+      <c r="L143" s="250"/>
+      <c r="M143" s="250"/>
+      <c r="N143" s="250"/>
+      <c r="O143" s="250"/>
+    </row>
+    <row r="144" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="C144" s="250"/>
+      <c r="D144" s="250"/>
+      <c r="E144" s="250"/>
+      <c r="F144" s="250"/>
+      <c r="G144" s="250"/>
+      <c r="H144" s="250"/>
+      <c r="I144" s="250"/>
+      <c r="J144" s="250"/>
+      <c r="K144" s="250"/>
+      <c r="L144" s="250"/>
+      <c r="M144" s="250"/>
+      <c r="N144" s="250"/>
+      <c r="O144" s="250"/>
+    </row>
+    <row r="145" spans="3:17" x14ac:dyDescent="0.25">
+      <c r="C145" s="250"/>
+      <c r="D145" s="250"/>
+      <c r="E145" s="250"/>
+      <c r="F145" s="250"/>
+      <c r="G145" s="250"/>
+      <c r="H145" s="250"/>
+      <c r="I145" s="250"/>
+      <c r="J145" s="250"/>
+      <c r="K145" s="250"/>
+      <c r="L145" s="250"/>
+      <c r="M145" s="250"/>
+      <c r="N145" s="250"/>
+      <c r="O145" s="250"/>
+    </row>
+    <row r="146" spans="3:17" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C146" s="77"/>
       <c r="D146" s="77"/>
       <c r="E146" s="77"/>
@@ -12868,7 +12907,7 @@
       <c r="N146" s="77"/>
       <c r="O146" s="77"/>
     </row>
-    <row r="147" spans="3:17" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="3:17" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C147" s="77"/>
       <c r="D147" s="77"/>
       <c r="E147" s="77"/>
@@ -12883,126 +12922,119 @@
       <c r="N147" s="77"/>
       <c r="O147" s="77"/>
     </row>
-    <row r="148" spans="3:17" x14ac:dyDescent="0.3">
-      <c r="C148" s="260" t="s">
+    <row r="148" spans="3:17" x14ac:dyDescent="0.25">
+      <c r="C148" s="275" t="s">
         <v>257</v>
       </c>
-      <c r="D148" s="260"/>
-      <c r="E148" s="260"/>
-      <c r="F148" s="260"/>
-      <c r="G148" s="260"/>
-      <c r="H148" s="260"/>
-      <c r="I148" s="260"/>
-      <c r="J148" s="260"/>
-      <c r="K148" s="260"/>
-      <c r="L148" s="260"/>
-      <c r="M148" s="260"/>
-      <c r="N148" s="260"/>
-      <c r="O148" s="260"/>
-    </row>
-    <row r="149" spans="3:17" x14ac:dyDescent="0.3">
-      <c r="C149" s="260"/>
-      <c r="D149" s="260"/>
-      <c r="E149" s="260"/>
-      <c r="F149" s="260"/>
-      <c r="G149" s="260"/>
-      <c r="H149" s="260"/>
-      <c r="I149" s="260"/>
-      <c r="J149" s="260"/>
-      <c r="K149" s="260"/>
-      <c r="L149" s="260"/>
-      <c r="M149" s="260"/>
-      <c r="N149" s="260"/>
-      <c r="O149" s="260"/>
-    </row>
-    <row r="150" spans="3:17" x14ac:dyDescent="0.3">
-      <c r="C150" s="260"/>
-      <c r="D150" s="260"/>
-      <c r="E150" s="260"/>
-      <c r="F150" s="260"/>
-      <c r="G150" s="260"/>
-      <c r="H150" s="260"/>
-      <c r="I150" s="260"/>
-      <c r="J150" s="260"/>
-      <c r="K150" s="260"/>
-      <c r="L150" s="260"/>
-      <c r="M150" s="260"/>
-      <c r="N150" s="260"/>
-      <c r="O150" s="260"/>
+      <c r="D148" s="275"/>
+      <c r="E148" s="275"/>
+      <c r="F148" s="275"/>
+      <c r="G148" s="275"/>
+      <c r="H148" s="275"/>
+      <c r="I148" s="275"/>
+      <c r="J148" s="275"/>
+      <c r="K148" s="275"/>
+      <c r="L148" s="275"/>
+      <c r="M148" s="275"/>
+      <c r="N148" s="275"/>
+      <c r="O148" s="275"/>
+    </row>
+    <row r="149" spans="3:17" x14ac:dyDescent="0.25">
+      <c r="C149" s="275"/>
+      <c r="D149" s="275"/>
+      <c r="E149" s="275"/>
+      <c r="F149" s="275"/>
+      <c r="G149" s="275"/>
+      <c r="H149" s="275"/>
+      <c r="I149" s="275"/>
+      <c r="J149" s="275"/>
+      <c r="K149" s="275"/>
+      <c r="L149" s="275"/>
+      <c r="M149" s="275"/>
+      <c r="N149" s="275"/>
+      <c r="O149" s="275"/>
+    </row>
+    <row r="150" spans="3:17" x14ac:dyDescent="0.25">
+      <c r="C150" s="275"/>
+      <c r="D150" s="275"/>
+      <c r="E150" s="275"/>
+      <c r="F150" s="275"/>
+      <c r="G150" s="275"/>
+      <c r="H150" s="275"/>
+      <c r="I150" s="275"/>
+      <c r="J150" s="275"/>
+      <c r="K150" s="275"/>
+      <c r="L150" s="275"/>
+      <c r="M150" s="275"/>
+      <c r="N150" s="275"/>
+      <c r="O150" s="275"/>
       <c r="Q150" s="84">
         <f>M1-L133</f>
         <v>4034495.9149199985</v>
       </c>
     </row>
-    <row r="151" spans="3:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C151" s="260"/>
-      <c r="D151" s="260"/>
-      <c r="E151" s="260"/>
-      <c r="F151" s="260"/>
-      <c r="G151" s="260"/>
-      <c r="H151" s="260"/>
-      <c r="I151" s="260"/>
-      <c r="J151" s="260"/>
-      <c r="K151" s="260"/>
-      <c r="L151" s="260"/>
-      <c r="M151" s="260"/>
-      <c r="N151" s="260"/>
-      <c r="O151" s="260"/>
-    </row>
-    <row r="152" spans="3:17" ht="5.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C152" s="260"/>
-      <c r="D152" s="260"/>
-      <c r="E152" s="260"/>
-      <c r="F152" s="260"/>
-      <c r="G152" s="260"/>
-      <c r="H152" s="260"/>
-      <c r="I152" s="260"/>
-      <c r="J152" s="260"/>
-      <c r="K152" s="260"/>
-      <c r="L152" s="260"/>
-      <c r="M152" s="260"/>
-      <c r="N152" s="260"/>
-      <c r="O152" s="260"/>
-    </row>
-    <row r="153" spans="3:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C153" s="260"/>
-      <c r="D153" s="260"/>
-      <c r="E153" s="260"/>
-      <c r="F153" s="260"/>
-      <c r="G153" s="260"/>
-      <c r="H153" s="260"/>
-      <c r="I153" s="260"/>
-      <c r="J153" s="260"/>
-      <c r="K153" s="260"/>
-      <c r="L153" s="260"/>
-      <c r="M153" s="260"/>
-      <c r="N153" s="260"/>
-      <c r="O153" s="260"/>
-    </row>
-    <row r="154" spans="3:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C154" s="260"/>
-      <c r="D154" s="260"/>
-      <c r="E154" s="260"/>
-      <c r="F154" s="260"/>
-      <c r="G154" s="260"/>
-      <c r="H154" s="260"/>
-      <c r="I154" s="260"/>
-      <c r="J154" s="260"/>
-      <c r="K154" s="260"/>
-      <c r="L154" s="260"/>
-      <c r="M154" s="260"/>
-      <c r="N154" s="260"/>
-      <c r="O154" s="260"/>
+    <row r="151" spans="3:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C151" s="275"/>
+      <c r="D151" s="275"/>
+      <c r="E151" s="275"/>
+      <c r="F151" s="275"/>
+      <c r="G151" s="275"/>
+      <c r="H151" s="275"/>
+      <c r="I151" s="275"/>
+      <c r="J151" s="275"/>
+      <c r="K151" s="275"/>
+      <c r="L151" s="275"/>
+      <c r="M151" s="275"/>
+      <c r="N151" s="275"/>
+      <c r="O151" s="275"/>
+    </row>
+    <row r="152" spans="3:17" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C152" s="275"/>
+      <c r="D152" s="275"/>
+      <c r="E152" s="275"/>
+      <c r="F152" s="275"/>
+      <c r="G152" s="275"/>
+      <c r="H152" s="275"/>
+      <c r="I152" s="275"/>
+      <c r="J152" s="275"/>
+      <c r="K152" s="275"/>
+      <c r="L152" s="275"/>
+      <c r="M152" s="275"/>
+      <c r="N152" s="275"/>
+      <c r="O152" s="275"/>
+    </row>
+    <row r="153" spans="3:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C153" s="275"/>
+      <c r="D153" s="275"/>
+      <c r="E153" s="275"/>
+      <c r="F153" s="275"/>
+      <c r="G153" s="275"/>
+      <c r="H153" s="275"/>
+      <c r="I153" s="275"/>
+      <c r="J153" s="275"/>
+      <c r="K153" s="275"/>
+      <c r="L153" s="275"/>
+      <c r="M153" s="275"/>
+      <c r="N153" s="275"/>
+      <c r="O153" s="275"/>
+    </row>
+    <row r="154" spans="3:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C154" s="275"/>
+      <c r="D154" s="275"/>
+      <c r="E154" s="275"/>
+      <c r="F154" s="275"/>
+      <c r="G154" s="275"/>
+      <c r="H154" s="275"/>
+      <c r="I154" s="275"/>
+      <c r="J154" s="275"/>
+      <c r="K154" s="275"/>
+      <c r="L154" s="275"/>
+      <c r="M154" s="275"/>
+      <c r="N154" s="275"/>
+      <c r="O154" s="275"/>
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="K11:K13"/>
-    <mergeCell ref="A11:A13"/>
-    <mergeCell ref="B11:B13"/>
-    <mergeCell ref="C11:C13"/>
-    <mergeCell ref="D11:D13"/>
-    <mergeCell ref="F11:F13"/>
-    <mergeCell ref="E11:E13"/>
     <mergeCell ref="R14:S15"/>
     <mergeCell ref="G11:G13"/>
     <mergeCell ref="C148:O154"/>
@@ -13019,6 +13051,13 @@
     <mergeCell ref="C5:O8"/>
     <mergeCell ref="C9:O10"/>
     <mergeCell ref="A1:E4"/>
+    <mergeCell ref="K11:K13"/>
+    <mergeCell ref="A11:A13"/>
+    <mergeCell ref="B11:B13"/>
+    <mergeCell ref="C11:C13"/>
+    <mergeCell ref="D11:D13"/>
+    <mergeCell ref="F11:F13"/>
+    <mergeCell ref="E11:E13"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -13029,180 +13068,180 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7AB47CA-548A-40FB-AC1D-01E96423736C}">
   <dimension ref="A1:DH83"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.109375" customWidth="1"/>
-    <col min="2" max="2" width="8.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="47.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.33203125" customWidth="1"/>
-    <col min="5" max="5" width="14.109375" customWidth="1"/>
-    <col min="6" max="6" width="13.33203125" customWidth="1"/>
-    <col min="7" max="7" width="21.44140625" hidden="1" customWidth="1"/>
-    <col min="8" max="9" width="17.33203125" customWidth="1"/>
+    <col min="1" max="1" width="7.140625" customWidth="1"/>
+    <col min="2" max="2" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="47.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.28515625" customWidth="1"/>
+    <col min="5" max="5" width="14.140625" customWidth="1"/>
+    <col min="6" max="6" width="13.28515625" customWidth="1"/>
+    <col min="7" max="7" width="21.42578125" hidden="1" customWidth="1"/>
+    <col min="8" max="9" width="17.28515625" customWidth="1"/>
     <col min="10" max="10" width="15" customWidth="1"/>
-    <col min="11" max="11" width="15.109375" hidden="1" customWidth="1"/>
-    <col min="12" max="12" width="15.109375" customWidth="1"/>
-    <col min="13" max="13" width="19.5546875" customWidth="1"/>
-    <col min="14" max="14" width="5.5546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="43.33203125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="17.88671875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.140625" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="15.140625" customWidth="1"/>
+    <col min="13" max="13" width="19.5703125" customWidth="1"/>
+    <col min="14" max="14" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="43.28515625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="296" t="s">
+    <row r="1" spans="1:25" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="310" t="s">
         <v>329</v>
       </c>
-      <c r="B1" s="296"/>
-      <c r="C1" s="296"/>
-      <c r="D1" s="296"/>
-      <c r="E1" s="296"/>
-      <c r="F1" s="296"/>
-      <c r="G1" s="296"/>
-      <c r="H1" s="296"/>
-      <c r="I1" s="296"/>
-      <c r="J1" s="296"/>
-      <c r="K1" s="296"/>
-      <c r="L1" s="296"/>
-      <c r="M1" s="297"/>
+      <c r="B1" s="310"/>
+      <c r="C1" s="310"/>
+      <c r="D1" s="310"/>
+      <c r="E1" s="310"/>
+      <c r="F1" s="310"/>
+      <c r="G1" s="310"/>
+      <c r="H1" s="310"/>
+      <c r="I1" s="310"/>
+      <c r="J1" s="310"/>
+      <c r="K1" s="310"/>
+      <c r="L1" s="310"/>
+      <c r="M1" s="311"/>
       <c r="P1" s="43"/>
     </row>
-    <row r="2" spans="1:25" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="298"/>
-      <c r="B2" s="298"/>
-      <c r="C2" s="298"/>
-      <c r="D2" s="298"/>
-      <c r="E2" s="298"/>
-      <c r="F2" s="298"/>
-      <c r="G2" s="298"/>
-      <c r="H2" s="298"/>
-      <c r="I2" s="298"/>
-      <c r="J2" s="298"/>
-      <c r="K2" s="298"/>
-      <c r="L2" s="298"/>
-      <c r="M2" s="299"/>
+    <row r="2" spans="1:25" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="312"/>
+      <c r="B2" s="312"/>
+      <c r="C2" s="312"/>
+      <c r="D2" s="312"/>
+      <c r="E2" s="312"/>
+      <c r="F2" s="312"/>
+      <c r="G2" s="312"/>
+      <c r="H2" s="312"/>
+      <c r="I2" s="312"/>
+      <c r="J2" s="312"/>
+      <c r="K2" s="312"/>
+      <c r="L2" s="312"/>
+      <c r="M2" s="313"/>
       <c r="P2" s="43"/>
     </row>
-    <row r="3" spans="1:25" ht="109.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="313" t="s">
+    <row r="3" spans="1:25" ht="109.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="304" t="s">
         <v>393</v>
       </c>
-      <c r="B3" s="314"/>
-      <c r="C3" s="314"/>
-      <c r="D3" s="314"/>
-      <c r="E3" s="314"/>
-      <c r="F3" s="314"/>
-      <c r="G3" s="314"/>
-      <c r="H3" s="314"/>
-      <c r="I3" s="314"/>
-      <c r="J3" s="314"/>
-      <c r="K3" s="314"/>
-      <c r="L3" s="314"/>
-      <c r="M3" s="315"/>
+      <c r="B3" s="305"/>
+      <c r="C3" s="305"/>
+      <c r="D3" s="305"/>
+      <c r="E3" s="305"/>
+      <c r="F3" s="305"/>
+      <c r="G3" s="305"/>
+      <c r="H3" s="305"/>
+      <c r="I3" s="305"/>
+      <c r="J3" s="305"/>
+      <c r="K3" s="305"/>
+      <c r="L3" s="305"/>
+      <c r="M3" s="306"/>
       <c r="P3" s="43"/>
     </row>
-    <row r="4" spans="1:25" s="311" customFormat="1" ht="94.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="316" t="s">
+    <row r="4" spans="1:25" s="248" customFormat="1" ht="94.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="307" t="s">
         <v>394</v>
       </c>
-      <c r="B4" s="317"/>
-      <c r="C4" s="317"/>
-      <c r="D4" s="317"/>
-      <c r="E4" s="317"/>
-      <c r="F4" s="317"/>
-      <c r="G4" s="317"/>
-      <c r="H4" s="317"/>
-      <c r="I4" s="317"/>
-      <c r="J4" s="317"/>
-      <c r="K4" s="317"/>
-      <c r="L4" s="317"/>
-      <c r="M4" s="318"/>
-      <c r="N4" s="312"/>
-      <c r="O4" s="312"/>
-      <c r="P4" s="312"/>
-      <c r="Q4" s="312"/>
-      <c r="R4" s="312"/>
-      <c r="S4" s="312"/>
-      <c r="T4" s="312"/>
-      <c r="U4" s="312"/>
-      <c r="V4" s="312"/>
-      <c r="W4" s="312"/>
-      <c r="X4" s="312"/>
-      <c r="Y4" s="312"/>
-    </row>
-    <row r="5" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="258" t="s">
+      <c r="B4" s="308"/>
+      <c r="C4" s="308"/>
+      <c r="D4" s="308"/>
+      <c r="E4" s="308"/>
+      <c r="F4" s="308"/>
+      <c r="G4" s="308"/>
+      <c r="H4" s="308"/>
+      <c r="I4" s="308"/>
+      <c r="J4" s="308"/>
+      <c r="K4" s="308"/>
+      <c r="L4" s="308"/>
+      <c r="M4" s="309"/>
+      <c r="N4" s="249"/>
+      <c r="O4" s="249"/>
+      <c r="P4" s="249"/>
+      <c r="Q4" s="249"/>
+      <c r="R4" s="249"/>
+      <c r="S4" s="249"/>
+      <c r="T4" s="249"/>
+      <c r="U4" s="249"/>
+      <c r="V4" s="249"/>
+      <c r="W4" s="249"/>
+      <c r="X4" s="249"/>
+      <c r="Y4" s="249"/>
+    </row>
+    <row r="5" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="268" t="s">
         <v>330</v>
       </c>
-      <c r="B5" s="258" t="s">
+      <c r="B5" s="268" t="s">
         <v>331</v>
       </c>
-      <c r="C5" s="258" t="s">
+      <c r="C5" s="268" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="258" t="s">
+      <c r="D5" s="268" t="s">
         <v>27</v>
       </c>
-      <c r="E5" s="266" t="s">
+      <c r="E5" s="265" t="s">
         <v>358</v>
       </c>
-      <c r="F5" s="266" t="s">
+      <c r="F5" s="265" t="s">
         <v>359</v>
       </c>
-      <c r="G5" s="266" t="s">
+      <c r="G5" s="265" t="s">
         <v>277</v>
       </c>
-      <c r="H5" s="266" t="s">
+      <c r="H5" s="265" t="s">
         <v>391</v>
       </c>
-      <c r="I5" s="266" t="s">
+      <c r="I5" s="265" t="s">
         <v>392</v>
       </c>
-      <c r="J5" s="300" t="s">
+      <c r="J5" s="314" t="s">
         <v>360</v>
       </c>
       <c r="K5" s="131"/>
-      <c r="L5" s="266" t="s">
+      <c r="L5" s="265" t="s">
         <v>361</v>
       </c>
-      <c r="M5" s="266" t="s">
+      <c r="M5" s="265" t="s">
         <v>17</v>
       </c>
       <c r="P5" s="43"/>
     </row>
-    <row r="6" spans="1:25" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="259"/>
-      <c r="B6" s="259"/>
-      <c r="C6" s="259"/>
-      <c r="D6" s="259"/>
-      <c r="E6" s="267"/>
-      <c r="F6" s="267"/>
-      <c r="G6" s="267"/>
-      <c r="H6" s="267"/>
-      <c r="I6" s="267"/>
-      <c r="J6" s="301"/>
+    <row r="6" spans="1:25" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="269"/>
+      <c r="B6" s="269"/>
+      <c r="C6" s="269"/>
+      <c r="D6" s="269"/>
+      <c r="E6" s="266"/>
+      <c r="F6" s="266"/>
+      <c r="G6" s="266"/>
+      <c r="H6" s="266"/>
+      <c r="I6" s="266"/>
+      <c r="J6" s="315"/>
       <c r="K6" s="131"/>
-      <c r="L6" s="267"/>
-      <c r="M6" s="267"/>
+      <c r="L6" s="266"/>
+      <c r="M6" s="266"/>
       <c r="P6" s="43"/>
     </row>
-    <row r="7" spans="1:25" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="304"/>
-      <c r="B7" s="304"/>
-      <c r="C7" s="304"/>
-      <c r="D7" s="304"/>
-      <c r="E7" s="303"/>
-      <c r="F7" s="303"/>
-      <c r="G7" s="303"/>
-      <c r="H7" s="303"/>
-      <c r="I7" s="303"/>
-      <c r="J7" s="302"/>
+    <row r="7" spans="1:25" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="318"/>
+      <c r="B7" s="318"/>
+      <c r="C7" s="318"/>
+      <c r="D7" s="318"/>
+      <c r="E7" s="317"/>
+      <c r="F7" s="317"/>
+      <c r="G7" s="317"/>
+      <c r="H7" s="317"/>
+      <c r="I7" s="317"/>
+      <c r="J7" s="316"/>
       <c r="K7" s="209"/>
-      <c r="L7" s="303"/>
-      <c r="M7" s="303"/>
+      <c r="L7" s="317"/>
+      <c r="M7" s="317"/>
       <c r="P7" s="43"/>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A8" s="210" t="s">
         <v>113</v>
       </c>
@@ -13222,11 +13261,11 @@
       <c r="G8" s="225">
         <v>-197064.48265741928</v>
       </c>
-      <c r="H8" s="305">
+      <c r="H8" s="242">
         <f>J8/2</f>
         <v>98532.35</v>
       </c>
-      <c r="I8" s="308">
+      <c r="I8" s="245">
         <f>H8</f>
         <v>98532.35</v>
       </c>
@@ -13248,10 +13287,10 @@
       <c r="N8" s="115">
         <v>0.7</v>
       </c>
-      <c r="P8" s="257"/>
-      <c r="Q8" s="257"/>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="P8" s="274"/>
+      <c r="Q8" s="274"/>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A9" s="210" t="s">
         <v>337</v>
       </c>
@@ -13271,11 +13310,11 @@
       <c r="G9" s="146">
         <v>-34751.379392876712</v>
       </c>
-      <c r="H9" s="305">
+      <c r="H9" s="242">
         <f t="shared" ref="H9:H12" si="0">J9/2</f>
         <v>17375.855</v>
       </c>
-      <c r="I9" s="308">
+      <c r="I9" s="245">
         <f t="shared" ref="I9:I12" si="1">H9</f>
         <v>17375.855</v>
       </c>
@@ -13298,10 +13337,10 @@
         <f>N8+0.01</f>
         <v>0.71</v>
       </c>
-      <c r="P9" s="257"/>
-      <c r="Q9" s="257"/>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="P9" s="274"/>
+      <c r="Q9" s="274"/>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A10" s="210" t="s">
         <v>114</v>
       </c>
@@ -13321,11 +13360,11 @@
       <c r="G10" s="146">
         <v>-220785.20742173825</v>
       </c>
-      <c r="H10" s="305">
+      <c r="H10" s="242">
         <f t="shared" si="0"/>
         <v>110392.86</v>
       </c>
-      <c r="I10" s="308">
+      <c r="I10" s="245">
         <f t="shared" si="1"/>
         <v>110392.86</v>
       </c>
@@ -13350,7 +13389,7 @@
       </c>
       <c r="Q10" s="43"/>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A11" s="210" t="s">
         <v>115</v>
       </c>
@@ -13370,11 +13409,11 @@
       <c r="G11" s="146">
         <v>-271875.99922180991</v>
       </c>
-      <c r="H11" s="305">
+      <c r="H11" s="242">
         <f t="shared" si="0"/>
         <v>135938.36499999999</v>
       </c>
-      <c r="I11" s="308">
+      <c r="I11" s="245">
         <f t="shared" si="1"/>
         <v>135938.36499999999</v>
       </c>
@@ -13399,7 +13438,7 @@
       </c>
       <c r="Q11" s="43"/>
     </row>
-    <row r="12" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="214" t="s">
         <v>116</v>
       </c>
@@ -13419,11 +13458,11 @@
       <c r="G12" s="154">
         <v>-319317.44875044789</v>
       </c>
-      <c r="H12" s="306">
+      <c r="H12" s="243">
         <f t="shared" si="0"/>
         <v>159658.87</v>
       </c>
-      <c r="I12" s="309">
+      <c r="I12" s="246">
         <f t="shared" si="1"/>
         <v>159658.87</v>
       </c>
@@ -13448,7 +13487,7 @@
       </c>
       <c r="Q12" s="43"/>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A13" s="217" t="s">
         <v>44</v>
       </c>
@@ -13470,11 +13509,11 @@
       <c r="G13" s="187">
         <v>-519626.96981144731</v>
       </c>
-      <c r="H13" s="307">
+      <c r="H13" s="244">
         <f>ROUND((J13/2),0)+N13</f>
         <v>259814.01</v>
       </c>
-      <c r="I13" s="310">
+      <c r="I13" s="247">
         <f>H13</f>
         <v>259814.01</v>
       </c>
@@ -13498,7 +13537,7 @@
       </c>
       <c r="Q13" s="43"/>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A14" s="210" t="s">
         <v>45</v>
       </c>
@@ -13518,11 +13557,11 @@
       <c r="G14" s="147">
         <v>-206492.25424856588</v>
       </c>
-      <c r="H14" s="307">
+      <c r="H14" s="244">
         <f t="shared" ref="H14:H77" si="6">ROUND((J14/2),0)+N14</f>
         <v>103246.02</v>
       </c>
-      <c r="I14" s="310">
+      <c r="I14" s="247">
         <f t="shared" ref="I14:I77" si="7">H14</f>
         <v>103246.02</v>
       </c>
@@ -13547,7 +13586,7 @@
       </c>
       <c r="Q14" s="43"/>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A15" s="210" t="s">
         <v>46</v>
       </c>
@@ -13569,11 +13608,11 @@
       <c r="G15" s="147">
         <v>-557137.66415134736</v>
       </c>
-      <c r="H15" s="307">
+      <c r="H15" s="244">
         <f t="shared" si="6"/>
         <v>278569.03000000003</v>
       </c>
-      <c r="I15" s="310">
+      <c r="I15" s="247">
         <f t="shared" si="7"/>
         <v>278569.03000000003</v>
       </c>
@@ -13597,7 +13636,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A16" s="210" t="s">
         <v>47</v>
       </c>
@@ -13619,11 +13658,11 @@
       <c r="G16" s="147">
         <v>-327282.74303127197</v>
       </c>
-      <c r="H16" s="307">
+      <c r="H16" s="244">
         <f t="shared" si="6"/>
         <v>163642.04</v>
       </c>
-      <c r="I16" s="310">
+      <c r="I16" s="247">
         <f t="shared" si="7"/>
         <v>163642.04</v>
       </c>
@@ -13647,7 +13686,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="210" t="s">
         <v>48</v>
       </c>
@@ -13667,11 +13706,11 @@
       <c r="G17" s="147">
         <v>-206069.04832824506</v>
       </c>
-      <c r="H17" s="307">
+      <c r="H17" s="244">
         <f t="shared" si="6"/>
         <v>103035.05</v>
       </c>
-      <c r="I17" s="310">
+      <c r="I17" s="247">
         <f t="shared" si="7"/>
         <v>103035.05</v>
       </c>
@@ -13695,7 +13734,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="210" t="s">
         <v>49</v>
       </c>
@@ -13717,11 +13756,11 @@
       <c r="G18" s="147">
         <v>-329620.47691006673</v>
       </c>
-      <c r="H18" s="307">
+      <c r="H18" s="244">
         <f t="shared" si="6"/>
         <v>164810.06</v>
       </c>
-      <c r="I18" s="310">
+      <c r="I18" s="247">
         <f t="shared" si="7"/>
         <v>164810.06</v>
       </c>
@@ -13745,7 +13784,7 @@
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="210" t="s">
         <v>50</v>
       </c>
@@ -13767,11 +13806,11 @@
       <c r="G19" s="147">
         <v>-493261.84842570277</v>
       </c>
-      <c r="H19" s="307">
+      <c r="H19" s="244">
         <f t="shared" si="6"/>
         <v>246631.07</v>
       </c>
-      <c r="I19" s="310">
+      <c r="I19" s="247">
         <f t="shared" si="7"/>
         <v>246631.07</v>
       </c>
@@ -13795,7 +13834,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="210" t="s">
         <v>51</v>
       </c>
@@ -13815,11 +13854,11 @@
       <c r="G20" s="147">
         <v>-147681.21170563609</v>
       </c>
-      <c r="H20" s="307">
+      <c r="H20" s="244">
         <f t="shared" si="6"/>
         <v>73841.08</v>
       </c>
-      <c r="I20" s="310">
+      <c r="I20" s="247">
         <f t="shared" si="7"/>
         <v>73841.08</v>
       </c>
@@ -13843,7 +13882,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="210" t="s">
         <v>52</v>
       </c>
@@ -13863,11 +13902,11 @@
       <c r="G21" s="147">
         <v>-418454.36430426914</v>
       </c>
-      <c r="H21" s="307">
+      <c r="H21" s="244">
         <f t="shared" si="6"/>
         <v>209227.09</v>
       </c>
-      <c r="I21" s="310">
+      <c r="I21" s="247">
         <f t="shared" si="7"/>
         <v>209227.09</v>
       </c>
@@ -13891,7 +13930,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="210" t="s">
         <v>53</v>
       </c>
@@ -13911,11 +13950,11 @@
       <c r="G22" s="147">
         <v>-187595.05270715937</v>
       </c>
-      <c r="H22" s="307">
+      <c r="H22" s="244">
         <f t="shared" si="6"/>
         <v>93798.1</v>
       </c>
-      <c r="I22" s="310">
+      <c r="I22" s="247">
         <f t="shared" si="7"/>
         <v>93798.1</v>
       </c>
@@ -13939,7 +13978,7 @@
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="210" t="s">
         <v>54</v>
       </c>
@@ -13959,11 +13998,11 @@
       <c r="G23" s="147">
         <v>-173625.20835662619</v>
       </c>
-      <c r="H23" s="307">
+      <c r="H23" s="244">
         <f t="shared" si="6"/>
         <v>86813.11</v>
       </c>
-      <c r="I23" s="310">
+      <c r="I23" s="247">
         <f t="shared" si="7"/>
         <v>86813.11</v>
       </c>
@@ -13987,7 +14026,7 @@
         <v>0.10999999999999999</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="210" t="s">
         <v>55</v>
       </c>
@@ -14007,11 +14046,11 @@
       <c r="G24" s="147">
         <v>-189590.74475723552</v>
       </c>
-      <c r="H24" s="307">
+      <c r="H24" s="244">
         <f t="shared" si="6"/>
         <v>94796.12</v>
       </c>
-      <c r="I24" s="310">
+      <c r="I24" s="247">
         <f t="shared" si="7"/>
         <v>94796.12</v>
       </c>
@@ -14035,7 +14074,7 @@
         <v>0.11999999999999998</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="210" t="s">
         <v>56</v>
       </c>
@@ -14055,11 +14094,11 @@
       <c r="G25" s="147">
         <v>-403151.54400910489</v>
       </c>
-      <c r="H25" s="307">
+      <c r="H25" s="244">
         <f t="shared" si="6"/>
         <v>201576.13</v>
       </c>
-      <c r="I25" s="310">
+      <c r="I25" s="247">
         <f t="shared" si="7"/>
         <v>201576.13</v>
       </c>
@@ -14083,7 +14122,7 @@
         <v>0.12999999999999998</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="210" t="s">
         <v>57</v>
       </c>
@@ -14103,11 +14142,11 @@
       <c r="G26" s="147">
         <v>-172908.51181565388</v>
       </c>
-      <c r="H26" s="307">
+      <c r="H26" s="244">
         <f t="shared" si="6"/>
         <v>86455.14</v>
       </c>
-      <c r="I26" s="310">
+      <c r="I26" s="247">
         <f t="shared" si="7"/>
         <v>86455.14</v>
       </c>
@@ -14131,7 +14170,7 @@
         <v>0.13999999999999999</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="210" t="s">
         <v>58</v>
       </c>
@@ -14153,11 +14192,11 @@
       <c r="G27" s="147">
         <v>-540813.04684148217</v>
       </c>
-      <c r="H27" s="307">
+      <c r="H27" s="244">
         <f t="shared" si="6"/>
         <v>270407.15000000002</v>
       </c>
-      <c r="I27" s="310">
+      <c r="I27" s="247">
         <f t="shared" si="7"/>
         <v>270407.15000000002</v>
       </c>
@@ -14181,7 +14220,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="210" t="s">
         <v>59</v>
       </c>
@@ -14201,11 +14240,11 @@
       <c r="G28" s="147">
         <v>-187595.05270715937</v>
       </c>
-      <c r="H28" s="307">
+      <c r="H28" s="244">
         <f t="shared" si="6"/>
         <v>93798.16</v>
       </c>
-      <c r="I28" s="310">
+      <c r="I28" s="247">
         <f t="shared" si="7"/>
         <v>93798.16</v>
       </c>
@@ -14232,7 +14271,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="210" t="s">
         <v>60</v>
       </c>
@@ -14252,11 +14291,11 @@
       <c r="G29" s="147">
         <v>-173625.20835662619</v>
       </c>
-      <c r="H29" s="307">
+      <c r="H29" s="244">
         <f t="shared" si="6"/>
         <v>86813.17</v>
       </c>
-      <c r="I29" s="310">
+      <c r="I29" s="247">
         <f t="shared" si="7"/>
         <v>86813.17</v>
       </c>
@@ -14280,7 +14319,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="210" t="s">
         <v>61</v>
       </c>
@@ -14300,11 +14339,11 @@
       <c r="G30" s="147">
         <v>-189590.74475723552</v>
       </c>
-      <c r="H30" s="307">
+      <c r="H30" s="244">
         <f t="shared" si="6"/>
         <v>94796.18</v>
       </c>
-      <c r="I30" s="310">
+      <c r="I30" s="247">
         <f t="shared" si="7"/>
         <v>94796.18</v>
       </c>
@@ -14328,7 +14367,7 @@
         <v>0.18000000000000002</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="210" t="s">
         <v>62</v>
       </c>
@@ -14348,11 +14387,11 @@
       <c r="G31" s="147">
         <v>-388451.99914749648</v>
       </c>
-      <c r="H31" s="307">
+      <c r="H31" s="244">
         <f t="shared" si="6"/>
         <v>194226.19</v>
       </c>
-      <c r="I31" s="310">
+      <c r="I31" s="247">
         <f t="shared" si="7"/>
         <v>194226.19</v>
       </c>
@@ -14379,7 +14418,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="210" t="s">
         <v>63</v>
       </c>
@@ -14401,11 +14440,11 @@
       <c r="G32" s="147">
         <v>-224422.45236430079</v>
       </c>
-      <c r="H32" s="307">
+      <c r="H32" s="244">
         <f t="shared" si="6"/>
         <v>112211.2</v>
       </c>
-      <c r="I32" s="310">
+      <c r="I32" s="247">
         <f t="shared" si="7"/>
         <v>112211.2</v>
       </c>
@@ -14429,7 +14468,7 @@
         <v>0.20000000000000004</v>
       </c>
     </row>
-    <row r="33" spans="1:112" s="140" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:112" s="140" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="210" t="s">
         <v>64</v>
       </c>
@@ -14451,11 +14490,11 @@
       <c r="G33" s="147">
         <v>-460533.57412257558</v>
       </c>
-      <c r="H33" s="307">
+      <c r="H33" s="244">
         <f t="shared" si="6"/>
         <v>230267.21</v>
       </c>
-      <c r="I33" s="310">
+      <c r="I33" s="247">
         <f t="shared" si="7"/>
         <v>230267.21</v>
       </c>
@@ -14577,7 +14616,7 @@
       <c r="DG33" s="73"/>
       <c r="DH33" s="73"/>
     </row>
-    <row r="34" spans="1:112" s="140" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:112" s="140" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="210" t="s">
         <v>65</v>
       </c>
@@ -14597,11 +14636,11 @@
       <c r="G34" s="147">
         <v>-187595.05270715937</v>
       </c>
-      <c r="H34" s="307">
+      <c r="H34" s="244">
         <f t="shared" si="6"/>
         <v>93798.22</v>
       </c>
-      <c r="I34" s="310">
+      <c r="I34" s="247">
         <f t="shared" si="7"/>
         <v>93798.22</v>
       </c>
@@ -14725,7 +14764,7 @@
       <c r="DG34" s="73"/>
       <c r="DH34" s="73"/>
     </row>
-    <row r="35" spans="1:112" s="140" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:112" s="140" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="210" t="s">
         <v>66</v>
       </c>
@@ -14747,11 +14786,11 @@
       <c r="G35" s="147">
         <v>-219526.12550837794</v>
       </c>
-      <c r="H35" s="307">
+      <c r="H35" s="244">
         <f t="shared" si="6"/>
         <v>109763.23</v>
       </c>
-      <c r="I35" s="310">
+      <c r="I35" s="247">
         <f t="shared" si="7"/>
         <v>109763.23</v>
       </c>
@@ -14875,7 +14914,7 @@
       <c r="DG35" s="73"/>
       <c r="DH35" s="73"/>
     </row>
-    <row r="36" spans="1:112" s="140" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:112" s="140" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="210" t="s">
         <v>67</v>
       </c>
@@ -14895,11 +14934,11 @@
       <c r="G36" s="147">
         <v>-189590.74475723552</v>
       </c>
-      <c r="H36" s="307">
+      <c r="H36" s="244">
         <f t="shared" si="6"/>
         <v>94796.24</v>
       </c>
-      <c r="I36" s="310">
+      <c r="I36" s="247">
         <f t="shared" si="7"/>
         <v>94796.24</v>
       </c>
@@ -15021,7 +15060,7 @@
       <c r="DG36" s="73"/>
       <c r="DH36" s="73"/>
     </row>
-    <row r="37" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A37" s="210" t="s">
         <v>68</v>
       </c>
@@ -15043,11 +15082,11 @@
       <c r="G37" s="147">
         <v>-452316.22060054552</v>
       </c>
-      <c r="H37" s="307">
+      <c r="H37" s="244">
         <f t="shared" si="6"/>
         <v>226158.25</v>
       </c>
-      <c r="I37" s="310">
+      <c r="I37" s="247">
         <f t="shared" si="7"/>
         <v>226158.25</v>
       </c>
@@ -15071,7 +15110,7 @@
         <v>0.25000000000000006</v>
       </c>
     </row>
-    <row r="38" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A38" s="210" t="s">
         <v>69</v>
       </c>
@@ -15091,11 +15130,11 @@
       <c r="G38" s="147">
         <v>-175787.47145562258</v>
       </c>
-      <c r="H38" s="307">
+      <c r="H38" s="244">
         <f t="shared" si="6"/>
         <v>87894.26</v>
       </c>
-      <c r="I38" s="310">
+      <c r="I38" s="247">
         <f t="shared" si="7"/>
         <v>87894.26</v>
       </c>
@@ -15119,7 +15158,7 @@
         <v>0.26000000000000006</v>
       </c>
     </row>
-    <row r="39" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A39" s="210" t="s">
         <v>70</v>
       </c>
@@ -15141,11 +15180,11 @@
       <c r="G39" s="147">
         <v>-471560.18735745805</v>
       </c>
-      <c r="H39" s="307">
+      <c r="H39" s="244">
         <f t="shared" si="6"/>
         <v>235780.27</v>
       </c>
-      <c r="I39" s="310">
+      <c r="I39" s="247">
         <f t="shared" si="7"/>
         <v>235780.27</v>
       </c>
@@ -15175,7 +15214,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="40" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A40" s="210" t="s">
         <v>71</v>
       </c>
@@ -15197,11 +15236,11 @@
       <c r="G40" s="147">
         <v>-277127.3408552261</v>
       </c>
-      <c r="H40" s="307">
+      <c r="H40" s="244">
         <f t="shared" si="6"/>
         <v>138564.28</v>
       </c>
-      <c r="I40" s="310">
+      <c r="I40" s="247">
         <f t="shared" si="7"/>
         <v>138564.28</v>
       </c>
@@ -15225,7 +15264,7 @@
         <v>0.28000000000000008</v>
       </c>
     </row>
-    <row r="41" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A41" s="210" t="s">
         <v>72</v>
       </c>
@@ -15245,11 +15284,11 @@
       <c r="G41" s="147">
         <v>-206069.04832824506</v>
       </c>
-      <c r="H41" s="307">
+      <c r="H41" s="244">
         <f t="shared" si="6"/>
         <v>103035.29</v>
       </c>
-      <c r="I41" s="310">
+      <c r="I41" s="247">
         <f t="shared" si="7"/>
         <v>103035.29</v>
       </c>
@@ -15273,7 +15312,7 @@
         <v>0.29000000000000009</v>
       </c>
     </row>
-    <row r="42" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A42" s="210" t="s">
         <v>73</v>
       </c>
@@ -15293,11 +15332,11 @@
       <c r="G42" s="147">
         <v>-225017.92633544002</v>
       </c>
-      <c r="H42" s="307">
+      <c r="H42" s="244">
         <f t="shared" si="6"/>
         <v>112509.3</v>
       </c>
-      <c r="I42" s="310">
+      <c r="I42" s="247">
         <f t="shared" si="7"/>
         <v>112509.3</v>
       </c>
@@ -15321,7 +15360,7 @@
         <v>0.3000000000000001</v>
       </c>
     </row>
-    <row r="43" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A43" s="210" t="s">
         <v>74</v>
       </c>
@@ -15343,11 +15382,11 @@
       <c r="G43" s="147">
         <v>-435275.0052766751</v>
       </c>
-      <c r="H43" s="307">
+      <c r="H43" s="244">
         <f t="shared" si="6"/>
         <v>217638.31</v>
       </c>
-      <c r="I43" s="310">
+      <c r="I43" s="247">
         <f t="shared" si="7"/>
         <v>217638.31</v>
       </c>
@@ -15371,7 +15410,7 @@
         <v>0.31000000000000011</v>
       </c>
     </row>
-    <row r="44" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A44" s="210" t="s">
         <v>75</v>
       </c>
@@ -15393,11 +15432,11 @@
       <c r="G44" s="147">
         <v>-235991.14771264675</v>
       </c>
-      <c r="H44" s="307">
+      <c r="H44" s="244">
         <f t="shared" si="6"/>
         <v>117996.32</v>
       </c>
-      <c r="I44" s="310">
+      <c r="I44" s="247">
         <f t="shared" si="7"/>
         <v>117996.32</v>
       </c>
@@ -15422,7 +15461,7 @@
       </c>
       <c r="O44" s="43"/>
     </row>
-    <row r="45" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A45" s="210" t="s">
         <v>76</v>
       </c>
@@ -15444,11 +15483,11 @@
       <c r="G45" s="147">
         <v>-471560.18735745805</v>
       </c>
-      <c r="H45" s="307">
+      <c r="H45" s="244">
         <f t="shared" si="6"/>
         <v>235780.33</v>
       </c>
-      <c r="I45" s="310">
+      <c r="I45" s="247">
         <f t="shared" si="7"/>
         <v>235780.33</v>
       </c>
@@ -15473,7 +15512,7 @@
       </c>
       <c r="O45" s="43"/>
     </row>
-    <row r="46" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A46" s="210" t="s">
         <v>77</v>
       </c>
@@ -15493,11 +15532,11 @@
       <c r="G46" s="147">
         <v>-227367.51195963251</v>
       </c>
-      <c r="H46" s="307">
+      <c r="H46" s="244">
         <f t="shared" si="6"/>
         <v>113684.34</v>
       </c>
-      <c r="I46" s="310">
+      <c r="I46" s="247">
         <f t="shared" si="7"/>
         <v>113684.34</v>
       </c>
@@ -15524,7 +15563,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="47" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A47" s="210" t="s">
         <v>78</v>
       </c>
@@ -15544,11 +15583,11 @@
       <c r="G47" s="147">
         <v>-201632.39809641102</v>
       </c>
-      <c r="H47" s="307">
+      <c r="H47" s="244">
         <f t="shared" si="6"/>
         <v>100816.35</v>
       </c>
-      <c r="I47" s="310">
+      <c r="I47" s="247">
         <f t="shared" si="7"/>
         <v>100816.35</v>
       </c>
@@ -15572,7 +15611,7 @@
         <v>0.35000000000000014</v>
       </c>
     </row>
-    <row r="48" spans="1:112" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A48" s="210" t="s">
         <v>79</v>
       </c>
@@ -15592,11 +15631,11 @@
       <c r="G48" s="147">
         <v>-229786.31527835201</v>
       </c>
-      <c r="H48" s="307">
+      <c r="H48" s="244">
         <f t="shared" si="6"/>
         <v>114893.36</v>
       </c>
-      <c r="I48" s="310">
+      <c r="I48" s="247">
         <f t="shared" si="7"/>
         <v>114893.36</v>
       </c>
@@ -15620,7 +15659,7 @@
         <v>0.36000000000000015</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A49" s="210" t="s">
         <v>80</v>
       </c>
@@ -15642,11 +15681,11 @@
       <c r="G49" s="147">
         <v>-447623.12200936372</v>
       </c>
-      <c r="H49" s="307">
+      <c r="H49" s="244">
         <f t="shared" si="6"/>
         <v>223812.37</v>
       </c>
-      <c r="I49" s="310">
+      <c r="I49" s="247">
         <f t="shared" si="7"/>
         <v>223812.37</v>
       </c>
@@ -15671,7 +15710,7 @@
       </c>
       <c r="P49" s="59"/>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50" s="210" t="s">
         <v>81</v>
       </c>
@@ -15691,11 +15730,11 @@
       <c r="G50" s="147">
         <v>-170654.57315202037</v>
       </c>
-      <c r="H50" s="307">
+      <c r="H50" s="244">
         <f t="shared" si="6"/>
         <v>85328.38</v>
       </c>
-      <c r="I50" s="310">
+      <c r="I50" s="247">
         <f t="shared" si="7"/>
         <v>85328.38</v>
       </c>
@@ -15719,7 +15758,7 @@
         <v>0.38000000000000017</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A51" s="210" t="s">
         <v>82</v>
       </c>
@@ -15741,11 +15780,11 @@
       <c r="G51" s="147">
         <v>-460533.57412257558</v>
       </c>
-      <c r="H51" s="307">
+      <c r="H51" s="244">
         <f t="shared" si="6"/>
         <v>230267.39</v>
       </c>
-      <c r="I51" s="310">
+      <c r="I51" s="247">
         <f t="shared" si="7"/>
         <v>230267.39</v>
       </c>
@@ -15769,7 +15808,7 @@
         <v>0.39000000000000018</v>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A52" s="210" t="s">
         <v>83</v>
       </c>
@@ -15789,11 +15828,11 @@
       <c r="G52" s="147">
         <v>-225008.41427208658</v>
       </c>
-      <c r="H52" s="307">
+      <c r="H52" s="244">
         <f t="shared" si="6"/>
         <v>112504.4</v>
       </c>
-      <c r="I52" s="310">
+      <c r="I52" s="247">
         <f t="shared" si="7"/>
         <v>112504.4</v>
       </c>
@@ -15817,7 +15856,7 @@
         <v>0.40000000000000019</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A53" s="210" t="s">
         <v>84</v>
       </c>
@@ -15837,11 +15876,11 @@
       <c r="G53" s="147">
         <v>-206069.04832824506</v>
       </c>
-      <c r="H53" s="307">
+      <c r="H53" s="244">
         <f t="shared" si="6"/>
         <v>103035.41</v>
       </c>
-      <c r="I53" s="310">
+      <c r="I53" s="247">
         <f t="shared" si="7"/>
         <v>103035.41</v>
       </c>
@@ -15868,7 +15907,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A54" s="210" t="s">
         <v>85</v>
       </c>
@@ -15890,11 +15929,11 @@
       <c r="G54" s="147">
         <v>-282457.37110751297</v>
       </c>
-      <c r="H54" s="307">
+      <c r="H54" s="244">
         <f t="shared" si="6"/>
         <v>141229.42000000001</v>
       </c>
-      <c r="I54" s="310">
+      <c r="I54" s="247">
         <f t="shared" si="7"/>
         <v>141229.42000000001</v>
       </c>
@@ -15921,7 +15960,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A55" s="210" t="s">
         <v>86</v>
       </c>
@@ -15943,11 +15982,11 @@
       <c r="G55" s="147">
         <v>-447623.12200936372</v>
       </c>
-      <c r="H55" s="307">
+      <c r="H55" s="244">
         <f t="shared" si="6"/>
         <v>223812.43</v>
       </c>
-      <c r="I55" s="310">
+      <c r="I55" s="247">
         <f t="shared" si="7"/>
         <v>223812.43</v>
       </c>
@@ -15971,7 +16010,7 @@
         <v>0.43000000000000022</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A56" s="210" t="s">
         <v>87</v>
       </c>
@@ -15991,11 +16030,11 @@
       <c r="G56" s="147">
         <v>-174740.57704108849</v>
       </c>
-      <c r="H56" s="307">
+      <c r="H56" s="244">
         <f t="shared" si="6"/>
         <v>87371.44</v>
       </c>
-      <c r="I56" s="310">
+      <c r="I56" s="247">
         <f t="shared" si="7"/>
         <v>87371.44</v>
       </c>
@@ -16019,7 +16058,7 @@
         <v>0.44000000000000022</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A57" s="210" t="s">
         <v>88</v>
       </c>
@@ -16041,11 +16080,11 @@
       <c r="G57" s="147">
         <v>-487804.97705695755</v>
       </c>
-      <c r="H57" s="307">
+      <c r="H57" s="244">
         <f t="shared" si="6"/>
         <v>243903.45</v>
       </c>
-      <c r="I57" s="310">
+      <c r="I57" s="247">
         <f t="shared" si="7"/>
         <v>243903.45</v>
       </c>
@@ -16069,7 +16108,7 @@
         <v>0.45000000000000023</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A58" s="210" t="s">
         <v>89</v>
       </c>
@@ -16091,11 +16130,11 @@
       <c r="G58" s="147">
         <v>-280063.66457270354</v>
       </c>
-      <c r="H58" s="307">
+      <c r="H58" s="244">
         <f t="shared" si="6"/>
         <v>140032.46</v>
       </c>
-      <c r="I58" s="310">
+      <c r="I58" s="247">
         <f t="shared" si="7"/>
         <v>140032.46</v>
       </c>
@@ -16119,7 +16158,7 @@
         <v>0.46000000000000024</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A59" s="210" t="s">
         <v>90</v>
       </c>
@@ -16141,11 +16180,11 @@
       <c r="G59" s="147">
         <v>-260547.07259893051</v>
       </c>
-      <c r="H59" s="307">
+      <c r="H59" s="244">
         <f t="shared" si="6"/>
         <v>130274.47</v>
       </c>
-      <c r="I59" s="310">
+      <c r="I59" s="247">
         <f t="shared" si="7"/>
         <v>130274.47</v>
       </c>
@@ -16169,7 +16208,7 @@
         <v>0.47000000000000025</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A60" s="210" t="s">
         <v>91</v>
       </c>
@@ -16191,11 +16230,11 @@
       <c r="G60" s="147">
         <v>-275852.5976977864</v>
       </c>
-      <c r="H60" s="307">
+      <c r="H60" s="244">
         <f t="shared" si="6"/>
         <v>137927.48000000001</v>
       </c>
-      <c r="I60" s="310">
+      <c r="I60" s="247">
         <f t="shared" si="7"/>
         <v>137927.48000000001</v>
       </c>
@@ -16220,7 +16259,7 @@
       </c>
       <c r="Q60" s="181"/>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A61" s="210" t="s">
         <v>92</v>
       </c>
@@ -16242,11 +16281,11 @@
       <c r="G61" s="147">
         <v>-447623.12200936372</v>
       </c>
-      <c r="H61" s="307">
+      <c r="H61" s="244">
         <f t="shared" si="6"/>
         <v>223812.49</v>
       </c>
-      <c r="I61" s="310">
+      <c r="I61" s="247">
         <f t="shared" si="7"/>
         <v>223812.49</v>
       </c>
@@ -16271,7 +16310,7 @@
       </c>
       <c r="Q61" s="43"/>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A62" s="210" t="s">
         <v>93</v>
       </c>
@@ -16291,11 +16330,11 @@
       <c r="G62" s="147">
         <v>-174740.57704108849</v>
       </c>
-      <c r="H62" s="307">
+      <c r="H62" s="244">
         <f t="shared" si="6"/>
         <v>87371.5</v>
       </c>
-      <c r="I62" s="310">
+      <c r="I62" s="247">
         <f t="shared" si="7"/>
         <v>87371.5</v>
       </c>
@@ -16319,7 +16358,7 @@
         <v>0.50000000000000022</v>
       </c>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A63" s="210" t="s">
         <v>94</v>
       </c>
@@ -16341,11 +16380,11 @@
       <c r="G63" s="147">
         <v>-469441.3017444798</v>
       </c>
-      <c r="H63" s="307">
+      <c r="H63" s="244">
         <f t="shared" si="6"/>
         <v>234721.51</v>
       </c>
-      <c r="I63" s="310">
+      <c r="I63" s="247">
         <f t="shared" si="7"/>
         <v>234721.51</v>
       </c>
@@ -16369,7 +16408,7 @@
         <v>0.51000000000000023</v>
       </c>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A64" s="210" t="s">
         <v>95</v>
       </c>
@@ -16389,11 +16428,11 @@
       <c r="G64" s="147">
         <v>-164899.57136629923</v>
       </c>
-      <c r="H64" s="307">
+      <c r="H64" s="244">
         <f t="shared" si="6"/>
         <v>82450.52</v>
       </c>
-      <c r="I64" s="310">
+      <c r="I64" s="247">
         <f t="shared" si="7"/>
         <v>82450.52</v>
       </c>
@@ -16417,7 +16456,7 @@
         <v>0.52000000000000024</v>
       </c>
     </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A65" s="210" t="s">
         <v>96</v>
       </c>
@@ -16437,11 +16476,11 @@
       <c r="G65" s="147">
         <v>-206069.04832824506</v>
       </c>
-      <c r="H65" s="307">
+      <c r="H65" s="244">
         <f t="shared" si="6"/>
         <v>103035.53</v>
       </c>
-      <c r="I65" s="310">
+      <c r="I65" s="247">
         <f t="shared" si="7"/>
         <v>103035.53</v>
       </c>
@@ -16468,7 +16507,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="66" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A66" s="210" t="s">
         <v>97</v>
       </c>
@@ -16490,11 +16529,11 @@
       <c r="G66" s="147">
         <v>-285418.79160890041</v>
       </c>
-      <c r="H66" s="307">
+      <c r="H66" s="244">
         <f t="shared" si="6"/>
         <v>142710.54</v>
       </c>
-      <c r="I66" s="310">
+      <c r="I66" s="247">
         <f t="shared" si="7"/>
         <v>142710.54</v>
       </c>
@@ -16518,7 +16557,7 @@
         <v>0.54000000000000026</v>
       </c>
     </row>
-    <row r="67" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A67" s="210" t="s">
         <v>98</v>
       </c>
@@ -16540,11 +16579,11 @@
       <c r="G67" s="147">
         <v>-634226.20947773824</v>
       </c>
-      <c r="H67" s="307">
+      <c r="H67" s="244">
         <f t="shared" si="6"/>
         <v>317113.55</v>
       </c>
-      <c r="I67" s="310">
+      <c r="I67" s="247">
         <f t="shared" si="7"/>
         <v>317113.55</v>
       </c>
@@ -16569,7 +16608,7 @@
       </c>
       <c r="O67" s="73"/>
     </row>
-    <row r="68" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A68" s="210" t="s">
         <v>99</v>
       </c>
@@ -16591,11 +16630,11 @@
       <c r="G68" s="147">
         <v>-473679.07297043619</v>
       </c>
-      <c r="H68" s="307">
+      <c r="H68" s="244">
         <f t="shared" si="6"/>
         <v>236840.56</v>
       </c>
-      <c r="I68" s="310">
+      <c r="I68" s="247">
         <f t="shared" si="7"/>
         <v>236840.56</v>
       </c>
@@ -16619,7 +16658,7 @@
         <v>0.56000000000000028</v>
       </c>
     </row>
-    <row r="69" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A69" s="210" t="s">
         <v>100</v>
       </c>
@@ -16639,8 +16678,8 @@
       <c r="G69" s="147">
         <v>0</v>
       </c>
-      <c r="H69" s="307"/>
-      <c r="I69" s="310"/>
+      <c r="H69" s="244"/>
+      <c r="I69" s="247"/>
       <c r="J69" s="226"/>
       <c r="K69" s="147">
         <v>-306490.57802999998</v>
@@ -16658,7 +16697,7 @@
         <v>0.57000000000000028</v>
       </c>
     </row>
-    <row r="70" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A70" s="210" t="s">
         <v>101</v>
       </c>
@@ -16678,11 +16717,11 @@
       <c r="G70" s="147">
         <v>-213866.97761458607</v>
       </c>
-      <c r="H70" s="307">
+      <c r="H70" s="244">
         <f t="shared" si="6"/>
         <v>106934.58</v>
       </c>
-      <c r="I70" s="310">
+      <c r="I70" s="247">
         <f t="shared" si="7"/>
         <v>106934.58</v>
       </c>
@@ -16706,7 +16745,7 @@
         <v>0.58000000000000029</v>
       </c>
     </row>
-    <row r="71" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A71" s="210" t="s">
         <v>102</v>
       </c>
@@ -16728,11 +16767,11 @@
       <c r="G71" s="147">
         <v>-256859.2161501162</v>
       </c>
-      <c r="H71" s="307">
+      <c r="H71" s="244">
         <f t="shared" si="6"/>
         <v>128430.59</v>
       </c>
-      <c r="I71" s="310">
+      <c r="I71" s="247">
         <f t="shared" si="7"/>
         <v>128430.59</v>
       </c>
@@ -16756,7 +16795,7 @@
         <v>0.5900000000000003</v>
       </c>
     </row>
-    <row r="72" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A72" s="210" t="s">
         <v>103</v>
       </c>
@@ -16778,11 +16817,11 @@
       <c r="G72" s="147">
         <v>-382821.80090465758</v>
       </c>
-      <c r="H72" s="307">
+      <c r="H72" s="244">
         <f t="shared" si="6"/>
         <v>191411.6</v>
       </c>
-      <c r="I72" s="310">
+      <c r="I72" s="247">
         <f t="shared" si="7"/>
         <v>191411.6</v>
       </c>
@@ -16806,7 +16845,7 @@
         <v>0.60000000000000031</v>
       </c>
     </row>
-    <row r="73" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A73" s="210" t="s">
         <v>104</v>
       </c>
@@ -16828,11 +16867,11 @@
       <c r="G73" s="147">
         <v>-466616.12092717562</v>
       </c>
-      <c r="H73" s="307">
+      <c r="H73" s="244">
         <f t="shared" si="6"/>
         <v>233308.61</v>
       </c>
-      <c r="I73" s="310">
+      <c r="I73" s="247">
         <f t="shared" si="7"/>
         <v>233308.61</v>
       </c>
@@ -16856,7 +16895,7 @@
         <v>0.61000000000000032</v>
       </c>
     </row>
-    <row r="74" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A74" s="210" t="s">
         <v>105</v>
       </c>
@@ -16876,11 +16915,11 @@
       <c r="G74" s="147">
         <v>-228041.53987035993</v>
       </c>
-      <c r="H74" s="307">
+      <c r="H74" s="244">
         <f t="shared" si="6"/>
         <v>114021.62</v>
       </c>
-      <c r="I74" s="310">
+      <c r="I74" s="247">
         <f t="shared" si="7"/>
         <v>114021.62</v>
       </c>
@@ -16904,7 +16943,7 @@
         <v>0.62000000000000033</v>
       </c>
     </row>
-    <row r="75" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A75" s="210" t="s">
         <v>106</v>
       </c>
@@ -16926,11 +16965,11 @@
       <c r="G75" s="147">
         <v>-266857.12112488924</v>
       </c>
-      <c r="H75" s="307">
+      <c r="H75" s="244">
         <f t="shared" si="6"/>
         <v>133429.63</v>
       </c>
-      <c r="I75" s="310">
+      <c r="I75" s="247">
         <f t="shared" si="7"/>
         <v>133429.63</v>
       </c>
@@ -16954,7 +16993,7 @@
         <v>0.63000000000000034</v>
       </c>
     </row>
-    <row r="76" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A76" s="210" t="s">
         <v>107</v>
       </c>
@@ -16974,11 +17013,11 @@
       <c r="G76" s="147">
         <v>-229786.31527835201</v>
       </c>
-      <c r="H76" s="307">
+      <c r="H76" s="244">
         <f t="shared" si="6"/>
         <v>114893.64</v>
       </c>
-      <c r="I76" s="310">
+      <c r="I76" s="247">
         <f t="shared" si="7"/>
         <v>114893.64</v>
       </c>
@@ -17002,7 +17041,7 @@
         <v>0.64000000000000035</v>
       </c>
     </row>
-    <row r="77" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A77" s="210" t="s">
         <v>108</v>
       </c>
@@ -17024,11 +17063,11 @@
       <c r="G77" s="147">
         <v>-525270.52442663931</v>
       </c>
-      <c r="H77" s="307">
+      <c r="H77" s="244">
         <f t="shared" si="6"/>
         <v>262636.65000000002</v>
       </c>
-      <c r="I77" s="310">
+      <c r="I77" s="247">
         <f t="shared" si="7"/>
         <v>262636.65000000002</v>
       </c>
@@ -17052,7 +17091,7 @@
         <v>0.65000000000000036</v>
       </c>
     </row>
-    <row r="78" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A78" s="210" t="s">
         <v>109</v>
       </c>
@@ -17074,11 +17113,11 @@
       <c r="G78" s="147">
         <v>-477916.84419639257</v>
       </c>
-      <c r="H78" s="307">
+      <c r="H78" s="244">
         <f t="shared" ref="H78:H81" si="12">ROUND((J78/2),0)+N78</f>
         <v>238959.66</v>
       </c>
-      <c r="I78" s="310">
+      <c r="I78" s="247">
         <f t="shared" ref="I78:I81" si="13">H78</f>
         <v>238959.66</v>
       </c>
@@ -17102,7 +17141,7 @@
         <v>0.66000000000000036</v>
       </c>
     </row>
-    <row r="79" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A79" s="210" t="s">
         <v>110</v>
       </c>
@@ -17124,11 +17163,11 @@
       <c r="G79" s="147">
         <v>-338632.46462072933</v>
       </c>
-      <c r="H79" s="307">
+      <c r="H79" s="244">
         <f t="shared" si="12"/>
         <v>169316.67</v>
       </c>
-      <c r="I79" s="310">
+      <c r="I79" s="247">
         <f t="shared" si="13"/>
         <v>169316.67</v>
       </c>
@@ -17152,7 +17191,7 @@
         <v>0.67000000000000037</v>
       </c>
     </row>
-    <row r="80" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A80" s="210" t="s">
         <v>111</v>
       </c>
@@ -17174,11 +17213,11 @@
       <c r="G80" s="147">
         <v>-269617.76735499618</v>
       </c>
-      <c r="H80" s="307">
+      <c r="H80" s="244">
         <f t="shared" si="12"/>
         <v>134809.68</v>
       </c>
-      <c r="I80" s="310">
+      <c r="I80" s="247">
         <f t="shared" si="13"/>
         <v>134809.68</v>
       </c>
@@ -17202,7 +17241,7 @@
         <v>0.68000000000000038</v>
       </c>
     </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A81" s="210" t="s">
         <v>112</v>
       </c>
@@ -17224,11 +17263,11 @@
       <c r="G81" s="147">
         <v>-279495.95060612552</v>
       </c>
-      <c r="H81" s="307">
+      <c r="H81" s="244">
         <f t="shared" si="12"/>
         <v>139748.69</v>
       </c>
-      <c r="I81" s="310">
+      <c r="I81" s="247">
         <f t="shared" si="13"/>
         <v>139748.69</v>
       </c>
@@ -17252,7 +17291,7 @@
         <v>0.69000000000000039</v>
       </c>
     </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A82" s="35"/>
       <c r="B82" s="35"/>
       <c r="C82" s="108"/>
@@ -17267,7 +17306,7 @@
       <c r="L82" s="146"/>
       <c r="M82" s="147"/>
     </row>
-    <row r="83" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A83" s="27"/>
       <c r="B83" s="27"/>
       <c r="C83" s="27"/>
@@ -17325,9 +17364,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7365EFC1-5C09-4380-B9A2-A73102AE2F7A}">
   <dimension ref="A13"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="13" ht="15.6" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/2026/EL MIRADOR/Febrero/Febrero - EL MIRADOR.xlsx
+++ b/2026/EL MIRADOR/Febrero/Febrero - EL MIRADOR.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\EL MIRADOR\Febrero\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\EL MIRADOR\Febrero\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30E2F71E-F286-4BA9-B1BD-5E0423414185}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BFCF337-AB2E-4AE9-9DC3-D8B15E19466C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -24,16 +24,11 @@
     <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$J$144</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="690" uniqueCount="396">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="690" uniqueCount="395">
   <si>
     <t>LIQUIDACION DE EXPENSAS</t>
   </si>
@@ -826,9 +821,6 @@
   </si>
   <si>
     <t>COCHERA 33</t>
-  </si>
-  <si>
-    <t>Schiaffino, Edgardo Angel</t>
   </si>
   <si>
     <t>Orsi, Jose Luis - Fernandez, Cristian Gabriel</t>
@@ -1061,9 +1053,6 @@
     <t>Frigidi Guillermo Ariel</t>
   </si>
   <si>
-    <t>Schiaffino, Edgardo Ángel</t>
-  </si>
-  <si>
     <t xml:space="preserve">Orsi, José Luis - Fernández, Cristián Gabriel </t>
   </si>
   <si>
@@ -1230,6 +1219,9 @@
   </si>
   <si>
     <t>VTO 16/03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Patricia Mainieri </t>
   </si>
 </sst>
 </file>
@@ -2263,35 +2255,14 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -2310,6 +2281,15 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2379,6 +2359,18 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="26" fillId="15" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -2505,9 +2497,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2545,9 +2537,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2580,26 +2572,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2632,26 +2607,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2826,24 +2784,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:R154"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="33.42578125" customWidth="1"/>
-    <col min="2" max="2" width="36.85546875" customWidth="1"/>
-    <col min="3" max="3" width="17.42578125" customWidth="1"/>
-    <col min="4" max="4" width="21.7109375" customWidth="1"/>
+    <col min="1" max="1" width="33.44140625" customWidth="1"/>
+    <col min="2" max="2" width="36.88671875" customWidth="1"/>
+    <col min="3" max="3" width="17.44140625" customWidth="1"/>
+    <col min="4" max="4" width="21.6640625" customWidth="1"/>
     <col min="5" max="5" width="18" customWidth="1"/>
-    <col min="6" max="9" width="15.7109375" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.85546875" customWidth="1"/>
-    <col min="12" max="12" width="16.140625" customWidth="1"/>
+    <col min="6" max="9" width="15.6640625" customWidth="1"/>
+    <col min="10" max="10" width="14.6640625" customWidth="1"/>
+    <col min="11" max="11" width="15.88671875" customWidth="1"/>
+    <col min="12" max="12" width="16.109375" customWidth="1"/>
     <col min="13" max="13" width="13" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5546875" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="18" customWidth="1"/>
-    <col min="17" max="17" width="18.28515625" customWidth="1"/>
+    <col min="17" max="17" width="18.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="112"/>
       <c r="B1" s="121"/>
       <c r="C1" s="129" t="s">
@@ -2857,7 +2815,7 @@
       <c r="I1" s="110"/>
       <c r="J1" s="111"/>
     </row>
-    <row r="2" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" ht="18" x14ac:dyDescent="0.35">
       <c r="A2" s="113"/>
       <c r="B2" s="122"/>
       <c r="C2" s="122" t="s">
@@ -2871,11 +2829,11 @@
       <c r="I2" s="123"/>
       <c r="J2" s="109"/>
     </row>
-    <row r="3" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" ht="18" x14ac:dyDescent="0.35">
       <c r="A3" s="113"/>
       <c r="B3" s="122"/>
       <c r="C3" s="122" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D3" s="122"/>
       <c r="E3" s="122" t="s">
@@ -2887,7 +2845,7 @@
       <c r="I3" s="123"/>
       <c r="J3" s="109"/>
     </row>
-    <row r="4" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="113"/>
       <c r="B4" s="122"/>
       <c r="C4" s="122" t="s">
@@ -2901,15 +2859,15 @@
       <c r="I4" s="123"/>
       <c r="J4" s="109"/>
     </row>
-    <row r="5" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" ht="18" x14ac:dyDescent="0.35">
       <c r="A5" s="117"/>
       <c r="B5" s="122"/>
       <c r="C5" s="122" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="D5" s="122"/>
       <c r="E5" s="122" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="F5" s="122"/>
       <c r="G5" s="122"/>
@@ -2917,7 +2875,7 @@
       <c r="I5" s="122"/>
       <c r="J5" s="118"/>
     </row>
-    <row r="6" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" ht="18" x14ac:dyDescent="0.35">
       <c r="A6" s="117"/>
       <c r="B6" s="122"/>
       <c r="C6" s="122" t="s">
@@ -2931,7 +2889,7 @@
       <c r="I6" s="122"/>
       <c r="J6" s="118"/>
     </row>
-    <row r="7" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="119"/>
       <c r="B7" s="120"/>
       <c r="C7" s="120"/>
@@ -2943,11 +2901,11 @@
       <c r="I7" s="120"/>
       <c r="J7" s="124"/>
     </row>
-    <row r="9" spans="1:10" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="10" spans="1:10" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="10" spans="1:10" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="14" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="251" t="s">
         <v>258</v>
       </c>
@@ -2961,7 +2919,7 @@
       <c r="I14" s="251"/>
       <c r="J14" s="251"/>
     </row>
-    <row r="15" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="251"/>
       <c r="B15" s="251"/>
       <c r="C15" s="251"/>
@@ -2973,7 +2931,7 @@
       <c r="I15" s="251"/>
       <c r="J15" s="251"/>
     </row>
-    <row r="16" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="251"/>
       <c r="B16" s="251"/>
       <c r="C16" s="251"/>
@@ -2985,7 +2943,7 @@
       <c r="I16" s="251"/>
       <c r="J16" s="251"/>
     </row>
-    <row r="17" spans="1:10" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="251"/>
       <c r="B17" s="251"/>
       <c r="C17" s="251"/>
@@ -2997,7 +2955,7 @@
       <c r="I17" s="251"/>
       <c r="J17" s="251"/>
     </row>
-    <row r="18" spans="1:10" ht="47.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" ht="47.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="251"/>
       <c r="B18" s="251"/>
       <c r="C18" s="251"/>
@@ -3009,13 +2967,13 @@
       <c r="I18" s="251"/>
       <c r="J18" s="251"/>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" s="2"/>
       <c r="H19" s="94"/>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" s="260" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="B20" s="260"/>
       <c r="C20" s="260"/>
@@ -3027,7 +2985,7 @@
       <c r="I20" s="260"/>
       <c r="J20" s="260"/>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" s="260"/>
       <c r="B21" s="260"/>
       <c r="C21" s="260"/>
@@ -3039,7 +2997,7 @@
       <c r="I21" s="260"/>
       <c r="J21" s="260"/>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" s="260"/>
       <c r="B22" s="260"/>
       <c r="C22" s="260"/>
@@ -3051,10 +3009,10 @@
       <c r="I22" s="260"/>
       <c r="J22" s="260"/>
     </row>
-    <row r="23" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="H23" s="94"/>
     </row>
-    <row r="24" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="12" t="s">
         <v>19</v>
       </c>
@@ -3080,9 +3038,9 @@
         <v>174</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="50" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="B25" s="6"/>
       <c r="C25" s="6"/>
@@ -3094,7 +3052,7 @@
       <c r="I25" s="95"/>
       <c r="J25" s="95"/>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" s="6" t="s">
         <v>43</v>
       </c>
@@ -3110,7 +3068,7 @@
       <c r="I26" s="58"/>
       <c r="J26" s="58"/>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" s="6" t="s">
         <v>237</v>
       </c>
@@ -3126,7 +3084,7 @@
       <c r="I27" s="58"/>
       <c r="J27" s="58"/>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" s="6" t="s">
         <v>235</v>
       </c>
@@ -3143,7 +3101,7 @@
       <c r="I28" s="58"/>
       <c r="J28" s="58"/>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" s="6" t="s">
         <v>236</v>
       </c>
@@ -3159,9 +3117,9 @@
       <c r="I29" s="58"/>
       <c r="J29" s="58"/>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" s="6" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B30" s="6"/>
       <c r="C30" s="6"/>
@@ -3175,7 +3133,7 @@
       <c r="I30" s="58"/>
       <c r="J30" s="58"/>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" s="6" t="s">
         <v>238</v>
       </c>
@@ -3191,9 +3149,9 @@
       <c r="I31" s="58"/>
       <c r="J31" s="58"/>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" s="6" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="B32" s="6"/>
       <c r="C32" s="6"/>
@@ -3207,7 +3165,7 @@
       <c r="I32" s="58"/>
       <c r="J32" s="58"/>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" s="93" t="s">
         <v>168</v>
       </c>
@@ -3224,7 +3182,7 @@
       <c r="I33" s="92"/>
       <c r="J33" s="92"/>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" s="50" t="s">
         <v>234</v>
       </c>
@@ -3238,7 +3196,7 @@
       <c r="I34" s="6"/>
       <c r="J34" s="6"/>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" s="6" t="s">
         <v>43</v>
       </c>
@@ -3254,7 +3212,7 @@
       <c r="I35" s="58"/>
       <c r="J35" s="58"/>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" s="6" t="s">
         <v>237</v>
       </c>
@@ -3271,7 +3229,7 @@
       <c r="I36" s="58"/>
       <c r="J36" s="58"/>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" s="6" t="s">
         <v>235</v>
       </c>
@@ -3288,7 +3246,7 @@
       <c r="I37" s="58"/>
       <c r="J37" s="58"/>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38" s="6" t="s">
         <v>236</v>
       </c>
@@ -3305,9 +3263,9 @@
       <c r="I38" s="58"/>
       <c r="J38" s="58"/>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" s="6" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B39" s="6"/>
       <c r="C39" s="6"/>
@@ -3322,7 +3280,7 @@
       <c r="I39" s="58"/>
       <c r="J39" s="58"/>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" s="6" t="s">
         <v>238</v>
       </c>
@@ -3338,9 +3296,9 @@
       <c r="I40" s="58"/>
       <c r="J40" s="58"/>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41" s="6" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="B41" s="6"/>
       <c r="C41" s="6"/>
@@ -3354,9 +3312,9 @@
       <c r="I41" s="58"/>
       <c r="J41" s="58"/>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A42" s="6" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="B42" s="6"/>
       <c r="C42" s="6"/>
@@ -3370,7 +3328,7 @@
       <c r="I42" s="58"/>
       <c r="J42" s="58"/>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A43" s="93" t="s">
         <v>168</v>
       </c>
@@ -3387,7 +3345,7 @@
       <c r="I43" s="92"/>
       <c r="J43" s="92"/>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A44" s="33" t="s">
         <v>1</v>
       </c>
@@ -3430,9 +3388,9 @@
         <v/>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A45" s="32" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="B45" s="6"/>
       <c r="C45" s="6"/>
@@ -3447,13 +3405,13 @@
       <c r="J45" s="58"/>
       <c r="L45" s="69"/>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A46" s="32" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="B46" s="6"/>
       <c r="C46" s="6" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="D46" s="228">
         <v>47420.82</v>
@@ -3466,7 +3424,7 @@
       <c r="J46" s="6"/>
       <c r="L46" s="69"/>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A47" s="33" t="s">
         <v>38</v>
       </c>
@@ -3509,7 +3467,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A48" s="32" t="s">
         <v>247</v>
       </c>
@@ -3527,7 +3485,7 @@
       <c r="J48" s="58"/>
       <c r="L48" s="69"/>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A49" s="6"/>
       <c r="B49" s="6"/>
       <c r="C49" s="6"/>
@@ -3540,7 +3498,7 @@
       <c r="J49" s="58"/>
       <c r="L49" s="69"/>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A50" s="33" t="s">
         <v>17</v>
       </c>
@@ -3568,7 +3526,7 @@
         <v/>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A51" s="32" t="s">
         <v>243</v>
       </c>
@@ -3583,9 +3541,9 @@
       <c r="J51" s="49"/>
       <c r="L51" s="69"/>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A52" s="35" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="B52" s="35"/>
       <c r="C52" s="35"/>
@@ -3600,15 +3558,15 @@
       <c r="J52" s="49"/>
       <c r="L52" s="69"/>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A53" s="35" t="s">
         <v>246</v>
       </c>
       <c r="B53" s="35" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C53" s="35" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="D53" s="228">
         <v>256953</v>
@@ -3621,12 +3579,12 @@
       <c r="J53" s="49"/>
       <c r="L53" s="69"/>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A54" s="35" t="s">
         <v>246</v>
       </c>
       <c r="B54" s="35" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C54" s="35" t="str">
         <f>C53</f>
@@ -3643,7 +3601,7 @@
       <c r="J54" s="49"/>
       <c r="L54" s="69"/>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A55" s="33" t="s">
         <v>245</v>
       </c>
@@ -3686,7 +3644,7 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A56" s="32" t="s">
         <v>2</v>
       </c>
@@ -3701,13 +3659,13 @@
       <c r="J56" s="6"/>
       <c r="L56" s="69"/>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A57" s="6" t="s">
         <v>239</v>
       </c>
       <c r="B57" s="6"/>
       <c r="C57" s="6" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="D57" s="44">
         <v>64271</v>
@@ -3720,13 +3678,13 @@
       <c r="J57" s="6"/>
       <c r="L57" s="69"/>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A58" s="6" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B58" s="6"/>
       <c r="C58" s="6" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="D58" s="44">
         <v>74221.850000000006</v>
@@ -3739,7 +3697,7 @@
       <c r="J58" s="6"/>
       <c r="L58" s="69"/>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A59" s="6"/>
       <c r="B59" s="6"/>
       <c r="C59" s="182"/>
@@ -3752,7 +3710,7 @@
       <c r="J59" s="6"/>
       <c r="L59" s="69"/>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A60" s="33" t="s">
         <v>244</v>
       </c>
@@ -3795,7 +3753,7 @@
         <v/>
       </c>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A61" s="32" t="s">
         <v>227</v>
       </c>
@@ -3810,13 +3768,13 @@
       <c r="J61" s="36"/>
       <c r="L61" s="69"/>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A62" s="6" t="s">
         <v>231</v>
       </c>
       <c r="B62" s="6"/>
       <c r="C62" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D62" s="44">
         <v>160913</v>
@@ -3851,13 +3809,13 @@
       </c>
       <c r="L62" s="69"/>
     </row>
-    <row r="63" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="262" t="s">
         <v>232</v>
       </c>
       <c r="B63" s="263"/>
       <c r="C63" s="35" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D63" s="44">
         <v>7907</v>
@@ -3891,16 +3849,16 @@
         <v>7907</v>
       </c>
       <c r="L63" s="203" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="64" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="262" t="s">
         <v>233</v>
       </c>
       <c r="B64" s="263"/>
       <c r="C64" s="6" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="D64" s="44">
         <v>7907</v>
@@ -3935,7 +3893,7 @@
       </c>
       <c r="L64" s="69"/>
     </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A65" s="33" t="s">
         <v>3</v>
       </c>
@@ -3978,7 +3936,7 @@
         <v/>
       </c>
     </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A66" s="32" t="s">
         <v>4</v>
       </c>
@@ -3993,13 +3951,13 @@
       <c r="J66" s="6"/>
       <c r="L66" s="69"/>
     </row>
-    <row r="67" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="71" t="s">
         <v>240</v>
       </c>
       <c r="B67" s="6"/>
       <c r="C67" s="182" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="D67" s="234">
         <v>1399962.63</v>
@@ -4039,13 +3997,13 @@
       <c r="M67" s="84"/>
       <c r="N67" s="84"/>
     </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A68" s="6" t="s">
         <v>241</v>
       </c>
       <c r="B68" s="6"/>
       <c r="C68" s="182" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="D68" s="234">
         <v>1146488.52</v>
@@ -4085,13 +4043,13 @@
       <c r="M68" s="84"/>
       <c r="N68" s="84"/>
     </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A69" s="6" t="s">
         <v>242</v>
       </c>
       <c r="B69" s="6"/>
       <c r="C69" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D69" s="44">
         <v>130990.63</v>
@@ -4122,13 +4080,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A70" s="6" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B70" s="6"/>
       <c r="C70" s="182" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="D70" s="44">
         <v>352314.06</v>
@@ -4153,9 +4111,9 @@
       <c r="M70" s="84"/>
       <c r="N70" s="84"/>
     </row>
-    <row r="71" spans="1:14" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:14" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="258" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="B71" s="264"/>
       <c r="C71" s="35"/>
@@ -4186,13 +4144,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A72" s="35" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B72" s="35"/>
       <c r="C72" s="182" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="D72" s="44">
         <v>911759.61</v>
@@ -4238,13 +4196,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A73" s="35" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B73" s="35"/>
       <c r="C73" s="182" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="D73" s="44">
         <v>6126.48</v>
@@ -4290,9 +4248,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A74" s="142" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B74" s="141"/>
       <c r="C74" s="6"/>
@@ -4340,7 +4298,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="33" t="s">
         <v>5</v>
       </c>
@@ -4387,7 +4345,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" s="6"/>
       <c r="B76" s="6"/>
       <c r="C76" s="6"/>
@@ -4400,7 +4358,7 @@
       <c r="J76" s="6"/>
       <c r="L76" s="69"/>
     </row>
-    <row r="77" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" s="6"/>
       <c r="B77" s="6"/>
       <c r="C77" s="6"/>
@@ -4413,7 +4371,7 @@
       <c r="J77" s="6"/>
       <c r="L77" s="69"/>
     </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A78" s="32" t="s">
         <v>228</v>
       </c>
@@ -4428,13 +4386,13 @@
       <c r="J78" s="6"/>
       <c r="L78" s="69"/>
     </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A79" s="45" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B79" s="193"/>
       <c r="C79" s="35" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D79" s="44">
         <v>60000</v>
@@ -4450,13 +4408,13 @@
       <c r="J79" s="58"/>
       <c r="L79" s="69"/>
     </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A80" s="45" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B80" s="193"/>
       <c r="C80" s="35" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="D80" s="44">
         <v>41371.07</v>
@@ -4472,13 +4430,13 @@
       <c r="J80" s="58"/>
       <c r="L80" s="69"/>
     </row>
-    <row r="81" spans="1:14" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:14" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="262" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="B81" s="263"/>
       <c r="C81" s="137" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="D81" s="44">
         <v>307200</v>
@@ -4494,13 +4452,13 @@
       <c r="J81" s="58"/>
       <c r="L81" s="69"/>
     </row>
-    <row r="82" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="262" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B82" s="263"/>
       <c r="C82" s="137" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="D82" s="44">
         <v>95700</v>
@@ -4531,13 +4489,13 @@
       </c>
       <c r="L82" s="69"/>
     </row>
-    <row r="83" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="262" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B83" s="263"/>
       <c r="C83" s="137" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D83" s="44">
         <v>95700</v>
@@ -4569,7 +4527,7 @@
       <c r="L83" s="69"/>
       <c r="M83" s="43"/>
     </row>
-    <row r="84" spans="1:14" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:14" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="33" t="s">
         <v>229</v>
       </c>
@@ -4613,7 +4571,7 @@
       </c>
       <c r="N84" s="43"/>
     </row>
-    <row r="85" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" s="6"/>
       <c r="B85" s="6"/>
       <c r="C85" s="6"/>
@@ -4626,7 +4584,7 @@
       <c r="J85" s="6"/>
       <c r="L85" s="69"/>
     </row>
-    <row r="86" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86" s="6"/>
       <c r="B86" s="6"/>
       <c r="C86" s="6"/>
@@ -4639,7 +4597,7 @@
       <c r="J86" s="6"/>
       <c r="L86" s="69"/>
     </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A87" s="32" t="s">
         <v>6</v>
       </c>
@@ -4654,7 +4612,7 @@
       <c r="J87" s="6"/>
       <c r="L87" s="69"/>
     </row>
-    <row r="88" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="6" t="s">
         <v>7</v>
       </c>
@@ -4690,10 +4648,10 @@
         <v>13114.38</v>
       </c>
       <c r="L88" s="69" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.25">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="89" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A89" s="32"/>
       <c r="B89" s="6"/>
       <c r="C89" s="6"/>
@@ -4707,7 +4665,7 @@
       <c r="L89" s="69"/>
       <c r="N89" s="44"/>
     </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A90" s="6"/>
       <c r="B90" s="6"/>
       <c r="C90" s="6"/>
@@ -4721,7 +4679,7 @@
       <c r="L90" s="69"/>
       <c r="N90" s="43"/>
     </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A91" s="33" t="s">
         <v>8</v>
       </c>
@@ -4765,7 +4723,7 @@
       </c>
       <c r="N91" s="43"/>
     </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A92" s="6" t="s">
         <v>28</v>
       </c>
@@ -4800,7 +4758,7 @@
       </c>
       <c r="L92" s="69"/>
     </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A93" s="6" t="s">
         <v>29</v>
       </c>
@@ -4833,7 +4791,7 @@
       </c>
       <c r="L93" s="69"/>
     </row>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A94" s="33" t="s">
         <v>230</v>
       </c>
@@ -4876,7 +4834,7 @@
         <v/>
       </c>
     </row>
-    <row r="95" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A95" s="98"/>
       <c r="B95" s="98"/>
       <c r="C95" s="98"/>
@@ -4889,9 +4847,9 @@
       <c r="J95" s="98"/>
       <c r="L95" s="69"/>
     </row>
-    <row r="96" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A96" s="100" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B96" s="101"/>
       <c r="C96" s="101"/>
@@ -4929,7 +4887,7 @@
         <v/>
       </c>
     </row>
-    <row r="97" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A97" s="103"/>
       <c r="B97" s="104"/>
       <c r="C97" s="104"/>
@@ -4943,7 +4901,7 @@
       <c r="K97" s="43"/>
       <c r="L97" s="69"/>
     </row>
-    <row r="98" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A98" s="3" t="s">
         <v>30</v>
       </c>
@@ -4990,7 +4948,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D99" s="85"/>
       <c r="E99" s="43"/>
       <c r="F99" s="43"/>
@@ -4998,7 +4956,7 @@
       <c r="H99" s="43"/>
       <c r="I99" s="43"/>
     </row>
-    <row r="100" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A100" s="64" t="s">
         <v>39</v>
       </c>
@@ -5010,7 +4968,7 @@
       <c r="H100" s="43"/>
       <c r="I100" s="43"/>
     </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A101" s="1"/>
       <c r="C101" s="128"/>
       <c r="E101" s="43"/>
@@ -5019,7 +4977,7 @@
       <c r="H101" s="43"/>
       <c r="I101" s="43"/>
     </row>
-    <row r="102" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A102" s="1"/>
       <c r="C102" s="128"/>
       <c r="E102" s="43"/>
@@ -5028,7 +4986,7 @@
       <c r="H102" s="43"/>
       <c r="I102" s="43"/>
     </row>
-    <row r="103" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A103" s="65" t="s">
         <v>17</v>
       </c>
@@ -5043,21 +5001,21 @@
       <c r="H103" s="43"/>
       <c r="I103" s="43"/>
     </row>
-    <row r="104" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:13" x14ac:dyDescent="0.3">
       <c r="E104" s="43"/>
       <c r="F104" s="43"/>
       <c r="G104" s="43"/>
       <c r="H104" s="43"/>
       <c r="I104" s="43"/>
     </row>
-    <row r="105" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:13" x14ac:dyDescent="0.3">
       <c r="E105" s="60"/>
       <c r="F105" s="60"/>
       <c r="G105" s="60"/>
       <c r="H105" s="60"/>
       <c r="I105" s="60"/>
     </row>
-    <row r="106" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A106" s="256" t="s">
         <v>34</v>
       </c>
@@ -5083,7 +5041,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="107" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="258"/>
       <c r="B107" s="259"/>
       <c r="C107" s="82"/>
@@ -5098,7 +5056,7 @@
       <c r="I107" s="68"/>
       <c r="J107" s="58"/>
     </row>
-    <row r="108" spans="1:13" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:13" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="258"/>
       <c r="B108" s="259"/>
       <c r="C108" s="82"/>
@@ -5110,7 +5068,7 @@
       <c r="I108" s="68"/>
       <c r="J108" s="58"/>
     </row>
-    <row r="109" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A109" s="253" t="s">
         <v>17</v>
       </c>
@@ -5141,14 +5099,14 @@
         <v/>
       </c>
     </row>
-    <row r="111" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E111" s="43"/>
       <c r="F111" s="43"/>
       <c r="G111" s="43"/>
       <c r="H111" s="43"/>
       <c r="I111" s="43"/>
     </row>
-    <row r="112" spans="1:13" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:13" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A112" s="38" t="s">
         <v>31</v>
       </c>
@@ -5157,7 +5115,7 @@
         <v>14242326.569999998</v>
       </c>
     </row>
-    <row r="113" spans="1:11" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:11" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A113" s="40" t="s">
         <v>33</v>
       </c>
@@ -5166,7 +5124,7 @@
         <v>14242326.569999998</v>
       </c>
       <c r="D113" s="261" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="E113" s="261"/>
       <c r="F113" s="261"/>
@@ -5174,7 +5132,7 @@
       <c r="H113" s="261"/>
       <c r="I113" s="261"/>
     </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:11" x14ac:dyDescent="0.3">
       <c r="D114" s="261"/>
       <c r="E114" s="261"/>
       <c r="F114" s="261"/>
@@ -5182,9 +5140,9 @@
       <c r="H114" s="261"/>
       <c r="I114" s="261"/>
     </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A115" s="250" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B115" s="250"/>
       <c r="D115" s="261"/>
@@ -5194,7 +5152,7 @@
       <c r="H115" s="261"/>
       <c r="I115" s="261"/>
     </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A116" s="250"/>
       <c r="B116" s="250"/>
       <c r="D116" s="261"/>
@@ -5204,7 +5162,7 @@
       <c r="H116" s="261"/>
       <c r="I116" s="261"/>
     </row>
-    <row r="117" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A117" s="250"/>
       <c r="B117" s="250"/>
       <c r="D117" s="261"/>
@@ -5214,7 +5172,7 @@
       <c r="H117" s="261"/>
       <c r="I117" s="261"/>
     </row>
-    <row r="118" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A118" s="250"/>
       <c r="B118" s="250"/>
       <c r="D118" s="261"/>
@@ -5224,7 +5182,7 @@
       <c r="H118" s="261"/>
       <c r="I118" s="261"/>
     </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A119" s="250"/>
       <c r="B119" s="250"/>
       <c r="D119" s="261"/>
@@ -5234,7 +5192,7 @@
       <c r="H119" s="261"/>
       <c r="I119" s="261"/>
     </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A120" s="250"/>
       <c r="B120" s="250"/>
       <c r="D120" s="261"/>
@@ -5244,7 +5202,7 @@
       <c r="H120" s="261"/>
       <c r="I120" s="261"/>
     </row>
-    <row r="121" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:11" x14ac:dyDescent="0.3">
       <c r="D121" s="261"/>
       <c r="E121" s="261"/>
       <c r="F121" s="261"/>
@@ -5252,7 +5210,7 @@
       <c r="H121" s="261"/>
       <c r="I121" s="261"/>
     </row>
-    <row r="122" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A122" s="16" t="s">
         <v>20</v>
       </c>
@@ -5265,7 +5223,7 @@
       <c r="H122" s="261"/>
       <c r="I122" s="261"/>
     </row>
-    <row r="123" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A123" s="19" t="s">
         <v>21</v>
       </c>
@@ -5280,7 +5238,7 @@
       <c r="H123" s="261"/>
       <c r="I123" s="261"/>
     </row>
-    <row r="124" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A124" s="21" t="s">
         <v>22</v>
       </c>
@@ -5298,7 +5256,7 @@
       <c r="H124" s="261"/>
       <c r="I124" s="261"/>
     </row>
-    <row r="125" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A125" s="21" t="s">
         <v>36</v>
       </c>
@@ -5315,7 +5273,7 @@
       <c r="I125" s="261"/>
       <c r="K125" s="44"/>
     </row>
-    <row r="126" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A126" s="21" t="s">
         <v>35</v>
       </c>
@@ -5332,9 +5290,9 @@
       <c r="I126" s="261"/>
       <c r="K126" s="52"/>
     </row>
-    <row r="127" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A127" s="21" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B127" s="30">
         <f>B136</f>
@@ -5349,7 +5307,7 @@
       <c r="I127" s="261"/>
       <c r="K127" s="52"/>
     </row>
-    <row r="128" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A128" s="21" t="s">
         <v>32</v>
       </c>
@@ -5365,9 +5323,9 @@
       <c r="H128" s="261"/>
       <c r="I128" s="261"/>
     </row>
-    <row r="129" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A129" s="21" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B129" s="189">
         <f>-87300</f>
@@ -5381,7 +5339,7 @@
       <c r="H129" s="261"/>
       <c r="I129" s="261"/>
     </row>
-    <row r="130" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A130" s="21" t="s">
         <v>39</v>
       </c>
@@ -5397,7 +5355,7 @@
       <c r="H130" s="261"/>
       <c r="I130" s="261"/>
     </row>
-    <row r="131" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A131" s="21"/>
       <c r="B131" s="168"/>
       <c r="C131" s="22"/>
@@ -5408,7 +5366,7 @@
       <c r="H131" s="261"/>
       <c r="I131" s="261"/>
     </row>
-    <row r="132" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A132" s="19" t="s">
         <v>24</v>
       </c>
@@ -5424,7 +5382,7 @@
       <c r="H132" s="261"/>
       <c r="I132" s="261"/>
     </row>
-    <row r="133" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A133" s="22"/>
       <c r="C133" s="18"/>
       <c r="D133" s="261"/>
@@ -5434,9 +5392,9 @@
       <c r="H133" s="261"/>
       <c r="I133" s="261"/>
     </row>
-    <row r="134" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A134" s="16" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B134" s="8"/>
       <c r="C134" s="18"/>
@@ -5447,9 +5405,9 @@
       <c r="H134" s="261"/>
       <c r="I134" s="261"/>
     </row>
-    <row r="135" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="19" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B135" s="30">
         <v>141730</v>
@@ -5457,7 +5415,7 @@
       <c r="C135" s="18"/>
       <c r="D135" s="25"/>
     </row>
-    <row r="136" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A136" s="36" t="s">
         <v>17</v>
       </c>
@@ -5468,17 +5426,17 @@
       <c r="C136" s="18"/>
       <c r="D136" s="25"/>
     </row>
-    <row r="137" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A137" s="22"/>
       <c r="C137" s="18"/>
       <c r="D137" s="25"/>
     </row>
-    <row r="138" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A138" s="22"/>
       <c r="C138" s="18"/>
       <c r="D138" s="25"/>
     </row>
-    <row r="139" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C139" s="18"/>
       <c r="D139" s="43"/>
       <c r="E139" s="84"/>
@@ -5487,7 +5445,7 @@
       <c r="H139" s="84"/>
       <c r="I139" s="84"/>
     </row>
-    <row r="140" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A140" s="16" t="s">
         <v>25</v>
       </c>
@@ -5503,7 +5461,7 @@
       <c r="I140" s="84"/>
       <c r="J140" s="84"/>
     </row>
-    <row r="141" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" s="19" t="s">
         <v>253</v>
       </c>
@@ -5518,7 +5476,7 @@
       <c r="H141" s="88"/>
       <c r="I141" s="88"/>
     </row>
-    <row r="142" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A142" s="19"/>
       <c r="B142" s="83"/>
       <c r="C142" s="24"/>
@@ -5529,7 +5487,7 @@
       <c r="H142" s="43"/>
       <c r="I142" s="43"/>
     </row>
-    <row r="143" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A143" s="36" t="s">
         <v>17</v>
       </c>
@@ -5539,18 +5497,18 @@
       </c>
       <c r="C143" s="24"/>
     </row>
-    <row r="144" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C144" s="25"/>
       <c r="D144" s="84"/>
     </row>
-    <row r="145" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="145" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B145" s="22"/>
       <c r="C145" s="18"/>
     </row>
-    <row r="147" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="147" spans="2:18" x14ac:dyDescent="0.3">
       <c r="R147" s="9"/>
     </row>
-    <row r="150" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="150" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B150" s="252"/>
       <c r="C150" s="252"/>
       <c r="D150" s="252"/>
@@ -5560,7 +5518,7 @@
       <c r="H150" s="90"/>
       <c r="I150" s="90"/>
     </row>
-    <row r="151" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="151" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B151" s="252"/>
       <c r="C151" s="252"/>
       <c r="D151" s="252"/>
@@ -5570,7 +5528,7 @@
       <c r="H151" s="90"/>
       <c r="I151" s="90"/>
     </row>
-    <row r="152" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="152" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B152" s="252"/>
       <c r="C152" s="252"/>
       <c r="D152" s="252"/>
@@ -5580,7 +5538,7 @@
       <c r="H152" s="90"/>
       <c r="I152" s="90"/>
     </row>
-    <row r="153" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="153" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B153" s="252"/>
       <c r="C153" s="252"/>
       <c r="D153" s="252"/>
@@ -5590,7 +5548,7 @@
       <c r="H153" s="90"/>
       <c r="I153" s="90"/>
     </row>
-    <row r="154" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="154" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B154" s="252"/>
       <c r="C154" s="252"/>
       <c r="D154" s="252"/>
@@ -5627,38 +5585,38 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:DJ154"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.5703125" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="5.85546875" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="8.140625" customWidth="1"/>
-    <col min="4" max="4" width="42.7109375" customWidth="1"/>
-    <col min="5" max="5" width="25.5703125" customWidth="1"/>
-    <col min="6" max="6" width="9.42578125" customWidth="1"/>
-    <col min="7" max="7" width="13.28515625" customWidth="1"/>
+    <col min="1" max="1" width="4.5546875" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="5.88671875" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="8.109375" customWidth="1"/>
+    <col min="4" max="4" width="42.6640625" customWidth="1"/>
+    <col min="5" max="5" width="25.5546875" customWidth="1"/>
+    <col min="6" max="6" width="9.44140625" customWidth="1"/>
+    <col min="7" max="7" width="13.33203125" customWidth="1"/>
     <col min="8" max="8" width="13" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.85546875" customWidth="1"/>
-    <col min="10" max="11" width="13.7109375" customWidth="1"/>
-    <col min="12" max="12" width="13.28515625" customWidth="1"/>
-    <col min="13" max="13" width="10.42578125" customWidth="1"/>
-    <col min="14" max="14" width="15.42578125" customWidth="1"/>
-    <col min="15" max="15" width="13.7109375" customWidth="1"/>
-    <col min="16" max="16" width="11.42578125" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.88671875" customWidth="1"/>
+    <col min="10" max="11" width="13.6640625" customWidth="1"/>
+    <col min="12" max="12" width="13.33203125" customWidth="1"/>
+    <col min="13" max="13" width="10.44140625" customWidth="1"/>
+    <col min="14" max="14" width="15.44140625" customWidth="1"/>
+    <col min="15" max="15" width="13.6640625" customWidth="1"/>
+    <col min="16" max="16" width="11.44140625" customWidth="1"/>
+    <col min="17" max="17" width="14.5546875" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="13" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A1" s="298" t="s">
-        <v>327</v>
-      </c>
-      <c r="B1" s="299"/>
-      <c r="C1" s="299"/>
-      <c r="D1" s="299"/>
-      <c r="E1" s="299"/>
+    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1" s="294" t="s">
+        <v>326</v>
+      </c>
+      <c r="B1" s="295"/>
+      <c r="C1" s="295"/>
+      <c r="D1" s="295"/>
+      <c r="E1" s="295"/>
       <c r="F1" s="158" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="G1" s="158"/>
       <c r="H1" s="158"/>
@@ -5668,22 +5626,22 @@
       <c r="L1" s="190" t="s">
         <v>41</v>
       </c>
-      <c r="M1" s="277">
+      <c r="M1" s="270">
         <f>RESUMEN!D98-RESUMEN!D96</f>
         <v>14242326.569999998</v>
       </c>
-      <c r="N1" s="278"/>
+      <c r="N1" s="271"/>
       <c r="O1" s="159"/>
       <c r="P1" s="59"/>
     </row>
-    <row r="2" spans="1:19" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="300"/>
-      <c r="B2" s="301"/>
-      <c r="C2" s="301"/>
-      <c r="D2" s="301"/>
-      <c r="E2" s="301"/>
+    <row r="2" spans="1:19" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="296"/>
+      <c r="B2" s="297"/>
+      <c r="C2" s="297"/>
+      <c r="D2" s="297"/>
+      <c r="E2" s="297"/>
       <c r="F2" s="7" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="G2" s="7"/>
       <c r="H2" s="7"/>
@@ -5700,14 +5658,14 @@
       <c r="O2" s="160"/>
       <c r="P2" s="59"/>
     </row>
-    <row r="3" spans="1:19" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="300"/>
-      <c r="B3" s="301"/>
-      <c r="C3" s="301"/>
-      <c r="D3" s="301"/>
-      <c r="E3" s="301"/>
+    <row r="3" spans="1:19" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="296"/>
+      <c r="B3" s="297"/>
+      <c r="C3" s="297"/>
+      <c r="D3" s="297"/>
+      <c r="E3" s="297"/>
       <c r="F3" s="7" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="G3" s="7"/>
       <c r="H3" s="7"/>
@@ -5715,7 +5673,7 @@
       <c r="J3" s="161"/>
       <c r="K3" s="161"/>
       <c r="L3" s="191" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="M3" s="7"/>
       <c r="N3" s="241">
@@ -5725,12 +5683,12 @@
       <c r="O3" s="162"/>
       <c r="P3" s="15"/>
     </row>
-    <row r="4" spans="1:19" ht="2.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="302"/>
-      <c r="B4" s="303"/>
-      <c r="C4" s="303"/>
-      <c r="D4" s="303"/>
-      <c r="E4" s="303"/>
+    <row r="4" spans="1:19" ht="2.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="298"/>
+      <c r="B4" s="299"/>
+      <c r="C4" s="299"/>
+      <c r="D4" s="299"/>
+      <c r="E4" s="299"/>
       <c r="F4" s="163"/>
       <c r="G4" s="163"/>
       <c r="H4" s="163"/>
@@ -5743,98 +5701,98 @@
       <c r="O4" s="166"/>
       <c r="P4" s="15"/>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A5" s="7"/>
       <c r="B5" s="7"/>
-      <c r="C5" s="283" t="s">
-        <v>310</v>
-      </c>
-      <c r="D5" s="284"/>
-      <c r="E5" s="284"/>
-      <c r="F5" s="284"/>
-      <c r="G5" s="284"/>
-      <c r="H5" s="284"/>
-      <c r="I5" s="284"/>
-      <c r="J5" s="284"/>
-      <c r="K5" s="284"/>
-      <c r="L5" s="284"/>
-      <c r="M5" s="284"/>
-      <c r="N5" s="284"/>
-      <c r="O5" s="285"/>
+      <c r="C5" s="279" t="s">
+        <v>309</v>
+      </c>
+      <c r="D5" s="280"/>
+      <c r="E5" s="280"/>
+      <c r="F5" s="280"/>
+      <c r="G5" s="280"/>
+      <c r="H5" s="280"/>
+      <c r="I5" s="280"/>
+      <c r="J5" s="280"/>
+      <c r="K5" s="280"/>
+      <c r="L5" s="280"/>
+      <c r="M5" s="280"/>
+      <c r="N5" s="280"/>
+      <c r="O5" s="281"/>
       <c r="P5" s="15"/>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A6" s="7"/>
       <c r="B6" s="7"/>
-      <c r="C6" s="286"/>
-      <c r="D6" s="287"/>
-      <c r="E6" s="287"/>
-      <c r="F6" s="287"/>
-      <c r="G6" s="287"/>
-      <c r="H6" s="287"/>
-      <c r="I6" s="287"/>
-      <c r="J6" s="287"/>
-      <c r="K6" s="287"/>
-      <c r="L6" s="287"/>
-      <c r="M6" s="287"/>
-      <c r="N6" s="287"/>
-      <c r="O6" s="288"/>
+      <c r="C6" s="282"/>
+      <c r="D6" s="283"/>
+      <c r="E6" s="283"/>
+      <c r="F6" s="283"/>
+      <c r="G6" s="283"/>
+      <c r="H6" s="283"/>
+      <c r="I6" s="283"/>
+      <c r="J6" s="283"/>
+      <c r="K6" s="283"/>
+      <c r="L6" s="283"/>
+      <c r="M6" s="283"/>
+      <c r="N6" s="283"/>
+      <c r="O6" s="284"/>
       <c r="P6" s="15"/>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A7" s="7"/>
       <c r="B7" s="7"/>
-      <c r="C7" s="286"/>
-      <c r="D7" s="287"/>
-      <c r="E7" s="287"/>
-      <c r="F7" s="287"/>
-      <c r="G7" s="287"/>
-      <c r="H7" s="287"/>
-      <c r="I7" s="287"/>
-      <c r="J7" s="287"/>
-      <c r="K7" s="287"/>
-      <c r="L7" s="287"/>
-      <c r="M7" s="287"/>
-      <c r="N7" s="287"/>
-      <c r="O7" s="288"/>
+      <c r="C7" s="282"/>
+      <c r="D7" s="283"/>
+      <c r="E7" s="283"/>
+      <c r="F7" s="283"/>
+      <c r="G7" s="283"/>
+      <c r="H7" s="283"/>
+      <c r="I7" s="283"/>
+      <c r="J7" s="283"/>
+      <c r="K7" s="283"/>
+      <c r="L7" s="283"/>
+      <c r="M7" s="283"/>
+      <c r="N7" s="283"/>
+      <c r="O7" s="284"/>
       <c r="P7" s="15"/>
     </row>
-    <row r="8" spans="1:19" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:19" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="7"/>
       <c r="B8" s="7"/>
-      <c r="C8" s="289"/>
-      <c r="D8" s="290"/>
-      <c r="E8" s="290"/>
-      <c r="F8" s="290"/>
-      <c r="G8" s="290"/>
-      <c r="H8" s="290"/>
-      <c r="I8" s="290"/>
-      <c r="J8" s="290"/>
-      <c r="K8" s="290"/>
-      <c r="L8" s="290"/>
-      <c r="M8" s="290"/>
-      <c r="N8" s="290"/>
-      <c r="O8" s="291"/>
+      <c r="C8" s="285"/>
+      <c r="D8" s="286"/>
+      <c r="E8" s="286"/>
+      <c r="F8" s="286"/>
+      <c r="G8" s="286"/>
+      <c r="H8" s="286"/>
+      <c r="I8" s="286"/>
+      <c r="J8" s="286"/>
+      <c r="K8" s="286"/>
+      <c r="L8" s="286"/>
+      <c r="M8" s="286"/>
+      <c r="N8" s="286"/>
+      <c r="O8" s="287"/>
       <c r="Q8" s="84"/>
     </row>
-    <row r="9" spans="1:19" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
-      <c r="C9" s="292" t="s">
-        <v>308</v>
-      </c>
-      <c r="D9" s="293"/>
-      <c r="E9" s="293"/>
-      <c r="F9" s="293"/>
-      <c r="G9" s="293"/>
-      <c r="H9" s="293"/>
-      <c r="I9" s="293"/>
-      <c r="J9" s="293"/>
-      <c r="K9" s="293"/>
-      <c r="L9" s="293"/>
-      <c r="M9" s="293"/>
-      <c r="N9" s="293"/>
-      <c r="O9" s="294"/>
+      <c r="C9" s="288" t="s">
+        <v>307</v>
+      </c>
+      <c r="D9" s="289"/>
+      <c r="E9" s="289"/>
+      <c r="F9" s="289"/>
+      <c r="G9" s="289"/>
+      <c r="H9" s="289"/>
+      <c r="I9" s="289"/>
+      <c r="J9" s="289"/>
+      <c r="K9" s="289"/>
+      <c r="L9" s="289"/>
+      <c r="M9" s="289"/>
+      <c r="N9" s="289"/>
+      <c r="O9" s="290"/>
       <c r="Q9" t="s">
         <v>248</v>
       </c>
@@ -5843,22 +5801,22 @@
         <v>144184.86874800001</v>
       </c>
     </row>
-    <row r="10" spans="1:19" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:19" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="7"/>
       <c r="B10" s="7"/>
-      <c r="C10" s="295"/>
-      <c r="D10" s="296"/>
-      <c r="E10" s="296"/>
-      <c r="F10" s="296"/>
-      <c r="G10" s="296"/>
-      <c r="H10" s="296"/>
-      <c r="I10" s="296"/>
-      <c r="J10" s="296"/>
-      <c r="K10" s="296"/>
-      <c r="L10" s="296"/>
-      <c r="M10" s="296"/>
-      <c r="N10" s="296"/>
-      <c r="O10" s="297"/>
+      <c r="C10" s="291"/>
+      <c r="D10" s="292"/>
+      <c r="E10" s="292"/>
+      <c r="F10" s="292"/>
+      <c r="G10" s="292"/>
+      <c r="H10" s="292"/>
+      <c r="I10" s="292"/>
+      <c r="J10" s="292"/>
+      <c r="K10" s="292"/>
+      <c r="L10" s="292"/>
+      <c r="M10" s="292"/>
+      <c r="N10" s="292"/>
+      <c r="O10" s="293"/>
       <c r="Q10" t="s">
         <v>249</v>
       </c>
@@ -5867,51 +5825,51 @@
         <v>170885.77036800003</v>
       </c>
     </row>
-    <row r="11" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="268" t="s">
+    <row r="11" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="266" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="270" t="s">
+      <c r="B11" s="300" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="268" t="s">
+      <c r="C11" s="266" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="272" t="s">
+      <c r="D11" s="302" t="s">
         <v>12</v>
       </c>
-      <c r="E11" s="272" t="s">
-        <v>266</v>
-      </c>
-      <c r="F11" s="268" t="s">
+      <c r="E11" s="302" t="s">
+        <v>265</v>
+      </c>
+      <c r="F11" s="266" t="s">
         <v>27</v>
       </c>
-      <c r="G11" s="268" t="s">
+      <c r="G11" s="266" t="s">
         <v>13</v>
       </c>
-      <c r="H11" s="268" t="s">
+      <c r="H11" s="266" t="s">
         <v>14</v>
       </c>
-      <c r="I11" s="279" t="s">
+      <c r="I11" s="272" t="s">
         <v>15</v>
       </c>
-      <c r="J11" s="265" t="s">
+      <c r="J11" s="274" t="s">
         <v>16</v>
       </c>
-      <c r="K11" s="265" t="s">
-        <v>390</v>
-      </c>
-      <c r="L11" s="265" t="s">
+      <c r="K11" s="274" t="s">
+        <v>388</v>
+      </c>
+      <c r="L11" s="274" t="s">
         <v>18</v>
       </c>
-      <c r="M11" s="281" t="s">
+      <c r="M11" s="277" t="s">
         <v>40</v>
       </c>
-      <c r="N11" s="265" t="s">
-        <v>277</v>
-      </c>
-      <c r="O11" s="265" t="s">
+      <c r="N11" s="274" t="s">
         <v>276</v>
+      </c>
+      <c r="O11" s="274" t="s">
+        <v>275</v>
       </c>
       <c r="Q11" t="s">
         <v>250</v>
@@ -5921,22 +5879,22 @@
         <v>161540.45480100001</v>
       </c>
     </row>
-    <row r="12" spans="1:19" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="269"/>
-      <c r="B12" s="271"/>
-      <c r="C12" s="269"/>
-      <c r="D12" s="273"/>
-      <c r="E12" s="273"/>
-      <c r="F12" s="269"/>
-      <c r="G12" s="269"/>
-      <c r="H12" s="269"/>
-      <c r="I12" s="280"/>
-      <c r="J12" s="266"/>
-      <c r="K12" s="266"/>
-      <c r="L12" s="266"/>
-      <c r="M12" s="282"/>
-      <c r="N12" s="266"/>
-      <c r="O12" s="266"/>
+    <row r="12" spans="1:19" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="267"/>
+      <c r="B12" s="301"/>
+      <c r="C12" s="267"/>
+      <c r="D12" s="303"/>
+      <c r="E12" s="303"/>
+      <c r="F12" s="267"/>
+      <c r="G12" s="267"/>
+      <c r="H12" s="267"/>
+      <c r="I12" s="273"/>
+      <c r="J12" s="275"/>
+      <c r="K12" s="275"/>
+      <c r="L12" s="275"/>
+      <c r="M12" s="278"/>
+      <c r="N12" s="275"/>
+      <c r="O12" s="275"/>
       <c r="Q12" t="s">
         <v>251</v>
       </c>
@@ -5945,20 +5903,20 @@
         <v>198921.71706900001</v>
       </c>
     </row>
-    <row r="13" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="269"/>
-      <c r="B13" s="271"/>
-      <c r="C13" s="269"/>
-      <c r="D13" s="273"/>
-      <c r="E13" s="273"/>
-      <c r="F13" s="269"/>
-      <c r="G13" s="269"/>
-      <c r="H13" s="269"/>
-      <c r="I13" s="280"/>
-      <c r="J13" s="266"/>
-      <c r="K13" s="267"/>
-      <c r="L13" s="267"/>
-      <c r="M13" s="282"/>
+    <row r="13" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="267"/>
+      <c r="B13" s="301"/>
+      <c r="C13" s="267"/>
+      <c r="D13" s="303"/>
+      <c r="E13" s="303"/>
+      <c r="F13" s="267"/>
+      <c r="G13" s="267"/>
+      <c r="H13" s="267"/>
+      <c r="I13" s="273"/>
+      <c r="J13" s="275"/>
+      <c r="K13" s="276"/>
+      <c r="L13" s="276"/>
+      <c r="M13" s="278"/>
       <c r="N13" s="132" t="str">
         <f>RESUMEN!A20</f>
         <v>VTO 16/03</v>
@@ -5975,7 +5933,7 @@
         <v>232297.84409400003</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
         <v>118</v>
       </c>
@@ -5987,7 +5945,7 @@
         <v>175</v>
       </c>
       <c r="E14" s="108" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="F14" s="143">
         <v>1.0800000000000001E-2</v>
@@ -6022,17 +5980,17 @@
         <v>655631.62013736006</v>
       </c>
       <c r="P14" s="115"/>
-      <c r="R14" s="274"/>
-      <c r="S14" s="274"/>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R14" s="265"/>
+      <c r="S14" s="265"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A15" s="6"/>
       <c r="B15" s="6"/>
       <c r="C15" s="35" t="s">
         <v>117</v>
       </c>
       <c r="D15" s="108" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E15" s="188"/>
       <c r="F15" s="143">
@@ -6071,10 +6029,10 @@
         <v>254997.15626608004</v>
       </c>
       <c r="P15" s="115"/>
-      <c r="R15" s="274"/>
-      <c r="S15" s="274"/>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R15" s="265"/>
+      <c r="S15" s="265"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
         <v>118</v>
       </c>
@@ -6083,10 +6041,10 @@
         <v>114</v>
       </c>
       <c r="D16" s="108" t="s">
-        <v>264</v>
+        <v>394</v>
       </c>
       <c r="E16" s="108" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="F16" s="143">
         <v>1.21E-2</v>
@@ -6126,7 +6084,7 @@
       <c r="P16" s="115"/>
       <c r="S16" s="43"/>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
         <v>118</v>
       </c>
@@ -6173,7 +6131,7 @@
       <c r="P17" s="115"/>
       <c r="S17" s="43"/>
     </row>
-    <row r="18" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="6" t="s">
         <v>118</v>
       </c>
@@ -6182,7 +6140,7 @@
         <v>116</v>
       </c>
       <c r="D18" s="149" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E18" s="149"/>
       <c r="F18" s="150">
@@ -6220,7 +6178,7 @@
       <c r="P18" s="115"/>
       <c r="S18" s="43"/>
     </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A19" s="57" t="s">
         <v>120</v>
       </c>
@@ -6273,7 +6231,7 @@
       </c>
       <c r="S19" s="43"/>
     </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A20" s="57" t="s">
         <v>121</v>
       </c>
@@ -6328,7 +6286,7 @@
       </c>
       <c r="S20" s="43"/>
     </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A21" s="57" t="s">
         <v>120</v>
       </c>
@@ -6382,7 +6340,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A22" s="57" t="s">
         <v>122</v>
       </c>
@@ -6394,7 +6352,7 @@
         <v>180</v>
       </c>
       <c r="E22" s="196" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F22" s="197">
         <v>9.4000000000000004E-3</v>
@@ -6437,10 +6395,10 @@
         <v>0.04</v>
       </c>
       <c r="Q22" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A23" s="57" t="s">
         <v>122</v>
       </c>
@@ -6452,7 +6410,7 @@
         <v>181</v>
       </c>
       <c r="E23" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F23" s="136">
         <v>8.6999999999999994E-3</v>
@@ -6496,7 +6454,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A24" s="57" t="s">
         <v>122</v>
       </c>
@@ -6508,7 +6466,7 @@
         <v>182</v>
       </c>
       <c r="E24" s="135" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F24" s="136">
         <v>9.4999999999999998E-3</v>
@@ -6552,7 +6510,7 @@
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A25" s="57" t="s">
         <v>120</v>
       </c>
@@ -6564,7 +6522,7 @@
         <v>182</v>
       </c>
       <c r="E25" s="135" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F25" s="136">
         <v>1.6500000000000001E-2</v>
@@ -6605,7 +6563,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A26" s="57" t="s">
         <v>121</v>
       </c>
@@ -6614,7 +6572,7 @@
         <v>51</v>
       </c>
       <c r="D26" s="108" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E26" s="135"/>
       <c r="F26" s="136">
@@ -6659,7 +6617,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A27" s="108" t="s">
         <v>120</v>
       </c>
@@ -6671,7 +6629,7 @@
         <v>182</v>
       </c>
       <c r="E27" s="196" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="F27" s="197">
         <v>1.78E-2</v>
@@ -6712,7 +6670,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A28" s="108" t="s">
         <v>122</v>
       </c>
@@ -6721,7 +6679,7 @@
         <v>53</v>
       </c>
       <c r="D28" s="108" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="E28" s="135"/>
       <c r="F28" s="136">
@@ -6766,7 +6724,7 @@
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A29" s="108" t="s">
         <v>122</v>
       </c>
@@ -6775,7 +6733,7 @@
         <v>54</v>
       </c>
       <c r="D29" s="108" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E29" s="135"/>
       <c r="F29" s="136">
@@ -6820,7 +6778,7 @@
         <v>0.10999999999999999</v>
       </c>
     </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A30" s="108" t="s">
         <v>122</v>
       </c>
@@ -6871,7 +6829,7 @@
         <v>0.11999999999999998</v>
       </c>
     </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A31" s="108" t="s">
         <v>120</v>
       </c>
@@ -6925,7 +6883,7 @@
         <v>0.12999999999999998</v>
       </c>
     </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A32" s="57" t="s">
         <v>121</v>
       </c>
@@ -6937,7 +6895,7 @@
         <v>254</v>
       </c>
       <c r="E32" s="135" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="F32" s="136">
         <v>7.1999999999999998E-3</v>
@@ -6981,7 +6939,7 @@
         <v>0.13999999999999999</v>
       </c>
     </row>
-    <row r="33" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A33" s="57" t="s">
         <v>120</v>
       </c>
@@ -7035,7 +6993,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="34" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A34" s="139" t="s">
         <v>122</v>
       </c>
@@ -7044,7 +7002,7 @@
         <v>59</v>
       </c>
       <c r="D34" s="108" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E34" s="135"/>
       <c r="F34" s="136">
@@ -7089,10 +7047,10 @@
         <v>0.16</v>
       </c>
       <c r="Q34" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="35" spans="1:114" x14ac:dyDescent="0.25">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="35" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A35" s="57" t="s">
         <v>122</v>
       </c>
@@ -7104,7 +7062,7 @@
         <v>183</v>
       </c>
       <c r="E35" s="135" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="F35" s="136">
         <v>8.6999999999999994E-3</v>
@@ -7148,7 +7106,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="36" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A36" s="57" t="s">
         <v>122</v>
       </c>
@@ -7199,7 +7157,7 @@
         <v>0.18000000000000002</v>
       </c>
     </row>
-    <row r="37" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A37" s="57" t="s">
         <v>120</v>
       </c>
@@ -7211,7 +7169,7 @@
         <v>186</v>
       </c>
       <c r="E37" s="135" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F37" s="136">
         <v>1.6400000000000001E-2</v>
@@ -7252,10 +7210,10 @@
         <v>0.19000000000000003</v>
       </c>
       <c r="Q37" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="38" spans="1:114" x14ac:dyDescent="0.25">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="38" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A38" s="57" t="s">
         <v>121</v>
       </c>
@@ -7309,7 +7267,7 @@
         <v>0.20000000000000004</v>
       </c>
     </row>
-    <row r="39" spans="1:114" s="140" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:114" s="140" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A39" s="108" t="s">
         <v>120</v>
       </c>
@@ -7458,7 +7416,7 @@
       <c r="DI39" s="73"/>
       <c r="DJ39" s="73"/>
     </row>
-    <row r="40" spans="1:114" s="140" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:114" s="140" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A40" s="108" t="s">
         <v>122</v>
       </c>
@@ -7467,7 +7425,7 @@
         <v>65</v>
       </c>
       <c r="D40" s="108" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E40" s="135"/>
       <c r="F40" s="136">
@@ -7509,7 +7467,7 @@
         <v>0.22000000000000006</v>
       </c>
       <c r="Q40" s="73" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="R40" s="73"/>
       <c r="S40" s="73"/>
@@ -7609,7 +7567,7 @@
       <c r="DI40" s="73"/>
       <c r="DJ40" s="73"/>
     </row>
-    <row r="41" spans="1:114" s="140" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:114" s="140" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A41" s="108" t="s">
         <v>122</v>
       </c>
@@ -7663,7 +7621,7 @@
         <v>0.23000000000000007</v>
       </c>
       <c r="Q41" s="73" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="R41" s="73"/>
       <c r="S41" s="73"/>
@@ -7763,7 +7721,7 @@
       <c r="DI41" s="73"/>
       <c r="DJ41" s="73"/>
     </row>
-    <row r="42" spans="1:114" s="140" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:114" s="140" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A42" s="108" t="s">
         <v>122</v>
       </c>
@@ -7772,7 +7730,7 @@
         <v>67</v>
       </c>
       <c r="D42" s="108" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E42" s="135"/>
       <c r="F42" s="136">
@@ -7914,7 +7872,7 @@
       <c r="DI42" s="73"/>
       <c r="DJ42" s="73"/>
     </row>
-    <row r="43" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A43" s="57" t="s">
         <v>120</v>
       </c>
@@ -7968,7 +7926,7 @@
         <v>0.25000000000000006</v>
       </c>
     </row>
-    <row r="44" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A44" s="57" t="s">
         <v>121</v>
       </c>
@@ -7980,7 +7938,7 @@
         <v>189</v>
       </c>
       <c r="E44" s="135" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="F44" s="136">
         <v>7.1999999999999998E-3</v>
@@ -8024,7 +7982,7 @@
         <v>0.26000000000000006</v>
       </c>
     </row>
-    <row r="45" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A45" s="57" t="s">
         <v>120</v>
       </c>
@@ -8084,7 +8042,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="46" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A46" s="171" t="s">
         <v>122</v>
       </c>
@@ -8093,7 +8051,7 @@
         <v>71</v>
       </c>
       <c r="D46" s="108" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E46" s="135"/>
       <c r="F46" s="136">
@@ -8138,7 +8096,7 @@
         <v>0.28000000000000008</v>
       </c>
     </row>
-    <row r="47" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A47" s="57" t="s">
         <v>122</v>
       </c>
@@ -8150,7 +8108,7 @@
         <v>181</v>
       </c>
       <c r="E47" s="135" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F47" s="136">
         <v>8.6999999999999994E-3</v>
@@ -8194,7 +8152,7 @@
         <v>0.29000000000000009</v>
       </c>
     </row>
-    <row r="48" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A48" s="57" t="s">
         <v>122</v>
       </c>
@@ -8248,7 +8206,7 @@
         <v>0.3000000000000001</v>
       </c>
     </row>
-    <row r="49" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A49" s="57" t="s">
         <v>120</v>
       </c>
@@ -8302,7 +8260,7 @@
         <v>0.31000000000000011</v>
       </c>
     </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A50" s="57" t="s">
         <v>121</v>
       </c>
@@ -8357,7 +8315,7 @@
       </c>
       <c r="Q50" s="43"/>
     </row>
-    <row r="51" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A51" s="57" t="s">
         <v>120</v>
       </c>
@@ -8412,7 +8370,7 @@
       </c>
       <c r="Q51" s="43"/>
     </row>
-    <row r="52" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A52" s="57" t="s">
         <v>122</v>
       </c>
@@ -8421,7 +8379,7 @@
         <v>77</v>
       </c>
       <c r="D52" s="108" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="E52" s="135"/>
       <c r="F52" s="136">
@@ -8466,10 +8424,10 @@
         <v>0.34000000000000014</v>
       </c>
       <c r="Q52" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="53" spans="1:18" x14ac:dyDescent="0.25">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="53" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A53" s="57" t="s">
         <v>122</v>
       </c>
@@ -8523,7 +8481,7 @@
         <v>0.35000000000000014</v>
       </c>
     </row>
-    <row r="54" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A54" s="57" t="s">
         <v>122</v>
       </c>
@@ -8574,7 +8532,7 @@
         <v>0.36000000000000015</v>
       </c>
     </row>
-    <row r="55" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A55" s="57" t="s">
         <v>120</v>
       </c>
@@ -8629,7 +8587,7 @@
       </c>
       <c r="R55" s="59"/>
     </row>
-    <row r="56" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A56" s="57" t="s">
         <v>121</v>
       </c>
@@ -8641,7 +8599,7 @@
         <v>196</v>
       </c>
       <c r="E56" s="135" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F56" s="136">
         <v>7.1999999999999998E-3</v>
@@ -8685,7 +8643,7 @@
         <v>0.38000000000000017</v>
       </c>
     </row>
-    <row r="57" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A57" s="57" t="s">
         <v>120</v>
       </c>
@@ -8736,7 +8694,7 @@
         <v>0.39000000000000018</v>
       </c>
     </row>
-    <row r="58" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A58" s="57" t="s">
         <v>122</v>
       </c>
@@ -8748,7 +8706,7 @@
         <v>198</v>
       </c>
       <c r="E58" s="135" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F58" s="136">
         <v>9.4000000000000004E-3</v>
@@ -8791,7 +8749,7 @@
         <v>0.40000000000000019</v>
       </c>
     </row>
-    <row r="59" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A59" s="108" t="s">
         <v>122</v>
       </c>
@@ -8800,7 +8758,7 @@
         <v>84</v>
       </c>
       <c r="D59" s="108" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E59" s="135"/>
       <c r="F59" s="136">
@@ -8848,7 +8806,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="60" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A60" s="108" t="s">
         <v>122</v>
       </c>
@@ -8902,10 +8860,10 @@
         <v>0.42000000000000021</v>
       </c>
       <c r="Q60" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="61" spans="1:18" x14ac:dyDescent="0.25">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="61" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A61" s="108" t="s">
         <v>120</v>
       </c>
@@ -8959,7 +8917,7 @@
         <v>0.43000000000000022</v>
       </c>
     </row>
-    <row r="62" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A62" s="108" t="s">
         <v>121</v>
       </c>
@@ -9013,7 +8971,7 @@
         <v>0.44000000000000022</v>
       </c>
     </row>
-    <row r="63" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A63" s="57" t="s">
         <v>120</v>
       </c>
@@ -9067,7 +9025,7 @@
         <v>0.45000000000000023</v>
       </c>
     </row>
-    <row r="64" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A64" s="57" t="s">
         <v>122</v>
       </c>
@@ -9079,7 +9037,7 @@
         <v>202</v>
       </c>
       <c r="E64" s="135" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="F64" s="136">
         <v>9.4000000000000004E-3</v>
@@ -9123,7 +9081,7 @@
         <v>0.46000000000000024</v>
       </c>
     </row>
-    <row r="65" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A65" s="57" t="s">
         <v>122</v>
       </c>
@@ -9177,7 +9135,7 @@
         <v>0.47000000000000025</v>
       </c>
     </row>
-    <row r="66" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A66" s="57" t="s">
         <v>122</v>
       </c>
@@ -9232,7 +9190,7 @@
       </c>
       <c r="S66" s="181"/>
     </row>
-    <row r="67" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A67" s="57" t="s">
         <v>120</v>
       </c>
@@ -9287,7 +9245,7 @@
       </c>
       <c r="S67" s="43"/>
     </row>
-    <row r="68" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A68" s="139" t="s">
         <v>121</v>
       </c>
@@ -9341,7 +9299,7 @@
         <v>0.50000000000000022</v>
       </c>
     </row>
-    <row r="69" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A69" s="57" t="s">
         <v>120</v>
       </c>
@@ -9395,7 +9353,7 @@
         <v>0.51000000000000023</v>
       </c>
     </row>
-    <row r="70" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A70" s="57" t="s">
         <v>122</v>
       </c>
@@ -9449,7 +9407,7 @@
         <v>0.52000000000000024</v>
       </c>
     </row>
-    <row r="71" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A71" s="57" t="s">
         <v>122</v>
       </c>
@@ -9506,7 +9464,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="72" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A72" s="57" t="s">
         <v>122</v>
       </c>
@@ -9560,7 +9518,7 @@
         <v>0.54000000000000026</v>
       </c>
     </row>
-    <row r="73" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A73" s="57" t="s">
         <v>123</v>
       </c>
@@ -9615,7 +9573,7 @@
       </c>
       <c r="Q73" s="73"/>
     </row>
-    <row r="74" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A74" s="57" t="s">
         <v>120</v>
       </c>
@@ -9669,7 +9627,7 @@
         <v>0.56000000000000028</v>
       </c>
     </row>
-    <row r="75" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A75" s="57" t="s">
         <v>122</v>
       </c>
@@ -9722,7 +9680,7 @@
         <v>0.57000000000000028</v>
       </c>
     </row>
-    <row r="76" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A76" s="57" t="s">
         <v>122</v>
       </c>
@@ -9734,7 +9692,7 @@
         <v>211</v>
       </c>
       <c r="E76" s="135" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F76" s="136">
         <v>8.6999999999999994E-3</v>
@@ -9775,7 +9733,7 @@
         <v>0.58000000000000029</v>
       </c>
     </row>
-    <row r="77" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A77" s="57" t="s">
         <v>122</v>
       </c>
@@ -9829,7 +9787,7 @@
         <v>0.5900000000000003</v>
       </c>
     </row>
-    <row r="78" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A78" s="57" t="s">
         <v>123</v>
       </c>
@@ -9883,7 +9841,7 @@
         <v>0.60000000000000031</v>
       </c>
     </row>
-    <row r="79" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A79" s="57" t="s">
         <v>120</v>
       </c>
@@ -9937,7 +9895,7 @@
         <v>0.61000000000000032</v>
       </c>
     </row>
-    <row r="80" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A80" s="57" t="s">
         <v>122</v>
       </c>
@@ -9991,7 +9949,7 @@
         <v>0.62000000000000033</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A81" s="57" t="s">
         <v>122</v>
       </c>
@@ -10003,7 +9961,7 @@
         <v>216</v>
       </c>
       <c r="E81" s="196" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F81" s="197">
         <v>8.6999999999999994E-3</v>
@@ -10047,7 +10005,7 @@
         <v>0.63000000000000034</v>
       </c>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A82" s="57" t="s">
         <v>122</v>
       </c>
@@ -10101,10 +10059,10 @@
         <v>0.64000000000000035</v>
       </c>
       <c r="Q82" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="83" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A83" s="57" t="s">
         <v>123</v>
       </c>
@@ -10113,7 +10071,7 @@
         <v>108</v>
       </c>
       <c r="D83" s="108" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E83" s="135"/>
       <c r="F83" s="136">
@@ -10158,7 +10116,7 @@
         <v>0.65000000000000036</v>
       </c>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A84" s="57" t="s">
         <v>120</v>
       </c>
@@ -10212,7 +10170,7 @@
         <v>0.66000000000000036</v>
       </c>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A85" s="57" t="s">
         <v>122</v>
       </c>
@@ -10266,7 +10224,7 @@
         <v>0.67000000000000037</v>
       </c>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A86" s="57" t="s">
         <v>122</v>
       </c>
@@ -10320,7 +10278,7 @@
         <v>0.68000000000000038</v>
       </c>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A87" s="108" t="s">
         <v>122</v>
       </c>
@@ -10374,7 +10332,7 @@
         <v>0.69000000000000039</v>
       </c>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A88" s="108"/>
       <c r="B88" s="35"/>
       <c r="C88" s="35" t="s">
@@ -10426,7 +10384,7 @@
         <v>0.7000000000000004</v>
       </c>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A89" s="108"/>
       <c r="B89" s="35"/>
       <c r="C89" s="35" t="s">
@@ -10478,7 +10436,7 @@
         <v>0.71000000000000041</v>
       </c>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A90" s="108"/>
       <c r="B90" s="35"/>
       <c r="C90" s="35" t="s">
@@ -10530,7 +10488,7 @@
         <v>0.72000000000000042</v>
       </c>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A91" s="108"/>
       <c r="B91" s="35"/>
       <c r="C91" s="35" t="s">
@@ -10581,7 +10539,7 @@
         <v>0.73000000000000043</v>
       </c>
     </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A92" s="108"/>
       <c r="B92" s="35"/>
       <c r="C92" s="175" t="s">
@@ -10633,10 +10591,10 @@
         <v>0.74000000000000044</v>
       </c>
       <c r="Q92" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="93" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A93" s="108"/>
       <c r="B93" s="35"/>
       <c r="C93" s="35" t="s">
@@ -10688,7 +10646,7 @@
         <v>0.75000000000000044</v>
       </c>
     </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A94" s="108"/>
       <c r="B94" s="35"/>
       <c r="C94" s="35" t="s">
@@ -10740,7 +10698,7 @@
         <v>0.76000000000000045</v>
       </c>
     </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A95" s="108"/>
       <c r="B95" s="35"/>
       <c r="C95" s="35" t="s">
@@ -10792,14 +10750,14 @@
         <v>0.77000000000000046</v>
       </c>
     </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A96" s="108"/>
       <c r="B96" s="35"/>
       <c r="C96" s="35" t="s">
         <v>132</v>
       </c>
       <c r="D96" s="108" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E96" s="108"/>
       <c r="F96" s="143">
@@ -10844,7 +10802,7 @@
         <v>0.78000000000000047</v>
       </c>
     </row>
-    <row r="97" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A97" s="108"/>
       <c r="B97" s="35"/>
       <c r="C97" s="35" t="s">
@@ -10893,7 +10851,7 @@
         <v>0.79000000000000048</v>
       </c>
     </row>
-    <row r="98" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A98" s="108"/>
       <c r="B98" s="35"/>
       <c r="C98" s="35" t="s">
@@ -10945,7 +10903,7 @@
         <v>0.80000000000000049</v>
       </c>
     </row>
-    <row r="99" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A99" s="108"/>
       <c r="B99" s="35"/>
       <c r="C99" s="35" t="s">
@@ -10997,14 +10955,14 @@
         <v>0.8100000000000005</v>
       </c>
     </row>
-    <row r="100" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A100" s="108"/>
       <c r="B100" s="35"/>
       <c r="C100" s="35" t="s">
         <v>136</v>
       </c>
       <c r="D100" s="108" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E100" s="108"/>
       <c r="F100" s="89">
@@ -11049,7 +11007,7 @@
         <v>0.82000000000000051</v>
       </c>
     </row>
-    <row r="101" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A101" s="108"/>
       <c r="B101" s="35"/>
       <c r="C101" s="35" t="s">
@@ -11098,7 +11056,7 @@
         <v>0.83000000000000052</v>
       </c>
     </row>
-    <row r="102" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="108"/>
       <c r="B102" s="35"/>
       <c r="C102" s="35" t="s">
@@ -11150,7 +11108,7 @@
         <v>0.84000000000000052</v>
       </c>
     </row>
-    <row r="103" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="108"/>
       <c r="B103" s="35"/>
       <c r="C103" s="35" t="s">
@@ -11202,7 +11160,7 @@
         <v>0.85000000000000053</v>
       </c>
     </row>
-    <row r="104" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="108"/>
       <c r="B104" s="35"/>
       <c r="C104" s="35" t="s">
@@ -11254,7 +11212,7 @@
         <v>0.86000000000000054</v>
       </c>
     </row>
-    <row r="105" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="108"/>
       <c r="B105" s="35"/>
       <c r="C105" s="35" t="s">
@@ -11306,7 +11264,7 @@
         <v>0.87000000000000055</v>
       </c>
     </row>
-    <row r="106" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="108"/>
       <c r="B106" s="35"/>
       <c r="C106" s="35" t="s">
@@ -11358,7 +11316,7 @@
         <v>0.88000000000000056</v>
       </c>
     </row>
-    <row r="107" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="108"/>
       <c r="B107" s="35"/>
       <c r="C107" s="35" t="s">
@@ -11409,7 +11367,7 @@
         <v>0.89000000000000057</v>
       </c>
     </row>
-    <row r="108" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="108"/>
       <c r="B108" s="35"/>
       <c r="C108" s="35" t="s">
@@ -11461,7 +11419,7 @@
         <v>0.90000000000000058</v>
       </c>
     </row>
-    <row r="109" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="108"/>
       <c r="B109" s="35"/>
       <c r="C109" s="35" t="s">
@@ -11513,7 +11471,7 @@
         <v>0.91000000000000059</v>
       </c>
     </row>
-    <row r="110" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="108"/>
       <c r="B110" s="35"/>
       <c r="C110" s="35" t="s">
@@ -11565,7 +11523,7 @@
         <v>0.9200000000000006</v>
       </c>
     </row>
-    <row r="111" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="108"/>
       <c r="B111" s="35"/>
       <c r="C111" s="35" t="s">
@@ -11617,7 +11575,7 @@
         <v>0.9300000000000006</v>
       </c>
     </row>
-    <row r="112" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A112" s="108"/>
       <c r="B112" s="35"/>
       <c r="C112" s="35" t="s">
@@ -11668,7 +11626,7 @@
         <v>0.94000000000000061</v>
       </c>
     </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A113" s="108"/>
       <c r="B113" s="35"/>
       <c r="C113" s="35" t="s">
@@ -11720,7 +11678,7 @@
         <v>0.95000000000000062</v>
       </c>
     </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A114" s="108"/>
       <c r="B114" s="35"/>
       <c r="C114" s="35" t="s">
@@ -11772,7 +11730,7 @@
         <v>0.96000000000000063</v>
       </c>
     </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A115" s="108"/>
       <c r="B115" s="35"/>
       <c r="C115" s="35" t="s">
@@ -11824,7 +11782,7 @@
         <v>0.97000000000000064</v>
       </c>
     </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A116" s="108"/>
       <c r="B116" s="35"/>
       <c r="C116" s="35" t="s">
@@ -11834,7 +11792,7 @@
         <v>182</v>
       </c>
       <c r="E116" s="108" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F116" s="143">
         <v>2.3E-3</v>
@@ -11875,7 +11833,7 @@
         <v>0.98000000000000065</v>
       </c>
     </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A117" s="108"/>
       <c r="B117" s="35"/>
       <c r="C117" s="35" t="s">
@@ -11924,7 +11882,7 @@
         <v>0.99000000000000066</v>
       </c>
     </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A118" s="108"/>
       <c r="B118" s="35"/>
       <c r="C118" s="194" t="s">
@@ -11976,17 +11934,17 @@
         <v>1.0000000000000007</v>
       </c>
       <c r="Q118" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.25">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="119" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A119" s="127"/>
       <c r="B119" s="35"/>
       <c r="C119" s="35" t="s">
         <v>155</v>
       </c>
       <c r="D119" s="108" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E119" s="108"/>
       <c r="F119" s="143">
@@ -12031,7 +11989,7 @@
         <v>1.0100000000000007</v>
       </c>
     </row>
-    <row r="120" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A120" s="127"/>
       <c r="B120" s="35"/>
       <c r="C120" s="35" t="s">
@@ -12083,7 +12041,7 @@
         <v>1.0200000000000007</v>
       </c>
     </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A121" s="127"/>
       <c r="B121" s="35"/>
       <c r="C121" s="35" t="s">
@@ -12132,7 +12090,7 @@
         <v>1.0300000000000007</v>
       </c>
     </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A122" s="127"/>
       <c r="B122" s="35"/>
       <c r="C122" s="35" t="s">
@@ -12184,7 +12142,7 @@
         <v>1.0400000000000007</v>
       </c>
     </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A123" s="127"/>
       <c r="B123" s="35"/>
       <c r="C123" s="35" t="s">
@@ -12236,7 +12194,7 @@
         <v>1.0500000000000007</v>
       </c>
     </row>
-    <row r="124" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A124" s="127"/>
       <c r="B124" s="35"/>
       <c r="C124" s="35" t="s">
@@ -12288,10 +12246,10 @@
         <v>1.0600000000000007</v>
       </c>
       <c r="Q124" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="125" spans="1:17" x14ac:dyDescent="0.25">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="125" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A125" s="174"/>
       <c r="B125" s="169"/>
       <c r="C125" s="35" t="s">
@@ -12301,7 +12259,7 @@
         <v>182</v>
       </c>
       <c r="E125" s="135" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F125" s="143">
         <v>2.3E-3</v>
@@ -12342,7 +12300,7 @@
         <v>1.0700000000000007</v>
       </c>
     </row>
-    <row r="126" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A126" s="174"/>
       <c r="B126" s="169"/>
       <c r="C126" s="35" t="s">
@@ -12394,7 +12352,7 @@
         <v>1.0800000000000007</v>
       </c>
     </row>
-    <row r="127" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A127" s="127"/>
       <c r="B127" s="35"/>
       <c r="C127" s="35" t="s">
@@ -12446,7 +12404,7 @@
         <v>1.0900000000000007</v>
       </c>
     </row>
-    <row r="128" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A128" s="127"/>
       <c r="B128" s="35"/>
       <c r="C128" s="35" t="s">
@@ -12498,7 +12456,7 @@
         <v>1.1000000000000008</v>
       </c>
     </row>
-    <row r="129" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A129" s="127"/>
       <c r="B129" s="35"/>
       <c r="C129" s="35" t="s">
@@ -12550,7 +12508,7 @@
         <v>1.1100000000000008</v>
       </c>
     </row>
-    <row r="130" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A130" s="127" t="s">
         <v>26</v>
       </c>
@@ -12604,7 +12562,7 @@
         <v>1.1200000000000008</v>
       </c>
     </row>
-    <row r="131" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A131" s="127" t="s">
         <v>26</v>
       </c>
@@ -12613,7 +12571,7 @@
         <v>167</v>
       </c>
       <c r="D131" s="108" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E131" s="108"/>
       <c r="F131" s="89">
@@ -12658,7 +12616,7 @@
         <v>1.1300000000000008</v>
       </c>
     </row>
-    <row r="132" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A132" s="53" t="s">
         <v>26</v>
       </c>
@@ -12677,7 +12635,7 @@
       <c r="N132" s="5"/>
       <c r="O132" s="8"/>
     </row>
-    <row r="133" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="27"/>
       <c r="B133" s="27"/>
       <c r="C133" s="27"/>
@@ -12719,43 +12677,43 @@
       </c>
       <c r="Q133" s="59"/>
     </row>
-    <row r="134" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="L134" s="61">
         <f>L133-M1</f>
         <v>-4034495.9149199985</v>
       </c>
     </row>
-    <row r="135" spans="1:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C135" s="276"/>
-      <c r="D135" s="276"/>
-      <c r="E135" s="276"/>
-      <c r="F135" s="276"/>
-      <c r="G135" s="276"/>
-      <c r="H135" s="276"/>
-      <c r="I135" s="276"/>
-      <c r="J135" s="276"/>
-      <c r="K135" s="276"/>
-      <c r="L135" s="276"/>
-      <c r="M135" s="276"/>
-      <c r="N135" s="276"/>
-      <c r="O135" s="276"/>
-    </row>
-    <row r="136" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C136" s="276"/>
-      <c r="D136" s="276"/>
-      <c r="E136" s="276"/>
-      <c r="F136" s="276"/>
-      <c r="G136" s="276"/>
-      <c r="H136" s="276"/>
-      <c r="I136" s="276"/>
-      <c r="J136" s="276"/>
-      <c r="K136" s="276"/>
-      <c r="L136" s="276"/>
-      <c r="M136" s="276"/>
-      <c r="N136" s="276"/>
-      <c r="O136" s="276"/>
-    </row>
-    <row r="137" spans="1:17" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C135" s="269"/>
+      <c r="D135" s="269"/>
+      <c r="E135" s="269"/>
+      <c r="F135" s="269"/>
+      <c r="G135" s="269"/>
+      <c r="H135" s="269"/>
+      <c r="I135" s="269"/>
+      <c r="J135" s="269"/>
+      <c r="K135" s="269"/>
+      <c r="L135" s="269"/>
+      <c r="M135" s="269"/>
+      <c r="N135" s="269"/>
+      <c r="O135" s="269"/>
+    </row>
+    <row r="136" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+      <c r="C136" s="269"/>
+      <c r="D136" s="269"/>
+      <c r="E136" s="269"/>
+      <c r="F136" s="269"/>
+      <c r="G136" s="269"/>
+      <c r="H136" s="269"/>
+      <c r="I136" s="269"/>
+      <c r="J136" s="269"/>
+      <c r="K136" s="269"/>
+      <c r="L136" s="269"/>
+      <c r="M136" s="269"/>
+      <c r="N136" s="269"/>
+      <c r="O136" s="269"/>
+    </row>
+    <row r="137" spans="1:17" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C137" s="77"/>
       <c r="D137" s="77"/>
       <c r="E137" s="77"/>
@@ -12770,7 +12728,7 @@
       <c r="N137" s="77"/>
       <c r="O137" s="77"/>
     </row>
-    <row r="138" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:17" x14ac:dyDescent="0.3">
       <c r="C138" s="250" t="s">
         <v>258</v>
       </c>
@@ -12787,7 +12745,7 @@
       <c r="N138" s="250"/>
       <c r="O138" s="250"/>
     </row>
-    <row r="139" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:17" x14ac:dyDescent="0.3">
       <c r="C139" s="250"/>
       <c r="D139" s="250"/>
       <c r="E139" s="250"/>
@@ -12802,7 +12760,7 @@
       <c r="N139" s="250"/>
       <c r="O139" s="250"/>
     </row>
-    <row r="140" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:17" x14ac:dyDescent="0.3">
       <c r="C140" s="250"/>
       <c r="D140" s="250"/>
       <c r="E140" s="250"/>
@@ -12817,7 +12775,7 @@
       <c r="N140" s="250"/>
       <c r="O140" s="250"/>
     </row>
-    <row r="141" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:17" x14ac:dyDescent="0.3">
       <c r="C141" s="250"/>
       <c r="D141" s="250"/>
       <c r="E141" s="250"/>
@@ -12832,7 +12790,7 @@
       <c r="N141" s="250"/>
       <c r="O141" s="250"/>
     </row>
-    <row r="142" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:17" x14ac:dyDescent="0.3">
       <c r="C142" s="250"/>
       <c r="D142" s="250"/>
       <c r="E142" s="250"/>
@@ -12847,7 +12805,7 @@
       <c r="N142" s="250"/>
       <c r="O142" s="250"/>
     </row>
-    <row r="143" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:17" x14ac:dyDescent="0.3">
       <c r="C143" s="250"/>
       <c r="D143" s="250"/>
       <c r="E143" s="250"/>
@@ -12862,7 +12820,7 @@
       <c r="N143" s="250"/>
       <c r="O143" s="250"/>
     </row>
-    <row r="144" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:17" x14ac:dyDescent="0.3">
       <c r="C144" s="250"/>
       <c r="D144" s="250"/>
       <c r="E144" s="250"/>
@@ -12877,7 +12835,7 @@
       <c r="N144" s="250"/>
       <c r="O144" s="250"/>
     </row>
-    <row r="145" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="145" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C145" s="250"/>
       <c r="D145" s="250"/>
       <c r="E145" s="250"/>
@@ -12892,7 +12850,7 @@
       <c r="N145" s="250"/>
       <c r="O145" s="250"/>
     </row>
-    <row r="146" spans="3:17" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="3:17" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C146" s="77"/>
       <c r="D146" s="77"/>
       <c r="E146" s="77"/>
@@ -12907,7 +12865,7 @@
       <c r="N146" s="77"/>
       <c r="O146" s="77"/>
     </row>
-    <row r="147" spans="3:17" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="3:17" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C147" s="77"/>
       <c r="D147" s="77"/>
       <c r="E147" s="77"/>
@@ -12922,119 +12880,126 @@
       <c r="N147" s="77"/>
       <c r="O147" s="77"/>
     </row>
-    <row r="148" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C148" s="275" t="s">
+    <row r="148" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="C148" s="268" t="s">
         <v>257</v>
       </c>
-      <c r="D148" s="275"/>
-      <c r="E148" s="275"/>
-      <c r="F148" s="275"/>
-      <c r="G148" s="275"/>
-      <c r="H148" s="275"/>
-      <c r="I148" s="275"/>
-      <c r="J148" s="275"/>
-      <c r="K148" s="275"/>
-      <c r="L148" s="275"/>
-      <c r="M148" s="275"/>
-      <c r="N148" s="275"/>
-      <c r="O148" s="275"/>
-    </row>
-    <row r="149" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C149" s="275"/>
-      <c r="D149" s="275"/>
-      <c r="E149" s="275"/>
-      <c r="F149" s="275"/>
-      <c r="G149" s="275"/>
-      <c r="H149" s="275"/>
-      <c r="I149" s="275"/>
-      <c r="J149" s="275"/>
-      <c r="K149" s="275"/>
-      <c r="L149" s="275"/>
-      <c r="M149" s="275"/>
-      <c r="N149" s="275"/>
-      <c r="O149" s="275"/>
-    </row>
-    <row r="150" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C150" s="275"/>
-      <c r="D150" s="275"/>
-      <c r="E150" s="275"/>
-      <c r="F150" s="275"/>
-      <c r="G150" s="275"/>
-      <c r="H150" s="275"/>
-      <c r="I150" s="275"/>
-      <c r="J150" s="275"/>
-      <c r="K150" s="275"/>
-      <c r="L150" s="275"/>
-      <c r="M150" s="275"/>
-      <c r="N150" s="275"/>
-      <c r="O150" s="275"/>
+      <c r="D148" s="268"/>
+      <c r="E148" s="268"/>
+      <c r="F148" s="268"/>
+      <c r="G148" s="268"/>
+      <c r="H148" s="268"/>
+      <c r="I148" s="268"/>
+      <c r="J148" s="268"/>
+      <c r="K148" s="268"/>
+      <c r="L148" s="268"/>
+      <c r="M148" s="268"/>
+      <c r="N148" s="268"/>
+      <c r="O148" s="268"/>
+    </row>
+    <row r="149" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="C149" s="268"/>
+      <c r="D149" s="268"/>
+      <c r="E149" s="268"/>
+      <c r="F149" s="268"/>
+      <c r="G149" s="268"/>
+      <c r="H149" s="268"/>
+      <c r="I149" s="268"/>
+      <c r="J149" s="268"/>
+      <c r="K149" s="268"/>
+      <c r="L149" s="268"/>
+      <c r="M149" s="268"/>
+      <c r="N149" s="268"/>
+      <c r="O149" s="268"/>
+    </row>
+    <row r="150" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="C150" s="268"/>
+      <c r="D150" s="268"/>
+      <c r="E150" s="268"/>
+      <c r="F150" s="268"/>
+      <c r="G150" s="268"/>
+      <c r="H150" s="268"/>
+      <c r="I150" s="268"/>
+      <c r="J150" s="268"/>
+      <c r="K150" s="268"/>
+      <c r="L150" s="268"/>
+      <c r="M150" s="268"/>
+      <c r="N150" s="268"/>
+      <c r="O150" s="268"/>
       <c r="Q150" s="84">
         <f>M1-L133</f>
         <v>4034495.9149199985</v>
       </c>
     </row>
-    <row r="151" spans="3:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C151" s="275"/>
-      <c r="D151" s="275"/>
-      <c r="E151" s="275"/>
-      <c r="F151" s="275"/>
-      <c r="G151" s="275"/>
-      <c r="H151" s="275"/>
-      <c r="I151" s="275"/>
-      <c r="J151" s="275"/>
-      <c r="K151" s="275"/>
-      <c r="L151" s="275"/>
-      <c r="M151" s="275"/>
-      <c r="N151" s="275"/>
-      <c r="O151" s="275"/>
-    </row>
-    <row r="152" spans="3:17" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C152" s="275"/>
-      <c r="D152" s="275"/>
-      <c r="E152" s="275"/>
-      <c r="F152" s="275"/>
-      <c r="G152" s="275"/>
-      <c r="H152" s="275"/>
-      <c r="I152" s="275"/>
-      <c r="J152" s="275"/>
-      <c r="K152" s="275"/>
-      <c r="L152" s="275"/>
-      <c r="M152" s="275"/>
-      <c r="N152" s="275"/>
-      <c r="O152" s="275"/>
-    </row>
-    <row r="153" spans="3:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C153" s="275"/>
-      <c r="D153" s="275"/>
-      <c r="E153" s="275"/>
-      <c r="F153" s="275"/>
-      <c r="G153" s="275"/>
-      <c r="H153" s="275"/>
-      <c r="I153" s="275"/>
-      <c r="J153" s="275"/>
-      <c r="K153" s="275"/>
-      <c r="L153" s="275"/>
-      <c r="M153" s="275"/>
-      <c r="N153" s="275"/>
-      <c r="O153" s="275"/>
-    </row>
-    <row r="154" spans="3:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C154" s="275"/>
-      <c r="D154" s="275"/>
-      <c r="E154" s="275"/>
-      <c r="F154" s="275"/>
-      <c r="G154" s="275"/>
-      <c r="H154" s="275"/>
-      <c r="I154" s="275"/>
-      <c r="J154" s="275"/>
-      <c r="K154" s="275"/>
-      <c r="L154" s="275"/>
-      <c r="M154" s="275"/>
-      <c r="N154" s="275"/>
-      <c r="O154" s="275"/>
+    <row r="151" spans="3:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C151" s="268"/>
+      <c r="D151" s="268"/>
+      <c r="E151" s="268"/>
+      <c r="F151" s="268"/>
+      <c r="G151" s="268"/>
+      <c r="H151" s="268"/>
+      <c r="I151" s="268"/>
+      <c r="J151" s="268"/>
+      <c r="K151" s="268"/>
+      <c r="L151" s="268"/>
+      <c r="M151" s="268"/>
+      <c r="N151" s="268"/>
+      <c r="O151" s="268"/>
+    </row>
+    <row r="152" spans="3:17" ht="5.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C152" s="268"/>
+      <c r="D152" s="268"/>
+      <c r="E152" s="268"/>
+      <c r="F152" s="268"/>
+      <c r="G152" s="268"/>
+      <c r="H152" s="268"/>
+      <c r="I152" s="268"/>
+      <c r="J152" s="268"/>
+      <c r="K152" s="268"/>
+      <c r="L152" s="268"/>
+      <c r="M152" s="268"/>
+      <c r="N152" s="268"/>
+      <c r="O152" s="268"/>
+    </row>
+    <row r="153" spans="3:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C153" s="268"/>
+      <c r="D153" s="268"/>
+      <c r="E153" s="268"/>
+      <c r="F153" s="268"/>
+      <c r="G153" s="268"/>
+      <c r="H153" s="268"/>
+      <c r="I153" s="268"/>
+      <c r="J153" s="268"/>
+      <c r="K153" s="268"/>
+      <c r="L153" s="268"/>
+      <c r="M153" s="268"/>
+      <c r="N153" s="268"/>
+      <c r="O153" s="268"/>
+    </row>
+    <row r="154" spans="3:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C154" s="268"/>
+      <c r="D154" s="268"/>
+      <c r="E154" s="268"/>
+      <c r="F154" s="268"/>
+      <c r="G154" s="268"/>
+      <c r="H154" s="268"/>
+      <c r="I154" s="268"/>
+      <c r="J154" s="268"/>
+      <c r="K154" s="268"/>
+      <c r="L154" s="268"/>
+      <c r="M154" s="268"/>
+      <c r="N154" s="268"/>
+      <c r="O154" s="268"/>
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="K11:K13"/>
+    <mergeCell ref="A11:A13"/>
+    <mergeCell ref="B11:B13"/>
+    <mergeCell ref="C11:C13"/>
+    <mergeCell ref="D11:D13"/>
+    <mergeCell ref="F11:F13"/>
+    <mergeCell ref="E11:E13"/>
     <mergeCell ref="R14:S15"/>
     <mergeCell ref="G11:G13"/>
     <mergeCell ref="C148:O154"/>
@@ -13051,13 +13016,6 @@
     <mergeCell ref="C5:O8"/>
     <mergeCell ref="C9:O10"/>
     <mergeCell ref="A1:E4"/>
-    <mergeCell ref="K11:K13"/>
-    <mergeCell ref="A11:A13"/>
-    <mergeCell ref="B11:B13"/>
-    <mergeCell ref="C11:C13"/>
-    <mergeCell ref="D11:D13"/>
-    <mergeCell ref="F11:F13"/>
-    <mergeCell ref="E11:E13"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -13068,29 +13026,29 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7AB47CA-548A-40FB-AC1D-01E96423736C}">
   <dimension ref="A1:DH83"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.140625" customWidth="1"/>
-    <col min="2" max="2" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="47.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.28515625" customWidth="1"/>
-    <col min="5" max="5" width="14.140625" customWidth="1"/>
-    <col min="6" max="6" width="13.28515625" customWidth="1"/>
-    <col min="7" max="7" width="21.42578125" hidden="1" customWidth="1"/>
-    <col min="8" max="9" width="17.28515625" customWidth="1"/>
+    <col min="1" max="1" width="7.109375" customWidth="1"/>
+    <col min="2" max="2" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="47.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.33203125" customWidth="1"/>
+    <col min="5" max="5" width="14.109375" customWidth="1"/>
+    <col min="6" max="6" width="13.33203125" customWidth="1"/>
+    <col min="7" max="7" width="21.44140625" hidden="1" customWidth="1"/>
+    <col min="8" max="9" width="17.33203125" customWidth="1"/>
     <col min="10" max="10" width="15" customWidth="1"/>
-    <col min="11" max="11" width="15.140625" hidden="1" customWidth="1"/>
-    <col min="12" max="12" width="15.140625" customWidth="1"/>
-    <col min="13" max="13" width="19.5703125" customWidth="1"/>
-    <col min="14" max="14" width="5.5703125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="43.28515625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.109375" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="15.109375" customWidth="1"/>
+    <col min="13" max="13" width="19.5546875" customWidth="1"/>
+    <col min="14" max="14" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="43.33203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="17.88671875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:25" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="310" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B1" s="310"/>
       <c r="C1" s="310"/>
@@ -13106,7 +13064,7 @@
       <c r="M1" s="311"/>
       <c r="P1" s="43"/>
     </row>
-    <row r="2" spans="1:25" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:25" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="312"/>
       <c r="B2" s="312"/>
       <c r="C2" s="312"/>
@@ -13122,9 +13080,9 @@
       <c r="M2" s="313"/>
       <c r="P2" s="43"/>
     </row>
-    <row r="3" spans="1:25" ht="109.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:25" ht="109.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="304" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B3" s="305"/>
       <c r="C3" s="305"/>
@@ -13140,9 +13098,9 @@
       <c r="M3" s="306"/>
       <c r="P3" s="43"/>
     </row>
-    <row r="4" spans="1:25" s="248" customFormat="1" ht="94.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:25" s="248" customFormat="1" ht="94.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="307" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="B4" s="308"/>
       <c r="C4" s="308"/>
@@ -13169,63 +13127,63 @@
       <c r="X4" s="249"/>
       <c r="Y4" s="249"/>
     </row>
-    <row r="5" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="268" t="s">
+    <row r="5" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="266" t="s">
+        <v>329</v>
+      </c>
+      <c r="B5" s="266" t="s">
         <v>330</v>
       </c>
-      <c r="B5" s="268" t="s">
-        <v>331</v>
-      </c>
-      <c r="C5" s="268" t="s">
+      <c r="C5" s="266" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="268" t="s">
+      <c r="D5" s="266" t="s">
         <v>27</v>
       </c>
-      <c r="E5" s="265" t="s">
+      <c r="E5" s="274" t="s">
+        <v>356</v>
+      </c>
+      <c r="F5" s="274" t="s">
+        <v>357</v>
+      </c>
+      <c r="G5" s="274" t="s">
+        <v>276</v>
+      </c>
+      <c r="H5" s="274" t="s">
+        <v>389</v>
+      </c>
+      <c r="I5" s="274" t="s">
+        <v>390</v>
+      </c>
+      <c r="J5" s="314" t="s">
         <v>358</v>
       </c>
-      <c r="F5" s="265" t="s">
+      <c r="K5" s="131"/>
+      <c r="L5" s="274" t="s">
         <v>359</v>
       </c>
-      <c r="G5" s="265" t="s">
-        <v>277</v>
-      </c>
-      <c r="H5" s="265" t="s">
-        <v>391</v>
-      </c>
-      <c r="I5" s="265" t="s">
-        <v>392</v>
-      </c>
-      <c r="J5" s="314" t="s">
-        <v>360</v>
-      </c>
-      <c r="K5" s="131"/>
-      <c r="L5" s="265" t="s">
-        <v>361</v>
-      </c>
-      <c r="M5" s="265" t="s">
+      <c r="M5" s="274" t="s">
         <v>17</v>
       </c>
       <c r="P5" s="43"/>
     </row>
-    <row r="6" spans="1:25" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="269"/>
-      <c r="B6" s="269"/>
-      <c r="C6" s="269"/>
-      <c r="D6" s="269"/>
-      <c r="E6" s="266"/>
-      <c r="F6" s="266"/>
-      <c r="G6" s="266"/>
-      <c r="H6" s="266"/>
-      <c r="I6" s="266"/>
+    <row r="6" spans="1:25" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="267"/>
+      <c r="B6" s="267"/>
+      <c r="C6" s="267"/>
+      <c r="D6" s="267"/>
+      <c r="E6" s="275"/>
+      <c r="F6" s="275"/>
+      <c r="G6" s="275"/>
+      <c r="H6" s="275"/>
+      <c r="I6" s="275"/>
       <c r="J6" s="315"/>
       <c r="K6" s="131"/>
-      <c r="L6" s="266"/>
-      <c r="M6" s="266"/>
+      <c r="L6" s="275"/>
+      <c r="M6" s="275"/>
       <c r="P6" s="43"/>
     </row>
-    <row r="7" spans="1:25" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:25" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="318"/>
       <c r="B7" s="318"/>
       <c r="C7" s="318"/>
@@ -13241,7 +13199,7 @@
       <c r="M7" s="317"/>
       <c r="P7" s="43"/>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A8" s="210" t="s">
         <v>113</v>
       </c>
@@ -13287,16 +13245,16 @@
       <c r="N8" s="115">
         <v>0.7</v>
       </c>
-      <c r="P8" s="274"/>
-      <c r="Q8" s="274"/>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="P8" s="265"/>
+      <c r="Q8" s="265"/>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A9" s="210" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B9" s="211"/>
       <c r="C9" s="35" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D9" s="143">
         <v>1.2800000000000001E-2</v>
@@ -13337,16 +13295,16 @@
         <f>N8+0.01</f>
         <v>0.71</v>
       </c>
-      <c r="P9" s="274"/>
-      <c r="Q9" s="274"/>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="P9" s="265"/>
+      <c r="Q9" s="265"/>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A10" s="210" t="s">
         <v>114</v>
       </c>
       <c r="B10" s="211"/>
       <c r="C10" s="213" t="s">
-        <v>339</v>
+        <v>394</v>
       </c>
       <c r="D10" s="143">
         <v>1.21E-2</v>
@@ -13389,7 +13347,7 @@
       </c>
       <c r="Q10" s="43"/>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A11" s="210" t="s">
         <v>115</v>
       </c>
@@ -13438,13 +13396,13 @@
       </c>
       <c r="Q11" s="43"/>
     </row>
-    <row r="12" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="214" t="s">
         <v>116</v>
       </c>
       <c r="B12" s="215"/>
       <c r="C12" s="216" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D12" s="150">
         <v>1.7500000000000002E-2</v>
@@ -13487,7 +13445,7 @@
       </c>
       <c r="Q12" s="43"/>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A13" s="217" t="s">
         <v>44</v>
       </c>
@@ -13537,7 +13495,7 @@
       </c>
       <c r="Q13" s="43"/>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A14" s="210" t="s">
         <v>45</v>
       </c>
@@ -13586,7 +13544,7 @@
       </c>
       <c r="Q14" s="43"/>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A15" s="210" t="s">
         <v>46</v>
       </c>
@@ -13636,12 +13594,12 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A16" s="210" t="s">
         <v>47</v>
       </c>
       <c r="B16" s="211" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C16" s="108" t="s">
         <v>180</v>
@@ -13686,7 +13644,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" s="210" t="s">
         <v>48</v>
       </c>
@@ -13734,12 +13692,12 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" s="210" t="s">
         <v>49</v>
       </c>
       <c r="B18" s="211" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C18" s="108" t="s">
         <v>182</v>
@@ -13784,15 +13742,15 @@
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19" s="210" t="s">
         <v>50</v>
       </c>
       <c r="B19" s="211" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C19" s="108" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="D19" s="136">
         <v>2.1100000000000001E-2</v>
@@ -13834,13 +13792,13 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" s="210" t="s">
         <v>51</v>
       </c>
       <c r="B20" s="211"/>
       <c r="C20" s="108" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="D20" s="136">
         <v>7.4000000000000003E-3</v>
@@ -13882,7 +13840,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" s="210" t="s">
         <v>52</v>
       </c>
@@ -13930,7 +13888,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" s="210" t="s">
         <v>53</v>
       </c>
@@ -13978,13 +13936,13 @@
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" s="210" t="s">
         <v>54</v>
       </c>
       <c r="B23" s="211"/>
       <c r="C23" s="108" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="D23" s="136">
         <v>8.6999999999999994E-3</v>
@@ -14026,7 +13984,7 @@
         <v>0.10999999999999999</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24" s="210" t="s">
         <v>55</v>
       </c>
@@ -14074,7 +14032,7 @@
         <v>0.11999999999999998</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25" s="210" t="s">
         <v>56</v>
       </c>
@@ -14122,13 +14080,13 @@
         <v>0.12999999999999998</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" s="210" t="s">
         <v>57</v>
       </c>
       <c r="B26" s="211"/>
       <c r="C26" s="108" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="D26" s="136">
         <v>7.3000000000000001E-3</v>
@@ -14170,12 +14128,12 @@
         <v>0.13999999999999999</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27" s="210" t="s">
         <v>58</v>
       </c>
       <c r="B27" s="219" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C27" s="108" t="s">
         <v>185</v>
@@ -14220,7 +14178,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A28" s="210" t="s">
         <v>59</v>
       </c>
@@ -14268,16 +14226,16 @@
         <v>0.16</v>
       </c>
       <c r="O28" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A29" s="210" t="s">
         <v>60</v>
       </c>
       <c r="B29" s="211"/>
       <c r="C29" s="108" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="D29" s="136">
         <v>8.6999999999999994E-3</v>
@@ -14319,7 +14277,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A30" s="210" t="s">
         <v>61</v>
       </c>
@@ -14367,7 +14325,7 @@
         <v>0.18000000000000002</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A31" s="210" t="s">
         <v>62</v>
       </c>
@@ -14415,10 +14373,10 @@
         <v>0.19000000000000003</v>
       </c>
       <c r="O31" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A32" s="210" t="s">
         <v>63</v>
       </c>
@@ -14468,7 +14426,7 @@
         <v>0.20000000000000004</v>
       </c>
     </row>
-    <row r="33" spans="1:112" s="140" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:112" s="140" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A33" s="210" t="s">
         <v>64</v>
       </c>
@@ -14616,7 +14574,7 @@
       <c r="DG33" s="73"/>
       <c r="DH33" s="73"/>
     </row>
-    <row r="34" spans="1:112" s="140" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:112" s="140" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A34" s="210" t="s">
         <v>65</v>
       </c>
@@ -14664,7 +14622,7 @@
         <v>0.22000000000000006</v>
       </c>
       <c r="O34" s="73" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="P34" s="73"/>
       <c r="Q34" s="73"/>
@@ -14764,7 +14722,7 @@
       <c r="DG34" s="73"/>
       <c r="DH34" s="73"/>
     </row>
-    <row r="35" spans="1:112" s="140" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:112" s="140" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A35" s="210" t="s">
         <v>66</v>
       </c>
@@ -14772,7 +14730,7 @@
         <v>31</v>
       </c>
       <c r="C35" s="108" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D35" s="136">
         <v>1.0999999999999999E-2</v>
@@ -14814,7 +14772,7 @@
         <v>0.23000000000000007</v>
       </c>
       <c r="O35" s="73" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="P35" s="73"/>
       <c r="Q35" s="73"/>
@@ -14914,7 +14872,7 @@
       <c r="DG35" s="73"/>
       <c r="DH35" s="73"/>
     </row>
-    <row r="36" spans="1:112" s="140" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:112" s="140" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A36" s="210" t="s">
         <v>67</v>
       </c>
@@ -15060,7 +15018,7 @@
       <c r="DG36" s="73"/>
       <c r="DH36" s="73"/>
     </row>
-    <row r="37" spans="1:112" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A37" s="210" t="s">
         <v>68</v>
       </c>
@@ -15110,13 +15068,13 @@
         <v>0.25000000000000006</v>
       </c>
     </row>
-    <row r="38" spans="1:112" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A38" s="210" t="s">
         <v>69</v>
       </c>
       <c r="B38" s="211"/>
       <c r="C38" s="108" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="D38" s="136">
         <v>7.3000000000000001E-3</v>
@@ -15158,7 +15116,7 @@
         <v>0.26000000000000006</v>
       </c>
     </row>
-    <row r="39" spans="1:112" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A39" s="210" t="s">
         <v>70</v>
       </c>
@@ -15214,7 +15172,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="40" spans="1:112" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A40" s="210" t="s">
         <v>71</v>
       </c>
@@ -15222,7 +15180,7 @@
         <v>44</v>
       </c>
       <c r="C40" s="108" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="D40" s="136">
         <v>1.17E-2</v>
@@ -15264,7 +15222,7 @@
         <v>0.28000000000000008</v>
       </c>
     </row>
-    <row r="41" spans="1:112" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A41" s="210" t="s">
         <v>72</v>
       </c>
@@ -15312,13 +15270,13 @@
         <v>0.29000000000000009</v>
       </c>
     </row>
-    <row r="42" spans="1:112" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A42" s="210" t="s">
         <v>73</v>
       </c>
       <c r="B42" s="211"/>
       <c r="C42" s="108" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="D42" s="136">
         <v>9.4999999999999998E-3</v>
@@ -15360,7 +15318,7 @@
         <v>0.3000000000000001</v>
       </c>
     </row>
-    <row r="43" spans="1:112" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A43" s="210" t="s">
         <v>74</v>
       </c>
@@ -15410,7 +15368,7 @@
         <v>0.31000000000000011</v>
       </c>
     </row>
-    <row r="44" spans="1:112" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A44" s="210" t="s">
         <v>75</v>
       </c>
@@ -15461,7 +15419,7 @@
       </c>
       <c r="O44" s="43"/>
     </row>
-    <row r="45" spans="1:112" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A45" s="210" t="s">
         <v>76</v>
       </c>
@@ -15512,13 +15470,13 @@
       </c>
       <c r="O45" s="43"/>
     </row>
-    <row r="46" spans="1:112" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A46" s="210" t="s">
         <v>77</v>
       </c>
       <c r="B46" s="211"/>
       <c r="C46" s="108" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="D46" s="136">
         <v>9.4000000000000004E-3</v>
@@ -15560,16 +15518,16 @@
         <v>0.34000000000000014</v>
       </c>
       <c r="O46" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="47" spans="1:112" x14ac:dyDescent="0.25">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="47" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A47" s="210" t="s">
         <v>78</v>
       </c>
       <c r="B47" s="211"/>
       <c r="C47" s="108" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="D47" s="136">
         <v>8.6999999999999994E-3</v>
@@ -15611,7 +15569,7 @@
         <v>0.35000000000000014</v>
       </c>
     </row>
-    <row r="48" spans="1:112" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A48" s="210" t="s">
         <v>79</v>
       </c>
@@ -15659,7 +15617,7 @@
         <v>0.36000000000000015</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A49" s="210" t="s">
         <v>80</v>
       </c>
@@ -15710,7 +15668,7 @@
       </c>
       <c r="P49" s="59"/>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A50" s="210" t="s">
         <v>81</v>
       </c>
@@ -15758,7 +15716,7 @@
         <v>0.38000000000000017</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A51" s="210" t="s">
         <v>82</v>
       </c>
@@ -15808,7 +15766,7 @@
         <v>0.39000000000000018</v>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A52" s="210" t="s">
         <v>83</v>
       </c>
@@ -15856,13 +15814,13 @@
         <v>0.40000000000000019</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A53" s="210" t="s">
         <v>84</v>
       </c>
       <c r="B53" s="211"/>
       <c r="C53" s="108" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="D53" s="136">
         <v>8.6999999999999994E-3</v>
@@ -15907,7 +15865,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A54" s="210" t="s">
         <v>85</v>
       </c>
@@ -15957,10 +15915,10 @@
         <v>0.42000000000000021</v>
       </c>
       <c r="O54" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A55" s="210" t="s">
         <v>86</v>
       </c>
@@ -16010,7 +15968,7 @@
         <v>0.43000000000000022</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A56" s="210" t="s">
         <v>87</v>
       </c>
@@ -16058,7 +16016,7 @@
         <v>0.44000000000000022</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A57" s="210" t="s">
         <v>88</v>
       </c>
@@ -16108,7 +16066,7 @@
         <v>0.45000000000000023</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A58" s="210" t="s">
         <v>89</v>
       </c>
@@ -16158,7 +16116,7 @@
         <v>0.46000000000000024</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A59" s="210" t="s">
         <v>90</v>
       </c>
@@ -16208,7 +16166,7 @@
         <v>0.47000000000000025</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A60" s="210" t="s">
         <v>91</v>
       </c>
@@ -16259,7 +16217,7 @@
       </c>
       <c r="Q60" s="181"/>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A61" s="210" t="s">
         <v>92</v>
       </c>
@@ -16267,7 +16225,7 @@
         <v>4</v>
       </c>
       <c r="C61" s="108" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="D61" s="136">
         <v>1.8700000000000001E-2</v>
@@ -16310,7 +16268,7 @@
       </c>
       <c r="Q61" s="43"/>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A62" s="210" t="s">
         <v>93</v>
       </c>
@@ -16358,7 +16316,7 @@
         <v>0.50000000000000022</v>
       </c>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A63" s="210" t="s">
         <v>94</v>
       </c>
@@ -16408,7 +16366,7 @@
         <v>0.51000000000000023</v>
       </c>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A64" s="210" t="s">
         <v>95</v>
       </c>
@@ -16456,13 +16414,13 @@
         <v>0.52000000000000024</v>
       </c>
     </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A65" s="210" t="s">
         <v>96</v>
       </c>
       <c r="B65" s="211"/>
       <c r="C65" s="108" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="D65" s="136">
         <v>8.6999999999999994E-3</v>
@@ -16507,7 +16465,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="66" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A66" s="210" t="s">
         <v>97</v>
       </c>
@@ -16557,7 +16515,7 @@
         <v>0.54000000000000026</v>
       </c>
     </row>
-    <row r="67" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A67" s="210" t="s">
         <v>98</v>
       </c>
@@ -16608,7 +16566,7 @@
       </c>
       <c r="O67" s="73"/>
     </row>
-    <row r="68" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A68" s="210" t="s">
         <v>99</v>
       </c>
@@ -16616,7 +16574,7 @@
         <v>41</v>
       </c>
       <c r="C68" s="108" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="D68" s="136">
         <v>1.9699999999999999E-2</v>
@@ -16658,7 +16616,7 @@
         <v>0.56000000000000028</v>
       </c>
     </row>
-    <row r="69" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A69" s="210" t="s">
         <v>100</v>
       </c>
@@ -16666,7 +16624,7 @@
         <v>2</v>
       </c>
       <c r="C69" s="108" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="D69" s="136">
         <v>1.17E-2</v>
@@ -16697,7 +16655,7 @@
         <v>0.57000000000000028</v>
       </c>
     </row>
-    <row r="70" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A70" s="210" t="s">
         <v>101</v>
       </c>
@@ -16745,7 +16703,7 @@
         <v>0.58000000000000029</v>
       </c>
     </row>
-    <row r="71" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A71" s="210" t="s">
         <v>102</v>
       </c>
@@ -16795,7 +16753,7 @@
         <v>0.5900000000000003</v>
       </c>
     </row>
-    <row r="72" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A72" s="210" t="s">
         <v>103</v>
       </c>
@@ -16845,7 +16803,7 @@
         <v>0.60000000000000031</v>
       </c>
     </row>
-    <row r="73" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A73" s="210" t="s">
         <v>104</v>
       </c>
@@ -16895,7 +16853,7 @@
         <v>0.61000000000000032</v>
       </c>
     </row>
-    <row r="74" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A74" s="210" t="s">
         <v>105</v>
       </c>
@@ -16943,7 +16901,7 @@
         <v>0.62000000000000033</v>
       </c>
     </row>
-    <row r="75" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A75" s="210" t="s">
         <v>106</v>
       </c>
@@ -16993,7 +16951,7 @@
         <v>0.63000000000000034</v>
       </c>
     </row>
-    <row r="76" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A76" s="210" t="s">
         <v>107</v>
       </c>
@@ -17041,7 +16999,7 @@
         <v>0.64000000000000035</v>
       </c>
     </row>
-    <row r="77" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A77" s="210" t="s">
         <v>108</v>
       </c>
@@ -17049,7 +17007,7 @@
         <v>9</v>
       </c>
       <c r="C77" s="108" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="D77" s="136">
         <v>2.58E-2</v>
@@ -17091,7 +17049,7 @@
         <v>0.65000000000000036</v>
       </c>
     </row>
-    <row r="78" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A78" s="210" t="s">
         <v>109</v>
       </c>
@@ -17141,12 +17099,12 @@
         <v>0.66000000000000036</v>
       </c>
     </row>
-    <row r="79" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A79" s="210" t="s">
         <v>110</v>
       </c>
       <c r="B79" s="211" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C79" s="108" t="s">
         <v>219</v>
@@ -17191,7 +17149,7 @@
         <v>0.67000000000000037</v>
       </c>
     </row>
-    <row r="80" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A80" s="210" t="s">
         <v>111</v>
       </c>
@@ -17241,7 +17199,7 @@
         <v>0.68000000000000038</v>
       </c>
     </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A81" s="210" t="s">
         <v>112</v>
       </c>
@@ -17291,7 +17249,7 @@
         <v>0.69000000000000039</v>
       </c>
     </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A82" s="35"/>
       <c r="B82" s="35"/>
       <c r="C82" s="108"/>
@@ -17306,7 +17264,7 @@
       <c r="L82" s="146"/>
       <c r="M82" s="147"/>
     </row>
-    <row r="83" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A83" s="27"/>
       <c r="B83" s="27"/>
       <c r="C83" s="27"/>
@@ -17364,9 +17322,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7365EFC1-5C09-4380-B9A2-A73102AE2F7A}">
   <dimension ref="A13"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="13" ht="15.6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/2026/EL MIRADOR/Febrero/Febrero - EL MIRADOR.xlsx
+++ b/2026/EL MIRADOR/Febrero/Febrero - EL MIRADOR.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\EL MIRADOR\Febrero\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BFCF337-AB2E-4AE9-9DC3-D8B15E19466C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C4C344F-B8C4-447B-9744-E5AE893BABEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="690" uniqueCount="395">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="691" uniqueCount="396">
   <si>
     <t>LIQUIDACION DE EXPENSAS</t>
   </si>
@@ -1222,6 +1222,9 @@
   </si>
   <si>
     <t xml:space="preserve">Patricia Mainieri </t>
+  </si>
+  <si>
+    <t>El 12A deposito 16/03 $35.500 y 361.000</t>
   </si>
 </sst>
 </file>
@@ -1889,7 +1892,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="319">
+  <cellXfs count="322">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2255,14 +2258,35 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -2281,15 +2305,6 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2360,18 +2375,6 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="1" fontId="26" fillId="15" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2417,6 +2420,9 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Millares" xfId="3" builtinId="3"/>
@@ -5608,13 +5614,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A1" s="294" t="s">
+      <c r="A1" s="298" t="s">
         <v>326</v>
       </c>
-      <c r="B1" s="295"/>
-      <c r="C1" s="295"/>
-      <c r="D1" s="295"/>
-      <c r="E1" s="295"/>
+      <c r="B1" s="299"/>
+      <c r="C1" s="299"/>
+      <c r="D1" s="299"/>
+      <c r="E1" s="299"/>
       <c r="F1" s="158" t="s">
         <v>292</v>
       </c>
@@ -5626,20 +5632,20 @@
       <c r="L1" s="190" t="s">
         <v>41</v>
       </c>
-      <c r="M1" s="270">
+      <c r="M1" s="277">
         <f>RESUMEN!D98-RESUMEN!D96</f>
         <v>14242326.569999998</v>
       </c>
-      <c r="N1" s="271"/>
+      <c r="N1" s="278"/>
       <c r="O1" s="159"/>
       <c r="P1" s="59"/>
     </row>
     <row r="2" spans="1:19" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="296"/>
-      <c r="B2" s="297"/>
-      <c r="C2" s="297"/>
-      <c r="D2" s="297"/>
-      <c r="E2" s="297"/>
+      <c r="A2" s="300"/>
+      <c r="B2" s="301"/>
+      <c r="C2" s="301"/>
+      <c r="D2" s="301"/>
+      <c r="E2" s="301"/>
       <c r="F2" s="7" t="s">
         <v>291</v>
       </c>
@@ -5659,11 +5665,11 @@
       <c r="P2" s="59"/>
     </row>
     <row r="3" spans="1:19" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="296"/>
-      <c r="B3" s="297"/>
-      <c r="C3" s="297"/>
-      <c r="D3" s="297"/>
-      <c r="E3" s="297"/>
+      <c r="A3" s="300"/>
+      <c r="B3" s="301"/>
+      <c r="C3" s="301"/>
+      <c r="D3" s="301"/>
+      <c r="E3" s="301"/>
       <c r="F3" s="7" t="s">
         <v>293</v>
       </c>
@@ -5684,11 +5690,11 @@
       <c r="P3" s="15"/>
     </row>
     <row r="4" spans="1:19" ht="2.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="298"/>
-      <c r="B4" s="299"/>
-      <c r="C4" s="299"/>
-      <c r="D4" s="299"/>
-      <c r="E4" s="299"/>
+      <c r="A4" s="302"/>
+      <c r="B4" s="303"/>
+      <c r="C4" s="303"/>
+      <c r="D4" s="303"/>
+      <c r="E4" s="303"/>
       <c r="F4" s="163"/>
       <c r="G4" s="163"/>
       <c r="H4" s="163"/>
@@ -5704,95 +5710,95 @@
     <row r="5" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A5" s="7"/>
       <c r="B5" s="7"/>
-      <c r="C5" s="279" t="s">
+      <c r="C5" s="283" t="s">
         <v>309</v>
       </c>
-      <c r="D5" s="280"/>
-      <c r="E5" s="280"/>
-      <c r="F5" s="280"/>
-      <c r="G5" s="280"/>
-      <c r="H5" s="280"/>
-      <c r="I5" s="280"/>
-      <c r="J5" s="280"/>
-      <c r="K5" s="280"/>
-      <c r="L5" s="280"/>
-      <c r="M5" s="280"/>
-      <c r="N5" s="280"/>
-      <c r="O5" s="281"/>
+      <c r="D5" s="284"/>
+      <c r="E5" s="284"/>
+      <c r="F5" s="284"/>
+      <c r="G5" s="284"/>
+      <c r="H5" s="284"/>
+      <c r="I5" s="284"/>
+      <c r="J5" s="284"/>
+      <c r="K5" s="284"/>
+      <c r="L5" s="284"/>
+      <c r="M5" s="284"/>
+      <c r="N5" s="284"/>
+      <c r="O5" s="285"/>
       <c r="P5" s="15"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A6" s="7"/>
       <c r="B6" s="7"/>
-      <c r="C6" s="282"/>
-      <c r="D6" s="283"/>
-      <c r="E6" s="283"/>
-      <c r="F6" s="283"/>
-      <c r="G6" s="283"/>
-      <c r="H6" s="283"/>
-      <c r="I6" s="283"/>
-      <c r="J6" s="283"/>
-      <c r="K6" s="283"/>
-      <c r="L6" s="283"/>
-      <c r="M6" s="283"/>
-      <c r="N6" s="283"/>
-      <c r="O6" s="284"/>
+      <c r="C6" s="286"/>
+      <c r="D6" s="287"/>
+      <c r="E6" s="287"/>
+      <c r="F6" s="287"/>
+      <c r="G6" s="287"/>
+      <c r="H6" s="287"/>
+      <c r="I6" s="287"/>
+      <c r="J6" s="287"/>
+      <c r="K6" s="287"/>
+      <c r="L6" s="287"/>
+      <c r="M6" s="287"/>
+      <c r="N6" s="287"/>
+      <c r="O6" s="288"/>
       <c r="P6" s="15"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A7" s="7"/>
       <c r="B7" s="7"/>
-      <c r="C7" s="282"/>
-      <c r="D7" s="283"/>
-      <c r="E7" s="283"/>
-      <c r="F7" s="283"/>
-      <c r="G7" s="283"/>
-      <c r="H7" s="283"/>
-      <c r="I7" s="283"/>
-      <c r="J7" s="283"/>
-      <c r="K7" s="283"/>
-      <c r="L7" s="283"/>
-      <c r="M7" s="283"/>
-      <c r="N7" s="283"/>
-      <c r="O7" s="284"/>
+      <c r="C7" s="286"/>
+      <c r="D7" s="287"/>
+      <c r="E7" s="287"/>
+      <c r="F7" s="287"/>
+      <c r="G7" s="287"/>
+      <c r="H7" s="287"/>
+      <c r="I7" s="287"/>
+      <c r="J7" s="287"/>
+      <c r="K7" s="287"/>
+      <c r="L7" s="287"/>
+      <c r="M7" s="287"/>
+      <c r="N7" s="287"/>
+      <c r="O7" s="288"/>
       <c r="P7" s="15"/>
     </row>
     <row r="8" spans="1:19" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="7"/>
       <c r="B8" s="7"/>
-      <c r="C8" s="285"/>
-      <c r="D8" s="286"/>
-      <c r="E8" s="286"/>
-      <c r="F8" s="286"/>
-      <c r="G8" s="286"/>
-      <c r="H8" s="286"/>
-      <c r="I8" s="286"/>
-      <c r="J8" s="286"/>
-      <c r="K8" s="286"/>
-      <c r="L8" s="286"/>
-      <c r="M8" s="286"/>
-      <c r="N8" s="286"/>
-      <c r="O8" s="287"/>
+      <c r="C8" s="289"/>
+      <c r="D8" s="290"/>
+      <c r="E8" s="290"/>
+      <c r="F8" s="290"/>
+      <c r="G8" s="290"/>
+      <c r="H8" s="290"/>
+      <c r="I8" s="290"/>
+      <c r="J8" s="290"/>
+      <c r="K8" s="290"/>
+      <c r="L8" s="290"/>
+      <c r="M8" s="290"/>
+      <c r="N8" s="290"/>
+      <c r="O8" s="291"/>
       <c r="Q8" s="84"/>
     </row>
     <row r="9" spans="1:19" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
-      <c r="C9" s="288" t="s">
+      <c r="C9" s="292" t="s">
         <v>307</v>
       </c>
-      <c r="D9" s="289"/>
-      <c r="E9" s="289"/>
-      <c r="F9" s="289"/>
-      <c r="G9" s="289"/>
-      <c r="H9" s="289"/>
-      <c r="I9" s="289"/>
-      <c r="J9" s="289"/>
-      <c r="K9" s="289"/>
-      <c r="L9" s="289"/>
-      <c r="M9" s="289"/>
-      <c r="N9" s="289"/>
-      <c r="O9" s="290"/>
+      <c r="D9" s="293"/>
+      <c r="E9" s="293"/>
+      <c r="F9" s="293"/>
+      <c r="G9" s="293"/>
+      <c r="H9" s="293"/>
+      <c r="I9" s="293"/>
+      <c r="J9" s="293"/>
+      <c r="K9" s="293"/>
+      <c r="L9" s="293"/>
+      <c r="M9" s="293"/>
+      <c r="N9" s="293"/>
+      <c r="O9" s="294"/>
       <c r="Q9" t="s">
         <v>248</v>
       </c>
@@ -5804,19 +5810,19 @@
     <row r="10" spans="1:19" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="7"/>
       <c r="B10" s="7"/>
-      <c r="C10" s="291"/>
-      <c r="D10" s="292"/>
-      <c r="E10" s="292"/>
-      <c r="F10" s="292"/>
-      <c r="G10" s="292"/>
-      <c r="H10" s="292"/>
-      <c r="I10" s="292"/>
-      <c r="J10" s="292"/>
-      <c r="K10" s="292"/>
-      <c r="L10" s="292"/>
-      <c r="M10" s="292"/>
-      <c r="N10" s="292"/>
-      <c r="O10" s="293"/>
+      <c r="C10" s="295"/>
+      <c r="D10" s="296"/>
+      <c r="E10" s="296"/>
+      <c r="F10" s="296"/>
+      <c r="G10" s="296"/>
+      <c r="H10" s="296"/>
+      <c r="I10" s="296"/>
+      <c r="J10" s="296"/>
+      <c r="K10" s="296"/>
+      <c r="L10" s="296"/>
+      <c r="M10" s="296"/>
+      <c r="N10" s="296"/>
+      <c r="O10" s="297"/>
       <c r="Q10" t="s">
         <v>249</v>
       </c>
@@ -5826,49 +5832,49 @@
       </c>
     </row>
     <row r="11" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="266" t="s">
+      <c r="A11" s="268" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="300" t="s">
+      <c r="B11" s="270" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="266" t="s">
+      <c r="C11" s="268" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="302" t="s">
+      <c r="D11" s="272" t="s">
         <v>12</v>
       </c>
-      <c r="E11" s="302" t="s">
+      <c r="E11" s="272" t="s">
         <v>265</v>
       </c>
-      <c r="F11" s="266" t="s">
+      <c r="F11" s="268" t="s">
         <v>27</v>
       </c>
-      <c r="G11" s="266" t="s">
+      <c r="G11" s="268" t="s">
         <v>13</v>
       </c>
-      <c r="H11" s="266" t="s">
+      <c r="H11" s="268" t="s">
         <v>14</v>
       </c>
-      <c r="I11" s="272" t="s">
+      <c r="I11" s="279" t="s">
         <v>15</v>
       </c>
-      <c r="J11" s="274" t="s">
+      <c r="J11" s="265" t="s">
         <v>16</v>
       </c>
-      <c r="K11" s="274" t="s">
+      <c r="K11" s="265" t="s">
         <v>388</v>
       </c>
-      <c r="L11" s="274" t="s">
+      <c r="L11" s="265" t="s">
         <v>18</v>
       </c>
-      <c r="M11" s="277" t="s">
+      <c r="M11" s="281" t="s">
         <v>40</v>
       </c>
-      <c r="N11" s="274" t="s">
+      <c r="N11" s="265" t="s">
         <v>276</v>
       </c>
-      <c r="O11" s="274" t="s">
+      <c r="O11" s="265" t="s">
         <v>275</v>
       </c>
       <c r="Q11" t="s">
@@ -5880,21 +5886,21 @@
       </c>
     </row>
     <row r="12" spans="1:19" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="267"/>
-      <c r="B12" s="301"/>
-      <c r="C12" s="267"/>
-      <c r="D12" s="303"/>
-      <c r="E12" s="303"/>
-      <c r="F12" s="267"/>
-      <c r="G12" s="267"/>
-      <c r="H12" s="267"/>
-      <c r="I12" s="273"/>
-      <c r="J12" s="275"/>
-      <c r="K12" s="275"/>
-      <c r="L12" s="275"/>
-      <c r="M12" s="278"/>
-      <c r="N12" s="275"/>
-      <c r="O12" s="275"/>
+      <c r="A12" s="269"/>
+      <c r="B12" s="271"/>
+      <c r="C12" s="269"/>
+      <c r="D12" s="273"/>
+      <c r="E12" s="273"/>
+      <c r="F12" s="269"/>
+      <c r="G12" s="269"/>
+      <c r="H12" s="269"/>
+      <c r="I12" s="280"/>
+      <c r="J12" s="266"/>
+      <c r="K12" s="266"/>
+      <c r="L12" s="266"/>
+      <c r="M12" s="282"/>
+      <c r="N12" s="266"/>
+      <c r="O12" s="266"/>
       <c r="Q12" t="s">
         <v>251</v>
       </c>
@@ -5904,19 +5910,19 @@
       </c>
     </row>
     <row r="13" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="267"/>
-      <c r="B13" s="301"/>
-      <c r="C13" s="267"/>
-      <c r="D13" s="303"/>
-      <c r="E13" s="303"/>
-      <c r="F13" s="267"/>
-      <c r="G13" s="267"/>
-      <c r="H13" s="267"/>
-      <c r="I13" s="273"/>
-      <c r="J13" s="275"/>
-      <c r="K13" s="276"/>
-      <c r="L13" s="276"/>
-      <c r="M13" s="278"/>
+      <c r="A13" s="269"/>
+      <c r="B13" s="271"/>
+      <c r="C13" s="269"/>
+      <c r="D13" s="273"/>
+      <c r="E13" s="273"/>
+      <c r="F13" s="269"/>
+      <c r="G13" s="269"/>
+      <c r="H13" s="269"/>
+      <c r="I13" s="280"/>
+      <c r="J13" s="266"/>
+      <c r="K13" s="267"/>
+      <c r="L13" s="267"/>
+      <c r="M13" s="282"/>
       <c r="N13" s="132" t="str">
         <f>RESUMEN!A20</f>
         <v>VTO 16/03</v>
@@ -5980,8 +5986,8 @@
         <v>655631.62013736006</v>
       </c>
       <c r="P14" s="115"/>
-      <c r="R14" s="265"/>
-      <c r="S14" s="265"/>
+      <c r="R14" s="274"/>
+      <c r="S14" s="274"/>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A15" s="6"/>
@@ -6029,8 +6035,8 @@
         <v>254997.15626608004</v>
       </c>
       <c r="P15" s="115"/>
-      <c r="R15" s="265"/>
-      <c r="S15" s="265"/>
+      <c r="R15" s="274"/>
+      <c r="S15" s="274"/>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
@@ -9792,10 +9798,10 @@
         <v>123</v>
       </c>
       <c r="B78" s="6"/>
-      <c r="C78" s="35" t="s">
+      <c r="C78" s="319" t="s">
         <v>103</v>
       </c>
-      <c r="D78" s="108" t="s">
+      <c r="D78" s="320" t="s">
         <v>213</v>
       </c>
       <c r="E78" s="135"/>
@@ -12684,34 +12690,34 @@
       </c>
     </row>
     <row r="135" spans="1:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C135" s="269"/>
-      <c r="D135" s="269"/>
-      <c r="E135" s="269"/>
-      <c r="F135" s="269"/>
-      <c r="G135" s="269"/>
-      <c r="H135" s="269"/>
-      <c r="I135" s="269"/>
-      <c r="J135" s="269"/>
-      <c r="K135" s="269"/>
-      <c r="L135" s="269"/>
-      <c r="M135" s="269"/>
-      <c r="N135" s="269"/>
-      <c r="O135" s="269"/>
+      <c r="C135" s="276"/>
+      <c r="D135" s="276"/>
+      <c r="E135" s="276"/>
+      <c r="F135" s="276"/>
+      <c r="G135" s="276"/>
+      <c r="H135" s="276"/>
+      <c r="I135" s="276"/>
+      <c r="J135" s="276"/>
+      <c r="K135" s="276"/>
+      <c r="L135" s="276"/>
+      <c r="M135" s="276"/>
+      <c r="N135" s="276"/>
+      <c r="O135" s="276"/>
     </row>
     <row r="136" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
-      <c r="C136" s="269"/>
-      <c r="D136" s="269"/>
-      <c r="E136" s="269"/>
-      <c r="F136" s="269"/>
-      <c r="G136" s="269"/>
-      <c r="H136" s="269"/>
-      <c r="I136" s="269"/>
-      <c r="J136" s="269"/>
-      <c r="K136" s="269"/>
-      <c r="L136" s="269"/>
-      <c r="M136" s="269"/>
-      <c r="N136" s="269"/>
-      <c r="O136" s="269"/>
+      <c r="C136" s="276"/>
+      <c r="D136" s="276"/>
+      <c r="E136" s="276"/>
+      <c r="F136" s="276"/>
+      <c r="G136" s="276"/>
+      <c r="H136" s="276"/>
+      <c r="I136" s="276"/>
+      <c r="J136" s="276"/>
+      <c r="K136" s="276"/>
+      <c r="L136" s="276"/>
+      <c r="M136" s="276"/>
+      <c r="N136" s="276"/>
+      <c r="O136" s="276"/>
     </row>
     <row r="137" spans="1:17" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C137" s="77"/>
@@ -12881,125 +12887,118 @@
       <c r="O147" s="77"/>
     </row>
     <row r="148" spans="3:17" x14ac:dyDescent="0.3">
-      <c r="C148" s="268" t="s">
+      <c r="C148" s="275" t="s">
         <v>257</v>
       </c>
-      <c r="D148" s="268"/>
-      <c r="E148" s="268"/>
-      <c r="F148" s="268"/>
-      <c r="G148" s="268"/>
-      <c r="H148" s="268"/>
-      <c r="I148" s="268"/>
-      <c r="J148" s="268"/>
-      <c r="K148" s="268"/>
-      <c r="L148" s="268"/>
-      <c r="M148" s="268"/>
-      <c r="N148" s="268"/>
-      <c r="O148" s="268"/>
+      <c r="D148" s="275"/>
+      <c r="E148" s="275"/>
+      <c r="F148" s="275"/>
+      <c r="G148" s="275"/>
+      <c r="H148" s="275"/>
+      <c r="I148" s="275"/>
+      <c r="J148" s="275"/>
+      <c r="K148" s="275"/>
+      <c r="L148" s="275"/>
+      <c r="M148" s="275"/>
+      <c r="N148" s="275"/>
+      <c r="O148" s="275"/>
     </row>
     <row r="149" spans="3:17" x14ac:dyDescent="0.3">
-      <c r="C149" s="268"/>
-      <c r="D149" s="268"/>
-      <c r="E149" s="268"/>
-      <c r="F149" s="268"/>
-      <c r="G149" s="268"/>
-      <c r="H149" s="268"/>
-      <c r="I149" s="268"/>
-      <c r="J149" s="268"/>
-      <c r="K149" s="268"/>
-      <c r="L149" s="268"/>
-      <c r="M149" s="268"/>
-      <c r="N149" s="268"/>
-      <c r="O149" s="268"/>
+      <c r="C149" s="275"/>
+      <c r="D149" s="275"/>
+      <c r="E149" s="275"/>
+      <c r="F149" s="275"/>
+      <c r="G149" s="275"/>
+      <c r="H149" s="275"/>
+      <c r="I149" s="275"/>
+      <c r="J149" s="275"/>
+      <c r="K149" s="275"/>
+      <c r="L149" s="275"/>
+      <c r="M149" s="275"/>
+      <c r="N149" s="275"/>
+      <c r="O149" s="275"/>
     </row>
     <row r="150" spans="3:17" x14ac:dyDescent="0.3">
-      <c r="C150" s="268"/>
-      <c r="D150" s="268"/>
-      <c r="E150" s="268"/>
-      <c r="F150" s="268"/>
-      <c r="G150" s="268"/>
-      <c r="H150" s="268"/>
-      <c r="I150" s="268"/>
-      <c r="J150" s="268"/>
-      <c r="K150" s="268"/>
-      <c r="L150" s="268"/>
-      <c r="M150" s="268"/>
-      <c r="N150" s="268"/>
-      <c r="O150" s="268"/>
+      <c r="C150" s="275"/>
+      <c r="D150" s="275"/>
+      <c r="E150" s="275"/>
+      <c r="F150" s="275"/>
+      <c r="G150" s="275"/>
+      <c r="H150" s="275"/>
+      <c r="I150" s="275"/>
+      <c r="J150" s="275"/>
+      <c r="K150" s="275"/>
+      <c r="L150" s="275"/>
+      <c r="M150" s="275"/>
+      <c r="N150" s="275"/>
+      <c r="O150" s="275"/>
       <c r="Q150" s="84">
         <f>M1-L133</f>
         <v>4034495.9149199985</v>
       </c>
     </row>
     <row r="151" spans="3:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C151" s="268"/>
-      <c r="D151" s="268"/>
-      <c r="E151" s="268"/>
-      <c r="F151" s="268"/>
-      <c r="G151" s="268"/>
-      <c r="H151" s="268"/>
-      <c r="I151" s="268"/>
-      <c r="J151" s="268"/>
-      <c r="K151" s="268"/>
-      <c r="L151" s="268"/>
-      <c r="M151" s="268"/>
-      <c r="N151" s="268"/>
-      <c r="O151" s="268"/>
+      <c r="C151" s="275"/>
+      <c r="D151" s="275"/>
+      <c r="E151" s="275"/>
+      <c r="F151" s="275"/>
+      <c r="G151" s="275"/>
+      <c r="H151" s="275"/>
+      <c r="I151" s="275"/>
+      <c r="J151" s="275"/>
+      <c r="K151" s="275"/>
+      <c r="L151" s="275"/>
+      <c r="M151" s="275"/>
+      <c r="N151" s="275"/>
+      <c r="O151" s="275"/>
     </row>
     <row r="152" spans="3:17" ht="5.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C152" s="268"/>
-      <c r="D152" s="268"/>
-      <c r="E152" s="268"/>
-      <c r="F152" s="268"/>
-      <c r="G152" s="268"/>
-      <c r="H152" s="268"/>
-      <c r="I152" s="268"/>
-      <c r="J152" s="268"/>
-      <c r="K152" s="268"/>
-      <c r="L152" s="268"/>
-      <c r="M152" s="268"/>
-      <c r="N152" s="268"/>
-      <c r="O152" s="268"/>
+      <c r="C152" s="275"/>
+      <c r="D152" s="275"/>
+      <c r="E152" s="275"/>
+      <c r="F152" s="275"/>
+      <c r="G152" s="275"/>
+      <c r="H152" s="275"/>
+      <c r="I152" s="275"/>
+      <c r="J152" s="275"/>
+      <c r="K152" s="275"/>
+      <c r="L152" s="275"/>
+      <c r="M152" s="275"/>
+      <c r="N152" s="275"/>
+      <c r="O152" s="275"/>
     </row>
     <row r="153" spans="3:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C153" s="268"/>
-      <c r="D153" s="268"/>
-      <c r="E153" s="268"/>
-      <c r="F153" s="268"/>
-      <c r="G153" s="268"/>
-      <c r="H153" s="268"/>
-      <c r="I153" s="268"/>
-      <c r="J153" s="268"/>
-      <c r="K153" s="268"/>
-      <c r="L153" s="268"/>
-      <c r="M153" s="268"/>
-      <c r="N153" s="268"/>
-      <c r="O153" s="268"/>
+      <c r="C153" s="275"/>
+      <c r="D153" s="275"/>
+      <c r="E153" s="275"/>
+      <c r="F153" s="275"/>
+      <c r="G153" s="275"/>
+      <c r="H153" s="275"/>
+      <c r="I153" s="275"/>
+      <c r="J153" s="275"/>
+      <c r="K153" s="275"/>
+      <c r="L153" s="275"/>
+      <c r="M153" s="275"/>
+      <c r="N153" s="275"/>
+      <c r="O153" s="275"/>
     </row>
     <row r="154" spans="3:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C154" s="268"/>
-      <c r="D154" s="268"/>
-      <c r="E154" s="268"/>
-      <c r="F154" s="268"/>
-      <c r="G154" s="268"/>
-      <c r="H154" s="268"/>
-      <c r="I154" s="268"/>
-      <c r="J154" s="268"/>
-      <c r="K154" s="268"/>
-      <c r="L154" s="268"/>
-      <c r="M154" s="268"/>
-      <c r="N154" s="268"/>
-      <c r="O154" s="268"/>
+      <c r="C154" s="275"/>
+      <c r="D154" s="275"/>
+      <c r="E154" s="275"/>
+      <c r="F154" s="275"/>
+      <c r="G154" s="275"/>
+      <c r="H154" s="275"/>
+      <c r="I154" s="275"/>
+      <c r="J154" s="275"/>
+      <c r="K154" s="275"/>
+      <c r="L154" s="275"/>
+      <c r="M154" s="275"/>
+      <c r="N154" s="275"/>
+      <c r="O154" s="275"/>
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="K11:K13"/>
-    <mergeCell ref="A11:A13"/>
-    <mergeCell ref="B11:B13"/>
-    <mergeCell ref="C11:C13"/>
-    <mergeCell ref="D11:D13"/>
-    <mergeCell ref="F11:F13"/>
-    <mergeCell ref="E11:E13"/>
     <mergeCell ref="R14:S15"/>
     <mergeCell ref="G11:G13"/>
     <mergeCell ref="C148:O154"/>
@@ -13016,6 +13015,13 @@
     <mergeCell ref="C5:O8"/>
     <mergeCell ref="C9:O10"/>
     <mergeCell ref="A1:E4"/>
+    <mergeCell ref="K11:K13"/>
+    <mergeCell ref="A11:A13"/>
+    <mergeCell ref="B11:B13"/>
+    <mergeCell ref="C11:C13"/>
+    <mergeCell ref="D11:D13"/>
+    <mergeCell ref="F11:F13"/>
+    <mergeCell ref="E11:E13"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -13128,59 +13134,59 @@
       <c r="Y4" s="249"/>
     </row>
     <row r="5" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="266" t="s">
+      <c r="A5" s="268" t="s">
         <v>329</v>
       </c>
-      <c r="B5" s="266" t="s">
+      <c r="B5" s="268" t="s">
         <v>330</v>
       </c>
-      <c r="C5" s="266" t="s">
+      <c r="C5" s="268" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="266" t="s">
+      <c r="D5" s="268" t="s">
         <v>27</v>
       </c>
-      <c r="E5" s="274" t="s">
+      <c r="E5" s="265" t="s">
         <v>356</v>
       </c>
-      <c r="F5" s="274" t="s">
+      <c r="F5" s="265" t="s">
         <v>357</v>
       </c>
-      <c r="G5" s="274" t="s">
+      <c r="G5" s="265" t="s">
         <v>276</v>
       </c>
-      <c r="H5" s="274" t="s">
+      <c r="H5" s="265" t="s">
         <v>389</v>
       </c>
-      <c r="I5" s="274" t="s">
+      <c r="I5" s="265" t="s">
         <v>390</v>
       </c>
       <c r="J5" s="314" t="s">
         <v>358</v>
       </c>
       <c r="K5" s="131"/>
-      <c r="L5" s="274" t="s">
+      <c r="L5" s="265" t="s">
         <v>359</v>
       </c>
-      <c r="M5" s="274" t="s">
+      <c r="M5" s="265" t="s">
         <v>17</v>
       </c>
       <c r="P5" s="43"/>
     </row>
     <row r="6" spans="1:25" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="267"/>
-      <c r="B6" s="267"/>
-      <c r="C6" s="267"/>
-      <c r="D6" s="267"/>
-      <c r="E6" s="275"/>
-      <c r="F6" s="275"/>
-      <c r="G6" s="275"/>
-      <c r="H6" s="275"/>
-      <c r="I6" s="275"/>
+      <c r="A6" s="269"/>
+      <c r="B6" s="269"/>
+      <c r="C6" s="269"/>
+      <c r="D6" s="269"/>
+      <c r="E6" s="266"/>
+      <c r="F6" s="266"/>
+      <c r="G6" s="266"/>
+      <c r="H6" s="266"/>
+      <c r="I6" s="266"/>
       <c r="J6" s="315"/>
       <c r="K6" s="131"/>
-      <c r="L6" s="275"/>
-      <c r="M6" s="275"/>
+      <c r="L6" s="266"/>
+      <c r="M6" s="266"/>
       <c r="P6" s="43"/>
     </row>
     <row r="7" spans="1:25" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -13245,8 +13251,8 @@
       <c r="N8" s="115">
         <v>0.7</v>
       </c>
-      <c r="P8" s="265"/>
-      <c r="Q8" s="265"/>
+      <c r="P8" s="274"/>
+      <c r="Q8" s="274"/>
     </row>
     <row r="9" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A9" s="210" t="s">
@@ -13295,8 +13301,8 @@
         <f>N8+0.01</f>
         <v>0.71</v>
       </c>
-      <c r="P9" s="265"/>
-      <c r="Q9" s="265"/>
+      <c r="P9" s="274"/>
+      <c r="Q9" s="274"/>
     </row>
     <row r="10" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A10" s="210" t="s">
@@ -17321,10 +17327,15 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7365EFC1-5C09-4380-B9A2-A73102AE2F7A}">
-  <dimension ref="A13"/>
+  <dimension ref="C4:C13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C4" s="321" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="13" spans="3:3" ht="15.6" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/2026/EL MIRADOR/Febrero/Febrero - EL MIRADOR.xlsx
+++ b/2026/EL MIRADOR/Febrero/Febrero - EL MIRADOR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\EL MIRADOR\Febrero\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C4C344F-B8C4-447B-9744-E5AE893BABEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AAD3D82-41B9-4E36-A42F-F56BC8D9911A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="691" uniqueCount="396">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="692" uniqueCount="397">
   <si>
     <t>LIQUIDACION DE EXPENSAS</t>
   </si>
@@ -1225,6 +1225,9 @@
   </si>
   <si>
     <t>El 12A deposito 16/03 $35.500 y 361.000</t>
+  </si>
+  <si>
+    <t>Hay que sacar a Di Mito de la cadena de mails del mirador</t>
   </si>
 </sst>
 </file>
@@ -1892,7 +1895,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="322">
+  <cellXfs count="323">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2213,6 +2216,9 @@
     <xf numFmtId="1" fontId="23" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2258,35 +2264,14 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -2305,6 +2290,15 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2375,6 +2369,18 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="1" fontId="26" fillId="15" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2420,9 +2426,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Millares" xfId="3" builtinId="3"/>
@@ -2912,108 +2916,108 @@
     <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.3"/>
     <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.3"/>
     <row r="14" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="251" t="s">
+      <c r="A14" s="254" t="s">
         <v>258</v>
       </c>
-      <c r="B14" s="251"/>
-      <c r="C14" s="251"/>
-      <c r="D14" s="251"/>
-      <c r="E14" s="251"/>
-      <c r="F14" s="251"/>
-      <c r="G14" s="251"/>
-      <c r="H14" s="251"/>
-      <c r="I14" s="251"/>
-      <c r="J14" s="251"/>
+      <c r="B14" s="254"/>
+      <c r="C14" s="254"/>
+      <c r="D14" s="254"/>
+      <c r="E14" s="254"/>
+      <c r="F14" s="254"/>
+      <c r="G14" s="254"/>
+      <c r="H14" s="254"/>
+      <c r="I14" s="254"/>
+      <c r="J14" s="254"/>
     </row>
     <row r="15" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="251"/>
-      <c r="B15" s="251"/>
-      <c r="C15" s="251"/>
-      <c r="D15" s="251"/>
-      <c r="E15" s="251"/>
-      <c r="F15" s="251"/>
-      <c r="G15" s="251"/>
-      <c r="H15" s="251"/>
-      <c r="I15" s="251"/>
-      <c r="J15" s="251"/>
+      <c r="A15" s="254"/>
+      <c r="B15" s="254"/>
+      <c r="C15" s="254"/>
+      <c r="D15" s="254"/>
+      <c r="E15" s="254"/>
+      <c r="F15" s="254"/>
+      <c r="G15" s="254"/>
+      <c r="H15" s="254"/>
+      <c r="I15" s="254"/>
+      <c r="J15" s="254"/>
     </row>
     <row r="16" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="251"/>
-      <c r="B16" s="251"/>
-      <c r="C16" s="251"/>
-      <c r="D16" s="251"/>
-      <c r="E16" s="251"/>
-      <c r="F16" s="251"/>
-      <c r="G16" s="251"/>
-      <c r="H16" s="251"/>
-      <c r="I16" s="251"/>
-      <c r="J16" s="251"/>
+      <c r="A16" s="254"/>
+      <c r="B16" s="254"/>
+      <c r="C16" s="254"/>
+      <c r="D16" s="254"/>
+      <c r="E16" s="254"/>
+      <c r="F16" s="254"/>
+      <c r="G16" s="254"/>
+      <c r="H16" s="254"/>
+      <c r="I16" s="254"/>
+      <c r="J16" s="254"/>
     </row>
     <row r="17" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="251"/>
-      <c r="B17" s="251"/>
-      <c r="C17" s="251"/>
-      <c r="D17" s="251"/>
-      <c r="E17" s="251"/>
-      <c r="F17" s="251"/>
-      <c r="G17" s="251"/>
-      <c r="H17" s="251"/>
-      <c r="I17" s="251"/>
-      <c r="J17" s="251"/>
+      <c r="A17" s="254"/>
+      <c r="B17" s="254"/>
+      <c r="C17" s="254"/>
+      <c r="D17" s="254"/>
+      <c r="E17" s="254"/>
+      <c r="F17" s="254"/>
+      <c r="G17" s="254"/>
+      <c r="H17" s="254"/>
+      <c r="I17" s="254"/>
+      <c r="J17" s="254"/>
     </row>
     <row r="18" spans="1:10" ht="47.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="251"/>
-      <c r="B18" s="251"/>
-      <c r="C18" s="251"/>
-      <c r="D18" s="251"/>
-      <c r="E18" s="251"/>
-      <c r="F18" s="251"/>
-      <c r="G18" s="251"/>
-      <c r="H18" s="251"/>
-      <c r="I18" s="251"/>
-      <c r="J18" s="251"/>
+      <c r="A18" s="254"/>
+      <c r="B18" s="254"/>
+      <c r="C18" s="254"/>
+      <c r="D18" s="254"/>
+      <c r="E18" s="254"/>
+      <c r="F18" s="254"/>
+      <c r="G18" s="254"/>
+      <c r="H18" s="254"/>
+      <c r="I18" s="254"/>
+      <c r="J18" s="254"/>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" s="2"/>
       <c r="H19" s="94"/>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A20" s="260" t="s">
+      <c r="A20" s="263" t="s">
         <v>393</v>
       </c>
-      <c r="B20" s="260"/>
-      <c r="C20" s="260"/>
-      <c r="D20" s="260"/>
-      <c r="E20" s="260"/>
-      <c r="F20" s="260"/>
-      <c r="G20" s="260"/>
-      <c r="H20" s="260"/>
-      <c r="I20" s="260"/>
-      <c r="J20" s="260"/>
+      <c r="B20" s="263"/>
+      <c r="C20" s="263"/>
+      <c r="D20" s="263"/>
+      <c r="E20" s="263"/>
+      <c r="F20" s="263"/>
+      <c r="G20" s="263"/>
+      <c r="H20" s="263"/>
+      <c r="I20" s="263"/>
+      <c r="J20" s="263"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A21" s="260"/>
-      <c r="B21" s="260"/>
-      <c r="C21" s="260"/>
-      <c r="D21" s="260"/>
-      <c r="E21" s="260"/>
-      <c r="F21" s="260"/>
-      <c r="G21" s="260"/>
-      <c r="H21" s="260"/>
-      <c r="I21" s="260"/>
-      <c r="J21" s="260"/>
+      <c r="A21" s="263"/>
+      <c r="B21" s="263"/>
+      <c r="C21" s="263"/>
+      <c r="D21" s="263"/>
+      <c r="E21" s="263"/>
+      <c r="F21" s="263"/>
+      <c r="G21" s="263"/>
+      <c r="H21" s="263"/>
+      <c r="I21" s="263"/>
+      <c r="J21" s="263"/>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A22" s="260"/>
-      <c r="B22" s="260"/>
-      <c r="C22" s="260"/>
-      <c r="D22" s="260"/>
-      <c r="E22" s="260"/>
-      <c r="F22" s="260"/>
-      <c r="G22" s="260"/>
-      <c r="H22" s="260"/>
-      <c r="I22" s="260"/>
-      <c r="J22" s="260"/>
+      <c r="A22" s="263"/>
+      <c r="B22" s="263"/>
+      <c r="C22" s="263"/>
+      <c r="D22" s="263"/>
+      <c r="E22" s="263"/>
+      <c r="F22" s="263"/>
+      <c r="G22" s="263"/>
+      <c r="H22" s="263"/>
+      <c r="I22" s="263"/>
+      <c r="J22" s="263"/>
     </row>
     <row r="23" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="H23" s="94"/>
@@ -3816,10 +3820,10 @@
       <c r="L62" s="69"/>
     </row>
     <row r="63" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="262" t="s">
+      <c r="A63" s="265" t="s">
         <v>232</v>
       </c>
-      <c r="B63" s="263"/>
+      <c r="B63" s="266"/>
       <c r="C63" s="35" t="s">
         <v>310</v>
       </c>
@@ -3859,10 +3863,10 @@
       </c>
     </row>
     <row r="64" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="262" t="s">
+      <c r="A64" s="265" t="s">
         <v>233</v>
       </c>
-      <c r="B64" s="263"/>
+      <c r="B64" s="266"/>
       <c r="C64" s="6" t="s">
         <v>378</v>
       </c>
@@ -4118,10 +4122,10 @@
       <c r="N70" s="84"/>
     </row>
     <row r="71" spans="1:14" ht="33" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="258" t="s">
+      <c r="A71" s="261" t="s">
         <v>365</v>
       </c>
-      <c r="B71" s="264"/>
+      <c r="B71" s="267"/>
       <c r="C71" s="35"/>
       <c r="D71" s="44"/>
       <c r="E71" s="68">
@@ -4437,10 +4441,10 @@
       <c r="L80" s="69"/>
     </row>
     <row r="81" spans="1:14" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="262" t="s">
+      <c r="A81" s="265" t="s">
         <v>372</v>
       </c>
-      <c r="B81" s="263"/>
+      <c r="B81" s="266"/>
       <c r="C81" s="137" t="s">
         <v>373</v>
       </c>
@@ -4459,10 +4463,10 @@
       <c r="L81" s="69"/>
     </row>
     <row r="82" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="262" t="s">
+      <c r="A82" s="265" t="s">
         <v>374</v>
       </c>
-      <c r="B82" s="263"/>
+      <c r="B82" s="266"/>
       <c r="C82" s="137" t="s">
         <v>373</v>
       </c>
@@ -4496,10 +4500,10 @@
       <c r="L82" s="69"/>
     </row>
     <row r="83" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="262" t="s">
+      <c r="A83" s="265" t="s">
         <v>375</v>
       </c>
-      <c r="B83" s="263"/>
+      <c r="B83" s="266"/>
       <c r="C83" s="137" t="s">
         <v>317</v>
       </c>
@@ -5022,12 +5026,12 @@
       <c r="I105" s="60"/>
     </row>
     <row r="106" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A106" s="256" t="s">
+      <c r="A106" s="259" t="s">
         <v>34</v>
       </c>
-      <c r="B106" s="257"/>
-      <c r="C106" s="257"/>
-      <c r="D106" s="257"/>
+      <c r="B106" s="260"/>
+      <c r="C106" s="260"/>
+      <c r="D106" s="260"/>
       <c r="E106" s="80" t="s">
         <v>11</v>
       </c>
@@ -5048,8 +5052,8 @@
       </c>
     </row>
     <row r="107" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A107" s="258"/>
-      <c r="B107" s="259"/>
+      <c r="A107" s="261"/>
+      <c r="B107" s="262"/>
       <c r="C107" s="82"/>
       <c r="D107" s="44"/>
       <c r="E107" s="68">
@@ -5063,8 +5067,8 @@
       <c r="J107" s="58"/>
     </row>
     <row r="108" spans="1:13" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A108" s="258"/>
-      <c r="B108" s="259"/>
+      <c r="A108" s="261"/>
+      <c r="B108" s="262"/>
       <c r="C108" s="82"/>
       <c r="D108" s="44"/>
       <c r="E108" s="68"/>
@@ -5075,11 +5079,11 @@
       <c r="J108" s="58"/>
     </row>
     <row r="109" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A109" s="253" t="s">
+      <c r="A109" s="256" t="s">
         <v>17</v>
       </c>
-      <c r="B109" s="254"/>
-      <c r="C109" s="255"/>
+      <c r="B109" s="257"/>
+      <c r="C109" s="258"/>
       <c r="D109" s="79">
         <f>SUM(D107:D108)</f>
         <v>0</v>
@@ -5129,92 +5133,92 @@
         <f>D98-D96</f>
         <v>14242326.569999998</v>
       </c>
-      <c r="D113" s="261" t="s">
+      <c r="D113" s="264" t="s">
         <v>301</v>
       </c>
-      <c r="E113" s="261"/>
-      <c r="F113" s="261"/>
-      <c r="G113" s="261"/>
-      <c r="H113" s="261"/>
-      <c r="I113" s="261"/>
+      <c r="E113" s="264"/>
+      <c r="F113" s="264"/>
+      <c r="G113" s="264"/>
+      <c r="H113" s="264"/>
+      <c r="I113" s="264"/>
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="D114" s="261"/>
-      <c r="E114" s="261"/>
-      <c r="F114" s="261"/>
-      <c r="G114" s="261"/>
-      <c r="H114" s="261"/>
-      <c r="I114" s="261"/>
+      <c r="D114" s="264"/>
+      <c r="E114" s="264"/>
+      <c r="F114" s="264"/>
+      <c r="G114" s="264"/>
+      <c r="H114" s="264"/>
+      <c r="I114" s="264"/>
     </row>
     <row r="115" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A115" s="250" t="s">
+      <c r="A115" s="253" t="s">
         <v>381</v>
       </c>
-      <c r="B115" s="250"/>
-      <c r="D115" s="261"/>
-      <c r="E115" s="261"/>
-      <c r="F115" s="261"/>
-      <c r="G115" s="261"/>
-      <c r="H115" s="261"/>
-      <c r="I115" s="261"/>
+      <c r="B115" s="253"/>
+      <c r="D115" s="264"/>
+      <c r="E115" s="264"/>
+      <c r="F115" s="264"/>
+      <c r="G115" s="264"/>
+      <c r="H115" s="264"/>
+      <c r="I115" s="264"/>
     </row>
     <row r="116" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A116" s="250"/>
-      <c r="B116" s="250"/>
-      <c r="D116" s="261"/>
-      <c r="E116" s="261"/>
-      <c r="F116" s="261"/>
-      <c r="G116" s="261"/>
-      <c r="H116" s="261"/>
-      <c r="I116" s="261"/>
+      <c r="A116" s="253"/>
+      <c r="B116" s="253"/>
+      <c r="D116" s="264"/>
+      <c r="E116" s="264"/>
+      <c r="F116" s="264"/>
+      <c r="G116" s="264"/>
+      <c r="H116" s="264"/>
+      <c r="I116" s="264"/>
     </row>
     <row r="117" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A117" s="250"/>
-      <c r="B117" s="250"/>
-      <c r="D117" s="261"/>
-      <c r="E117" s="261"/>
-      <c r="F117" s="261"/>
-      <c r="G117" s="261"/>
-      <c r="H117" s="261"/>
-      <c r="I117" s="261"/>
+      <c r="A117" s="253"/>
+      <c r="B117" s="253"/>
+      <c r="D117" s="264"/>
+      <c r="E117" s="264"/>
+      <c r="F117" s="264"/>
+      <c r="G117" s="264"/>
+      <c r="H117" s="264"/>
+      <c r="I117" s="264"/>
     </row>
     <row r="118" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A118" s="250"/>
-      <c r="B118" s="250"/>
-      <c r="D118" s="261"/>
-      <c r="E118" s="261"/>
-      <c r="F118" s="261"/>
-      <c r="G118" s="261"/>
-      <c r="H118" s="261"/>
-      <c r="I118" s="261"/>
+      <c r="A118" s="253"/>
+      <c r="B118" s="253"/>
+      <c r="D118" s="264"/>
+      <c r="E118" s="264"/>
+      <c r="F118" s="264"/>
+      <c r="G118" s="264"/>
+      <c r="H118" s="264"/>
+      <c r="I118" s="264"/>
     </row>
     <row r="119" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A119" s="250"/>
-      <c r="B119" s="250"/>
-      <c r="D119" s="261"/>
-      <c r="E119" s="261"/>
-      <c r="F119" s="261"/>
-      <c r="G119" s="261"/>
-      <c r="H119" s="261"/>
-      <c r="I119" s="261"/>
+      <c r="A119" s="253"/>
+      <c r="B119" s="253"/>
+      <c r="D119" s="264"/>
+      <c r="E119" s="264"/>
+      <c r="F119" s="264"/>
+      <c r="G119" s="264"/>
+      <c r="H119" s="264"/>
+      <c r="I119" s="264"/>
     </row>
     <row r="120" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A120" s="250"/>
-      <c r="B120" s="250"/>
-      <c r="D120" s="261"/>
-      <c r="E120" s="261"/>
-      <c r="F120" s="261"/>
-      <c r="G120" s="261"/>
-      <c r="H120" s="261"/>
-      <c r="I120" s="261"/>
+      <c r="A120" s="253"/>
+      <c r="B120" s="253"/>
+      <c r="D120" s="264"/>
+      <c r="E120" s="264"/>
+      <c r="F120" s="264"/>
+      <c r="G120" s="264"/>
+      <c r="H120" s="264"/>
+      <c r="I120" s="264"/>
     </row>
     <row r="121" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="D121" s="261"/>
-      <c r="E121" s="261"/>
-      <c r="F121" s="261"/>
-      <c r="G121" s="261"/>
-      <c r="H121" s="261"/>
-      <c r="I121" s="261"/>
+      <c r="D121" s="264"/>
+      <c r="E121" s="264"/>
+      <c r="F121" s="264"/>
+      <c r="G121" s="264"/>
+      <c r="H121" s="264"/>
+      <c r="I121" s="264"/>
     </row>
     <row r="122" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A122" s="16" t="s">
@@ -5222,12 +5226,12 @@
       </c>
       <c r="B122" s="17"/>
       <c r="C122" s="18"/>
-      <c r="D122" s="261"/>
-      <c r="E122" s="261"/>
-      <c r="F122" s="261"/>
-      <c r="G122" s="261"/>
-      <c r="H122" s="261"/>
-      <c r="I122" s="261"/>
+      <c r="D122" s="264"/>
+      <c r="E122" s="264"/>
+      <c r="F122" s="264"/>
+      <c r="G122" s="264"/>
+      <c r="H122" s="264"/>
+      <c r="I122" s="264"/>
     </row>
     <row r="123" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A123" s="19" t="s">
@@ -5237,12 +5241,12 @@
         <v>1767072.6013971008</v>
       </c>
       <c r="C123" s="20"/>
-      <c r="D123" s="261"/>
-      <c r="E123" s="261"/>
-      <c r="F123" s="261"/>
-      <c r="G123" s="261"/>
-      <c r="H123" s="261"/>
-      <c r="I123" s="261"/>
+      <c r="D123" s="264"/>
+      <c r="E123" s="264"/>
+      <c r="F123" s="264"/>
+      <c r="G123" s="264"/>
+      <c r="H123" s="264"/>
+      <c r="I123" s="264"/>
     </row>
     <row r="124" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A124" s="21" t="s">
@@ -5255,12 +5259,12 @@
       <c r="C124" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="D124" s="261"/>
-      <c r="E124" s="261"/>
-      <c r="F124" s="261"/>
-      <c r="G124" s="261"/>
-      <c r="H124" s="261"/>
-      <c r="I124" s="261"/>
+      <c r="D124" s="264"/>
+      <c r="E124" s="264"/>
+      <c r="F124" s="264"/>
+      <c r="G124" s="264"/>
+      <c r="H124" s="264"/>
+      <c r="I124" s="264"/>
     </row>
     <row r="125" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A125" s="21" t="s">
@@ -5271,12 +5275,12 @@
         <v>-14242326.569999998</v>
       </c>
       <c r="C125" s="18"/>
-      <c r="D125" s="261"/>
-      <c r="E125" s="261"/>
-      <c r="F125" s="261"/>
-      <c r="G125" s="261"/>
-      <c r="H125" s="261"/>
-      <c r="I125" s="261"/>
+      <c r="D125" s="264"/>
+      <c r="E125" s="264"/>
+      <c r="F125" s="264"/>
+      <c r="G125" s="264"/>
+      <c r="H125" s="264"/>
+      <c r="I125" s="264"/>
       <c r="K125" s="44"/>
     </row>
     <row r="126" spans="1:11" x14ac:dyDescent="0.3">
@@ -5288,12 +5292,12 @@
         <v>0</v>
       </c>
       <c r="C126" s="18"/>
-      <c r="D126" s="261"/>
-      <c r="E126" s="261"/>
-      <c r="F126" s="261"/>
-      <c r="G126" s="261"/>
-      <c r="H126" s="261"/>
-      <c r="I126" s="261"/>
+      <c r="D126" s="264"/>
+      <c r="E126" s="264"/>
+      <c r="F126" s="264"/>
+      <c r="G126" s="264"/>
+      <c r="H126" s="264"/>
+      <c r="I126" s="264"/>
       <c r="K126" s="52"/>
     </row>
     <row r="127" spans="1:11" x14ac:dyDescent="0.3">
@@ -5305,12 +5309,12 @@
         <v>141730</v>
       </c>
       <c r="C127" s="18"/>
-      <c r="D127" s="261"/>
-      <c r="E127" s="261"/>
-      <c r="F127" s="261"/>
-      <c r="G127" s="261"/>
-      <c r="H127" s="261"/>
-      <c r="I127" s="261"/>
+      <c r="D127" s="264"/>
+      <c r="E127" s="264"/>
+      <c r="F127" s="264"/>
+      <c r="G127" s="264"/>
+      <c r="H127" s="264"/>
+      <c r="I127" s="264"/>
       <c r="K127" s="52"/>
     </row>
     <row r="128" spans="1:11" x14ac:dyDescent="0.3">
@@ -5322,12 +5326,12 @@
         <v>-145000</v>
       </c>
       <c r="C128" s="22"/>
-      <c r="D128" s="261"/>
-      <c r="E128" s="261"/>
-      <c r="F128" s="261"/>
-      <c r="G128" s="261"/>
-      <c r="H128" s="261"/>
-      <c r="I128" s="261"/>
+      <c r="D128" s="264"/>
+      <c r="E128" s="264"/>
+      <c r="F128" s="264"/>
+      <c r="G128" s="264"/>
+      <c r="H128" s="264"/>
+      <c r="I128" s="264"/>
     </row>
     <row r="129" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A129" s="21" t="s">
@@ -5338,12 +5342,12 @@
         <v>-87300</v>
       </c>
       <c r="C129" s="22"/>
-      <c r="D129" s="261"/>
-      <c r="E129" s="261"/>
-      <c r="F129" s="261"/>
-      <c r="G129" s="261"/>
-      <c r="H129" s="261"/>
-      <c r="I129" s="261"/>
+      <c r="D129" s="264"/>
+      <c r="E129" s="264"/>
+      <c r="F129" s="264"/>
+      <c r="G129" s="264"/>
+      <c r="H129" s="264"/>
+      <c r="I129" s="264"/>
     </row>
     <row r="130" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A130" s="21" t="s">
@@ -5354,23 +5358,23 @@
         <v>0</v>
       </c>
       <c r="C130" s="22"/>
-      <c r="D130" s="261"/>
-      <c r="E130" s="261"/>
-      <c r="F130" s="261"/>
-      <c r="G130" s="261"/>
-      <c r="H130" s="261"/>
-      <c r="I130" s="261"/>
+      <c r="D130" s="264"/>
+      <c r="E130" s="264"/>
+      <c r="F130" s="264"/>
+      <c r="G130" s="264"/>
+      <c r="H130" s="264"/>
+      <c r="I130" s="264"/>
     </row>
     <row r="131" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A131" s="21"/>
       <c r="B131" s="168"/>
       <c r="C131" s="22"/>
-      <c r="D131" s="261"/>
-      <c r="E131" s="261"/>
-      <c r="F131" s="261"/>
-      <c r="G131" s="261"/>
-      <c r="H131" s="261"/>
-      <c r="I131" s="261"/>
+      <c r="D131" s="264"/>
+      <c r="E131" s="264"/>
+      <c r="F131" s="264"/>
+      <c r="G131" s="264"/>
+      <c r="H131" s="264"/>
+      <c r="I131" s="264"/>
     </row>
     <row r="132" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A132" s="19" t="s">
@@ -5381,22 +5385,22 @@
         <v>1499395.7189351022</v>
       </c>
       <c r="C132" s="70"/>
-      <c r="D132" s="261"/>
-      <c r="E132" s="261"/>
-      <c r="F132" s="261"/>
-      <c r="G132" s="261"/>
-      <c r="H132" s="261"/>
-      <c r="I132" s="261"/>
+      <c r="D132" s="264"/>
+      <c r="E132" s="264"/>
+      <c r="F132" s="264"/>
+      <c r="G132" s="264"/>
+      <c r="H132" s="264"/>
+      <c r="I132" s="264"/>
     </row>
     <row r="133" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A133" s="22"/>
       <c r="C133" s="18"/>
-      <c r="D133" s="261"/>
-      <c r="E133" s="261"/>
-      <c r="F133" s="261"/>
-      <c r="G133" s="261"/>
-      <c r="H133" s="261"/>
-      <c r="I133" s="261"/>
+      <c r="D133" s="264"/>
+      <c r="E133" s="264"/>
+      <c r="F133" s="264"/>
+      <c r="G133" s="264"/>
+      <c r="H133" s="264"/>
+      <c r="I133" s="264"/>
     </row>
     <row r="134" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A134" s="16" t="s">
@@ -5404,12 +5408,12 @@
       </c>
       <c r="B134" s="8"/>
       <c r="C134" s="18"/>
-      <c r="D134" s="261"/>
-      <c r="E134" s="261"/>
-      <c r="F134" s="261"/>
-      <c r="G134" s="261"/>
-      <c r="H134" s="261"/>
-      <c r="I134" s="261"/>
+      <c r="D134" s="264"/>
+      <c r="E134" s="264"/>
+      <c r="F134" s="264"/>
+      <c r="G134" s="264"/>
+      <c r="H134" s="264"/>
+      <c r="I134" s="264"/>
     </row>
     <row r="135" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="19" t="s">
@@ -5515,50 +5519,50 @@
       <c r="R147" s="9"/>
     </row>
     <row r="150" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B150" s="252"/>
-      <c r="C150" s="252"/>
-      <c r="D150" s="252"/>
-      <c r="E150" s="252"/>
+      <c r="B150" s="255"/>
+      <c r="C150" s="255"/>
+      <c r="D150" s="255"/>
+      <c r="E150" s="255"/>
       <c r="F150" s="90"/>
       <c r="G150" s="90"/>
       <c r="H150" s="90"/>
       <c r="I150" s="90"/>
     </row>
     <row r="151" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B151" s="252"/>
-      <c r="C151" s="252"/>
-      <c r="D151" s="252"/>
-      <c r="E151" s="252"/>
+      <c r="B151" s="255"/>
+      <c r="C151" s="255"/>
+      <c r="D151" s="255"/>
+      <c r="E151" s="255"/>
       <c r="F151" s="90"/>
       <c r="G151" s="90"/>
       <c r="H151" s="90"/>
       <c r="I151" s="90"/>
     </row>
     <row r="152" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B152" s="252"/>
-      <c r="C152" s="252"/>
-      <c r="D152" s="252"/>
-      <c r="E152" s="252"/>
+      <c r="B152" s="255"/>
+      <c r="C152" s="255"/>
+      <c r="D152" s="255"/>
+      <c r="E152" s="255"/>
       <c r="F152" s="90"/>
       <c r="G152" s="90"/>
       <c r="H152" s="90"/>
       <c r="I152" s="90"/>
     </row>
     <row r="153" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B153" s="252"/>
-      <c r="C153" s="252"/>
-      <c r="D153" s="252"/>
-      <c r="E153" s="252"/>
+      <c r="B153" s="255"/>
+      <c r="C153" s="255"/>
+      <c r="D153" s="255"/>
+      <c r="E153" s="255"/>
       <c r="F153" s="90"/>
       <c r="G153" s="90"/>
       <c r="H153" s="90"/>
       <c r="I153" s="90"/>
     </row>
     <row r="154" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B154" s="252"/>
-      <c r="C154" s="252"/>
-      <c r="D154" s="252"/>
-      <c r="E154" s="252"/>
+      <c r="B154" s="255"/>
+      <c r="C154" s="255"/>
+      <c r="D154" s="255"/>
+      <c r="E154" s="255"/>
       <c r="F154" s="90"/>
       <c r="G154" s="90"/>
       <c r="H154" s="90"/>
@@ -5614,13 +5618,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A1" s="298" t="s">
+      <c r="A1" s="297" t="s">
         <v>326</v>
       </c>
-      <c r="B1" s="299"/>
-      <c r="C1" s="299"/>
-      <c r="D1" s="299"/>
-      <c r="E1" s="299"/>
+      <c r="B1" s="298"/>
+      <c r="C1" s="298"/>
+      <c r="D1" s="298"/>
+      <c r="E1" s="298"/>
       <c r="F1" s="158" t="s">
         <v>292</v>
       </c>
@@ -5632,20 +5636,20 @@
       <c r="L1" s="190" t="s">
         <v>41</v>
       </c>
-      <c r="M1" s="277">
+      <c r="M1" s="273">
         <f>RESUMEN!D98-RESUMEN!D96</f>
         <v>14242326.569999998</v>
       </c>
-      <c r="N1" s="278"/>
+      <c r="N1" s="274"/>
       <c r="O1" s="159"/>
       <c r="P1" s="59"/>
     </row>
     <row r="2" spans="1:19" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="300"/>
-      <c r="B2" s="301"/>
-      <c r="C2" s="301"/>
-      <c r="D2" s="301"/>
-      <c r="E2" s="301"/>
+      <c r="A2" s="299"/>
+      <c r="B2" s="300"/>
+      <c r="C2" s="300"/>
+      <c r="D2" s="300"/>
+      <c r="E2" s="300"/>
       <c r="F2" s="7" t="s">
         <v>291</v>
       </c>
@@ -5665,11 +5669,11 @@
       <c r="P2" s="59"/>
     </row>
     <row r="3" spans="1:19" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="300"/>
-      <c r="B3" s="301"/>
-      <c r="C3" s="301"/>
-      <c r="D3" s="301"/>
-      <c r="E3" s="301"/>
+      <c r="A3" s="299"/>
+      <c r="B3" s="300"/>
+      <c r="C3" s="300"/>
+      <c r="D3" s="300"/>
+      <c r="E3" s="300"/>
       <c r="F3" s="7" t="s">
         <v>293</v>
       </c>
@@ -5690,11 +5694,11 @@
       <c r="P3" s="15"/>
     </row>
     <row r="4" spans="1:19" ht="2.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="302"/>
-      <c r="B4" s="303"/>
-      <c r="C4" s="303"/>
-      <c r="D4" s="303"/>
-      <c r="E4" s="303"/>
+      <c r="A4" s="301"/>
+      <c r="B4" s="302"/>
+      <c r="C4" s="302"/>
+      <c r="D4" s="302"/>
+      <c r="E4" s="302"/>
       <c r="F4" s="163"/>
       <c r="G4" s="163"/>
       <c r="H4" s="163"/>
@@ -5710,95 +5714,95 @@
     <row r="5" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A5" s="7"/>
       <c r="B5" s="7"/>
-      <c r="C5" s="283" t="s">
+      <c r="C5" s="282" t="s">
         <v>309</v>
       </c>
-      <c r="D5" s="284"/>
-      <c r="E5" s="284"/>
-      <c r="F5" s="284"/>
-      <c r="G5" s="284"/>
-      <c r="H5" s="284"/>
-      <c r="I5" s="284"/>
-      <c r="J5" s="284"/>
-      <c r="K5" s="284"/>
-      <c r="L5" s="284"/>
-      <c r="M5" s="284"/>
-      <c r="N5" s="284"/>
-      <c r="O5" s="285"/>
+      <c r="D5" s="283"/>
+      <c r="E5" s="283"/>
+      <c r="F5" s="283"/>
+      <c r="G5" s="283"/>
+      <c r="H5" s="283"/>
+      <c r="I5" s="283"/>
+      <c r="J5" s="283"/>
+      <c r="K5" s="283"/>
+      <c r="L5" s="283"/>
+      <c r="M5" s="283"/>
+      <c r="N5" s="283"/>
+      <c r="O5" s="284"/>
       <c r="P5" s="15"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A6" s="7"/>
       <c r="B6" s="7"/>
-      <c r="C6" s="286"/>
-      <c r="D6" s="287"/>
-      <c r="E6" s="287"/>
-      <c r="F6" s="287"/>
-      <c r="G6" s="287"/>
-      <c r="H6" s="287"/>
-      <c r="I6" s="287"/>
-      <c r="J6" s="287"/>
-      <c r="K6" s="287"/>
-      <c r="L6" s="287"/>
-      <c r="M6" s="287"/>
-      <c r="N6" s="287"/>
-      <c r="O6" s="288"/>
+      <c r="C6" s="285"/>
+      <c r="D6" s="286"/>
+      <c r="E6" s="286"/>
+      <c r="F6" s="286"/>
+      <c r="G6" s="286"/>
+      <c r="H6" s="286"/>
+      <c r="I6" s="286"/>
+      <c r="J6" s="286"/>
+      <c r="K6" s="286"/>
+      <c r="L6" s="286"/>
+      <c r="M6" s="286"/>
+      <c r="N6" s="286"/>
+      <c r="O6" s="287"/>
       <c r="P6" s="15"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A7" s="7"/>
       <c r="B7" s="7"/>
-      <c r="C7" s="286"/>
-      <c r="D7" s="287"/>
-      <c r="E7" s="287"/>
-      <c r="F7" s="287"/>
-      <c r="G7" s="287"/>
-      <c r="H7" s="287"/>
-      <c r="I7" s="287"/>
-      <c r="J7" s="287"/>
-      <c r="K7" s="287"/>
-      <c r="L7" s="287"/>
-      <c r="M7" s="287"/>
-      <c r="N7" s="287"/>
-      <c r="O7" s="288"/>
+      <c r="C7" s="285"/>
+      <c r="D7" s="286"/>
+      <c r="E7" s="286"/>
+      <c r="F7" s="286"/>
+      <c r="G7" s="286"/>
+      <c r="H7" s="286"/>
+      <c r="I7" s="286"/>
+      <c r="J7" s="286"/>
+      <c r="K7" s="286"/>
+      <c r="L7" s="286"/>
+      <c r="M7" s="286"/>
+      <c r="N7" s="286"/>
+      <c r="O7" s="287"/>
       <c r="P7" s="15"/>
     </row>
     <row r="8" spans="1:19" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="7"/>
       <c r="B8" s="7"/>
-      <c r="C8" s="289"/>
-      <c r="D8" s="290"/>
-      <c r="E8" s="290"/>
-      <c r="F8" s="290"/>
-      <c r="G8" s="290"/>
-      <c r="H8" s="290"/>
-      <c r="I8" s="290"/>
-      <c r="J8" s="290"/>
-      <c r="K8" s="290"/>
-      <c r="L8" s="290"/>
-      <c r="M8" s="290"/>
-      <c r="N8" s="290"/>
-      <c r="O8" s="291"/>
+      <c r="C8" s="288"/>
+      <c r="D8" s="289"/>
+      <c r="E8" s="289"/>
+      <c r="F8" s="289"/>
+      <c r="G8" s="289"/>
+      <c r="H8" s="289"/>
+      <c r="I8" s="289"/>
+      <c r="J8" s="289"/>
+      <c r="K8" s="289"/>
+      <c r="L8" s="289"/>
+      <c r="M8" s="289"/>
+      <c r="N8" s="289"/>
+      <c r="O8" s="290"/>
       <c r="Q8" s="84"/>
     </row>
     <row r="9" spans="1:19" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
-      <c r="C9" s="292" t="s">
+      <c r="C9" s="291" t="s">
         <v>307</v>
       </c>
-      <c r="D9" s="293"/>
-      <c r="E9" s="293"/>
-      <c r="F9" s="293"/>
-      <c r="G9" s="293"/>
-      <c r="H9" s="293"/>
-      <c r="I9" s="293"/>
-      <c r="J9" s="293"/>
-      <c r="K9" s="293"/>
-      <c r="L9" s="293"/>
-      <c r="M9" s="293"/>
-      <c r="N9" s="293"/>
-      <c r="O9" s="294"/>
+      <c r="D9" s="292"/>
+      <c r="E9" s="292"/>
+      <c r="F9" s="292"/>
+      <c r="G9" s="292"/>
+      <c r="H9" s="292"/>
+      <c r="I9" s="292"/>
+      <c r="J9" s="292"/>
+      <c r="K9" s="292"/>
+      <c r="L9" s="292"/>
+      <c r="M9" s="292"/>
+      <c r="N9" s="292"/>
+      <c r="O9" s="293"/>
       <c r="Q9" t="s">
         <v>248</v>
       </c>
@@ -5810,19 +5814,19 @@
     <row r="10" spans="1:19" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="7"/>
       <c r="B10" s="7"/>
-      <c r="C10" s="295"/>
-      <c r="D10" s="296"/>
-      <c r="E10" s="296"/>
-      <c r="F10" s="296"/>
-      <c r="G10" s="296"/>
-      <c r="H10" s="296"/>
-      <c r="I10" s="296"/>
-      <c r="J10" s="296"/>
-      <c r="K10" s="296"/>
-      <c r="L10" s="296"/>
-      <c r="M10" s="296"/>
-      <c r="N10" s="296"/>
-      <c r="O10" s="297"/>
+      <c r="C10" s="294"/>
+      <c r="D10" s="295"/>
+      <c r="E10" s="295"/>
+      <c r="F10" s="295"/>
+      <c r="G10" s="295"/>
+      <c r="H10" s="295"/>
+      <c r="I10" s="295"/>
+      <c r="J10" s="295"/>
+      <c r="K10" s="295"/>
+      <c r="L10" s="295"/>
+      <c r="M10" s="295"/>
+      <c r="N10" s="295"/>
+      <c r="O10" s="296"/>
       <c r="Q10" t="s">
         <v>249</v>
       </c>
@@ -5832,49 +5836,49 @@
       </c>
     </row>
     <row r="11" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="268" t="s">
+      <c r="A11" s="269" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="270" t="s">
+      <c r="B11" s="303" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="268" t="s">
+      <c r="C11" s="269" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="272" t="s">
+      <c r="D11" s="305" t="s">
         <v>12</v>
       </c>
-      <c r="E11" s="272" t="s">
+      <c r="E11" s="305" t="s">
         <v>265</v>
       </c>
-      <c r="F11" s="268" t="s">
+      <c r="F11" s="269" t="s">
         <v>27</v>
       </c>
-      <c r="G11" s="268" t="s">
+      <c r="G11" s="269" t="s">
         <v>13</v>
       </c>
-      <c r="H11" s="268" t="s">
+      <c r="H11" s="269" t="s">
         <v>14</v>
       </c>
-      <c r="I11" s="279" t="s">
+      <c r="I11" s="275" t="s">
         <v>15</v>
       </c>
-      <c r="J11" s="265" t="s">
+      <c r="J11" s="277" t="s">
         <v>16</v>
       </c>
-      <c r="K11" s="265" t="s">
+      <c r="K11" s="277" t="s">
         <v>388</v>
       </c>
-      <c r="L11" s="265" t="s">
+      <c r="L11" s="277" t="s">
         <v>18</v>
       </c>
-      <c r="M11" s="281" t="s">
+      <c r="M11" s="280" t="s">
         <v>40</v>
       </c>
-      <c r="N11" s="265" t="s">
+      <c r="N11" s="277" t="s">
         <v>276</v>
       </c>
-      <c r="O11" s="265" t="s">
+      <c r="O11" s="277" t="s">
         <v>275</v>
       </c>
       <c r="Q11" t="s">
@@ -5886,21 +5890,21 @@
       </c>
     </row>
     <row r="12" spans="1:19" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="269"/>
-      <c r="B12" s="271"/>
-      <c r="C12" s="269"/>
-      <c r="D12" s="273"/>
-      <c r="E12" s="273"/>
-      <c r="F12" s="269"/>
-      <c r="G12" s="269"/>
-      <c r="H12" s="269"/>
-      <c r="I12" s="280"/>
-      <c r="J12" s="266"/>
-      <c r="K12" s="266"/>
-      <c r="L12" s="266"/>
-      <c r="M12" s="282"/>
-      <c r="N12" s="266"/>
-      <c r="O12" s="266"/>
+      <c r="A12" s="270"/>
+      <c r="B12" s="304"/>
+      <c r="C12" s="270"/>
+      <c r="D12" s="306"/>
+      <c r="E12" s="306"/>
+      <c r="F12" s="270"/>
+      <c r="G12" s="270"/>
+      <c r="H12" s="270"/>
+      <c r="I12" s="276"/>
+      <c r="J12" s="278"/>
+      <c r="K12" s="278"/>
+      <c r="L12" s="278"/>
+      <c r="M12" s="281"/>
+      <c r="N12" s="278"/>
+      <c r="O12" s="278"/>
       <c r="Q12" t="s">
         <v>251</v>
       </c>
@@ -5910,19 +5914,19 @@
       </c>
     </row>
     <row r="13" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="269"/>
-      <c r="B13" s="271"/>
-      <c r="C13" s="269"/>
-      <c r="D13" s="273"/>
-      <c r="E13" s="273"/>
-      <c r="F13" s="269"/>
-      <c r="G13" s="269"/>
-      <c r="H13" s="269"/>
-      <c r="I13" s="280"/>
-      <c r="J13" s="266"/>
-      <c r="K13" s="267"/>
-      <c r="L13" s="267"/>
-      <c r="M13" s="282"/>
+      <c r="A13" s="270"/>
+      <c r="B13" s="304"/>
+      <c r="C13" s="270"/>
+      <c r="D13" s="306"/>
+      <c r="E13" s="306"/>
+      <c r="F13" s="270"/>
+      <c r="G13" s="270"/>
+      <c r="H13" s="270"/>
+      <c r="I13" s="276"/>
+      <c r="J13" s="278"/>
+      <c r="K13" s="279"/>
+      <c r="L13" s="279"/>
+      <c r="M13" s="281"/>
       <c r="N13" s="132" t="str">
         <f>RESUMEN!A20</f>
         <v>VTO 16/03</v>
@@ -5986,8 +5990,8 @@
         <v>655631.62013736006</v>
       </c>
       <c r="P14" s="115"/>
-      <c r="R14" s="274"/>
-      <c r="S14" s="274"/>
+      <c r="R14" s="268"/>
+      <c r="S14" s="268"/>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A15" s="6"/>
@@ -6035,8 +6039,8 @@
         <v>254997.15626608004</v>
       </c>
       <c r="P15" s="115"/>
-      <c r="R15" s="274"/>
-      <c r="S15" s="274"/>
+      <c r="R15" s="268"/>
+      <c r="S15" s="268"/>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
@@ -9798,10 +9802,10 @@
         <v>123</v>
       </c>
       <c r="B78" s="6"/>
-      <c r="C78" s="319" t="s">
+      <c r="C78" s="250" t="s">
         <v>103</v>
       </c>
-      <c r="D78" s="320" t="s">
+      <c r="D78" s="251" t="s">
         <v>213</v>
       </c>
       <c r="E78" s="135"/>
@@ -12690,34 +12694,34 @@
       </c>
     </row>
     <row r="135" spans="1:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C135" s="276"/>
-      <c r="D135" s="276"/>
-      <c r="E135" s="276"/>
-      <c r="F135" s="276"/>
-      <c r="G135" s="276"/>
-      <c r="H135" s="276"/>
-      <c r="I135" s="276"/>
-      <c r="J135" s="276"/>
-      <c r="K135" s="276"/>
-      <c r="L135" s="276"/>
-      <c r="M135" s="276"/>
-      <c r="N135" s="276"/>
-      <c r="O135" s="276"/>
+      <c r="C135" s="272"/>
+      <c r="D135" s="272"/>
+      <c r="E135" s="272"/>
+      <c r="F135" s="272"/>
+      <c r="G135" s="272"/>
+      <c r="H135" s="272"/>
+      <c r="I135" s="272"/>
+      <c r="J135" s="272"/>
+      <c r="K135" s="272"/>
+      <c r="L135" s="272"/>
+      <c r="M135" s="272"/>
+      <c r="N135" s="272"/>
+      <c r="O135" s="272"/>
     </row>
     <row r="136" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
-      <c r="C136" s="276"/>
-      <c r="D136" s="276"/>
-      <c r="E136" s="276"/>
-      <c r="F136" s="276"/>
-      <c r="G136" s="276"/>
-      <c r="H136" s="276"/>
-      <c r="I136" s="276"/>
-      <c r="J136" s="276"/>
-      <c r="K136" s="276"/>
-      <c r="L136" s="276"/>
-      <c r="M136" s="276"/>
-      <c r="N136" s="276"/>
-      <c r="O136" s="276"/>
+      <c r="C136" s="272"/>
+      <c r="D136" s="272"/>
+      <c r="E136" s="272"/>
+      <c r="F136" s="272"/>
+      <c r="G136" s="272"/>
+      <c r="H136" s="272"/>
+      <c r="I136" s="272"/>
+      <c r="J136" s="272"/>
+      <c r="K136" s="272"/>
+      <c r="L136" s="272"/>
+      <c r="M136" s="272"/>
+      <c r="N136" s="272"/>
+      <c r="O136" s="272"/>
     </row>
     <row r="137" spans="1:17" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C137" s="77"/>
@@ -12735,126 +12739,126 @@
       <c r="O137" s="77"/>
     </row>
     <row r="138" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="C138" s="250" t="s">
+      <c r="C138" s="253" t="s">
         <v>258</v>
       </c>
-      <c r="D138" s="250"/>
-      <c r="E138" s="250"/>
-      <c r="F138" s="250"/>
-      <c r="G138" s="250"/>
-      <c r="H138" s="250"/>
-      <c r="I138" s="250"/>
-      <c r="J138" s="250"/>
-      <c r="K138" s="250"/>
-      <c r="L138" s="250"/>
-      <c r="M138" s="250"/>
-      <c r="N138" s="250"/>
-      <c r="O138" s="250"/>
+      <c r="D138" s="253"/>
+      <c r="E138" s="253"/>
+      <c r="F138" s="253"/>
+      <c r="G138" s="253"/>
+      <c r="H138" s="253"/>
+      <c r="I138" s="253"/>
+      <c r="J138" s="253"/>
+      <c r="K138" s="253"/>
+      <c r="L138" s="253"/>
+      <c r="M138" s="253"/>
+      <c r="N138" s="253"/>
+      <c r="O138" s="253"/>
     </row>
     <row r="139" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="C139" s="250"/>
-      <c r="D139" s="250"/>
-      <c r="E139" s="250"/>
-      <c r="F139" s="250"/>
-      <c r="G139" s="250"/>
-      <c r="H139" s="250"/>
-      <c r="I139" s="250"/>
-      <c r="J139" s="250"/>
-      <c r="K139" s="250"/>
-      <c r="L139" s="250"/>
-      <c r="M139" s="250"/>
-      <c r="N139" s="250"/>
-      <c r="O139" s="250"/>
+      <c r="C139" s="253"/>
+      <c r="D139" s="253"/>
+      <c r="E139" s="253"/>
+      <c r="F139" s="253"/>
+      <c r="G139" s="253"/>
+      <c r="H139" s="253"/>
+      <c r="I139" s="253"/>
+      <c r="J139" s="253"/>
+      <c r="K139" s="253"/>
+      <c r="L139" s="253"/>
+      <c r="M139" s="253"/>
+      <c r="N139" s="253"/>
+      <c r="O139" s="253"/>
     </row>
     <row r="140" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="C140" s="250"/>
-      <c r="D140" s="250"/>
-      <c r="E140" s="250"/>
-      <c r="F140" s="250"/>
-      <c r="G140" s="250"/>
-      <c r="H140" s="250"/>
-      <c r="I140" s="250"/>
-      <c r="J140" s="250"/>
-      <c r="K140" s="250"/>
-      <c r="L140" s="250"/>
-      <c r="M140" s="250"/>
-      <c r="N140" s="250"/>
-      <c r="O140" s="250"/>
+      <c r="C140" s="253"/>
+      <c r="D140" s="253"/>
+      <c r="E140" s="253"/>
+      <c r="F140" s="253"/>
+      <c r="G140" s="253"/>
+      <c r="H140" s="253"/>
+      <c r="I140" s="253"/>
+      <c r="J140" s="253"/>
+      <c r="K140" s="253"/>
+      <c r="L140" s="253"/>
+      <c r="M140" s="253"/>
+      <c r="N140" s="253"/>
+      <c r="O140" s="253"/>
     </row>
     <row r="141" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="C141" s="250"/>
-      <c r="D141" s="250"/>
-      <c r="E141" s="250"/>
-      <c r="F141" s="250"/>
-      <c r="G141" s="250"/>
-      <c r="H141" s="250"/>
-      <c r="I141" s="250"/>
-      <c r="J141" s="250"/>
-      <c r="K141" s="250"/>
-      <c r="L141" s="250"/>
-      <c r="M141" s="250"/>
-      <c r="N141" s="250"/>
-      <c r="O141" s="250"/>
+      <c r="C141" s="253"/>
+      <c r="D141" s="253"/>
+      <c r="E141" s="253"/>
+      <c r="F141" s="253"/>
+      <c r="G141" s="253"/>
+      <c r="H141" s="253"/>
+      <c r="I141" s="253"/>
+      <c r="J141" s="253"/>
+      <c r="K141" s="253"/>
+      <c r="L141" s="253"/>
+      <c r="M141" s="253"/>
+      <c r="N141" s="253"/>
+      <c r="O141" s="253"/>
     </row>
     <row r="142" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="C142" s="250"/>
-      <c r="D142" s="250"/>
-      <c r="E142" s="250"/>
-      <c r="F142" s="250"/>
-      <c r="G142" s="250"/>
-      <c r="H142" s="250"/>
-      <c r="I142" s="250"/>
-      <c r="J142" s="250"/>
-      <c r="K142" s="250"/>
-      <c r="L142" s="250"/>
-      <c r="M142" s="250"/>
-      <c r="N142" s="250"/>
-      <c r="O142" s="250"/>
+      <c r="C142" s="253"/>
+      <c r="D142" s="253"/>
+      <c r="E142" s="253"/>
+      <c r="F142" s="253"/>
+      <c r="G142" s="253"/>
+      <c r="H142" s="253"/>
+      <c r="I142" s="253"/>
+      <c r="J142" s="253"/>
+      <c r="K142" s="253"/>
+      <c r="L142" s="253"/>
+      <c r="M142" s="253"/>
+      <c r="N142" s="253"/>
+      <c r="O142" s="253"/>
     </row>
     <row r="143" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="C143" s="250"/>
-      <c r="D143" s="250"/>
-      <c r="E143" s="250"/>
-      <c r="F143" s="250"/>
-      <c r="G143" s="250"/>
-      <c r="H143" s="250"/>
-      <c r="I143" s="250"/>
-      <c r="J143" s="250"/>
-      <c r="K143" s="250"/>
-      <c r="L143" s="250"/>
-      <c r="M143" s="250"/>
-      <c r="N143" s="250"/>
-      <c r="O143" s="250"/>
+      <c r="C143" s="253"/>
+      <c r="D143" s="253"/>
+      <c r="E143" s="253"/>
+      <c r="F143" s="253"/>
+      <c r="G143" s="253"/>
+      <c r="H143" s="253"/>
+      <c r="I143" s="253"/>
+      <c r="J143" s="253"/>
+      <c r="K143" s="253"/>
+      <c r="L143" s="253"/>
+      <c r="M143" s="253"/>
+      <c r="N143" s="253"/>
+      <c r="O143" s="253"/>
     </row>
     <row r="144" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="C144" s="250"/>
-      <c r="D144" s="250"/>
-      <c r="E144" s="250"/>
-      <c r="F144" s="250"/>
-      <c r="G144" s="250"/>
-      <c r="H144" s="250"/>
-      <c r="I144" s="250"/>
-      <c r="J144" s="250"/>
-      <c r="K144" s="250"/>
-      <c r="L144" s="250"/>
-      <c r="M144" s="250"/>
-      <c r="N144" s="250"/>
-      <c r="O144" s="250"/>
+      <c r="C144" s="253"/>
+      <c r="D144" s="253"/>
+      <c r="E144" s="253"/>
+      <c r="F144" s="253"/>
+      <c r="G144" s="253"/>
+      <c r="H144" s="253"/>
+      <c r="I144" s="253"/>
+      <c r="J144" s="253"/>
+      <c r="K144" s="253"/>
+      <c r="L144" s="253"/>
+      <c r="M144" s="253"/>
+      <c r="N144" s="253"/>
+      <c r="O144" s="253"/>
     </row>
     <row r="145" spans="3:17" x14ac:dyDescent="0.3">
-      <c r="C145" s="250"/>
-      <c r="D145" s="250"/>
-      <c r="E145" s="250"/>
-      <c r="F145" s="250"/>
-      <c r="G145" s="250"/>
-      <c r="H145" s="250"/>
-      <c r="I145" s="250"/>
-      <c r="J145" s="250"/>
-      <c r="K145" s="250"/>
-      <c r="L145" s="250"/>
-      <c r="M145" s="250"/>
-      <c r="N145" s="250"/>
-      <c r="O145" s="250"/>
+      <c r="C145" s="253"/>
+      <c r="D145" s="253"/>
+      <c r="E145" s="253"/>
+      <c r="F145" s="253"/>
+      <c r="G145" s="253"/>
+      <c r="H145" s="253"/>
+      <c r="I145" s="253"/>
+      <c r="J145" s="253"/>
+      <c r="K145" s="253"/>
+      <c r="L145" s="253"/>
+      <c r="M145" s="253"/>
+      <c r="N145" s="253"/>
+      <c r="O145" s="253"/>
     </row>
     <row r="146" spans="3:17" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C146" s="77"/>
@@ -12887,118 +12891,125 @@
       <c r="O147" s="77"/>
     </row>
     <row r="148" spans="3:17" x14ac:dyDescent="0.3">
-      <c r="C148" s="275" t="s">
+      <c r="C148" s="271" t="s">
         <v>257</v>
       </c>
-      <c r="D148" s="275"/>
-      <c r="E148" s="275"/>
-      <c r="F148" s="275"/>
-      <c r="G148" s="275"/>
-      <c r="H148" s="275"/>
-      <c r="I148" s="275"/>
-      <c r="J148" s="275"/>
-      <c r="K148" s="275"/>
-      <c r="L148" s="275"/>
-      <c r="M148" s="275"/>
-      <c r="N148" s="275"/>
-      <c r="O148" s="275"/>
+      <c r="D148" s="271"/>
+      <c r="E148" s="271"/>
+      <c r="F148" s="271"/>
+      <c r="G148" s="271"/>
+      <c r="H148" s="271"/>
+      <c r="I148" s="271"/>
+      <c r="J148" s="271"/>
+      <c r="K148" s="271"/>
+      <c r="L148" s="271"/>
+      <c r="M148" s="271"/>
+      <c r="N148" s="271"/>
+      <c r="O148" s="271"/>
     </row>
     <row r="149" spans="3:17" x14ac:dyDescent="0.3">
-      <c r="C149" s="275"/>
-      <c r="D149" s="275"/>
-      <c r="E149" s="275"/>
-      <c r="F149" s="275"/>
-      <c r="G149" s="275"/>
-      <c r="H149" s="275"/>
-      <c r="I149" s="275"/>
-      <c r="J149" s="275"/>
-      <c r="K149" s="275"/>
-      <c r="L149" s="275"/>
-      <c r="M149" s="275"/>
-      <c r="N149" s="275"/>
-      <c r="O149" s="275"/>
+      <c r="C149" s="271"/>
+      <c r="D149" s="271"/>
+      <c r="E149" s="271"/>
+      <c r="F149" s="271"/>
+      <c r="G149" s="271"/>
+      <c r="H149" s="271"/>
+      <c r="I149" s="271"/>
+      <c r="J149" s="271"/>
+      <c r="K149" s="271"/>
+      <c r="L149" s="271"/>
+      <c r="M149" s="271"/>
+      <c r="N149" s="271"/>
+      <c r="O149" s="271"/>
     </row>
     <row r="150" spans="3:17" x14ac:dyDescent="0.3">
-      <c r="C150" s="275"/>
-      <c r="D150" s="275"/>
-      <c r="E150" s="275"/>
-      <c r="F150" s="275"/>
-      <c r="G150" s="275"/>
-      <c r="H150" s="275"/>
-      <c r="I150" s="275"/>
-      <c r="J150" s="275"/>
-      <c r="K150" s="275"/>
-      <c r="L150" s="275"/>
-      <c r="M150" s="275"/>
-      <c r="N150" s="275"/>
-      <c r="O150" s="275"/>
+      <c r="C150" s="271"/>
+      <c r="D150" s="271"/>
+      <c r="E150" s="271"/>
+      <c r="F150" s="271"/>
+      <c r="G150" s="271"/>
+      <c r="H150" s="271"/>
+      <c r="I150" s="271"/>
+      <c r="J150" s="271"/>
+      <c r="K150" s="271"/>
+      <c r="L150" s="271"/>
+      <c r="M150" s="271"/>
+      <c r="N150" s="271"/>
+      <c r="O150" s="271"/>
       <c r="Q150" s="84">
         <f>M1-L133</f>
         <v>4034495.9149199985</v>
       </c>
     </row>
     <row r="151" spans="3:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C151" s="275"/>
-      <c r="D151" s="275"/>
-      <c r="E151" s="275"/>
-      <c r="F151" s="275"/>
-      <c r="G151" s="275"/>
-      <c r="H151" s="275"/>
-      <c r="I151" s="275"/>
-      <c r="J151" s="275"/>
-      <c r="K151" s="275"/>
-      <c r="L151" s="275"/>
-      <c r="M151" s="275"/>
-      <c r="N151" s="275"/>
-      <c r="O151" s="275"/>
+      <c r="C151" s="271"/>
+      <c r="D151" s="271"/>
+      <c r="E151" s="271"/>
+      <c r="F151" s="271"/>
+      <c r="G151" s="271"/>
+      <c r="H151" s="271"/>
+      <c r="I151" s="271"/>
+      <c r="J151" s="271"/>
+      <c r="K151" s="271"/>
+      <c r="L151" s="271"/>
+      <c r="M151" s="271"/>
+      <c r="N151" s="271"/>
+      <c r="O151" s="271"/>
     </row>
     <row r="152" spans="3:17" ht="5.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C152" s="275"/>
-      <c r="D152" s="275"/>
-      <c r="E152" s="275"/>
-      <c r="F152" s="275"/>
-      <c r="G152" s="275"/>
-      <c r="H152" s="275"/>
-      <c r="I152" s="275"/>
-      <c r="J152" s="275"/>
-      <c r="K152" s="275"/>
-      <c r="L152" s="275"/>
-      <c r="M152" s="275"/>
-      <c r="N152" s="275"/>
-      <c r="O152" s="275"/>
+      <c r="C152" s="271"/>
+      <c r="D152" s="271"/>
+      <c r="E152" s="271"/>
+      <c r="F152" s="271"/>
+      <c r="G152" s="271"/>
+      <c r="H152" s="271"/>
+      <c r="I152" s="271"/>
+      <c r="J152" s="271"/>
+      <c r="K152" s="271"/>
+      <c r="L152" s="271"/>
+      <c r="M152" s="271"/>
+      <c r="N152" s="271"/>
+      <c r="O152" s="271"/>
     </row>
     <row r="153" spans="3:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C153" s="275"/>
-      <c r="D153" s="275"/>
-      <c r="E153" s="275"/>
-      <c r="F153" s="275"/>
-      <c r="G153" s="275"/>
-      <c r="H153" s="275"/>
-      <c r="I153" s="275"/>
-      <c r="J153" s="275"/>
-      <c r="K153" s="275"/>
-      <c r="L153" s="275"/>
-      <c r="M153" s="275"/>
-      <c r="N153" s="275"/>
-      <c r="O153" s="275"/>
+      <c r="C153" s="271"/>
+      <c r="D153" s="271"/>
+      <c r="E153" s="271"/>
+      <c r="F153" s="271"/>
+      <c r="G153" s="271"/>
+      <c r="H153" s="271"/>
+      <c r="I153" s="271"/>
+      <c r="J153" s="271"/>
+      <c r="K153" s="271"/>
+      <c r="L153" s="271"/>
+      <c r="M153" s="271"/>
+      <c r="N153" s="271"/>
+      <c r="O153" s="271"/>
     </row>
     <row r="154" spans="3:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C154" s="275"/>
-      <c r="D154" s="275"/>
-      <c r="E154" s="275"/>
-      <c r="F154" s="275"/>
-      <c r="G154" s="275"/>
-      <c r="H154" s="275"/>
-      <c r="I154" s="275"/>
-      <c r="J154" s="275"/>
-      <c r="K154" s="275"/>
-      <c r="L154" s="275"/>
-      <c r="M154" s="275"/>
-      <c r="N154" s="275"/>
-      <c r="O154" s="275"/>
+      <c r="C154" s="271"/>
+      <c r="D154" s="271"/>
+      <c r="E154" s="271"/>
+      <c r="F154" s="271"/>
+      <c r="G154" s="271"/>
+      <c r="H154" s="271"/>
+      <c r="I154" s="271"/>
+      <c r="J154" s="271"/>
+      <c r="K154" s="271"/>
+      <c r="L154" s="271"/>
+      <c r="M154" s="271"/>
+      <c r="N154" s="271"/>
+      <c r="O154" s="271"/>
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="K11:K13"/>
+    <mergeCell ref="A11:A13"/>
+    <mergeCell ref="B11:B13"/>
+    <mergeCell ref="C11:C13"/>
+    <mergeCell ref="D11:D13"/>
+    <mergeCell ref="F11:F13"/>
+    <mergeCell ref="E11:E13"/>
     <mergeCell ref="R14:S15"/>
     <mergeCell ref="G11:G13"/>
     <mergeCell ref="C148:O154"/>
@@ -13015,13 +13026,6 @@
     <mergeCell ref="C5:O8"/>
     <mergeCell ref="C9:O10"/>
     <mergeCell ref="A1:E4"/>
-    <mergeCell ref="K11:K13"/>
-    <mergeCell ref="A11:A13"/>
-    <mergeCell ref="B11:B13"/>
-    <mergeCell ref="C11:C13"/>
-    <mergeCell ref="D11:D13"/>
-    <mergeCell ref="F11:F13"/>
-    <mergeCell ref="E11:E13"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -13053,73 +13057,73 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="310" t="s">
+      <c r="A1" s="313" t="s">
         <v>328</v>
       </c>
-      <c r="B1" s="310"/>
-      <c r="C1" s="310"/>
-      <c r="D1" s="310"/>
-      <c r="E1" s="310"/>
-      <c r="F1" s="310"/>
-      <c r="G1" s="310"/>
-      <c r="H1" s="310"/>
-      <c r="I1" s="310"/>
-      <c r="J1" s="310"/>
-      <c r="K1" s="310"/>
-      <c r="L1" s="310"/>
-      <c r="M1" s="311"/>
+      <c r="B1" s="313"/>
+      <c r="C1" s="313"/>
+      <c r="D1" s="313"/>
+      <c r="E1" s="313"/>
+      <c r="F1" s="313"/>
+      <c r="G1" s="313"/>
+      <c r="H1" s="313"/>
+      <c r="I1" s="313"/>
+      <c r="J1" s="313"/>
+      <c r="K1" s="313"/>
+      <c r="L1" s="313"/>
+      <c r="M1" s="314"/>
       <c r="P1" s="43"/>
     </row>
     <row r="2" spans="1:25" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="312"/>
-      <c r="B2" s="312"/>
-      <c r="C2" s="312"/>
-      <c r="D2" s="312"/>
-      <c r="E2" s="312"/>
-      <c r="F2" s="312"/>
-      <c r="G2" s="312"/>
-      <c r="H2" s="312"/>
-      <c r="I2" s="312"/>
-      <c r="J2" s="312"/>
-      <c r="K2" s="312"/>
-      <c r="L2" s="312"/>
-      <c r="M2" s="313"/>
+      <c r="A2" s="315"/>
+      <c r="B2" s="315"/>
+      <c r="C2" s="315"/>
+      <c r="D2" s="315"/>
+      <c r="E2" s="315"/>
+      <c r="F2" s="315"/>
+      <c r="G2" s="315"/>
+      <c r="H2" s="315"/>
+      <c r="I2" s="315"/>
+      <c r="J2" s="315"/>
+      <c r="K2" s="315"/>
+      <c r="L2" s="315"/>
+      <c r="M2" s="316"/>
       <c r="P2" s="43"/>
     </row>
     <row r="3" spans="1:25" ht="109.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="304" t="s">
+      <c r="A3" s="307" t="s">
         <v>391</v>
       </c>
-      <c r="B3" s="305"/>
-      <c r="C3" s="305"/>
-      <c r="D3" s="305"/>
-      <c r="E3" s="305"/>
-      <c r="F3" s="305"/>
-      <c r="G3" s="305"/>
-      <c r="H3" s="305"/>
-      <c r="I3" s="305"/>
-      <c r="J3" s="305"/>
-      <c r="K3" s="305"/>
-      <c r="L3" s="305"/>
-      <c r="M3" s="306"/>
+      <c r="B3" s="308"/>
+      <c r="C3" s="308"/>
+      <c r="D3" s="308"/>
+      <c r="E3" s="308"/>
+      <c r="F3" s="308"/>
+      <c r="G3" s="308"/>
+      <c r="H3" s="308"/>
+      <c r="I3" s="308"/>
+      <c r="J3" s="308"/>
+      <c r="K3" s="308"/>
+      <c r="L3" s="308"/>
+      <c r="M3" s="309"/>
       <c r="P3" s="43"/>
     </row>
     <row r="4" spans="1:25" s="248" customFormat="1" ht="94.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="307" t="s">
+      <c r="A4" s="310" t="s">
         <v>392</v>
       </c>
-      <c r="B4" s="308"/>
-      <c r="C4" s="308"/>
-      <c r="D4" s="308"/>
-      <c r="E4" s="308"/>
-      <c r="F4" s="308"/>
-      <c r="G4" s="308"/>
-      <c r="H4" s="308"/>
-      <c r="I4" s="308"/>
-      <c r="J4" s="308"/>
-      <c r="K4" s="308"/>
-      <c r="L4" s="308"/>
-      <c r="M4" s="309"/>
+      <c r="B4" s="311"/>
+      <c r="C4" s="311"/>
+      <c r="D4" s="311"/>
+      <c r="E4" s="311"/>
+      <c r="F4" s="311"/>
+      <c r="G4" s="311"/>
+      <c r="H4" s="311"/>
+      <c r="I4" s="311"/>
+      <c r="J4" s="311"/>
+      <c r="K4" s="311"/>
+      <c r="L4" s="311"/>
+      <c r="M4" s="312"/>
       <c r="N4" s="249"/>
       <c r="O4" s="249"/>
       <c r="P4" s="249"/>
@@ -13134,75 +13138,75 @@
       <c r="Y4" s="249"/>
     </row>
     <row r="5" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="268" t="s">
+      <c r="A5" s="269" t="s">
         <v>329</v>
       </c>
-      <c r="B5" s="268" t="s">
+      <c r="B5" s="269" t="s">
         <v>330</v>
       </c>
-      <c r="C5" s="268" t="s">
+      <c r="C5" s="269" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="268" t="s">
+      <c r="D5" s="269" t="s">
         <v>27</v>
       </c>
-      <c r="E5" s="265" t="s">
+      <c r="E5" s="277" t="s">
         <v>356</v>
       </c>
-      <c r="F5" s="265" t="s">
+      <c r="F5" s="277" t="s">
         <v>357</v>
       </c>
-      <c r="G5" s="265" t="s">
+      <c r="G5" s="277" t="s">
         <v>276</v>
       </c>
-      <c r="H5" s="265" t="s">
+      <c r="H5" s="277" t="s">
         <v>389</v>
       </c>
-      <c r="I5" s="265" t="s">
+      <c r="I5" s="277" t="s">
         <v>390</v>
       </c>
-      <c r="J5" s="314" t="s">
+      <c r="J5" s="317" t="s">
         <v>358</v>
       </c>
       <c r="K5" s="131"/>
-      <c r="L5" s="265" t="s">
+      <c r="L5" s="277" t="s">
         <v>359</v>
       </c>
-      <c r="M5" s="265" t="s">
+      <c r="M5" s="277" t="s">
         <v>17</v>
       </c>
       <c r="P5" s="43"/>
     </row>
     <row r="6" spans="1:25" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="269"/>
-      <c r="B6" s="269"/>
-      <c r="C6" s="269"/>
-      <c r="D6" s="269"/>
-      <c r="E6" s="266"/>
-      <c r="F6" s="266"/>
-      <c r="G6" s="266"/>
-      <c r="H6" s="266"/>
-      <c r="I6" s="266"/>
-      <c r="J6" s="315"/>
+      <c r="A6" s="270"/>
+      <c r="B6" s="270"/>
+      <c r="C6" s="270"/>
+      <c r="D6" s="270"/>
+      <c r="E6" s="278"/>
+      <c r="F6" s="278"/>
+      <c r="G6" s="278"/>
+      <c r="H6" s="278"/>
+      <c r="I6" s="278"/>
+      <c r="J6" s="318"/>
       <c r="K6" s="131"/>
-      <c r="L6" s="266"/>
-      <c r="M6" s="266"/>
+      <c r="L6" s="278"/>
+      <c r="M6" s="278"/>
       <c r="P6" s="43"/>
     </row>
     <row r="7" spans="1:25" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="318"/>
-      <c r="B7" s="318"/>
-      <c r="C7" s="318"/>
-      <c r="D7" s="318"/>
-      <c r="E7" s="317"/>
-      <c r="F7" s="317"/>
-      <c r="G7" s="317"/>
-      <c r="H7" s="317"/>
-      <c r="I7" s="317"/>
-      <c r="J7" s="316"/>
+      <c r="A7" s="321"/>
+      <c r="B7" s="321"/>
+      <c r="C7" s="321"/>
+      <c r="D7" s="321"/>
+      <c r="E7" s="320"/>
+      <c r="F7" s="320"/>
+      <c r="G7" s="320"/>
+      <c r="H7" s="320"/>
+      <c r="I7" s="320"/>
+      <c r="J7" s="319"/>
       <c r="K7" s="209"/>
-      <c r="L7" s="317"/>
-      <c r="M7" s="317"/>
+      <c r="L7" s="320"/>
+      <c r="M7" s="320"/>
       <c r="P7" s="43"/>
     </row>
     <row r="8" spans="1:25" x14ac:dyDescent="0.3">
@@ -13251,8 +13255,8 @@
       <c r="N8" s="115">
         <v>0.7</v>
       </c>
-      <c r="P8" s="274"/>
-      <c r="Q8" s="274"/>
+      <c r="P8" s="268"/>
+      <c r="Q8" s="268"/>
     </row>
     <row r="9" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A9" s="210" t="s">
@@ -13301,8 +13305,8 @@
         <f>N8+0.01</f>
         <v>0.71</v>
       </c>
-      <c r="P9" s="274"/>
-      <c r="Q9" s="274"/>
+      <c r="P9" s="268"/>
+      <c r="Q9" s="268"/>
     </row>
     <row r="10" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A10" s="210" t="s">
@@ -17331,8 +17335,13 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="4" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C4" s="321" t="s">
+      <c r="C4" s="252" t="s">
         <v>395</v>
+      </c>
+    </row>
+    <row r="6" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C6" s="322" t="s">
+        <v>396</v>
       </c>
     </row>
     <row r="13" spans="3:3" ht="15.6" customHeight="1" x14ac:dyDescent="0.3"/>
